--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -262,7 +262,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue / Total Income Trend, FY19-FY23 (₹ crore)</a:t>
+              <a:t>Revenue / Total Income Trend, FY19-FY26 (₹ crore)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -287,12 +287,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$2:$A$6</f>
+              <f>'2b_Growth_Chart_Data'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$B$2:$B$6</f>
+              <f>'2b_Growth_Chart_Data'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$2:$A$6</f>
+              <f>'2b_Growth_Chart_Data'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$C$2:$C$6</f>
+              <f>'2b_Growth_Chart_Data'!$C$2:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -335,12 +335,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$2:$A$6</f>
+              <f>'2b_Growth_Chart_Data'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$D$2:$D$6</f>
+              <f>'2b_Growth_Chart_Data'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -422,7 +422,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Net Profit / PAT Trend, FY19-FY23 (₹ crore)</a:t>
+              <a:t>Net Profit / PAT Trend, FY19-FY26 (₹ crore)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -437,7 +437,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!B8</f>
+              <f>'2b_Growth_Chart_Data'!B11</f>
             </strRef>
           </tx>
           <spPr>
@@ -447,12 +447,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$9:$A$13</f>
+              <f>'2b_Growth_Chart_Data'!$A$12:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$B$9:$B$13</f>
+              <f>'2b_Growth_Chart_Data'!$B$12:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -461,7 +461,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!C8</f>
+              <f>'2b_Growth_Chart_Data'!C11</f>
             </strRef>
           </tx>
           <spPr>
@@ -471,12 +471,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$9:$A$13</f>
+              <f>'2b_Growth_Chart_Data'!$A$12:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$C$9:$C$13</f>
+              <f>'2b_Growth_Chart_Data'!$C$12:$C$19</f>
             </numRef>
           </val>
         </ser>
@@ -485,7 +485,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!D8</f>
+              <f>'2b_Growth_Chart_Data'!D11</f>
             </strRef>
           </tx>
           <spPr>
@@ -495,12 +495,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$9:$A$13</f>
+              <f>'2b_Growth_Chart_Data'!$A$12:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$D$9:$D$13</f>
+              <f>'2b_Growth_Chart_Data'!$D$12:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -833,6 +833,11 @@
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
+      </text>
+    </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
@@ -849,6 +854,16 @@
       </text>
     </comment>
     <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
@@ -903,6 +918,21 @@
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
+    <comment ref="E16" authorId="0" shapeId="0">
+      <text>
+        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
+      </text>
+    </comment>
+    <comment ref="G16" authorId="0" shapeId="0">
+      <text>
+        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
+      </text>
+    </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
@@ -929,11 +959,6 @@
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
@@ -965,77 +990,122 @@
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="C26" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="D26" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="E26" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="F26" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="G26" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="B27" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="C27" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="D27" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="E27" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="F27" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="C28" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="D28" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
     <comment ref="F28" authorId="0" shapeId="0">
       <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like 5-yr series.</t>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0">
+      <text>
+        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
   </commentList>
@@ -3415,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3440,10 +3510,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="115" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers in this workbook therefore come from search-engine snippets of secondary coverage of those primary sources, not from the primary documents themselves. Every figure that could not be cross-verified across at least two independent secondary sources is shaded YELLOW and carries a cell comment explaining the gap.</t>
+          <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers not otherwise flagged therefore come from search-engine snippets of secondary coverage of those primary sources, not the primary documents themselves. UPDATE: the user subsequently uploaded the actual Integrated Annual Report PDFs for Adani Power (FY24-25, FY25-26), Tata Power (FY24-25, FY25-26) and Torrent Power (FY23-24, FY24-25, FY25-26). Figures for those specific years/companies in Sheets 2, 3 and 5 have been re-extracted directly from the audited financial statements and shareholding tables in those PDFs and are now VERIFIED (noted inline). Everything outside that coverage (FY19-FY23 Total Assets/Employees, market prices, segment tables, weekly price series) remains as before and is still shaded YELLOW.</t>
         </is>
       </c>
     </row>
@@ -3451,141 +3521,142 @@
     <row r="8"/>
     <row r="9"/>
     <row r="10"/>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="11"/>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Priority list — verify these before submission</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>1. Year-end (31-Mar) share prices, FY19-FY23, all three companies — pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>2. Total Assets, FY19-FY23, all three companies — pull from screener.in balance sheet tab or the Annual Reports.</t>
+          <t>1. Year-end (31-Mar) share prices, FY19-FY26, all three companies — still not found for any year; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>3. Employee headcount, FY19-FY23, all three companies — pull from each Annual Report's HR/workforce disclosure (current figures used are partly third-party estimates, not company-reported).</t>
+          <t>2. Total Assets, FY19-FY23 (FY24-FY26 now VERIFIED from Annual Reports) — pull remaining years from screener.in balance sheet tab.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>4. Segment-wise (Ind AS 108) revenue/assets/profit tables, 5-yr, all three companies — pull from the 'Segment Reporting' note in each Annual Report.</t>
+          <t>3. Employee headcount, FY19-FY23 (FY24/FY25/FY26 now VERIFIED, standalone-parent basis only) — group-wide/consolidated headcount (incl. subsidiaries) is still not available for any company/year and would be needed for a true Sales/Employee comparison.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>5. Full weekly (52-point) price series for all 3 stocks + Nifty 50 + Sensex + Nifty Energy — pull from NSE/Yahoo Finance to compute exact weekly returns and standard deviation (volatility).</t>
+          <t>4. Segment-wise (Ind AS 108) revenue/assets/profit tables, 5-yr, all three companies — pull from the 'Segment Reporting' note in each Annual Report (the PDFs now in the repo contain this — worth a follow-up extraction pass).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>6. Shareholding pattern — pull ONE consistent-quarter BSE/NSE Shareholding Pattern (SHP) XBRL filing per company (current data is a patchwork of conflicting secondary-source snapshots from different dates).</t>
+          <t>5. Full weekly (52-point) price series for all 3 stocks + Nifty 50 + Sensex + Nifty Energy — pull from NSE/Yahoo Finance to compute exact weekly returns and standard deviation (volatility).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>7. Complete subsidiary/associate/JV lists with exact % holdings — pull the AOC-1 annexure from each company's Annual Report.</t>
+          <t>6. Shareholding pattern — Promoter %, promoter pledge (nil, all 3), and the single largest non-promoter &gt;5% holder are now VERIFIED as at 31-Mar-2026 from the Annual Reports for all three companies (Sheet 5). FII/DII category-level % breakdowns are still secondary-source/unverified — pull the full SHP table from each PDF or BSE/NSE XBRL filing if needed.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>8. Investments note (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — pull from each company's Balance Sheet notes.</t>
+          <t>7. Complete subsidiary/associate/JV lists with exact % holdings — pull the AOC-1 annexure from each company's Annual Report (now in the repo — worth a follow-up extraction pass).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>9. Promoter pledge status, all three companies — verify on BSE 'Disclosures — Consolidated Pledge Data'.</t>
+          <t>8. Investments note (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — pull from each company's Balance Sheet notes.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>9. Promoter pledge status — now VERIFIED as NIL for all three companies as at FY26 (Sheet 5), from the Annual Reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
           <t>10. Exact announcement dates + daily price reaction for Adani Power's major events (Sheet 12) — cross-check against BSE corporate announcements page.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Key sources cited across this workbook (non-exhaustive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Business Standard (business-standard.com) — quarterly results coverage, all 3 companies</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>BusinessToday (businesstoday.in) — results, stock-move coverage</t>
+          <t>Business Standard (business-standard.com) — quarterly results coverage, all 3 companies</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Equitymaster (equitymaster.com) — annual report analyses (Torrent Power, Tata Power)</t>
+          <t>BusinessToday (businesstoday.in) — results, stock-move coverage</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>CRISIL Ratings (crisil.com) — rating rationales for all 3 companies</t>
+          <t>Equitymaster (equitymaster.com) — annual report analyses (Torrent Power, Tata Power)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Trendlyne, ScanX, HDFC Sky, Kotak Neo, ICICI Direct, Groww — shareholding, price, beta/volatility snapshots</t>
+          <t>CRISIL Ratings (crisil.com) — rating rationales for all 3 companies</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Mercom India, Saurenergy, PV Magazine India — renewable/PPA/project news</t>
+          <t>Trendlyne, ScanX, HDFC Sky, Kotak Neo, ICICI Direct, Groww — shareholding, price, beta/volatility snapshots</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>NSE India, BSE India (nseindia.com, bseindia.com) — REFERENCED but not directly fetchable in this session; primary source for final verification</t>
+          <t>Mercom India, Saurenergy, PV Magazine India — renewable/PPA/project news</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NSE India, BSE India (nseindia.com, bseindia.com) — REFERENCED but not directly fetchable in this session; primary source for final verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>screener.in, moneycontrol.com — REFERENCED but not directly fetchable in this session; primary source for financial-statement data</t>
         </is>
@@ -3595,24 +3666,24 @@
   <mergeCells count="21">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B11"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A6:B10"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3792,29 +3863,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>2. 5-Year Growth Comparison: Sales, Assets, Profit, Market Price</t>
+          <t>2. Growth Comparison: Sales, Assets, Profit, Market Price (FY19-FY26)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Figures in ₹ crore unless noted. Consolidated. Yellow = verify from primary source.</t>
+          <t>₹ crore, Consolidated. FY24-FY26 columns VERIFIED from primary Annual Reports (uploaded). Yellow = still needs verification.</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3926,22 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>5-yr CAGR</t>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>CAGR</t>
         </is>
       </c>
     </row>
@@ -3877,13 +3966,22 @@
       <c r="F7" t="n">
         <v>43041</v>
       </c>
-      <c r="G7" s="12">
-        <f>IFERROR(IF(OR(B7="N/A",F7="N/A"),"N/A",(F7/B7)^(1/4)-1),"N/A")</f>
+      <c r="G7" t="n">
+        <v>60281.48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>58905.83</v>
+      </c>
+      <c r="I7" t="n">
+        <v>57865.28</v>
+      </c>
+      <c r="J7" s="12">
+        <f>IFERROR(IF(OR(B7="N/A",I7="N/A"),"N/A",(I7/B7)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Adani Power — Net Profit / PAT (₹ cr)</t>
         </is>
@@ -3903,13 +4001,22 @@
       <c r="F8" t="n">
         <v>10727</v>
       </c>
-      <c r="G8" s="12">
-        <f>IFERROR(IF(OR(B8="N/A",F8="N/A"),"N/A",(F8/B8)^(1/4)-1),"N/A")</f>
+      <c r="G8" t="n">
+        <v>20828.79</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12749.61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12971.08</v>
+      </c>
+      <c r="J8" s="12">
+        <f>IFERROR(IF(OR(B8="N/A",I8="N/A"),"N/A",(I8/B8)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Adani Power — Total Assets (₹ cr)</t>
         </is>
@@ -3934,16 +4041,27 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>85821</v>
-      </c>
-      <c r="G9" s="12">
-        <f>IFERROR(IF(OR(B9="N/A",F9="N/A"),"N/A",(F9/B9)^(1/4)-1),"N/A")</f>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>92324.77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>112917.57</v>
+      </c>
+      <c r="I9" t="n">
+        <v>142279.92</v>
+      </c>
+      <c r="J9" s="12">
+        <f>IFERROR(IF(OR(B9="N/A",I9="N/A"),"N/A",(I9/B9)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Adani Power — Employees (#)</t>
         </is>
@@ -3968,18 +4086,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>9885</v>
-      </c>
-      <c r="G10" s="12">
-        <f>IFERROR(IF(OR(B10="N/A",F10="N/A"),"N/A",(F10/B10)^(1/4)-1),"N/A")</f>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4210</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3967</v>
+      </c>
+      <c r="J10" s="12">
+        <f>IFERROR(IF(OR(B10="N/A",I10="N/A"),"N/A",(I10/B10)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Total Assets FY19-22 and Employees FY19-21 not found via search; FY23 Total Assets figure is single-sourced, verify on screener.in.</t>
+          <t>FY24-FY26 figures verified from Adani Power's audited Integrated Annual Reports (Directors' Report financial highlights &amp; Balance Sheet). FY24 Total Assets/FY19-24 Employees still unverified. Employee count is STANDALONE permanent employees on Company rolls (not group-wide headcount incl. subsidiaries) — prior FY23 estimate of 9,885 (third-party, group-wide basis) is not comparable to this basis and has been removed pending a like-for-like figure. FY24 PAT (₹20,829cr) was inflated by one-off other income/prior-period items vs FY25's more normalised ₹12,750cr — see Directors' Report MD&amp;A.</t>
         </is>
       </c>
     </row>
@@ -4004,13 +4135,22 @@
       <c r="F13" t="n">
         <v>56033</v>
       </c>
-      <c r="G13" s="12">
-        <f>IFERROR(IF(OR(B13="N/A",F13="N/A"),"N/A",(F13/B13)^(1/4)-1),"N/A")</f>
+      <c r="G13" t="n">
+        <v>63272.32</v>
+      </c>
+      <c r="H13" t="n">
+        <v>66992.17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>64171.66</v>
+      </c>
+      <c r="J13" s="12">
+        <f>IFERROR(IF(OR(B13="N/A",I13="N/A"),"N/A",(I13/B13)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Tata Power — Net Profit / PAT (₹ cr)</t>
         </is>
@@ -4034,13 +4174,22 @@
       <c r="F14" t="n">
         <v>3878</v>
       </c>
-      <c r="G14" s="12">
-        <f>IFERROR(IF(OR(B14="N/A",F14="N/A"),"N/A",(F14/B14)^(1/4)-1),"N/A")</f>
+      <c r="G14" t="n">
+        <v>4280</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4775</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5118</v>
+      </c>
+      <c r="J14" s="12">
+        <f>IFERROR(IF(OR(B14="N/A",I14="N/A"),"N/A",(I14/B14)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Tata Power — Total Assets (₹ cr)</t>
         </is>
@@ -4070,13 +4219,22 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="G15" s="12">
-        <f>IFERROR(IF(OR(B15="N/A",F15="N/A"),"N/A",(F15/B15)^(1/4)-1),"N/A")</f>
+      <c r="G15" t="n">
+        <v>139553.49</v>
+      </c>
+      <c r="H15" t="n">
+        <v>156711.29</v>
+      </c>
+      <c r="I15" t="n">
+        <v>175171.78</v>
+      </c>
+      <c r="J15" s="12">
+        <f>IFERROR(IF(OR(B15="N/A",I15="N/A"),"N/A",(I15/B15)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Tata Power — Employees (#)</t>
         </is>
@@ -4096,21 +4254,36 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>87700</v>
-      </c>
-      <c r="F16" t="n">
-        <v>95558</v>
-      </c>
-      <c r="G16" s="12">
-        <f>IFERROR(IF(OR(B16="N/A",F16="N/A"),"N/A",(F16/B16)^(1/4)-1),"N/A")</f>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>3130</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3295</v>
+      </c>
+      <c r="J16" s="12">
+        <f>IFERROR(IF(OR(B16="N/A",I16="N/A"),"N/A",(I16/B16)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>PAT FY19/FY20 and Total Assets (all years) not found; employee counts FY22/FY23 are third-party (Revelio Labs) estimates, not company-reported. FY22 PAT alt. figure: ₹2,156 cr (reported, post-exceptional).</t>
+          <t>FY24-FY26 figures verified from Tata Power's Integrated Annual Reports. PAT FY19/FY20 and Total Assets FY19-23 still unverified. Employee count is STANDALONE (parent company only, ~3,100-3,300) — Tata Power runs most of its business (TPREL, discoms) through subsidiaries with separate, much larger workforces (prior third-party group-wide estimate was ~88-96k); the two bases are not comparable, so both are shown separately rather than merged.</t>
         </is>
       </c>
     </row>
@@ -4135,15 +4308,24 @@
         <v>14493</v>
       </c>
       <c r="F19" t="n">
-        <v>26076</v>
-      </c>
-      <c r="G19" s="12">
-        <f>IFERROR(IF(OR(B19="N/A",F19="N/A"),"N/A",(F19/B19)^(1/4)-1),"N/A")</f>
+        <v>26075.97</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27527.53</v>
+      </c>
+      <c r="H19" t="n">
+        <v>29652.47</v>
+      </c>
+      <c r="I19" t="n">
+        <v>29288.92</v>
+      </c>
+      <c r="J19" s="12">
+        <f>IFERROR(IF(OR(B19="N/A",I19="N/A"),"N/A",(I19/B19)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Torrent Power — Net Profit / PAT (₹ cr)</t>
         </is>
@@ -4165,13 +4347,22 @@
       <c r="F20" t="n">
         <v>2164.67</v>
       </c>
-      <c r="G20" s="12">
-        <f>IFERROR(IF(OR(B20="N/A",F20="N/A"),"N/A",(F20/B20)^(1/4)-1),"N/A")</f>
+      <c r="G20" t="n">
+        <v>1896</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3058.61</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2469.36</v>
+      </c>
+      <c r="J20" s="12">
+        <f>IFERROR(IF(OR(B20="N/A",I20="N/A"),"N/A",(I20/B20)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Torrent Power — Total Assets (₹ cr)</t>
         </is>
@@ -4196,56 +4387,72 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" t="n">
+        <v>29910.18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33392.48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>36573.38</v>
+      </c>
+      <c r="I21" t="n">
+        <v>45193.28</v>
+      </c>
+      <c r="J21" s="12">
+        <f>IFERROR(IF(OR(B21="N/A",I21="N/A"),"N/A",(I21/B21)^(1/7)-1),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Torrent Power — Employees (#)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G21" s="12">
-        <f>IFERROR(IF(OR(B21="N/A",F21="N/A"),"N/A",(F21/B21)^(1/4)-1),"N/A")</f>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6987</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7213</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6687</v>
+      </c>
+      <c r="J22" s="12">
+        <f>IFERROR(IF(OR(B22="N/A",I22="N/A"),"N/A",(I22/B22)^(1/7)-1),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Torrent Power — Employees (#)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="12">
-        <f>IFERROR(IF(OR(B22="N/A",F22="N/A"),"N/A",(F22/B22)^(1/4)-1),"N/A")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>FY19 revenue/PAT not found; Total Assets not found for any year; Employees not found for FY19-23 (only FY25 ~7,969 found). FY22 PAT depressed by a ~₹1,300cr DGEN plant impairment charge.</t>
+          <t>FY23-FY26 figures verified from Torrent Power's Integrated Annual Reports (FY23 Total Assets now confirmed at ₹29,910.18cr, resolving a prior gap). FY19 revenue/PAT and Employees FY19-23 still unverified. Employee count is standalone permanent employees on Company rolls. FY24 PAT dipped due to the DGEN plant impairment recognised in the prior year's comparatives; FY26 PAT eased from FY25's high on lower other income/merchant realisation per MD&amp;A.</t>
         </is>
       </c>
     </row>
@@ -4287,6 +4494,21 @@
           <t>TO FILL</t>
         </is>
       </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4319,6 +4541,21 @@
           <t>TO FILL</t>
         </is>
       </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4351,6 +4588,21 @@
           <t>TO FILL</t>
         </is>
       </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
@@ -4362,7 +4614,7 @@
     <row r="31" ht="100" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Adani Power shows the strongest turnaround: from consolidated net LOSSES in FY19-FY20 to PAT of ~₹10,727 cr in FY23 (FY26 PAT ~₹12,971 cr), driven by capacity additions via IBC acquisitions (Mahan, Korba, Moxie, Vidarbha) and improved plant availability/tariffs. Revenue CAGR FY19-23 is strong (~13%) but off a low, loss-making base. Tata Power shows steadier, diversified growth (T&amp;D + renewables mix), with revenue nearly doubling FY19-23 aided by the Odisha discom acquisitions (2020-21) and renewable capacity build-out; profit growth is more moderate/volatile. Torrent Power's FY22 profit was depressed by a one-off DGEN plant impairment; excluding that, underlying growth is steady, with FY23 revenue roughly doubling on distribution volume growth post the DNH&amp;DD acquisition. Total-assets and market-price trend lines could not be completed from public search in this session — these are essential to finish the growth picture and are flagged in yellow for you to fill from screener.in / NSE.</t>
+          <t>Adani Power shows the strongest turnaround: from consolidated net LOSSES in FY19-FY20 to PAT of ~₹12,971 cr in FY26, driven by capacity additions via IBC acquisitions (Mahan, Korba, Moxie, Vidarbha) — note FY24's ₹20,829cr PAT spike was one-off-boosted (see note), with FY25/FY26 (~₹12,750-12,971cr) the more comparable run-rate. Total assets nearly doubled FY24→FY26 (₹92,325cr → ₹142,280cr) on continued capacity build-out. Tata Power shows steadier growth (T&amp;D + renewables mix), with total assets up from ₹1,39,553cr (FY24) to ₹1,75,172cr (FY26) and PAT rising each year (₹4,280cr→₹5,118cr). Torrent Power's FY24 profit dipped versus FY23 (DGEN impairment effects), rebounded strongly in FY25 (₹3,059cr) partly on the DNH&amp;DD distribution volume gains, then eased in FY26; its asset base grew fastest in relative terms (+51% FY23→FY26, ₹29,910cr→₹45,193cr) reflecting the Nabha Power and other capex. Market-price trend lines still need to be filled from NSE/Yahoo Finance (flagged in yellow) to complete the picture.</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4624,12 @@
     <row r="35"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A31:G35"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A31:J35"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4391,7 +4643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4490,100 +4742,196 @@
         <v>56033</v>
       </c>
       <c r="D6" t="n">
-        <v>26076</v>
+        <v>26075.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60281.48</v>
+      </c>
+      <c r="C7" t="n">
+        <v>63272.32</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27527.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Adani Power PAT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tata Power PAT</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Torrent Power PAT</t>
-        </is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>58905.83</v>
+      </c>
+      <c r="C8" t="n">
+        <v>66992.17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>29652.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FY19</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-984.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FY20</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-2274.8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1178.88</v>
+        <v>57865.28</v>
+      </c>
+      <c r="C9" t="n">
+        <v>64171.66</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29288.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FY21</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1270</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1424</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1300</v>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Adani Power PAT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tata Power PAT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Torrent Power PAT</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4911.6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2298</v>
-      </c>
-      <c r="D12" t="n">
-        <v>458.7</v>
+        <v>-984.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>FY20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-2274.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1178.88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1424</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4911.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2298</v>
+      </c>
+      <c r="D15" t="n">
+        <v>458.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B16" t="n">
         <v>10727</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C16" t="n">
         <v>3878</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D16" t="n">
         <v>2164.67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>20828.79</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4280</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12749.61</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3058.61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12971.08</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5118</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2469.36</v>
       </c>
     </row>
   </sheetData>
@@ -4597,15 +4945,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4654,6 +5005,21 @@
           <t>FY23</t>
         </is>
       </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4681,6 +5047,18 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F7),ISTEXT('2_Growth_Comparison'!F9)),"N/A",'2_Growth_Comparison'!F7/'2_Growth_Comparison'!F9),"N/A")</f>
         <v/>
       </c>
+      <c r="G7" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G7),ISTEXT('2_Growth_Comparison'!G9)),"N/A",'2_Growth_Comparison'!G7/'2_Growth_Comparison'!G9),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H7),ISTEXT('2_Growth_Comparison'!H9)),"N/A",'2_Growth_Comparison'!H7/'2_Growth_Comparison'!H9),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I7),ISTEXT('2_Growth_Comparison'!I9)),"N/A",'2_Growth_Comparison'!I7/'2_Growth_Comparison'!I9),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4708,6 +5086,18 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F7),ISTEXT('2_Growth_Comparison'!F10)),"N/A",'2_Growth_Comparison'!F7*100/'2_Growth_Comparison'!F10),"N/A")</f>
         <v/>
       </c>
+      <c r="G8" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G7),ISTEXT('2_Growth_Comparison'!G10)),"N/A",'2_Growth_Comparison'!G7*100/'2_Growth_Comparison'!G10),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H7),ISTEXT('2_Growth_Comparison'!H10)),"N/A",'2_Growth_Comparison'!H7*100/'2_Growth_Comparison'!H10),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I7),ISTEXT('2_Growth_Comparison'!I10)),"N/A",'2_Growth_Comparison'!I7*100/'2_Growth_Comparison'!I10),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4735,6 +5125,18 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F13),ISTEXT('2_Growth_Comparison'!F15)),"N/A",'2_Growth_Comparison'!F13/'2_Growth_Comparison'!F15),"N/A")</f>
         <v/>
       </c>
+      <c r="G10" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G13),ISTEXT('2_Growth_Comparison'!G15)),"N/A",'2_Growth_Comparison'!G13/'2_Growth_Comparison'!G15),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H13),ISTEXT('2_Growth_Comparison'!H15)),"N/A",'2_Growth_Comparison'!H13/'2_Growth_Comparison'!H15),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I13),ISTEXT('2_Growth_Comparison'!I15)),"N/A",'2_Growth_Comparison'!I13/'2_Growth_Comparison'!I15),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4762,6 +5164,18 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F13),ISTEXT('2_Growth_Comparison'!F16)),"N/A",'2_Growth_Comparison'!F13*100/'2_Growth_Comparison'!F16),"N/A")</f>
         <v/>
       </c>
+      <c r="G11" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G13),ISTEXT('2_Growth_Comparison'!G16)),"N/A",'2_Growth_Comparison'!G13*100/'2_Growth_Comparison'!G16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H13),ISTEXT('2_Growth_Comparison'!H16)),"N/A",'2_Growth_Comparison'!H13*100/'2_Growth_Comparison'!H16),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I13),ISTEXT('2_Growth_Comparison'!I16)),"N/A",'2_Growth_Comparison'!I13*100/'2_Growth_Comparison'!I16),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4789,6 +5203,18 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F19),ISTEXT('2_Growth_Comparison'!F21)),"N/A",'2_Growth_Comparison'!F19/'2_Growth_Comparison'!F21),"N/A")</f>
         <v/>
       </c>
+      <c r="G13" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G19),ISTEXT('2_Growth_Comparison'!G21)),"N/A",'2_Growth_Comparison'!G19/'2_Growth_Comparison'!G21),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H19),ISTEXT('2_Growth_Comparison'!H21)),"N/A",'2_Growth_Comparison'!H19/'2_Growth_Comparison'!H21),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I19),ISTEXT('2_Growth_Comparison'!I21)),"N/A",'2_Growth_Comparison'!I19/'2_Growth_Comparison'!I21),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4816,6 +5242,18 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F19),ISTEXT('2_Growth_Comparison'!F22)),"N/A",'2_Growth_Comparison'!F19*100/'2_Growth_Comparison'!F22),"N/A")</f>
         <v/>
       </c>
+      <c r="G14" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G19),ISTEXT('2_Growth_Comparison'!G22)),"N/A",'2_Growth_Comparison'!G19*100/'2_Growth_Comparison'!G22),"N/A")</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H19),ISTEXT('2_Growth_Comparison'!H22)),"N/A",'2_Growth_Comparison'!H19*100/'2_Growth_Comparison'!H22),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I19),ISTEXT('2_Growth_Comparison'!I22)),"N/A",'2_Growth_Comparison'!I19*100/'2_Growth_Comparison'!I22),"N/A")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -4824,10 +5262,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="110" customHeight="1">
+    <row r="17" ht="130" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>These ratios could only be fully computed where both Revenue and Total Assets / Employee data were available — currently only Adani Power FY23 (Assets) and Adani Power FY23/Tata Power FY22-23 (Employees) have source data; all other cells show 'N/A' pending the Total-Assets and Employee-count series being filled in from screener.in / the Annual Reports' financial-highlights section (Sheet 2). Once those inputs are filled, this sheet updates automatically via formula. DIRECTIONAL READ (from what data exists): Power-generation businesses are capital-intensive, so Sales/Total-Assets ratios below 1.0x for all three companies would be typical (thermal/renewable assets carry a long depreciation life relative to annual revenue). Sales-per-employee tends to be structurally higher for Adani Power and Torrent Power (generation-heavy, thinner headcount per MW) than for Tata Power, whose large distribution/retail workforce (~90-100k employees incl. discom staff) dilutes revenue-per-employee versus a pure-generation peer.</t>
+          <t>FY24-FY26 ratios now compute from verified Annual Report data (Sheet 2). Sales/Total-Assets: Adani Power ~0.65x (FY24) declining to ~0.41x (FY26) as its asset base grew faster than revenue (heavy capex/acquisitions still ramping up utilisation); Tata Power steadier at ~0.45x-0.37x; Torrent Power highest of the three at ~0.82x-0.65x, reflecting a leaner, more revenue-dense (largely regulated distribution-driven) asset base. Sales/Employee is NOT directly comparable across companies here: all three employee counts are STANDALONE (parent company only) figures from the Annual Reports, so a holding-company-style parent with heavy operations inside subsidiaries (e.g., Tata Power, whose TPREL/discoms sit in separate entities) will show an inflated, misleading ratio versus a consolidated peer. A true comparison needs group-wide headcount (consolidated, incl. subsidiaries) for all three, which is not disclosed in one place in any of the Annual Reports reviewed — flag this limitation if quoting Sales/Employee externally. FY19-FY23 cells remain 'N/A' pending the pre-FY24 Total-Assets and Employee series (see Sheet 2 notes).</t>
         </is>
       </c>
     </row>
@@ -4837,11 +5275,12 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
+    <row r="24"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F23"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A17:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5602,7 +6041,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Most recent available quarter (~Jun 2026 unless noted). Major shareholder = &gt;5% of equity.</t>
+          <t>As at 31-Mar-2026 for Adani Power/Tata Power/Torrent Power — VERIFIED from each company's FY25-26 Annual Report. Major shareholder = &gt;5% of equity.</t>
         </is>
       </c>
     </row>
@@ -5642,22 +6081,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>74.96%</t>
+          <t>74.96% (Promoter &amp; Promoter Group, per FY26 Annual Report shareholding table)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>46.86% (Tata Sons Pvt Ltd)</t>
+          <t>46.86% total promoter group; Tata Sons Pvt Ltd alone = 45.21% (per FY26 Annual Report)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>~51.09% (Torrent Investments Pvt Ltd)</t>
+          <t>51.09% — Torrent Investments Ltd (formerly Torrent Investments Pvt Ltd), unchanged FY25→FY26 (per FY26 Annual Report)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Torrent figure as of ~Q4 FY26 aggregator snapshot — reconcile against latest BSE/NSE SHP filing.</t>
+          <t>VERIFIED from FY25-26 Annual Reports (uploaded).</t>
         </is>
       </c>
     </row>
@@ -5667,24 +6106,24 @@
           <t>Promoter pledge</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Not confirmed — no explicit Adani-Power-specific filing found; peer Adani cos filed 'nil encumbrance' for FY26.</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>No pledge of promoter shares disclosed in the FY26 Annual Report (only routine subsidiary-loan security pledges by the Company, unrelated to promoter shareholding).</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>0% — no pledge reported.</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Not confirmed — no pledge disclosure found; BSE consolidated-pledge-data page not accessible in this session.</t>
+          <t>'Company has not raised loans during the year on the pledge of securities held in its subsidiaries, joint ventures...' — no promoter share pledge disclosed.</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>No pledge of promoter shares disclosed in the FY26 Annual Report.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>VERIFY each directly on BSE 'Disclosures — Consolidated Pledge Data'.</t>
+          <t>VERIFIED (nil promoter pledge) from FY25-26 Annual Reports for all three.</t>
         </is>
       </c>
     </row>
@@ -5696,12 +6135,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>11.74%</t>
+          <t>11.74% (secondary-source snapshot; not separately re-verified in the Annual Report text extract)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>~10.0-10.04%</t>
+          <t>~10.0-10.04% (secondary-source snapshot)</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
@@ -5709,7 +6148,11 @@
           <t>8.4%-14.2% (conflicting across sources/dates)</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Category-wise FII/DII % not captured from the Annual Report's shareholding table in this pass — cross-check the full SHP table in each PDF if needed.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -5719,7 +6162,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>3.69% (DII)</t>
+          <t>3.69% (DII, secondary-source snapshot)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -5727,14 +6170,14 @@
           <t>8.64% (DII, one source) vs 18.28% (DII, another) — MFs alone ~8.89-9.63%</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>22.83% / 18.8% / 31.2% (conflicting) — named holders incl. SBI Funds ~8.57%, Axis AMC ~3.02%, LIC ~3.17%</t>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>SBI Mutual Fund confirmed at 8.57% (FY26, up from 7.95% FY25) — VERIFIED from Annual Report top-10-shareholders table.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>6-month change: not established from search for any of the 3 — pull last 2 quarterly SHP filings and diff manually.</t>
+          <t>6-month change for SBI MF in Torrent Power (7.95%→8.57%) is now VERIFIED; other DII figures remain secondary-source.</t>
         </is>
       </c>
     </row>
@@ -5746,7 +6189,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>9.62%</t>
+          <t>9.62% (secondary-source snapshot)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -5764,7 +6207,7 @@
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Free float (100% - promoter - pledge equivalent)</t>
+          <t>Free float (100% - promoter%)</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -5796,20 +6239,24 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>GQG Partners — ~7.7-8.1% (bought via block deal, Aug 2023, ~US$1.1bn; largest single GQG position in the Adani group)</t>
+          <t>NONE currently &gt;5% besides promoter group — GQG Partners (Goldman Sachs Trust II - Goldman Sachs GQG Partner) now holds only 3.30% as of FY26 (down from ~7.7-8.1% in 2023), per the FY26 Annual Report's top-10-shareholders table. No other non-promoter holder exceeds 5%.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Tata Sons Pvt Ltd (~45% of the promoter block) — no non-promoter holder &gt;5% identified</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Aditya Birla Group reportedly ~6.34% (single secondary source, ~Aug 2023) — UNCONFIRMED, verify</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr"/>
+          <t>Life Insurance Corporation of India (LIC) — 5.18% as at 31-Mar-2026 (up from 2.96% at 31-Mar-2025), crossing the 5% threshold during FY26 — VERIFIED from the FY26 Annual Report's 'shareholders holding more than 5%' table.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Gujarat Urja Vikas Nigam Ltd (GUVNL, Gujarat's state power utility) — 6.95%, unchanged FY25→FY26 — VERIFIED from the FY26 Annual Report's top-10-shareholders table. (Earlier flagged 'Aditya Birla Group ~6.34%' claim was NOT found in the primary source and should be disregarded.)</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>All three figures in this row are now VERIFIED from primary Annual Reports, replacing prior unconfirmed secondary-source claims.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -572,6 +572,166 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Total Assets Trend, FY20-FY26 (₹ crore, consolidated)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'2b_Growth_Chart_Data'!B21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2b_Growth_Chart_Data'!$A$22:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2b_Growth_Chart_Data'!$B$22:$B$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'2b_Growth_Chart_Data'!C21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2b_Growth_Chart_Data'!$A$22:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2b_Growth_Chart_Data'!$C$22:$C$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'2b_Growth_Chart_Data'!D21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'2b_Growth_Chart_Data'!$A$22:$A$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'2b_Growth_Chart_Data'!$D$22:$D$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Fiscal Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>₹ crore</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
@@ -674,7 +834,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -818,26 +978,6 @@
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
-    <comment ref="C9" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
@@ -848,17 +988,7 @@
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
     <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
@@ -888,21 +1018,6 @@
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
-    <comment ref="D15" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="E15" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
     <comment ref="B16" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
@@ -914,16 +1029,6 @@
       </text>
     </comment>
     <comment ref="D16" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="E16" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
@@ -948,42 +1053,12 @@
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="D21" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
     <comment ref="C22" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
@@ -1153,6 +1228,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3513,7 +3610,7 @@
     <row r="6" ht="115" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers not otherwise flagged therefore come from search-engine snippets of secondary coverage of those primary sources, not the primary documents themselves. UPDATE: the user subsequently uploaded the actual Integrated Annual Report PDFs for Adani Power (FY24-25, FY25-26), Tata Power (FY24-25, FY25-26) and Torrent Power (FY23-24, FY24-25, FY25-26). Figures for those specific years/companies in Sheets 2, 3 and 5 have been re-extracted directly from the audited financial statements and shareholding tables in those PDFs and are now VERIFIED (noted inline). Everything outside that coverage (FY19-FY23 Total Assets/Employees, market prices, segment tables, weekly price series) remains as before and is still shaded YELLOW.</t>
+          <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers not otherwise flagged therefore come from search-engine snippets of secondary coverage of those primary sources, not the primary documents themselves. UPDATE: the user subsequently uploaded the actual Integrated Annual Report PDFs covering — Adani Power FY20-21, FY22-23, FY23-24 (financials section), FY24-25 and FY25-26; Tata Power FY21-22, FY22-23, FY23-24, FY24-25 and FY25-26; Torrent Power FY20-21 through FY25-26 (all six). Using each report's current + prior-year comparative columns, the consolidated Revenue/Total Income, PAT and Total Assets series in Sheet 2 are now PRIMARY-VERIFIED for FY20-FY26 (Adani, Torrent) and FY21-FY26 (Tata), and standalone employee counts were extracted where disclosed. Only FY19 (all metrics beyond secondary-sourced revenue/PAT) and the share-price rows remain unverified/yellow. Segment tables, AOC-1 subsidiary lists and the Investments notes are IN these PDFs but not yet extracted into Sheets 6-9.</t>
         </is>
       </c>
     </row>
@@ -3539,14 +3636,14 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>2. Total Assets, FY19-FY23 (FY24-FY26 now VERIFIED from Annual Reports) — pull remaining years from screener.in balance sheet tab.</t>
+          <t>2. Total Assets — now VERIFIED FY20-FY26 (Adani, Torrent) and FY21-FY26 (Tata) from the Annual Reports. Only FY19 (all 3) and Tata FY20 remain open (needs the FY19-20 Annual Reports).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>3. Employee headcount, FY19-FY23 (FY24/FY25/FY26 now VERIFIED, standalone-parent basis only) — group-wide/consolidated headcount (incl. subsidiaries) is still not available for any company/year and would be needed for a true Sales/Employee comparison.</t>
+          <t>3. Employee headcount — standalone-parent counts now VERIFIED where disclosed (Adani FY21/23/25/26; Tata FY22/23/25/26; Torrent FY21-FY26). Group-wide/consolidated headcount is still not disclosed anywhere and would be needed for a true cross-company Sales/Employee comparison.</t>
         </is>
       </c>
     </row>
@@ -3955,16 +4052,16 @@
         <v>26362</v>
       </c>
       <c r="C7" t="n">
-        <v>27842</v>
+        <v>27841.81</v>
       </c>
       <c r="D7" t="n">
-        <v>28150</v>
+        <v>28149.68</v>
       </c>
       <c r="E7" t="n">
-        <v>31687</v>
+        <v>31686.47</v>
       </c>
       <c r="F7" t="n">
-        <v>43041</v>
+        <v>43040.52</v>
       </c>
       <c r="G7" t="n">
         <v>60281.48</v>
@@ -3990,16 +4087,16 @@
         <v>-984.4</v>
       </c>
       <c r="C8" t="n">
-        <v>-2274.8</v>
+        <v>-2274.77</v>
       </c>
       <c r="D8" t="n">
-        <v>1270</v>
+        <v>1269.98</v>
       </c>
       <c r="E8" t="n">
-        <v>4911.6</v>
+        <v>4911.58</v>
       </c>
       <c r="F8" t="n">
-        <v>10727</v>
+        <v>10726.64</v>
       </c>
       <c r="G8" t="n">
         <v>20828.79</v>
@@ -4026,25 +4123,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C9" t="n">
+        <v>75025</v>
+      </c>
+      <c r="D9" t="n">
+        <v>78535.47</v>
+      </c>
+      <c r="E9" t="n">
+        <v>81981.02</v>
+      </c>
+      <c r="F9" t="n">
+        <v>85821.27</v>
       </c>
       <c r="G9" t="n">
         <v>92324.77</v>
@@ -4076,20 +4165,16 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="n">
+        <v>84</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F10" t="n">
+        <v>2805</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -4110,7 +4195,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>FY24-FY26 figures verified from Adani Power's audited Integrated Annual Reports (Directors' Report financial highlights &amp; Balance Sheet). FY24 Total Assets/FY19-24 Employees still unverified. Employee count is STANDALONE permanent employees on Company rolls (not group-wide headcount incl. subsidiaries) — prior FY23 estimate of 9,885 (third-party, group-wide basis) is not comparable to this basis and has been removed pending a like-for-like figure. FY24 PAT (₹20,829cr) was inflated by one-off other income/prior-period items vs FY25's more normalised ₹12,750cr — see Directors' Report MD&amp;A.</t>
+          <t>FY20-FY26 figures VERIFIED from Adani Power's audited Integrated Annual Reports (consolidated). FY19 revenue/PAT are secondary-source (Business Standard, May-2019 results coverage); FY19 Total Assets not available. Employees = STANDALONE permanent employees on Company rolls: FY21's count of just 84 reflects the pre-amalgamation structure — until 1-Oct-2021 the parent was largely a holding shell, with operating staff employed by the 6 subsidiaries merged in that year, so the series has a structural break and FY21 is NOT comparable to FY23+. FY24 PAT (₹20,829cr) was inflated by one-off other income (₹9,781cr incl. prior-period revenue recognition) vs FY25's normalised ₹12,750cr.</t>
         </is>
       </c>
     </row>
@@ -4166,13 +4251,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1424</v>
+        <v>1439</v>
       </c>
       <c r="E14" t="n">
-        <v>2298</v>
+        <v>2156</v>
       </c>
       <c r="F14" t="n">
-        <v>3878</v>
+        <v>3810</v>
       </c>
       <c r="G14" t="n">
         <v>4280</v>
@@ -4204,20 +4289,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D15" t="n">
+        <v>98838.86</v>
+      </c>
+      <c r="E15" t="n">
+        <v>112884.59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>128349.04</v>
       </c>
       <c r="G15" t="n">
         <v>139553.49</v>
@@ -4254,15 +4333,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E16" t="n">
+        <v>2815</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3071</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -4283,7 +4358,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>FY24-FY26 figures verified from Tata Power's Integrated Annual Reports. PAT FY19/FY20 and Total Assets FY19-23 still unverified. Employee count is STANDALONE (parent company only, ~3,100-3,300) — Tata Power runs most of its business (TPREL, discoms) through subsidiaries with separate, much larger workforces (prior third-party group-wide estimate was ~88-96k); the two bases are not comparable, so both are shown separately rather than merged.</t>
+          <t>FY21-FY26 figures VERIFIED from Tata Power's Integrated Annual Reports (consolidated, reported basis): PAT FY21 ₹1,439cr / FY22 ₹2,156cr / FY23 ₹3,810cr replace earlier secondary-source variants (1,424/2,298/3,878, which were pre-exceptional or pre-minority-interest bases). Revenue FY21-23 (33,239/42,576/56,033) is the company's own highlights-basis series incl. regulatory income, now confirmed in the FY22/FY23 Annual Reports; as-reported P&amp;L 'Revenue from Operations' is slightly lower (32,703/42,816/55,109). FY19/FY20 figures remain secondary-source. Employees = STANDALONE parent only (~2,800-3,300) — most of the group workforce sits in subsidiaries (TPREL, discoms), so do not compare with consolidated revenue.</t>
         </is>
       </c>
     </row>
@@ -4299,13 +4374,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13820</v>
+        <v>13818.22</v>
       </c>
       <c r="D19" t="n">
-        <v>12310</v>
+        <v>12314.47</v>
       </c>
       <c r="E19" t="n">
-        <v>14493</v>
+        <v>14492.65</v>
       </c>
       <c r="F19" t="n">
         <v>26075.97</v>
@@ -4339,7 +4414,7 @@
         <v>1178.88</v>
       </c>
       <c r="D20" t="n">
-        <v>1300</v>
+        <v>1295.87</v>
       </c>
       <c r="E20" t="n">
         <v>458.7</v>
@@ -4372,20 +4447,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C21" t="n">
+        <v>23623.04</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23538.72</v>
+      </c>
+      <c r="E21" t="n">
+        <v>25022.7</v>
       </c>
       <c r="F21" t="n">
         <v>29910.18</v>
@@ -4420,20 +4489,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D22" t="n">
+        <v>7429</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7603</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6992</v>
       </c>
       <c r="G22" t="n">
         <v>6987</v>
@@ -4452,7 +4515,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>FY23-FY26 figures verified from Torrent Power's Integrated Annual Reports (FY23 Total Assets now confirmed at ₹29,910.18cr, resolving a prior gap). FY19 revenue/PAT and Employees FY19-23 still unverified. Employee count is standalone permanent employees on Company rolls. FY24 PAT dipped due to the DGEN plant impairment recognised in the prior year's comparatives; FY26 PAT eased from FY25's high on lower other income/merchant realisation per MD&amp;A.</t>
+          <t>FY20-FY26 figures VERIFIED from Torrent Power's Integrated Annual Reports (consolidated). Only FY19 remains unverified (no FY19-20 report uploaded). FY22 PAT (₹458.70cr) was depressed by a ~₹1,300cr DGEN plant impairment. Employees = standalone permanent employees on Company rolls (Rule 5(1) disclosure) — Torrent runs most operations in the parent entity, so this series is closer to a true group headcount than Adani/Tata's standalone counts.</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4677,7 @@
     <row r="31" ht="100" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Adani Power shows the strongest turnaround: from consolidated net LOSSES in FY19-FY20 to PAT of ~₹12,971 cr in FY26, driven by capacity additions via IBC acquisitions (Mahan, Korba, Moxie, Vidarbha) — note FY24's ₹20,829cr PAT spike was one-off-boosted (see note), with FY25/FY26 (~₹12,750-12,971cr) the more comparable run-rate. Total assets nearly doubled FY24→FY26 (₹92,325cr → ₹142,280cr) on continued capacity build-out. Tata Power shows steadier growth (T&amp;D + renewables mix), with total assets up from ₹1,39,553cr (FY24) to ₹1,75,172cr (FY26) and PAT rising each year (₹4,280cr→₹5,118cr). Torrent Power's FY24 profit dipped versus FY23 (DGEN impairment effects), rebounded strongly in FY25 (₹3,059cr) partly on the DNH&amp;DD distribution volume gains, then eased in FY26; its asset base grew fastest in relative terms (+51% FY23→FY26, ₹29,910cr→₹45,193cr) reflecting the Nabha Power and other capex. Market-price trend lines still need to be filled from NSE/Yahoo Finance (flagged in yellow) to complete the picture.</t>
+          <t>SALES GROWTH: Adani Power's revenue rose from ₹27,842cr (FY20) to ₹57,865cr (FY26), ~13% CAGR, with the big jumps in FY23-FY24 driven by IBC acquisitions (Mahan, Korba) plus tariff/prior-period recoveries; FY25-FY26 revenue plateaued. Tata Power roughly doubled revenue FY20→FY26 (₹30,350cr→₹64,172cr), the FY22-23 surge reflecting the four Odisha discoms and high Mundra fuel pass-throughs. Torrent Power's revenue more than doubled (₹13,818cr→₹29,289cr), with the single biggest step in FY23 (+80%) from the DNH&amp;DD discom takeover and merchant gas sales. PROFIT GROWTH: Adani Power's swing is the most dramatic — from a ₹2,275cr loss (FY20) to ₹12,971cr PAT (FY26); FY24's ₹20,829cr spike was one-off-boosted and FY25/FY26 is the cleaner run-rate. Tata Power compounded PAT steadily every single year (₹1,439cr FY21 → ₹5,118cr FY26, ~29% CAGR) — the most consistent grower. Torrent is profitable but lumpy (FY22 impairment, FY25 peak, FY26 dip). ASSETS GROWTH: Adani Power's asset base compounded ~11% (₹75,025cr FY20 → ₹1,42,280cr FY26), accelerating sharply after FY24 as acquisitions/new capacity landed. Tata Power grew assets ~12% CAGR (₹98,839cr FY21 → ₹1,75,172cr FY26) — the largest absolute base. Torrent was static FY20-FY22 (~₹23-25,000cr) then accelerated to ₹45,193cr by FY26 (Nabha + capex cycle). MARKET PRICE: year-end share-price rows still need NSE/Yahoo data (yellow) to complete the fourth growth lens.</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4688,13 +4751,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27842</v>
+        <v>27841.81</v>
       </c>
       <c r="C3" t="n">
         <v>30350</v>
       </c>
       <c r="D3" t="n">
-        <v>13820</v>
+        <v>13818.22</v>
       </c>
     </row>
     <row r="4">
@@ -4704,13 +4767,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28150</v>
+        <v>28149.68</v>
       </c>
       <c r="C4" t="n">
         <v>33239</v>
       </c>
       <c r="D4" t="n">
-        <v>12310</v>
+        <v>12314.47</v>
       </c>
     </row>
     <row r="5">
@@ -4720,13 +4783,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31687</v>
+        <v>31686.47</v>
       </c>
       <c r="C5" t="n">
         <v>42576</v>
       </c>
       <c r="D5" t="n">
-        <v>14493</v>
+        <v>14492.65</v>
       </c>
     </row>
     <row r="6">
@@ -4736,7 +4799,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43041</v>
+        <v>43040.52</v>
       </c>
       <c r="C6" t="n">
         <v>56033</v>
@@ -4832,7 +4895,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2274.8</v>
+        <v>-2274.77</v>
       </c>
       <c r="D13" t="n">
         <v>1178.88</v>
@@ -4845,13 +4908,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1270</v>
+        <v>1269.98</v>
       </c>
       <c r="C14" t="n">
-        <v>1424</v>
+        <v>1439</v>
       </c>
       <c r="D14" t="n">
-        <v>1300</v>
+        <v>1295.87</v>
       </c>
     </row>
     <row r="15">
@@ -4861,10 +4924,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4911.6</v>
+        <v>4911.58</v>
       </c>
       <c r="C15" t="n">
-        <v>2298</v>
+        <v>2156</v>
       </c>
       <c r="D15" t="n">
         <v>458.7</v>
@@ -4877,10 +4940,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10727</v>
+        <v>10726.64</v>
       </c>
       <c r="C16" t="n">
-        <v>3878</v>
+        <v>3810</v>
       </c>
       <c r="D16" t="n">
         <v>2164.67</v>
@@ -4932,6 +4995,137 @@
       </c>
       <c r="D19" t="n">
         <v>2469.36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Adani Power Assets</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tata Power Assets</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Torrent Power Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FY20</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>75025</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23623.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>78535.47</v>
+      </c>
+      <c r="C23" t="n">
+        <v>98838.86</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23538.72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>81981.02</v>
+      </c>
+      <c r="C24" t="n">
+        <v>112884.59</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25022.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>85821.27</v>
+      </c>
+      <c r="C25" t="n">
+        <v>128349.04</v>
+      </c>
+      <c r="D25" t="n">
+        <v>29910.18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>92324.77</v>
+      </c>
+      <c r="C26" t="n">
+        <v>139553.49</v>
+      </c>
+      <c r="D26" t="n">
+        <v>33392.48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>112917.57</v>
+      </c>
+      <c r="C27" t="n">
+        <v>156711.29</v>
+      </c>
+      <c r="D27" t="n">
+        <v>36573.38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>142279.92</v>
+      </c>
+      <c r="C28" t="n">
+        <v>175171.78</v>
+      </c>
+      <c r="D28" t="n">
+        <v>45193.28</v>
       </c>
     </row>
   </sheetData>
@@ -5265,7 +5459,7 @@
     <row r="17" ht="130" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>FY24-FY26 ratios now compute from verified Annual Report data (Sheet 2). Sales/Total-Assets: Adani Power ~0.65x (FY24) declining to ~0.41x (FY26) as its asset base grew faster than revenue (heavy capex/acquisitions still ramping up utilisation); Tata Power steadier at ~0.45x-0.37x; Torrent Power highest of the three at ~0.82x-0.65x, reflecting a leaner, more revenue-dense (largely regulated distribution-driven) asset base. Sales/Employee is NOT directly comparable across companies here: all three employee counts are STANDALONE (parent company only) figures from the Annual Reports, so a holding-company-style parent with heavy operations inside subsidiaries (e.g., Tata Power, whose TPREL/discoms sit in separate entities) will show an inflated, misleading ratio versus a consolidated peer. A true comparison needs group-wide headcount (consolidated, incl. subsidiaries) for all three, which is not disclosed in one place in any of the Annual Reports reviewed — flag this limitation if quoting Sales/Employee externally. FY19-FY23 cells remain 'N/A' pending the pre-FY24 Total-Assets and Employee series (see Sheet 2 notes).</t>
+          <t>SALES PER RUPEE OF ASSET (now computable FY20/FY21-FY26 from verified Annual Report data): Adani Power improved from ~0.37x (FY20, low utilisation/losses era) to a peak of ~0.65x (FY24), then fell back to ~0.41x (FY26) as its asset base ballooned ahead of revenue from new acquisitions still ramping up. Tata Power is stable in a ~0.34-0.45x band — typical of a regulated, asset-heavy integrated utility. Torrent Power is consistently the MOST asset-efficient of the three (~0.52-0.87x, peaking FY23 when DNH&amp;DD volumes hit a still-small asset base) — its regulated distribution business generates more revenue per rupee of assets than pure thermal generation does. SALES PER EMPLOYEE: comparable across time within Torrent (parent employs most staff: ~₹18-44 cr/employee trend) but NOT comparable across companies — Adani and Tata employee counts are standalone-parent only, while their revenue is consolidated (Tata's discoms/TPREL staff and Adani's pre-FY22 plant staff sit in subsidiaries). Adani's FY21 count of 84 (pre-amalgamation shell) makes that year's ratio meaningless and it is excluded from comment. Use the Torrent series as the benchmark and treat Adani/Tata Sales-per-Employee as indicative only, noting the basis in any write-up.</t>
         </is>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -15,15 +15,16 @@
     <sheet name="4_Acquisitions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="5_Shareholding_Pattern" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="6_Business_Segments" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="7_Group_Structure" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="8_Associates_JVs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="9_Investments" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="10_Financing_Changes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="11_Returns_Volatility" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Weekly_Price_Data" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="12_Major_Announcements" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="12b_Announcement_Chart_Data" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet name="13_Sources_and_Gaps" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="6b_Segment_Chart_Data" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="7_Group_Structure" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="8_Associates_JVs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="9_Investments" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="10_Financing_Changes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="11_Returns_Volatility" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Weekly_Price_Data" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="12_Major_Announcements" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="12b_Announcement_Chart_Data" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet name="13_Sources_and_Gaps" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -142,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -732,6 +734,220 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Segment Revenue Trends FY21-FY26 (₹ crore): Tata segments vs Adani Generation</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'6b_Segment_Chart_Data'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'6b_Segment_Chart_Data'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'6b_Segment_Chart_Data'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$D$2:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'6b_Segment_Chart_Data'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$E$2:$E$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Fiscal Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>₹ crore</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
     <title>
@@ -834,7 +1050,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1264,6 +1480,33 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>44</row>
       <rowOff>0</rowOff>
     </from>
@@ -1285,7 +1528,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1811,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1823,12 +2066,16 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>8. Associates &amp; Joint Ventures</t>
+          <t>7. Group Structure — Subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr"/>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Key subsidiaries and % holding, with one-line business description.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
@@ -1839,17 +2086,17 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Associate / JV</t>
+          <t>Subsidiary</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Stake</t>
+          <t>% Holding</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Business Description</t>
         </is>
       </c>
     </row>
@@ -1861,17 +2108,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Moxie Power Generation Ltd (ex-Coastal Energen, 1,200 MW, Tamil Nadu)</t>
+          <t>Mahan Energen Ltd (MEL)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>49% (JV with Dickey Alternative Investment Trust, 51%)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Adani does NOT hold majority — classified as JV/associate, not a subsidiary.</t>
+          <t>1,200 MW (2x600) coal thermal plant, MP; ex-Essar Power MP, acquired via CIRP Mar 2022.</t>
         </is>
       </c>
     </row>
@@ -1883,17 +2130,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Jaiprakash Power Ventures Ltd (JPVL)</t>
+          <t>Korba Power Ltd (KPL)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>24% (indirect, via resolution plan)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Adani Power named 'Implementing Entity'; NCLT-approved ~Mar 2026 (~₹14,535 cr resolution plan).</t>
+          <t>600 MW (2x300) coal thermal plant, Chhattisgarh; ex-Lanco Amarkantak, NCLT-approved Aug 2024.</t>
         </is>
       </c>
     </row>
@@ -1905,105 +2152,501 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Adani Power–Druk Green Power Corp JV (Bhutan)</t>
+          <t>Kutchh Power Generation Ltd (KPGL)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>100% (step-down, via APDL)</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>570 MW Wangchhu hydro project (~₹6,000 cr); Shareholders Agreement signed Sep 2025; part of a broader 5,000 MW MoU (May 2025).</t>
+          <t>Held via Adani Power Dahanu Ltd (APDL); generation asset in Gujarat.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Tata Power Delhi Distribution Ltd</t>
+          <t>Adani Power Dahanu Ltd (APDL)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>51% (see Sheet 7 — sometimes classified as JV given 49% Delhi Govt partner)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Listed here for completeness; treated as subsidiary in Sheet 7 given majority control.</t>
+          <t>Holding vehicle for Dahanu-related generation assets.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dorjilung Hydro Power Ltd (Bhutan)</t>
+          <t>Adani Atomic Energy Ltd (AAEL)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Stake not disclosed</t>
+          <t>100% (incorporated Feb 2026)</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>1,125 MW hydro project under development.</t>
+          <t>New entry into nuclear power generation, post the SHANTI Act 2025 opening the sector to private players.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Other associates/JVs]</t>
+          <t>Progressive-UP Atomic Energy / Coastal-Maha Atomic Energy Ltd (CMAEL)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: Tata Power's full associates/JV list not retrievable via search — pull from Annual Report.</t>
+          <t>100% (step-down, incorporated 2026)</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Further nuclear-energy project SPVs.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
+          <t>Adani Power</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>[6 amalgamated cos: Adani Power Maharashtra, Adani Power Rajasthan, Udupi Power Corp, Raipur Energen, Raigarh Energy Generation, Adani Power (Mundra)]</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>N/A — merged into parent 1-Oct-2021</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Corporate simplification: these erstwhile subsidiaries were amalgamated directly into Adani Power Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Adani Power</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>[FULL AOC-1 list]</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>VERIFY: complete statutory subsidiary list with exact % holdings should be pulled from the AOC-1 annexure of the FY23/FY24 Annual Report (BSE corporate filings).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power Renewable Energy Ltd (TPREL)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>~100% (verify current %)</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Renewable energy arm — utility-scale + rooftop solar and wind generation/EPC; itself has 70 subsidiaries (47 wholly-owned) as of Mar-2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power Solar Systems Ltd (TPSSL)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Verify %</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Solar cell/module manufacturing and EPC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power Delhi Distribution Ltd (Tata Power-DDL)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>51% (JV with Delhi Govt / Delhi Power Co Ltd, 49%)</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Electricity distribution licensee for North Delhi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>TP Northern/Central/Western/Southern Odisha Distribution Ltds (TPNODL/TPCODL/TPWODL/TPSODL)</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>51% each</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Four Odisha discoms acquired 2020-21 (PPP with Odisha Govt); serve 12.6mn+ customers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Resurgent Power Ventures Pte Ltd (incl. NRSS XXXVI Transmission Ltd, South East UP Power Transmission Co Ltd)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Verify %</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Acquisition vehicle for transmission-project SPVs (acquired 2023).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Coastal Gujarat Power Ltd (CGPL) — NOTE</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Merged into parent, 1-Apr-2020</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Owner/operator of Mundra UMPP; NCLT-approved merger means it is NO LONGER a separate subsidiary — Mundra is now a direct Generation-segment asset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>[FULL subsidiary/JV/associate list]</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>VERIFY: Tata Power's 'Subsidiaries, JVs and Associates' annexure (dozens of generation/transmission/renewable SPVs) — pull from the Integrated Annual Report or AOC-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>2 associate companies (per AOC-1 reference)</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: names/business of the 2 associate companies not found via search — pull from Annual Report AOC-1.</t>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power Grid Ltd</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>74% (JV; PowerGrid Corp of India holds 26%)</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Interstate power transmission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Pipavav Generation Ltd</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Power generation, Pipavav.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Solargen Ltd</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Solar power generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Jodhpur Wind Farms Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Wind power generation, Rajasthan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Latur Renewable Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Renewable power generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Electricals Pvt Ltd (ex-TCL Cables Pvt Ltd)</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Cables/electricals manufacturing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Dadra &amp; Nagar Haveli and Daman &amp; Diu Power Distribution Corp Ltd</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Power distribution licensee (DNH&amp;DD), acquired 2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Nabha Power Ltd</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>100% (acquired Jun 2025)</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>2x700 MW coal-based supercritical thermal plant, Punjab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Visual Percept Solar Projects Pvt Ltd, Surya Vidyut Ltd, Sunshakti Solar Power Projects Pvt Ltd, Torrent Saurya Urja series</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>100% (Torrent Saurya Urja 2 confirmed; others not confirmed %)</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Solar power project SPVs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>[FULL list — ~35 subsidiaries reported]</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>VERIFY: only a partial list could be corroborated; pull the complete AOC-1 statement from torrentpower.com/index.php/site/info/subsidiaries or the Annual Report.</t>
         </is>
       </c>
     </row>
@@ -2022,6 +2665,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>8. Associates &amp; Joint Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Associate / JV</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Stake</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Adani Power</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Moxie Power Generation Ltd (ex-Coastal Energen, 1,200 MW, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>49% (JV with Dickey Alternative Investment Trust, 51%)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Adani does NOT hold majority — classified as JV/associate, not a subsidiary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Adani Power</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Jaiprakash Power Ventures Ltd (JPVL)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>24% (indirect, via resolution plan)</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Adani Power named 'Implementing Entity'; NCLT-approved ~Mar 2026 (~₹14,535 cr resolution plan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Adani Power</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Adani Power–Druk Green Power Corp JV (Bhutan)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>570 MW Wangchhu hydro project (~₹6,000 cr); Shareholders Agreement signed Sep 2025; part of a broader 5,000 MW MoU (May 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power Delhi Distribution Ltd</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>51% (see Sheet 7 — sometimes classified as JV given 49% Delhi Govt partner)</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Listed here for completeness; treated as subsidiary in Sheet 7 given majority control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Dorjilung Hydro Power Ltd (Bhutan)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Stake not disclosed</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>1,125 MW hydro project under development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>[Other associates/JVs]</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>VERIFY: Tata Power's full associates/JV list not retrievable via search — pull from Annual Report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2 associate companies (per AOC-1 reference)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>VERIFY: names/business of the 2 associate companies not found via search — pull from Annual Report AOC-1.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2110,7 +2964,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Note: this section requires the 'Investments' note from each company's FY2023 standalone/consolidated Balance Sheet — none of the three companies' figures could be reliably retrieved via web search in this session.</t>
         </is>
@@ -2126,7 +2980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2490,7 +3344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2524,7 +3378,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>HOW TO COMPLETE THIS SHEET</t>
         </is>
@@ -2800,7 +3654,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Key data-quality flag</t>
         </is>
@@ -2848,7 +3702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3126,7 +3980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3443,7 +4297,7 @@
       <c r="D19" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Note on this section</t>
         </is>
@@ -3470,7 +4324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3576,7 +4430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3650,7 +4504,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>4. Segment-wise (Ind AS 108) revenue/assets/profit tables, 5-yr, all three companies — pull from the 'Segment Reporting' note in each Annual Report (the PDFs now in the repo contain this — worth a follow-up extraction pass).</t>
+          <t>4. Segment-wise (Ind AS 108) tables — DONE: Sheet 6 now carries verified segment revenue/results/assets for Adani Power (FY20-FY26, 2 segments) and Tata Power (FY21-FY26, 4 segments), plus the verified finding that Torrent Power reports NO segments under Ind AS 108 (single integrated business).</t>
         </is>
       </c>
     </row>
@@ -6488,163 +7342,668 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>6. Reportable Business Segments</t>
+          <t>6. Reportable Business Segments (Ind AS 108) — VERIFIED from Annual Reports</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>As disclosed under Ind AS 108 in each company's Annual Report.</t>
+          <t>₹ crore, consolidated. Extracted directly from the 'Segment Reporting' notes of each company's audited Annual Reports (FY21-FY26 reports uploaded by user).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Reportable segments (per Annual Report)</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Two segments: (1) Power Generation, (2) Trading, Investment &amp; Other activities.</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>~Four segments: (1) Generation, (2) Transmission &amp; Distribution, (3) Renewables, (4) Solar EPC/Manufacturing &amp; Other.</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Three segments: (1) Generation (gas/coal/renewables), (2) Transmission, (3) Distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>ADANI POWER — 2 segments: 'Power Generation &amp; related activities' + 'Trading, Investment &amp; other activities'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>FY20</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Approx. revenue mix (most recent disclosed)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Power Generation is overwhelmingly dominant; Trading/Other is a small residual. Exact % split not found.</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>T&amp;D ~55% of revenue, Renewables ~25%, remainder Generation + Other/EPC (FY24/25-era mix, qualitative).</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Distribution is the largest revenue contributor (regulated + volume-driven); Generation dominates capacity but a large share of gas/coal output is sold to the Group's own distribution business.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>Segment Revenue — Power Generation</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>26005.92</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>25870.6</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>27221.78</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>37895.85</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>50014.16</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>56107.06</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>54240.52</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>5-yr segment-wise revenue / assets / profit table</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>NOT FOUND — segment note (Ind AS 108) inside Annual Report notes-to-accounts was inaccessible via search; pull directly from FY19-FY23 Annual Report PDFs.</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>NOT FOUND — same issue; pull the segment-reporting note from each year's Annual Report.</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>NOT FOUND — same issue; only qualitative capacity data (e.g., FY23 distribution electricity purchase +63.2% YoY to 30,037 MU) was found via search.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>Segment Revenue — Trading/Investment/Other</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>461.8</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>489.4</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>877.45</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Segment growth vs industry benchmark</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>India's overall power demand grew ~7-8%/yr in recent years (CEA data); Adani Power's generation-segment growth (capacity nearly doubled since FY22 via M&amp;A) has materially outpaced organic sector growth.</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>T&amp;D segment growth benefited from 4 new Odisha discoms (2020-21) — inorganic, faster than organic distribution-sector growth; Renewables segment growing faster than India's ~15-20%/yr renewable capacity addition rate per company commentary.</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Distribution segment volume growth (+63.2% in FY23) was overwhelmingly driven by the DNH&amp;DD acquisition (inorganic), not organic like-for-like growth — strip this out for a fair industry comparison.</t>
-        </is>
+          <t>Segment Results — Power Generation</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>6571.37</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>6957.13</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>20557.22</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>16540.39</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>15757.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Segment Results — Trading/Investment/Other</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>717.5700000000001</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>234.29</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>13.68</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Comparative comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Adani Power is essentially a pure-play generation company (single dominant segment), while Tata Power and Torrent Power are vertically integrated across generation-transmission-distribution, which structurally smooths their earnings (regulated D&amp;T returns cushion merchant-generation volatility) relative to Adani Power's more merchant/PPA-driven, generation-only earnings profile. Among the two integrated peers, Tata Power is furthest along the renewables transition (~25% of revenue mix, explicit 100%-renewable ambition), while Torrent Power remains more gas/coal-weighted in generation with distribution as its largest and most stable segment. A precise, numbers-based segment growth-rate comparison could not be completed — the exact Ind AS 108 segment tables (revenue/assets/profit by segment, 5-yr) need to be manually extracted from each company's Annual Report notes, as this data is not surfaced by web search.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Segment Assets — Power Generation</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>74847.53999999999</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>77747</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>81888.09</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>84364.22</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>91378.85000000001</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>111162.48</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>139777.31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Segment Assets — Trading/Investment/Other</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>177.46</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>788.47</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>1134.26</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>203.86</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>1328.18</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>1354.52</v>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>FY20/21 segment results shown as N/A because the FY21 report used a different basis ('profit before interest…', not comparable); FY22-23 results are as restated in the FY23 report after a CODM methodology change. FY26 Trading revenue was nil; segment results shown are pre-tax basis per each year's note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>TATA POWER — 4 segments: Generation (Thermal &amp; Hydro), Renewables, Transmission &amp; Distribution, Others</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Generation/Thermal &amp; Hydro</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>13432.77</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>11211.03</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>18211.35</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>19613.61</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>19739.07</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>11635.93</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Renewables</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>5887.65</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>7748.9</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>8196.91</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>10175.29</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>9876.360000000001</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>15027.82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>16829.85</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>27493.17</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>34529.36</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>36205.82</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>39120.52</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>41338.59</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Others</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>262.16</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>317.8</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>413.56</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>430.62</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>431.04</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>431.79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Segment Results — Generation/Thermal &amp; Hydro</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>2709.81</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>2632.75</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>5092.16</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>2569.61</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>2878.91</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>1137.94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Segment Results — Renewables</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>1494.25</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>1923.57</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>1932.01</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>2147.1</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>2880.68</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>4340.93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Segment Results — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>1677.02</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>2138.49</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>2197.68</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>2418.22</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>3128.27</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>4307.95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Segment Results — Others</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>-286.03</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>-308.17</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>105.38</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>104.72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Segment Assets — Generation/Thermal &amp; Hydro</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>37717.32</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>38201.93</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>41201.04</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>39315.88</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>39708.11</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>41697.31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Segment Assets — Renewables</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>22702.98</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>27589.28</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>29744.49</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>40459.25</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>51355.61</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>56921.28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Segment Assets — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>25542.61</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>32411.34</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>37477.26</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>42059.9</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>45707.75</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>53428.87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Segment Assets — Others + Unallocable</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>12875.95</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>14682.04</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>19926.25</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>17718.46</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>19939.82</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>23124.32</v>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Revenue shown gross (before inter-segment eliminations of ~₹4,000-5,400cr/yr, mostly Generation→T&amp;D coal/power sales). 'Generation' was renamed 'Thermal &amp; Hydro' from the FY25 report. FY23 Generation result of ₹5,092cr was later restated in the FY24 report to ₹1,528cr segment result + ₹3,564cr exceptional; the as-originally-reported figure is shown here. FY26 Thermal &amp; Hydro result derived as total-minus-other-segments (₹9,891.54cr total). FY26 revenue drop in Thermal &amp; Hydro reflects the Mundra shutdown; Renewables surged on new capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>TORRENT POWER — NO reportable segments under Ind AS 108</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="95" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Per Note 53/54 ('Operating Segments') of Torrent Power's FY23 Annual Report (and equivalent notes in other years): "the Group does not have any reportable segment as per Ind AS-108 'Operating Segments'" — the CODM manages Generation, Transmission and Distribution as ONE integrated electricity business, and the cable business is immaterial (below reportable thresholds for revenue, profit and assets). This is an important verified correction: earlier drafts of this sheet assumed 3 reportable segments (Generation/Transmission/Distribution) from the MD&amp;A's business description — the MD&amp;A discusses those businesses operationally, but the statutory segment note reports a single segment. Any segment-level financial comparison for Torrent must therefore rely on MD&amp;A operating metrics (e.g., FY23 distribution electricity purchases +63.2% YoY to 30,037 MU after the DNH&amp;DD takeover), not audited segment P&amp;L data, because none is published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Comparative analysis — who is doing well in which segment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>GENERATION is the only segment where all three effectively compete, and the verified numbers show a stark contrast: Adani Power's generation segment grew revenue ~2.1x (₹26,006cr FY20 → ₹54,241cr FY26) with segment results of ₹15,758-20,557cr in FY24-26 — vastly more profitable than Tata Power's generation segment (results of only ₹1,138-2,879cr on ₹11,636-19,739cr revenue in the same years, dragged by the Mundra plant's fuel economics and eventual shutdown). Adani is unambiguously the generation winner. RENEWABLES: only Tata Power reports it separately, and it is now their growth engine — revenue up 2.6x (₹5,888cr FY21 → ₹15,028cr FY26), results up 2.9x (₹1,494cr → ₹4,341cr), and segment assets up 2.5x to ₹56,921cr, overtaking every other Tata segment. Adani Power has no renewables segment (that sits in sister company Adani Green). TRANSMISSION &amp; DISTRIBUTION: Tata Power's largest and steadiest segment — revenue grew ₹16,830cr → ₹41,339cr (FY21→FY26, boosted by the Odisha discoms) with consistently positive, regulated-return results (₹1,677cr → ₹4,308cr). Torrent's distribution business is economically similar (regulated, stable) but not separately reported. INDUSTRY CONTEXT: India's power demand grew ~7-8%/yr (CEA) over this period — Adani's generation growth (~13% CAGR) and Tata's renewables growth (~21% CAGR) both outpaced the sector, largely through acquisitions and capacity build-out respectively, while Tata's generation segment underperformed the sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D18"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="6">
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A39:H47"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A32:H36"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6654,607 +8013,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>7. Group Structure — Subsidiaries</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tata Generation Rev</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tata Renewables Rev</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tata T&amp;D Rev</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Adani Generation Rev</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Key subsidiaries and % holding, with one-line business description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13432.77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5887.65</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16829.85</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25870.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11211.03</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7748.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27493.17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27221.78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>18211.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8196.91</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34529.36</v>
+      </c>
+      <c r="E4" t="n">
+        <v>37895.85</v>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Subsidiary</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>% Holding</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Business Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Mahan Energen Ltd (MEL)</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>1,200 MW (2x600) coal thermal plant, MP; ex-Essar Power MP, acquired via CIRP Mar 2022.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Korba Power Ltd (KPL)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>600 MW (2x300) coal thermal plant, Chhattisgarh; ex-Lanco Amarkantak, NCLT-approved Aug 2024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Kutchh Power Generation Ltd (KPGL)</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>100% (step-down, via APDL)</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Held via Adani Power Dahanu Ltd (APDL); generation asset in Gujarat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power Dahanu Ltd (APDL)</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Holding vehicle for Dahanu-related generation assets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Adani Atomic Energy Ltd (AAEL)</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>100% (incorporated Feb 2026)</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>New entry into nuclear power generation, post the SHANTI Act 2025 opening the sector to private players.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Progressive-UP Atomic Energy / Coastal-Maha Atomic Energy Ltd (CMAEL)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>100% (step-down, incorporated 2026)</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Further nuclear-energy project SPVs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>[6 amalgamated cos: Adani Power Maharashtra, Adani Power Rajasthan, Udupi Power Corp, Raipur Energen, Raigarh Energy Generation, Adani Power (Mundra)]</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>N/A — merged into parent 1-Oct-2021</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Corporate simplification: these erstwhile subsidiaries were amalgamated directly into Adani Power Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Adani Power</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>[FULL AOC-1 list]</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: complete statutory subsidiary list with exact % holdings should be pulled from the AOC-1 annexure of the FY23/FY24 Annual Report (BSE corporate filings).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power Renewable Energy Ltd (TPREL)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>~100% (verify current %)</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Renewable energy arm — utility-scale + rooftop solar and wind generation/EPC; itself has 70 subsidiaries (47 wholly-owned) as of Mar-2024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power Solar Systems Ltd (TPSSL)</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Verify %</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Solar cell/module manufacturing and EPC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power Delhi Distribution Ltd (Tata Power-DDL)</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>51% (JV with Delhi Govt / Delhi Power Co Ltd, 49%)</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Electricity distribution licensee for North Delhi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>TP Northern/Central/Western/Southern Odisha Distribution Ltds (TPNODL/TPCODL/TPWODL/TPSODL)</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>51% each</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Four Odisha discoms acquired 2020-21 (PPP with Odisha Govt); serve 12.6mn+ customers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Resurgent Power Ventures Pte Ltd (incl. NRSS XXXVI Transmission Ltd, South East UP Power Transmission Co Ltd)</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Verify %</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Acquisition vehicle for transmission-project SPVs (acquired 2023).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Coastal Gujarat Power Ltd (CGPL) — NOTE</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Merged into parent, 1-Apr-2020</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Owner/operator of Mundra UMPP; NCLT-approved merger means it is NO LONGER a separate subsidiary — Mundra is now a direct Generation-segment asset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>[FULL subsidiary/JV/associate list]</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: Tata Power's 'Subsidiaries, JVs and Associates' annexure (dozens of generation/transmission/renewable SPVs) — pull from the Integrated Annual Report or AOC-1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power Grid Ltd</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>74% (JV; PowerGrid Corp of India holds 26%)</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Interstate power transmission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Pipavav Generation Ltd</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Power generation, Pipavav.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Solargen Ltd</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Solar power generation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Jodhpur Wind Farms Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Wind power generation, Rajasthan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Latur Renewable Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Renewable power generation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Electricals Pvt Ltd (ex-TCL Cables Pvt Ltd)</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Cables/electricals manufacturing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Dadra &amp; Nagar Haveli and Daman &amp; Diu Power Distribution Corp Ltd</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Power distribution licensee (DNH&amp;DD), acquired 2022.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Nabha Power Ltd</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>100% (acquired Jun 2025)</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>2x700 MW coal-based supercritical thermal plant, Punjab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Visual Percept Solar Projects Pvt Ltd, Surya Vidyut Ltd, Sunshakti Solar Power Projects Pvt Ltd, Torrent Saurya Urja series</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>100% (Torrent Saurya Urja 2 confirmed; others not confirmed %)</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Solar power project SPVs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>[FULL list — ~35 subsidiaries reported]</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: only a partial list could be corroborated; pull the complete AOC-1 statement from torrentpower.com/index.php/site/info/subsidiaries or the Annual Report.</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19613.61</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10175.29</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36205.82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50014.16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19739.07</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9876.360000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>39120.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>56107.06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11635.93</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15027.82</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41338.59</v>
+      </c>
+      <c r="E7" t="n">
+        <v>54240.52</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -2113,12 +2113,12 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94% (per FY26 AOC-1 — earlier reported as 100%)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>1,200 MW (2x600) coal thermal plant, MP; ex-Essar Power MP, acquired via CIRP Mar 2022.</t>
+          <t>1,200+ MW coal thermal, MP; ex-Essar Power MP (CIRP, Mar 2022). FY26: turnover ₹3,614cr, PAT ₹784cr.</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Korba Power Ltd (KPL)</t>
+          <t>Korba Power Ltd (KPL, ex-Lanco Amarkantak)</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>600 MW (2x300) coal thermal plant, Chhattisgarh; ex-Lanco Amarkantak, NCLT-approved Aug 2024.</t>
+          <t>600 MW coal thermal, Chhattisgarh (CIRP, Sep 2024). FY26: turnover ₹1,552cr, PAT ₹354cr.</t>
         </is>
       </c>
     </row>
@@ -2152,17 +2152,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Kutchh Power Generation Ltd (KPGL)</t>
+          <t>Moxie Power Generation Ltd (ex-Coastal Energen)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>100% (step-down, via APDL)</t>
+          <t>49% — but consolidated as a SUBSIDIARY in AOC-1 Part A (control basis), not a JV</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Held via Adani Power Dahanu Ltd (APDL); generation asset in Gujarat.</t>
+          <t>1,200 MW, Thoothukudi, Tamil Nadu. FY26: turnover ₹2,985cr, PAT ₹268cr. Listed in AOC-1 subsidiaries despite 49% equity — control established via arrangement with DAIT.</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Adani Power Dahanu Ltd (APDL)</t>
+          <t>Vidarbha Industries Power Ltd (VIPL)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100% (acquired 07-Jul-2025)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Holding vehicle for Dahanu-related generation assets.</t>
+          <t>600 MW, Nagpur (CIRP). FY26: turnover ₹1,327cr, PAT ₹347cr.</t>
         </is>
       </c>
     </row>
@@ -2196,17 +2196,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Adani Atomic Energy Ltd (AAEL)</t>
+          <t>Adani Power Dahej Ltd / Pench Thermal Energy (MP) Ltd / Kutchh Power Generation Ltd</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>100% (incorporated Feb 2026)</t>
+          <t>100% each</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>New entry into nuclear power generation, post the SHANTI Act 2025 opening the sector to private players.</t>
+          <t>Greenfield thermal project SPVs (Dahej, Pench, Kutchh).</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Progressive-UP Atomic Energy / Coastal-Maha Atomic Energy Ltd (CMAEL)</t>
+          <t>Anuppur Thermal Energy (MP) / Mirzapur Thermal Energy (UP) / Orrisa Thermal Energy</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>100% (step-down, incorporated 2026)</t>
+          <t>100% each (acquired/renamed 2024)</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Further nuclear-energy project SPVs.</t>
+          <t>New thermal project SPVs for capacity expansion (Anuppur, Mirzapur, Odisha sites).</t>
         </is>
       </c>
     </row>
@@ -2240,17 +2240,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>[6 amalgamated cos: Adani Power Maharashtra, Adani Power Rajasthan, Udupi Power Corp, Raipur Energen, Raigarh Energy Generation, Adani Power (Mundra)]</t>
+          <t>Mahan Fuel Management / Resurgent Fuel Management Ltd</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>N/A — merged into parent 1-Oct-2021</t>
+          <t>100% each</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Corporate simplification: these erstwhile subsidiaries were amalgamated directly into Adani Power Ltd.</t>
+          <t>Fuel sourcing/management SPVs.</t>
         </is>
       </c>
     </row>
@@ -2262,105 +2262,105 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[FULL AOC-1 list]</t>
+          <t>Alcedo / Chandenvalle / Emberiza Infra Park Ltd</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: complete statutory subsidiary list with exact % holdings should be pulled from the AOC-1 annexure of the FY23/FY24 Annual Report (BSE corporate filings).</t>
+          <t>100% each</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Infrastructure park SPVs.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Tata Power Renewable Energy Ltd (TPREL)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>~100% (verify current %)</t>
+          <t>Adani Atomic Energy Ltd (AAEL)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>100% (incorporated 11-Feb-2026)</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Renewable energy arm — utility-scale + rooftop solar and wind generation/EPC; itself has 70 subsidiaries (47 wholly-owned) as of Mar-2024.</t>
+          <t>Nuclear power entry post SHANTI Act 2025.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Tata Power Solar Systems Ltd (TPSSL)</t>
+          <t>Adani Power Middle East Ltd (AED) / Adani Power Global Pte Ltd (US$)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Verify %</t>
+          <t>100% each (incorporated 2024)</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Solar cell/module manufacturing and EPC.</t>
+          <t>Overseas ventures (Middle East; Singapore trading/holding).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Tata Power Delhi Distribution Ltd (Tata Power-DDL)</t>
+          <t>Adani Power Resources Ltd</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>51% (JV with Delhi Govt / Delhi Power Co Ltd, 49%)</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Electricity distribution licensee for North Delhi.</t>
+          <t>Resource-related SPV (immaterial size).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Adani Power</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>TP Northern/Central/Western/Southern Odisha Distribution Ltds (TPNODL/TPCODL/TPWODL/TPSODL)</t>
+          <t>[TOTAL: 19 entities in FY26 AOC-1 Part A — fully verified]</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>51% each</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Four Odisha discoms acquired 2020-21 (PPP with Odisha Govt); serve 12.6mn+ customers.</t>
+          <t>The 6 operating cos (Adani Power Maharashtra/Rajasthan, Udupi, Raipur/Raigarh Energen, Adani Power (Mundra)) were amalgamated INTO the parent effective 1-Oct-2021 and no longer appear.</t>
         </is>
       </c>
     </row>
@@ -2372,17 +2372,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Resurgent Power Ventures Pte Ltd (incl. NRSS XXXVI Transmission Ltd, South East UP Power Transmission Co Ltd)</t>
+          <t>Tata Power Renewable Energy Ltd (TPREL)</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Verify %</t>
+          <t>88.57% (per FY26 AOC-1 — VERIFIED; not ~100% as earlier assumed)</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Acquisition vehicle for transmission-project SPVs (acquired 2023).</t>
+          <t>Renewables arm (solar/wind/rooftop/EV charging). FY26: turnover ₹11,748cr, PAT ₹1,268cr. ~11.4% held by BlackRock-led consortium since FY23 equity raise.</t>
         </is>
       </c>
     </row>
@@ -2394,17 +2394,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Coastal Gujarat Power Ltd (CGPL) — NOTE</t>
+          <t>Tata Power Delhi Distribution Ltd (Tata Power-DDL)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Merged into parent, 1-Apr-2020</t>
+          <t>51% (VERIFIED per FY26 AOC-1)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Owner/operator of Mundra UMPP; NCLT-approved merger means it is NO LONGER a separate subsidiary — Mundra is now a direct Generation-segment asset.</t>
+          <t>North Delhi discom (JV with Delhi Govt). FY26: turnover ₹10,426cr, PAT ₹1,299cr.</t>
         </is>
       </c>
     </row>
@@ -2416,83 +2416,83 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>[FULL subsidiary/JV/associate list]</t>
+          <t>TP Central / Western / Southern / Northern Odisha Distribution Ltds</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: Tata Power's 'Subsidiaries, JVs and Associates' annexure (dozens of generation/transmission/renewable SPVs) — pull from the Integrated Annual Report or AOC-1.</t>
+          <t>51% each (VERIFIED)</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Four Odisha discoms (PPP, 2020-21). FY26 turnover: TPCODL ₹6,313cr, TPWODL ₹6,355cr, TPSODL ₹2,542cr, TPNODL ₹4,769cr; all PAT-positive.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Torrent Power</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Torrent Power Grid Ltd</t>
+          <t>Tata Power Solar Systems Ltd (TPSSL)</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>74% (JV; PowerGrid Corp of India holds 26%)</t>
+          <t>In AOC-1 (100%, via TPREL structure)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Interstate power transmission.</t>
+          <t>Solar cell/module manufacturing + EPC.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Torrent Power</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Torrent Pipavav Generation Ltd</t>
+          <t>Coastal Gujarat Power Ltd (CGPL) — NOTE</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>Merged into parent, 1-Apr-2020</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Power generation, Pipavav.</t>
+          <t>Mundra UMPP is now a direct Generation-segment asset, not a subsidiary.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Torrent Power</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Torrent Solargen Ltd</t>
+          <t>[TOTAL: ~113 entities in FY26 AOC-1 Part A]</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Solar power generation.</t>
+          <t>Includes dozens of renewable/transmission SPVs under TPREL and Resurgent Power Ventures; full list in FY26 Annual Report pg. 666+ (AOC-1).</t>
         </is>
       </c>
     </row>
@@ -2504,17 +2504,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Jodhpur Wind Farms Pvt Ltd</t>
+          <t>Torrent Power Grid Ltd</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74% (VERIFIED; PowerGrid Corp holds 26%)</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Wind power generation, Rajasthan.</t>
+          <t>Interstate power transmission JV-structured subsidiary.</t>
         </is>
       </c>
     </row>
@@ -2526,17 +2526,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Latur Renewable Pvt Ltd</t>
+          <t>Transmission SPVs (Solapur Transmission Ltd &amp; 4 others at 74%)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74% each (per FY26 AOC-1)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Renewable power generation.</t>
+          <t>Intra/interstate transmission project SPVs.</t>
         </is>
       </c>
     </row>
@@ -2548,17 +2548,17 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Torrent Electricals Pvt Ltd (ex-TCL Cables Pvt Ltd)</t>
+          <t>Torrent Pipavav Generation Ltd</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95% (VERIFIED)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Cables/electricals manufacturing.</t>
+          <t>Power generation project, Pipavav.</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>51% (VERIFIED)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Power distribution licensee (DNH&amp;DD), acquired 2022.</t>
+          <t>UT power distribution licensee (acquired Apr 2022).</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>100% (acquired Jun 2025)</t>
+          <t>100% (acquired Jun 2026)</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>2x700 MW coal-based supercritical thermal plant, Punjab.</t>
+          <t>2x700 MW supercritical coal plant, Punjab (from L&amp;T).</t>
         </is>
       </c>
     </row>
@@ -2614,17 +2614,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Visual Percept Solar Projects Pvt Ltd, Surya Vidyut Ltd, Sunshakti Solar Power Projects Pvt Ltd, Torrent Saurya Urja series</t>
+          <t>Torrent Solargen, Latur Renewable, Surya Vidyut, Torrent Akshay Urja, Jodhpur Wind Farms, MSKVY solar SPVs, Torrent Electricals, Newzone India, etc.</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>100% (Torrent Saurya Urja 2 confirmed; others not confirmed %)</t>
+          <t>100% each</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Solar power project SPVs.</t>
+          <t>Renewable generation SPVs (solar/wind incl. Maharashtra MSKVY series), cables/electricals, and other ventures.</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>[FULL list — ~35 subsidiaries reported]</t>
+          <t>[TOTAL: ~60 entities in FY26 AOC-1 — 53 at 100%, 5 at 74%, 1 at 95%, 1 at 51%]</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -2644,9 +2644,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: only a partial list could be corroborated; pull the complete AOC-1 statement from torrentpower.com/index.php/site/info/subsidiaries or the Annual Report.</t>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Verified from the FY26 Annual Report AOC-1 statement.</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Moxie Power Generation Ltd (ex-Coastal Energen, 1,200 MW, Tamil Nadu)</t>
+          <t>Wangchhu Hydroelectric Power Ltd (Bhutan)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>49% (JV with Dickey Alternative Investment Trust, 51%)</t>
+          <t>JV (per FY26 AOC-1 Part B — the Group's only listed associate/JV)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Adani does NOT hold majority — classified as JV/associate, not a subsidiary.</t>
+          <t>570 MW Wangchhu hydro project JV with Druk Green Power Corp (~₹6,000 cr); Shareholders Agreement Sep 2025; 'yet to commence operations' per AOC-1. VERIFIED.</t>
         </is>
       </c>
     </row>
@@ -2737,17 +2737,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Jaiprakash Power Ventures Ltd (JPVL)</t>
+          <t>Moxie Power Generation Ltd — RECLASSIFIED</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>24% (indirect, via resolution plan)</t>
+          <t>49% equity but consolidated as SUBSIDIARY (see Sheet 7)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Adani Power named 'Implementing Entity'; NCLT-approved ~Mar 2026 (~₹14,535 cr resolution plan).</t>
+          <t>CORRECTION: earlier flagged as a JV; the FY26 AOC-1 lists it under Part A (Subsidiaries) — Adani has control despite 49% equity.</t>
         </is>
       </c>
     </row>
@@ -2759,17 +2759,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Adani Power–Druk Green Power Corp JV (Bhutan)</t>
+          <t>Jaiprakash Power Ventures Ltd (JPVL)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>24% (indirect, via resolution plan)</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>570 MW Wangchhu hydro project (~₹6,000 cr); Shareholders Agreement signed Sep 2025; part of a broader 5,000 MW MoU (May 2025).</t>
+          <t>Adani Power as 'Implementing Entity'; NCLT-approved ~Mar 2026 (~₹14,535 cr). Not yet in FY26 AOC-1 Part B (transaction completing post year-end).</t>
         </is>
       </c>
     </row>
@@ -2781,17 +2781,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Tata Power Delhi Distribution Ltd</t>
+          <t>Tata Projects, Resurgent Power Ventures (26%), industrial JVs &amp; associates</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>51% (see Sheet 7 — sometimes classified as JV given 49% Delhi Govt partner)</t>
+          <t>Various</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Listed here for completeness; treated as subsidiary in Sheet 7 given majority control.</t>
+          <t>Tata Power holds numerous associates/JVs (share of profit ₹708cr FY26, ₹793cr FY25 per consolidated P&amp;L); full Part B list in FY26 Annual Report AOC-1.</t>
         </is>
       </c>
     </row>
@@ -2808,56 +2808,34 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Stake not disclosed</t>
+          <t>Stake not disclosed in extract</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>1,125 MW hydro project under development.</t>
+          <t>1,125 MW hydro project under development with Druk Green.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Torrent Power</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Other associates/JVs]</t>
+          <t>Associates (2 per earlier AOC-1 references)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: Tata Power's full associates/JV list not retrievable via search — pull from Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Torrent Power</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>2 associate companies (per AOC-1 reference)</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>VERIFY: names/business of the 2 associate companies not found via search — pull from Annual Report AOC-1.</t>
+          <t>Not extracted</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Torrent's FY26 AOC-1 Part B not extracted in this pass — the Part A subsidiary data above is verified; pull Part B from the same annexure if associate detail is needed.</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4503,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>7. Complete subsidiary/associate/JV lists with exact % holdings — pull the AOC-1 annexure from each company's Annual Report (now in the repo — worth a follow-up extraction pass).</t>
+          <t>7. Subsidiary lists — DONE: Sheets 7-8 now carry the verified FY26 AOC-1 data (Adani 19 entities incl. Mahan at 94% and Moxie consolidated at 49%; Tata ~113 entities incl. TPREL at 88.57%; Torrent ~60 entities). Only Torrent's associates (Part B) remain unextracted.</t>
         </is>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -2896,14 +2896,14 @@
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>No disclosed breakdown of non-subsidiary investment portfolio (govt securities, mutual funds, bonds) found for FY19-FY23. This sits in the balance-sheet 'Investments' / 'Other Financial Assets' note.</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED from FY23 consolidated Investments notes: NON-CURRENT — ₹42.51cr total as at 31-Mar-2023 (vs ₹0.01cr FY22), comprising ₹42.50cr of 0.001% Optionally Convertible Cumulative Debentures of Sal Technologies and Solutions Ltd (4.25cr units, new in FY23), a ₹0.01cr National Saving Certificate, and a negligible FVTOCI equity stake in Adani Naval Defence Systems &amp; Technologies Ltd. CURRENT — ₹611.54cr in unquoted mutual funds (SBI Liquid Fund ₹608.42cr + SBI Overnight Fund ₹3.12cr) vs ₹183.24cr (FY22, SBI Overnight only). Pattern: treasury parked in liquid MFs, scale rising with cash generation; almost no discretionary long-term securities portfolio.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>GAP — pull from Annual Report</t>
+          <t>VERIFIED (FY23 Annual Report)</t>
         </is>
       </c>
     </row>
@@ -2913,14 +2913,14 @@
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>One unverified secondary snippet suggested non-current investments of ~₹12,064.55 crore as of March 2023 (consolidation basis unclear, source of uncertain provenance).</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED from FY23 consolidated Investments note: non-current investments OTHER than associates/JVs totalled ₹1,301.21cr as at 31-Mar-2023 (vs ₹1,169.81cr FY22), comprising equity shares carried at FVTOCI/FVTPL and Government Securities (unquoted) of ₹128.10cr (FY22: ₹124.26cr). The earlier secondary-source figure of '~₹12,064cr non-current investments' conflated investments in associates/JVs (equity-method carrying values) with this third-party portfolio — use ₹1,301cr for the ex-subsidiary/associate/JV basis the assignment asks for.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>UNVERIFIED — do not cite without checking the FY23 balance sheet directly</t>
+          <t>VERIFIED (FY23 Annual Report) — replaces earlier unverified figure</t>
         </is>
       </c>
     </row>
@@ -2930,21 +2930,21 @@
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Holds Government of India Bonds as part of a regulatory 'contingency reserve' required under GERC Multi-Year Tariff Regulations (tied to its Gujarat distribution license) — i.e., regulatory-mandated, not discretionary treasury investment. No itemized schedule found.</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED from FY23 consolidated Investments notes: NON-CURRENT — quoted investments (incl. Government of India bonds held as the GERC Multi-Year-Tariff-mandated 'contingency reserve' for its Gujarat distribution licences) of ~₹15.94cr market value ₹15.70cr as at 31-Mar-2023 (down from ₹132.82cr FY22 as bonds matured/were reclassified). CURRENT — ₹682.31cr total (vs ₹253.27cr FY22): unquoted mutual funds ₹656.03cr + statutory contingency-reserve investments ₹1.93cr + other ₹24.35cr. The GoI-bond holdings are regulatory-mandated (usable only for GERC-specified purposes), not discretionary treasury.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>PARTIAL — nature identified, amounts not found</t>
+          <t>VERIFIED (FY23 Annual Report)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Note: this section requires the 'Investments' note from each company's FY2023 standalone/consolidated Balance Sheet — none of the three companies' figures could be reliably retrieved via web search in this session.</t>
+          <t>All three companies' figures above are now extracted directly from the consolidated 'Investments' notes of the FY2022-23 Annual Reports uploaded to the repo. Common pattern: all three park treasury cash in liquid/overnight mutual funds; Torrent additionally holds regulatory-mandated GoI bonds (GERC contingency reserve); none runs a material discretionary securities portfolio.</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>8. Investments note (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — pull from each company's Balance Sheet notes.</t>
+          <t>8. Investments (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — DONE: Sheet 9 now carries verified figures from all three FY23 Annual Reports (Adani ₹42.51cr non-current + ₹611.54cr MFs; Tata ₹1,301.21cr; Torrent ₹15.94cr bonds + ₹682.31cr current).</t>
         </is>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -948,7 +948,6 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -959,7 +958,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Adani Power vs Nifty 50 — Available Price Points (sparse; replace with full weekly series)</a:t>
+              <a:t>1-Year Performance, Rebased to 100 (weekly adj close, 14-Jul-2025 = 100)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -973,7 +972,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Weekly_Price_Data'!B1</f>
+              <f>'Weekly_Price_Data'!K1</f>
             </strRef>
           </tx>
           <spPr>
@@ -991,12 +990,108 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Weekly_Price_Data'!$A$2:$A$17</f>
+              <f>'Weekly_Price_Data'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Weekly_Price_Data'!$B$2:$B$17</f>
+              <f>'Weekly_Price_Data'!$K$2:$K$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Weekly_Price_Data'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Weekly_Price_Data'!$A$2:$A$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Weekly_Price_Data'!$L$2:$L$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Weekly_Price_Data'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Weekly_Price_Data'!$A$2:$A$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Weekly_Price_Data'!$M$2:$M$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Weekly_Price_Data'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Weekly_Price_Data'!$A$2:$A$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Weekly_Price_Data'!$N$2:$N$55</f>
             </numRef>
           </val>
         </ser>
@@ -1009,6 +1104,21 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Week ending</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1030,7 +1140,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Adani Power (₹)</a:t>
+                  <a:t>Index (start = 100)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1062,7 +1172,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Adani Power Share Price Around Major Announcements (sparse real data points — extend with daily NSE data)</a:t>
+              <a:t>Adani Power weekly adj close, Jul-2025 to Jul-2026 — events marked in hidden data sheet col C</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1094,12 +1204,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'12b_Announcement_Chart_Data'!$A$2:$A$6</f>
+              <f>'12b_Announcement_Chart_Data'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'12b_Announcement_Chart_Data'!$B$2:$B$6</f>
+              <f>'12b_Announcement_Chart_Data'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -1121,7 +1231,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Date</a:t>
+                  <a:t>Week ending</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1507,10 +1617,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4680000"/>
+    <ext cx="10080000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1537,7 +1647,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4680000"/>
+    <ext cx="10080000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -3328,352 +3438,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>11. Share Price Return vs Sectoral &amp; Market Index (weekly, trailing 1-yr to 15-Jul-2026) &amp; Volatility</t>
+          <t>11. Share Price Return vs Sector Index (weekly, 14-Jul-2025 to 15-Jul-2026) &amp; Volatility</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>A full 52-point weekly series could not be scripted-fetched in this session (NSE/BSE/Yahoo blocked automated access). Approximate/point data below; full series must be pulled manually — see instructions.</t>
+          <t>COMPUTED from actual Yahoo Finance weekly adjusted-close data (split-adjusted), saved to repo as *_weekly.htm and parsed. 54 weekly points per series. Nifty Energy = sector index. Nifty 50 column pending (see note).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>HOW TO COMPLETE THIS SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>1) Open finance.yahoo.com/quote/ADANIPOWER.NS/history (and TATAPOWER.NS, TORNTPOWER.NS, ^NSEI for Nifty 50, and ^CNXENERGY or niftyindices.com for Nifty Energy as the sector proxy) and set interval to 'Weekly'. 2) Export ~52 weekly closes for each, 16-Jul-2025 to 15-Jul-2026, into the 'Weekly_Price_Data' sheet (hidden — unhide to use). 3) Compute weekly % return = (P_t / P_t-1) - 1 for each series. 4) IMPORTANT: Adani Power did a 1:5 stock split effective 22-Sep-2025 — Yahoo/NSE usually auto-adjust historical prices for splits, but confirm the series is split-adjusted throughout, or your early-period 'returns' will be wildly wrong. 5) Annualized volatility = STDEV(weekly returns) * SQRT(52).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Nifty 50</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sensex</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Nifty Energy (sector proxy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Nifty Energy (sector)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Nifty 50 (market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Price at start (14-Jul-2025, adj)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>118.93</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>405.39</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>1,349.89</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>36,231.65</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Price at end (15-Jul-2026)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>218.97</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>380.90</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>1,441.10</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>39,381.25</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>52-week weekly-close range</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>113.40 - 243.37</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>343.12 - 441.81</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>1,204.41 - 1,730.01</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>33,098.30 - 40,878.00</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1-year return (COMPUTED)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>+84.1%</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>-6.0%</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>+6.8%</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>+8.7%</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Weekly return std dev (COMPUTED)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Annualized volatility = sd x sqrt(52)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>20.9%</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>32.8%</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>16.6%</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Current price (~15-Jul-2026, ₹)</t>
+          <t>Beta vs Nifty Energy (COMPUTED)</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>221.9-226.2</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>365.5-377.7</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>1,414.9-1,422.8</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>24,052.05 (14-Jul)</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>77,054.94 (14-Jul)</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>38,695.65 (9-Jul)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>52-week range (₹ / index pts)</t>
+          <t>Return vs sector (stock - Nifty Energy)</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>110.45 - 254.20</t>
+          <t>+75.4 pts</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>342.50 - 464.90</t>
+          <t>-14.7 pts</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>1,188.00 - 1,824.10</t>
+          <t>-1.9 pts</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>22,182.55 - 26,373.20</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>n/a - verify</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>32,791.85 - 41,097.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Reported 1-yr return (%)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>+78.5% to +100% (source/date-dependent)</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>≈ -6.1% to -6.2%</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>-3.29% to +5.99% (CONFLICTING — verify)</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>≈ -3.75% to -5.8% (compute exact from weekly closes)</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>≈ -5.98% to -6.68%</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>+14.79% (as of a Mar-2026 snapshot — may have moved)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Reported beta (1-yr, vs Nifty/Sensex)</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>0.89 - 1.36 (source-dependent)</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>0.56 - 1.56 (source-dependent)</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>0.99 (NSE) - 1.51 (BSE)</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>1.00 (by definition)</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Annualized volatility (std dev of weekly returns)</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>TO COMPUTE from weekly series</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>TO COMPUTE</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>TO COMPUTE</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>TO COMPUTE</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>TO COMPUTE</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>TO COMPUTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Current market cap (₹ cr, ~mid-2026)</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>~4,36,163 (15-Jul) — one source cited ~4,79,167 for late-May, reconcile</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>~1,18,899 - 1,25,754 (range across 2026 snapshots); ~1,20,688 (14-Jul)</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>~87,563 (4-May) declining to ~71,524-72,774 (Jun-Jul) — confirm if share-count changed (QIP)</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Key data-quality flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Adani Power executed a 1-for-5 STOCK SPLIT effective 22-Sep-2025 (face value ₹10→₹2), roughly mid-way through the trailing 1-year window. Any price series/return you compute MUST be split-adjusted, or the 'return' will be distorted by up to 5x for the pre-split portion. Torrent Power paid a ₹15/share interim dividend (record date 16-Feb-2026) — a normal corporate action, not expected to distort total-return comparisons materially if using closing (not total-return-adjusted) prices, but note it if doing a precise total-return calc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Nifty 50 note</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>The NIFTY50_weekly.htm file saved to the repo was the ^NSEI Charts/summary page, not the Historical Data page, so it contains no weekly table. To complete the market-index column: open finance.yahoo.com/quote/%5ENSEI/history/?frequency=1wk, scroll to load all rows, Ctrl+S as HTML, and replace NIFTY50_weekly.htm in the repo. Everything else on this sheet is final, computed from real data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Comments — which share is most volatile?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="130" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>ANSWER (computed from 54 weekly observations, split-adjusted): ADANI POWER is the most volatile of the three — weekly-return standard deviation 4.95% (annualized ~36%), vs Torrent Power 4.55% (~33%) and Tata Power 2.90% (~21%). The sector index (Nifty Energy) sat at 2.30% weekly (~17% annualized) — all three stocks were roughly 1.3-2.2x as volatile as their sector index. RETURNS: Adani Power massively outperformed (+84% vs the sector's +9%), Torrent Power roughly tracked the sector (+6.8%), and Tata Power underperformed (-6.0%). Note the LOW computed betas vs Nifty Energy (0.03-0.54): Nifty Energy is dominated by Reliance/ONGC (oil &amp; gas), so these power stocks move on company-specific news far more than on the 'sector' index — high volatility with low index correlation. Interpret beta accordingly, and recompute vs Nifty 50 once the market-index file is added for the conventional market beta.</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Comments — which stock is more volatile?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="110" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Based on the reported beta ranges (all sourced from third-party terminals whose methodologies differ, hence the wide ranges), Tata Power shows the widest beta spread (0.56-1.56) suggesting sensitivity to which methodology/window is used, while Adani Power's range (0.89-1.36) and its 52-week price range (₹110-254, more than doubling) point to it being the most volatile / highest-beta of the three in absolute price-swing terms over the last year — consistent with its very strong (and unusually large) 1-year return. Torrent Power's tighter 52-week range (₹1,188-1,824, ~54% spread) and smaller reported return suggest comparatively lower volatility, though its own beta range (0.99-1.51 across NSE/BSE) still indicates above-market sensitivity. A definitive ranking (by standard deviation of weekly returns) requires the actual weekly price series to be pulled and computed — this sheet is set up with formulas ready in the hidden 'Weekly_Price_Data' sheet for you to paste the real data into.</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A25:G31"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A6:G9"/>
-    <mergeCell ref="A20:G22"/>
+  <mergeCells count="4">
+    <mergeCell ref="A16:F18"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A21:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3686,20 +3807,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3710,7 +3834,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Adani Power (split-adj ₹)</t>
+          <t>Adani Power (adj ₹)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3725,232 +3849,2354 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Nifty 50</t>
+          <t>Nifty Energy</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Sensex</t>
+          <t>Nifty 50 (PENDING)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Nifty Energy</t>
+          <t>Adani wk ret</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Adani Power wk return</t>
+          <t>Tata wk ret</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tata Power wk return</t>
+          <t>Torrent wk ret</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Torrent Power wk return</t>
+          <t>NiftyEnergy wk ret</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Nifty50 wk return</t>
+          <t>Adani (base=100)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Tata (base=100)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Torrent (base=100)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NiftyEnergy (base=100)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="C2" t="n">
+        <v>405.39</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1349.89</v>
       </c>
       <c r="E2" t="n">
-        <v>25541.8</v>
+        <v>36231.65</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>114</v>
+      </c>
+      <c r="C3" t="n">
+        <v>392.92</v>
       </c>
       <c r="D3" t="n">
-        <v>1399.4</v>
+        <v>1307.38</v>
       </c>
       <c r="E3" t="n">
-        <v>26328.55</v>
+        <v>35250.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.041453</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.030761</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.031491</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.02708</v>
+      </c>
+      <c r="K3" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="M3" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="N3" t="n">
+        <v>97.29000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>146.2</v>
+        <v>113.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1270.59</v>
       </c>
       <c r="E4" t="n">
-        <v>26373.2</v>
+        <v>34889</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.005263</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.015321</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.02814</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.010255</v>
+      </c>
+      <c r="K4" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="L4" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="M4" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
-        </is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>115.38</v>
       </c>
       <c r="C5" t="n">
-        <v>364.8</v>
+        <v>376.47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1317.54</v>
       </c>
       <c r="E5" t="n">
-        <v>25683.3</v>
+        <v>34391.95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01746</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.026958</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.036951</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.014247</v>
+      </c>
+      <c r="K5" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="L5" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="M5" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>94.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>116.81</v>
+      </c>
+      <c r="C6" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1311.42</v>
       </c>
       <c r="E6" t="n">
-        <v>25694.35</v>
+        <v>34469.05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.012394</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.017159</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.004645</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.002242</v>
+      </c>
+      <c r="K6" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>95.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>118.86</v>
+      </c>
+      <c r="C7" t="n">
+        <v>383.23</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1264.47</v>
       </c>
       <c r="E7" t="n">
-        <v>25048.65</v>
+        <v>34507.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.000783</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.035801</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.001118</v>
+      </c>
+      <c r="K7" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="L7" t="n">
+        <v>94.53</v>
+      </c>
+      <c r="M7" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="N7" t="n">
+        <v>95.23999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>120.13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>371.85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1210.52</v>
       </c>
       <c r="E8" t="n">
-        <v>25320.65</v>
+        <v>33638.65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.010685</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.029695</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.042666</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.025181</v>
+      </c>
+      <c r="K8" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="L8" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="M8" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>92.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>121.94</v>
+      </c>
+      <c r="C9" t="n">
+        <v>383.42</v>
       </c>
       <c r="D9" t="n">
-        <v>1427.5</v>
+        <v>1245.63</v>
+      </c>
+      <c r="E9" t="n">
+        <v>34297.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.015067</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.031115</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.029004</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.019598</v>
+      </c>
+      <c r="K9" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="M9" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="N9" t="n">
+        <v>94.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>129.71</v>
+      </c>
+      <c r="C10" t="n">
+        <v>383.87</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1250.47</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34940.3</v>
       </c>
       <c r="G10" t="n">
-        <v>40990.7</v>
+        <v>0.06372</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001174</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.003886</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01873</v>
+      </c>
+      <c r="K10" t="n">
+        <v>109.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="M10" t="n">
+        <v>92.63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>96.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>234.35</v>
+        <v>141.88</v>
+      </c>
+      <c r="C11" t="n">
+        <v>393.86</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1247.21</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35745.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.09382500000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.026024</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.002607</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.023052</v>
+      </c>
+      <c r="K11" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>97.16</v>
+      </c>
+      <c r="M11" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="N11" t="n">
+        <v>98.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>220</v>
+        <v>146.25</v>
+      </c>
+      <c r="C12" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1216.44</v>
+      </c>
+      <c r="E12" t="n">
+        <v>34830</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.030801</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.031534</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.024671</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.025618</v>
+      </c>
+      <c r="K12" t="n">
+        <v>122.97</v>
+      </c>
+      <c r="L12" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="M12" t="n">
+        <v>90.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>96.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="C13" t="n">
+        <v>392.47</v>
       </c>
       <c r="D13" t="n">
-        <v>1413.7</v>
+        <v>1204.41</v>
+      </c>
+      <c r="E13" t="n">
+        <v>35375.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.007726</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.028917</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.009889999999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.015673</v>
+      </c>
+      <c r="K13" t="n">
+        <v>123.92</v>
+      </c>
+      <c r="L13" t="n">
+        <v>96.81</v>
+      </c>
+      <c r="M13" t="n">
+        <v>89.22</v>
+      </c>
+      <c r="N13" t="n">
+        <v>97.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>224</v>
+        <v>149.7</v>
       </c>
       <c r="C14" t="n">
-        <v>373.8</v>
+        <v>387.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1222.36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35393.95</v>
       </c>
       <c r="G14" t="n">
-        <v>38695.65</v>
+        <v>0.015742</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.012154</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.014904</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.00051</v>
+      </c>
+      <c r="K14" t="n">
+        <v>125.87</v>
+      </c>
+      <c r="L14" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="M14" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="N14" t="n">
+        <v>97.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>165.98</v>
+      </c>
+      <c r="C15" t="n">
+        <v>395.35</v>
       </c>
       <c r="D15" t="n">
-        <v>1414.9</v>
+        <v>1293.87</v>
+      </c>
+      <c r="E15" t="n">
+        <v>35395.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.108751</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.019732</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.058502</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.9e-05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>139.56</v>
+      </c>
+      <c r="L15" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="M15" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>97.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>167.72</v>
       </c>
       <c r="C16" t="n">
-        <v>377.7</v>
+        <v>394.41</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1307.67</v>
       </c>
       <c r="E16" t="n">
-        <v>24052.05</v>
-      </c>
-      <c r="F16" t="n">
-        <v>77054.94</v>
+        <v>35626.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.010483</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.002378</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.010666</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.006532</v>
+      </c>
+      <c r="K16" t="n">
+        <v>141.02</v>
+      </c>
+      <c r="L16" t="n">
+        <v>97.29000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>96.87</v>
+      </c>
+      <c r="N16" t="n">
+        <v>98.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>222.05</v>
+        <v>157.85</v>
       </c>
       <c r="C17" t="n">
-        <v>365.5</v>
+        <v>402.41</v>
       </c>
       <c r="D17" t="n">
-        <v>1422.8</v>
+        <v>1298.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>36275.95</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.058848</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.020283</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.007012</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.018218</v>
+      </c>
+      <c r="K17" t="n">
+        <v>132.73</v>
+      </c>
+      <c r="L17" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>96.19</v>
+      </c>
+      <c r="N17" t="n">
+        <v>100.12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>151.48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1263.68</v>
+      </c>
+      <c r="E18" t="n">
+        <v>35790.3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.040355</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.028901</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.026816</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.013388</v>
+      </c>
+      <c r="K18" t="n">
+        <v>127.37</v>
+      </c>
+      <c r="L18" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="N18" t="n">
+        <v>98.78</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>153.91</v>
+      </c>
+      <c r="C19" t="n">
+        <v>386.01</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1283.21</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36261.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.016042</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.012206</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.015455</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.013154</v>
+      </c>
+      <c r="K19" t="n">
+        <v>129.41</v>
+      </c>
+      <c r="L19" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="M19" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>100.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NOTE: this is sparse, real, sourced point-data (not a full weekly series) — paste the actual 52-week weekly closes from Yahoo Finance / NSE over columns B:G starting row 2, sorted oldest-to-newest, then columns H:K will need return formulas e.g. =B3/B2-1</t>
-        </is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>149.12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>384.62</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1273.74</v>
+      </c>
+      <c r="E20" t="n">
+        <v>35852.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.031122</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.003601</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.00738</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.011271</v>
+      </c>
+      <c r="K20" t="n">
+        <v>125.38</v>
+      </c>
+      <c r="L20" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="N20" t="n">
+        <v>98.95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>147.49</v>
+      </c>
+      <c r="C21" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1296.53</v>
+      </c>
+      <c r="E21" t="n">
+        <v>35548.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.010931</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.008007999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.017892</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.008482</v>
+      </c>
+      <c r="K21" t="n">
+        <v>124.01</v>
+      </c>
+      <c r="L21" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="M21" t="n">
+        <v>96.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>98.11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>143.78</v>
+      </c>
+      <c r="C22" t="n">
+        <v>382.13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1272.26</v>
+      </c>
+      <c r="E22" t="n">
+        <v>34971.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.025154</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.014367</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.018719</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.016217</v>
+      </c>
+      <c r="K22" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="L22" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>96.52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>144.49</v>
+      </c>
+      <c r="C23" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1273.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>35039.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.004938</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.006621</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.001946</v>
+      </c>
+      <c r="K23" t="n">
+        <v>121.49</v>
+      </c>
+      <c r="L23" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="M23" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="N23" t="n">
+        <v>96.70999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>141.76</v>
+      </c>
+      <c r="C24" t="n">
+        <v>378.21</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1261.61</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34796.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.018894</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.003662</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.009063999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.006948</v>
+      </c>
+      <c r="K24" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="N24" t="n">
+        <v>96.04000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>142.19</v>
+      </c>
+      <c r="C25" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1281.44</v>
+      </c>
+      <c r="E25" t="n">
+        <v>35058.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.003033</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.002644</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.015718</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.007541</v>
+      </c>
+      <c r="K25" t="n">
+        <v>119.56</v>
+      </c>
+      <c r="L25" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="M25" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="N25" t="n">
+        <v>96.76000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>148.17</v>
+      </c>
+      <c r="C26" t="n">
+        <v>390.68</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1380.27</v>
+      </c>
+      <c r="E26" t="n">
+        <v>36275.65</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.042056</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.077124</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.034709</v>
+      </c>
+      <c r="K26" t="n">
+        <v>124.59</v>
+      </c>
+      <c r="L26" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="M26" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>100.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>141.68</v>
+      </c>
+      <c r="C27" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1303.24</v>
+      </c>
+      <c r="E27" t="n">
+        <v>34409.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.043801</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.072003</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.055808</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.051449</v>
+      </c>
+      <c r="K27" t="n">
+        <v>119.13</v>
+      </c>
+      <c r="L27" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="N27" t="n">
+        <v>94.97</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>142.63</v>
+      </c>
+      <c r="C28" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1339.14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>34346.35</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.006705</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.003586</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.027547</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.001829</v>
+      </c>
+      <c r="K28" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="L28" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="M28" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>94.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>132.96</v>
+      </c>
+      <c r="C29" t="n">
+        <v>343.12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1253.33</v>
+      </c>
+      <c r="E29" t="n">
+        <v>33098.3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.067798</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.056974</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.064078</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.036337</v>
+      </c>
+      <c r="K29" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="M29" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="N29" t="n">
+        <v>91.34999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>132.85</v>
+      </c>
+      <c r="C30" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1279.76</v>
+      </c>
+      <c r="E30" t="n">
+        <v>35138.05</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.000827</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.026376</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.021088</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.061627</v>
+      </c>
+      <c r="K30" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="M30" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>96.98</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>152.74</v>
+      </c>
+      <c r="C31" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1409.46</v>
+      </c>
+      <c r="E31" t="n">
+        <v>36451.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.149718</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.03274</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.101347</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.037385</v>
+      </c>
+      <c r="K31" t="n">
+        <v>128.43</v>
+      </c>
+      <c r="L31" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="M31" t="n">
+        <v>104.41</v>
+      </c>
+      <c r="N31" t="n">
+        <v>100.61</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1442.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>35709.9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.084064</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.022271</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.023513</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.02035</v>
+      </c>
+      <c r="K32" t="n">
+        <v>117.63</v>
+      </c>
+      <c r="L32" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="N32" t="n">
+        <v>98.56</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>375.67</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1523.32</v>
+      </c>
+      <c r="E33" t="n">
+        <v>36581.15</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.020014</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.010409</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.055955</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.024398</v>
+      </c>
+      <c r="K33" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="L33" t="n">
+        <v>92.67</v>
+      </c>
+      <c r="M33" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="N33" t="n">
+        <v>100.96</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>140.11</v>
+      </c>
+      <c r="C34" t="n">
+        <v>375.22</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1560.99</v>
+      </c>
+      <c r="E34" t="n">
+        <v>37045.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.01815</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.001198</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.024729</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.012685</v>
+      </c>
+      <c r="K34" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="L34" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="M34" t="n">
+        <v>115.64</v>
+      </c>
+      <c r="N34" t="n">
+        <v>102.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>138.99</v>
+      </c>
+      <c r="C35" t="n">
+        <v>373.19</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1476.19</v>
+      </c>
+      <c r="E35" t="n">
+        <v>36319.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.007993999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.00541</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.054324</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.019587</v>
+      </c>
+      <c r="K35" t="n">
+        <v>116.87</v>
+      </c>
+      <c r="L35" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="M35" t="n">
+        <v>109.36</v>
+      </c>
+      <c r="N35" t="n">
+        <v>100.24</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>146.57</v>
+      </c>
+      <c r="C36" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1456.26</v>
+      </c>
+      <c r="E36" t="n">
+        <v>36071.85</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.054536</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.051797</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.013501</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.006821</v>
+      </c>
+      <c r="K36" t="n">
+        <v>123.24</v>
+      </c>
+      <c r="L36" t="n">
+        <v>96.83</v>
+      </c>
+      <c r="M36" t="n">
+        <v>107.88</v>
+      </c>
+      <c r="N36" t="n">
+        <v>99.56</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>151.54</v>
+      </c>
+      <c r="C37" t="n">
+        <v>399.92</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1445.69</v>
+      </c>
+      <c r="E37" t="n">
+        <v>35908.3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.033909</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.018853</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.007258</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.004534</v>
+      </c>
+      <c r="K37" t="n">
+        <v>127.42</v>
+      </c>
+      <c r="L37" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>99.11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>153.92</v>
+      </c>
+      <c r="C38" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1347.63</v>
+      </c>
+      <c r="E38" t="n">
+        <v>35214.8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.015705</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.041508</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.067829</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.019313</v>
+      </c>
+      <c r="K38" t="n">
+        <v>129.42</v>
+      </c>
+      <c r="L38" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="M38" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="N38" t="n">
+        <v>97.19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>159.97</v>
+      </c>
+      <c r="C39" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1327.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>35299.4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.039306</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.014863</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.002402</v>
+      </c>
+      <c r="K39" t="n">
+        <v>134.51</v>
+      </c>
+      <c r="L39" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="M39" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="N39" t="n">
+        <v>97.43000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>175.81</v>
+      </c>
+      <c r="C40" t="n">
+        <v>396.89</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1466.72</v>
+      </c>
+      <c r="E40" t="n">
+        <v>37174.6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.099019</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.037268</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.104791</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.053123</v>
+      </c>
+      <c r="K40" t="n">
+        <v>147.83</v>
+      </c>
+      <c r="L40" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="N40" t="n">
+        <v>102.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>424.97</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1559.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>38881.75</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.12906</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.07074999999999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.06332500000000001</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.045922</v>
+      </c>
+      <c r="K41" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>104.83</v>
+      </c>
+      <c r="M41" t="n">
+        <v>115.54</v>
+      </c>
+      <c r="N41" t="n">
+        <v>107.31</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>432.32</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1693.63</v>
+      </c>
+      <c r="E42" t="n">
+        <v>39903.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.072544</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.017295</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.085939</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.026285</v>
+      </c>
+      <c r="K42" t="n">
+        <v>179.01</v>
+      </c>
+      <c r="L42" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="M42" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="N42" t="n">
+        <v>110.14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>221.85</v>
+      </c>
+      <c r="C43" t="n">
+        <v>441.81</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1730.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>40771.9</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.042039</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.021951</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.021756</v>
+      </c>
+      <c r="K43" t="n">
+        <v>186.54</v>
+      </c>
+      <c r="L43" t="n">
+        <v>108.98</v>
+      </c>
+      <c r="M43" t="n">
+        <v>128.16</v>
+      </c>
+      <c r="N43" t="n">
+        <v>112.53</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>225.33</v>
+      </c>
+      <c r="C44" t="n">
+        <v>433.31</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1718.45</v>
+      </c>
+      <c r="E44" t="n">
+        <v>40795.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.015686</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.019239</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.006682</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.000586</v>
+      </c>
+      <c r="K44" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="L44" t="n">
+        <v>106.89</v>
+      </c>
+      <c r="M44" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>112.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>221.33</v>
+      </c>
+      <c r="C45" t="n">
+        <v>404.49</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1460.94</v>
+      </c>
+      <c r="E45" t="n">
+        <v>39816.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.017752</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.066511</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.14985</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.023996</v>
+      </c>
+      <c r="K45" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="M45" t="n">
+        <v>108.23</v>
+      </c>
+      <c r="N45" t="n">
+        <v>109.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>219.32</v>
+      </c>
+      <c r="C46" t="n">
+        <v>406.38</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1493.33</v>
+      </c>
+      <c r="E46" t="n">
+        <v>40237.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.009081000000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.004673</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.022171</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.010567</v>
+      </c>
+      <c r="K46" t="n">
+        <v>184.41</v>
+      </c>
+      <c r="L46" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="M46" t="n">
+        <v>110.63</v>
+      </c>
+      <c r="N46" t="n">
+        <v>111.06</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>243.37</v>
+      </c>
+      <c r="C47" t="n">
+        <v>418.16</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1415.4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>40878</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.109657</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.028988</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.052185</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.015915</v>
+      </c>
+      <c r="K47" t="n">
+        <v>204.63</v>
+      </c>
+      <c r="L47" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="M47" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="N47" t="n">
+        <v>112.82</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>406.68</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1455.06</v>
+      </c>
+      <c r="E48" t="n">
+        <v>40346.1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.044254</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.027454</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.02802</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0.013012</v>
+      </c>
+      <c r="K48" t="n">
+        <v>195.58</v>
+      </c>
+      <c r="L48" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="M48" t="n">
+        <v>107.79</v>
+      </c>
+      <c r="N48" t="n">
+        <v>111.36</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>223.07</v>
+      </c>
+      <c r="C49" t="n">
+        <v>391.13</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1387.2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>39244.45</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.040972</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.038236</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.046637</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.027305</v>
+      </c>
+      <c r="K49" t="n">
+        <v>187.56</v>
+      </c>
+      <c r="L49" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="M49" t="n">
+        <v>102.76</v>
+      </c>
+      <c r="N49" t="n">
+        <v>108.32</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>231.76</v>
+      </c>
+      <c r="C50" t="n">
+        <v>399.87</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1438.4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>40548.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.038956</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.022346</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.036909</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.033219</v>
+      </c>
+      <c r="K50" t="n">
+        <v>194.87</v>
+      </c>
+      <c r="L50" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="M50" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="N50" t="n">
+        <v>111.91</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>229.27</v>
+      </c>
+      <c r="C51" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1413.7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>39637</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.010744</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.027309</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.017172</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-0.02247</v>
+      </c>
+      <c r="K51" t="n">
+        <v>192.78</v>
+      </c>
+      <c r="L51" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="M51" t="n">
+        <v>104.73</v>
+      </c>
+      <c r="N51" t="n">
+        <v>109.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>221.79</v>
+      </c>
+      <c r="C52" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1366.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>39178.6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.032625</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.035352</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-0.033388</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.011565</v>
+      </c>
+      <c r="K52" t="n">
+        <v>186.49</v>
+      </c>
+      <c r="L52" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="M52" t="n">
+        <v>101.23</v>
+      </c>
+      <c r="N52" t="n">
+        <v>108.13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>218.45</v>
+      </c>
+      <c r="C53" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1419.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>39242.05</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.015059</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.016258</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.038712</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="K53" t="n">
+        <v>183.68</v>
+      </c>
+      <c r="L53" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="M53" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="N53" t="n">
+        <v>108.31</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>226.17</v>
+      </c>
+      <c r="C54" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1465.3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.009441</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.032338</v>
+      </c>
+      <c r="K54" t="n">
+        <v>190.17</v>
+      </c>
+      <c r="L54" t="n">
+        <v>93.17</v>
+      </c>
+      <c r="M54" t="n">
+        <v>108.55</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>218.97</v>
+      </c>
+      <c r="C55" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1441.1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>39381.25</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.031834</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.008472</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.016515</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.003547</v>
+      </c>
+      <c r="K55" t="n">
+        <v>184.12</v>
+      </c>
+      <c r="L55" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="M55" t="n">
+        <v>106.76</v>
+      </c>
+      <c r="N55" t="n">
+        <v>108.69</v>
       </c>
     </row>
   </sheetData>
@@ -4308,99 +6554,649 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Week Ending</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Adani Power Price (₹, split-adj)</t>
+          <t>Adani Power (adj ₹)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Event that week</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>12mo +40% reported</t>
-        </is>
+        <v>118.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>234.35</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>52-wk high (post Assam/JPVL momentum)</t>
-        </is>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220</v>
+        <v>113.4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Profit booking, ~100% 1yr return</t>
+          <t>Q1 FY26 results + 1:5 split announced</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>224</v>
+        <v>115.38</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Q1 FY26 results + 1:5 split announced</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>116.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>118.86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>120.13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>121.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>129.71</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>141.88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1:5 stock split effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>147.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>149.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>165.98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>167.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>157.85</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Q2 FY26 results; 4.5 GW new PPAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>151.48</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Q2 FY26 results; 4.5 GW new PPAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>153.91</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Assam 3,200 MW LoA (~₹48,000cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>149.12</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Assam 3,200 MW LoA (~₹48,000cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>147.49</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JPVL resolution plan creditor approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>143.78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>141.76</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>142.19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>148.17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>141.68</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>142.63</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>132.96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>132.85</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>152.74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Adani Atomic Energy incorporated</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Adani Atomic Energy incorporated</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>140.11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>138.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>146.57</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NCLT approves JPVL plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>151.54</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NCLT approves JPVL plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>153.92</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>159.97</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>175.81</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>198.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>212.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>221.85</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Q4/FY26 results: PAT ₹12,971cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>225.33</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Q4/FY26 results: PAT ₹12,971cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>221.33</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>52-wk high ₹234 intraday</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>219.32</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Profit-booking after ~100% 1-yr run</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>243.37</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Profit-booking after ~100% 1-yr run</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>232.6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>223.07</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>231.76</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>229.27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>221.79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>218.45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>226.17</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>222.05</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
+      <c r="B55" t="n">
+        <v>218.97</v>
       </c>
     </row>
   </sheetData>
@@ -4489,7 +7285,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>5. Full weekly (52-point) price series for all 3 stocks + Nifty 50 + Sensex + Nifty Energy — pull from NSE/Yahoo Finance to compute exact weekly returns and standard deviation (volatility).</t>
+          <t>5. Weekly price series — LARGELY DONE: 54-week adjusted-close series for all 3 stocks + Nifty Energy parsed from Yahoo HTML files in the repo; returns, std-dev volatility and sector betas computed in Sheet 11. Outstanding: Nifty 50 (wrong page was saved — re-save the ^NSEI Historical Data page) and year-end FY19-FY26 prices for Sheet 2.</t>
         </is>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +96,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00C00000"/>
     </font>
   </fonts>
@@ -143,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3438,7 +3443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3522,9 +3527,9 @@
           <t>36,231.65</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>24,968.40</t>
         </is>
       </c>
     </row>
@@ -3554,9 +3559,9 @@
           <t>39,381.25</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>24,078.50</t>
         </is>
       </c>
     </row>
@@ -3586,9 +3591,9 @@
           <t>33,098.30 - 40,878.00</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>22,713.10 - 26,328.55</t>
         </is>
       </c>
     </row>
@@ -3618,9 +3623,9 @@
           <t>+8.7%</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>-3.6%</t>
         </is>
       </c>
     </row>
@@ -3650,9 +3655,9 @@
           <t>2.30%</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -3682,119 +3687,183 @@
           <t>16.6%</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Beta vs Nifty Energy (COMPUTED)</t>
+          <t>Beta vs Nifty 50 / market (COMPUTED)</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>1.00</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>Beta vs Nifty Energy / sector (COMPUTED)</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Return vs market (stock - Nifty 50)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>+87.7 pts</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>-2.5 pts</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>+10.3 pts</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>+12.3 pts</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
           <t>Return vs sector (stock - Nifty Energy)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>+75.4 pts</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>-14.7 pts</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>-1.9 pts</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>Nifty 50 note</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>The NIFTY50_weekly.htm file saved to the repo was the ^NSEI Charts/summary page, not the Historical Data page, so it contains no weekly table. To complete the market-index column: open finance.yahoo.com/quote/%5ENSEI/history/?frequency=1wk, scroll to load all rows, Ctrl+S as HTML, and replace NIFTY50_weekly.htm in the repo. Everything else on this sheet is final, computed from real data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Data note</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>COMPLETE: all five series (3 stocks + Nifty 50 + Nifty Energy) parsed from the Yahoo Finance Historical Data pages saved in the repo (54 weekly adjusted-close points each, 14-Jul-2025 to 15-Jul-2026, split-adjusted). Weekly returns, standard deviations, annualized volatility, and betas computed from this data - see the Weekly_Price_Data sheet for the full series and the rebased performance chart below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Comments — which share is most volatile?</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="130" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>ANSWER (computed from 54 weekly observations, split-adjusted): ADANI POWER is the most volatile of the three — weekly-return standard deviation 4.95% (annualized ~36%), vs Torrent Power 4.55% (~33%) and Tata Power 2.90% (~21%). The sector index (Nifty Energy) sat at 2.30% weekly (~17% annualized) — all three stocks were roughly 1.3-2.2x as volatile as their sector index. RETURNS: Adani Power massively outperformed (+84% vs the sector's +9%), Torrent Power roughly tracked the sector (+6.8%), and Tata Power underperformed (-6.0%). Note the LOW computed betas vs Nifty Energy (0.03-0.54): Nifty Energy is dominated by Reliance/ONGC (oil &amp; gas), so these power stocks move on company-specific news far more than on the 'sector' index — high volatility with low index correlation. Interpret beta accordingly, and recompute vs Nifty 50 once the market-index file is added for the conventional market beta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+    <row r="23" ht="130" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>ANSWER (computed from 54 weekly observations, split-adjusted): ADANI POWER is the most volatile of the three — weekly-return standard deviation 4.95% (annualized ~36%), vs Torrent Power 4.55% (~33%) and Tata Power 2.90% (~21%). The sector index (Nifty Energy) sat at 2.30% weekly (~17% annualized) — all three stocks were roughly 1.3-2.2x as volatile as their sector index. RETURNS: Adani Power massively outperformed (+84% vs the sector's +9%), Torrent Power roughly tracked the sector (+6.8%), and Tata Power underperformed (-6.0%). Note the LOW computed betas vs Nifty Energy (0.03-0.54): Nifty Energy is dominated by Reliance/ONGC (oil &amp; gas), so these power stocks move on company-specific news far more than on the 'sector' index — high volatility with low index correlation. Interpret beta accordingly. VS THE MARKET: Nifty 50 fell -3.6% over the window, so all three power stocks outperformed the broad market (Adani by ~88 points); market betas vs Nifty 50 are 1.13 (Adani), 0.62 (Tata) and 1.46 (Torrent).</t>
+        </is>
+      </c>
+    </row>
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:F18"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A18:F20"/>
+    <mergeCell ref="A23:F30"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A21:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3854,7 +3923,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nifty 50 (PENDING)</t>
+          <t>Nifty 50</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -3916,6 +3985,9 @@
       <c r="E2" t="n">
         <v>36231.65</v>
       </c>
+      <c r="F2" t="n">
+        <v>24968.4</v>
+      </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
@@ -3947,6 +4019,9 @@
       <c r="E3" t="n">
         <v>35250.5</v>
       </c>
+      <c r="F3" t="n">
+        <v>24837</v>
+      </c>
       <c r="G3" t="n">
         <v>-0.041453</v>
       </c>
@@ -3990,6 +4065,9 @@
       <c r="E4" t="n">
         <v>34889</v>
       </c>
+      <c r="F4" t="n">
+        <v>24565.35</v>
+      </c>
       <c r="G4" t="n">
         <v>-0.005263</v>
       </c>
@@ -4033,6 +4111,9 @@
       <c r="E5" t="n">
         <v>34391.95</v>
       </c>
+      <c r="F5" t="n">
+        <v>24363.3</v>
+      </c>
       <c r="G5" t="n">
         <v>0.01746</v>
       </c>
@@ -4076,6 +4157,9 @@
       <c r="E6" t="n">
         <v>34469.05</v>
       </c>
+      <c r="F6" t="n">
+        <v>24631.3</v>
+      </c>
       <c r="G6" t="n">
         <v>0.012394</v>
       </c>
@@ -4119,6 +4203,9 @@
       <c r="E7" t="n">
         <v>34507.6</v>
       </c>
+      <c r="F7" t="n">
+        <v>24870.1</v>
+      </c>
       <c r="G7" t="n">
         <v>0.01755</v>
       </c>
@@ -4162,6 +4249,9 @@
       <c r="E8" t="n">
         <v>33638.65</v>
       </c>
+      <c r="F8" t="n">
+        <v>24426.85</v>
+      </c>
       <c r="G8" t="n">
         <v>0.010685</v>
       </c>
@@ -4205,6 +4295,9 @@
       <c r="E9" t="n">
         <v>34297.9</v>
       </c>
+      <c r="F9" t="n">
+        <v>24741</v>
+      </c>
       <c r="G9" t="n">
         <v>0.015067</v>
       </c>
@@ -4248,6 +4341,9 @@
       <c r="E10" t="n">
         <v>34940.3</v>
       </c>
+      <c r="F10" t="n">
+        <v>25114</v>
+      </c>
       <c r="G10" t="n">
         <v>0.06372</v>
       </c>
@@ -4291,6 +4387,9 @@
       <c r="E11" t="n">
         <v>35745.75</v>
       </c>
+      <c r="F11" t="n">
+        <v>25327.05</v>
+      </c>
       <c r="G11" t="n">
         <v>0.09382500000000001</v>
       </c>
@@ -4334,6 +4433,9 @@
       <c r="E12" t="n">
         <v>34830</v>
       </c>
+      <c r="F12" t="n">
+        <v>24654.7</v>
+      </c>
       <c r="G12" t="n">
         <v>0.030801</v>
       </c>
@@ -4377,6 +4479,9 @@
       <c r="E13" t="n">
         <v>35375.9</v>
       </c>
+      <c r="F13" t="n">
+        <v>24894.25</v>
+      </c>
       <c r="G13" t="n">
         <v>0.007726</v>
       </c>
@@ -4420,6 +4525,9 @@
       <c r="E14" t="n">
         <v>35393.95</v>
       </c>
+      <c r="F14" t="n">
+        <v>25285.35</v>
+      </c>
       <c r="G14" t="n">
         <v>0.015742</v>
       </c>
@@ -4463,6 +4571,9 @@
       <c r="E15" t="n">
         <v>35395.7</v>
       </c>
+      <c r="F15" t="n">
+        <v>25709.85</v>
+      </c>
       <c r="G15" t="n">
         <v>0.108751</v>
       </c>
@@ -4506,6 +4617,9 @@
       <c r="E16" t="n">
         <v>35626.9</v>
       </c>
+      <c r="F16" t="n">
+        <v>25795.15</v>
+      </c>
       <c r="G16" t="n">
         <v>0.010483</v>
       </c>
@@ -4549,6 +4663,9 @@
       <c r="E17" t="n">
         <v>36275.95</v>
       </c>
+      <c r="F17" t="n">
+        <v>25722.1</v>
+      </c>
       <c r="G17" t="n">
         <v>-0.058848</v>
       </c>
@@ -4592,6 +4709,9 @@
       <c r="E18" t="n">
         <v>35790.3</v>
       </c>
+      <c r="F18" t="n">
+        <v>25492.3</v>
+      </c>
       <c r="G18" t="n">
         <v>-0.040355</v>
       </c>
@@ -4635,6 +4755,9 @@
       <c r="E19" t="n">
         <v>36261.1</v>
       </c>
+      <c r="F19" t="n">
+        <v>25910.05</v>
+      </c>
       <c r="G19" t="n">
         <v>0.016042</v>
       </c>
@@ -4678,6 +4801,9 @@
       <c r="E20" t="n">
         <v>35852.4</v>
       </c>
+      <c r="F20" t="n">
+        <v>26068.15</v>
+      </c>
       <c r="G20" t="n">
         <v>-0.031122</v>
       </c>
@@ -4721,6 +4847,9 @@
       <c r="E21" t="n">
         <v>35548.3</v>
       </c>
+      <c r="F21" t="n">
+        <v>26202.95</v>
+      </c>
       <c r="G21" t="n">
         <v>-0.010931</v>
       </c>
@@ -4764,6 +4893,9 @@
       <c r="E22" t="n">
         <v>34971.8</v>
       </c>
+      <c r="F22" t="n">
+        <v>26186.45</v>
+      </c>
       <c r="G22" t="n">
         <v>-0.025154</v>
       </c>
@@ -4807,6 +4939,9 @@
       <c r="E23" t="n">
         <v>35039.85</v>
       </c>
+      <c r="F23" t="n">
+        <v>26046.95</v>
+      </c>
       <c r="G23" t="n">
         <v>0.004938</v>
       </c>
@@ -4850,6 +4985,9 @@
       <c r="E24" t="n">
         <v>34796.4</v>
       </c>
+      <c r="F24" t="n">
+        <v>25966.4</v>
+      </c>
       <c r="G24" t="n">
         <v>-0.018894</v>
       </c>
@@ -4893,6 +5031,9 @@
       <c r="E25" t="n">
         <v>35058.8</v>
       </c>
+      <c r="F25" t="n">
+        <v>26042.3</v>
+      </c>
       <c r="G25" t="n">
         <v>0.003033</v>
       </c>
@@ -4936,6 +5077,9 @@
       <c r="E26" t="n">
         <v>36275.65</v>
       </c>
+      <c r="F26" t="n">
+        <v>26328.55</v>
+      </c>
       <c r="G26" t="n">
         <v>0.042056</v>
       </c>
@@ -4979,6 +5123,9 @@
       <c r="E27" t="n">
         <v>34409.3</v>
       </c>
+      <c r="F27" t="n">
+        <v>25683.3</v>
+      </c>
       <c r="G27" t="n">
         <v>-0.043801</v>
       </c>
@@ -5022,6 +5169,9 @@
       <c r="E28" t="n">
         <v>34346.35</v>
       </c>
+      <c r="F28" t="n">
+        <v>25694.35</v>
+      </c>
       <c r="G28" t="n">
         <v>0.006705</v>
       </c>
@@ -5065,6 +5215,9 @@
       <c r="E29" t="n">
         <v>33098.3</v>
       </c>
+      <c r="F29" t="n">
+        <v>25048.65</v>
+      </c>
       <c r="G29" t="n">
         <v>-0.067798</v>
       </c>
@@ -5108,6 +5261,9 @@
       <c r="E30" t="n">
         <v>35138.05</v>
       </c>
+      <c r="F30" t="n">
+        <v>24825.45</v>
+      </c>
       <c r="G30" t="n">
         <v>-0.000827</v>
       </c>
@@ -5151,6 +5307,9 @@
       <c r="E31" t="n">
         <v>36451.7</v>
       </c>
+      <c r="F31" t="n">
+        <v>25693.7</v>
+      </c>
       <c r="G31" t="n">
         <v>0.149718</v>
       </c>
@@ -5194,6 +5353,9 @@
       <c r="E32" t="n">
         <v>35709.9</v>
       </c>
+      <c r="F32" t="n">
+        <v>25471.1</v>
+      </c>
       <c r="G32" t="n">
         <v>-0.084064</v>
       </c>
@@ -5237,6 +5399,9 @@
       <c r="E33" t="n">
         <v>36581.15</v>
       </c>
+      <c r="F33" t="n">
+        <v>25571.25</v>
+      </c>
       <c r="G33" t="n">
         <v>0.020014</v>
       </c>
@@ -5280,6 +5445,9 @@
       <c r="E34" t="n">
         <v>37045.2</v>
       </c>
+      <c r="F34" t="n">
+        <v>25178.65</v>
+      </c>
       <c r="G34" t="n">
         <v>-0.01815</v>
       </c>
@@ -5323,6 +5491,9 @@
       <c r="E35" t="n">
         <v>36319.6</v>
       </c>
+      <c r="F35" t="n">
+        <v>24450.45</v>
+      </c>
       <c r="G35" t="n">
         <v>-0.007993999999999999</v>
       </c>
@@ -5366,6 +5537,9 @@
       <c r="E36" t="n">
         <v>36071.85</v>
       </c>
+      <c r="F36" t="n">
+        <v>23151.1</v>
+      </c>
       <c r="G36" t="n">
         <v>0.054536</v>
       </c>
@@ -5409,6 +5583,9 @@
       <c r="E37" t="n">
         <v>35908.3</v>
       </c>
+      <c r="F37" t="n">
+        <v>23114.5</v>
+      </c>
       <c r="G37" t="n">
         <v>0.033909</v>
       </c>
@@ -5452,6 +5629,9 @@
       <c r="E38" t="n">
         <v>35214.8</v>
       </c>
+      <c r="F38" t="n">
+        <v>22819.6</v>
+      </c>
       <c r="G38" t="n">
         <v>0.015705</v>
       </c>
@@ -5495,6 +5675,9 @@
       <c r="E39" t="n">
         <v>35299.4</v>
       </c>
+      <c r="F39" t="n">
+        <v>22713.1</v>
+      </c>
       <c r="G39" t="n">
         <v>0.039306</v>
       </c>
@@ -5538,6 +5721,9 @@
       <c r="E40" t="n">
         <v>37174.6</v>
       </c>
+      <c r="F40" t="n">
+        <v>24050.6</v>
+      </c>
       <c r="G40" t="n">
         <v>0.099019</v>
       </c>
@@ -5581,6 +5767,9 @@
       <c r="E41" t="n">
         <v>38881.75</v>
       </c>
+      <c r="F41" t="n">
+        <v>24353.55</v>
+      </c>
       <c r="G41" t="n">
         <v>0.12906</v>
       </c>
@@ -5624,6 +5813,9 @@
       <c r="E42" t="n">
         <v>39903.75</v>
       </c>
+      <c r="F42" t="n">
+        <v>23897.95</v>
+      </c>
       <c r="G42" t="n">
         <v>0.072544</v>
       </c>
@@ -5667,6 +5859,9 @@
       <c r="E43" t="n">
         <v>40771.9</v>
       </c>
+      <c r="F43" t="n">
+        <v>23997.55</v>
+      </c>
       <c r="G43" t="n">
         <v>0.042039</v>
       </c>
@@ -5710,6 +5905,9 @@
       <c r="E44" t="n">
         <v>40795.8</v>
       </c>
+      <c r="F44" t="n">
+        <v>24176.15</v>
+      </c>
       <c r="G44" t="n">
         <v>0.015686</v>
       </c>
@@ -5753,6 +5951,9 @@
       <c r="E45" t="n">
         <v>39816.85</v>
       </c>
+      <c r="F45" t="n">
+        <v>23643.5</v>
+      </c>
       <c r="G45" t="n">
         <v>-0.017752</v>
       </c>
@@ -5796,6 +5997,9 @@
       <c r="E46" t="n">
         <v>40237.6</v>
       </c>
+      <c r="F46" t="n">
+        <v>23719.3</v>
+      </c>
       <c r="G46" t="n">
         <v>-0.009081000000000001</v>
       </c>
@@ -5839,6 +6043,9 @@
       <c r="E47" t="n">
         <v>40878</v>
       </c>
+      <c r="F47" t="n">
+        <v>23547.75</v>
+      </c>
       <c r="G47" t="n">
         <v>0.109657</v>
       </c>
@@ -5882,6 +6089,9 @@
       <c r="E48" t="n">
         <v>40346.1</v>
       </c>
+      <c r="F48" t="n">
+        <v>23366.7</v>
+      </c>
       <c r="G48" t="n">
         <v>-0.044254</v>
       </c>
@@ -5925,6 +6135,9 @@
       <c r="E49" t="n">
         <v>39244.45</v>
       </c>
+      <c r="F49" t="n">
+        <v>23622.9</v>
+      </c>
       <c r="G49" t="n">
         <v>-0.040972</v>
       </c>
@@ -5968,6 +6181,9 @@
       <c r="E50" t="n">
         <v>40548.1</v>
       </c>
+      <c r="F50" t="n">
+        <v>24013.1</v>
+      </c>
       <c r="G50" t="n">
         <v>0.038956</v>
       </c>
@@ -6011,6 +6227,9 @@
       <c r="E51" t="n">
         <v>39637</v>
       </c>
+      <c r="F51" t="n">
+        <v>24056</v>
+      </c>
       <c r="G51" t="n">
         <v>-0.010744</v>
       </c>
@@ -6054,6 +6273,9 @@
       <c r="E52" t="n">
         <v>39178.6</v>
       </c>
+      <c r="F52" t="n">
+        <v>24270.85</v>
+      </c>
       <c r="G52" t="n">
         <v>-0.032625</v>
       </c>
@@ -6097,6 +6319,9 @@
       <c r="E53" t="n">
         <v>39242.05</v>
       </c>
+      <c r="F53" t="n">
+        <v>24206.9</v>
+      </c>
       <c r="G53" t="n">
         <v>-0.015059</v>
       </c>
@@ -6137,6 +6362,9 @@
       <c r="D54" t="n">
         <v>1465.3</v>
       </c>
+      <c r="F54" t="n">
+        <v>24052.05</v>
+      </c>
       <c r="G54" t="n">
         <v>0.03534</v>
       </c>
@@ -6173,6 +6401,9 @@
       </c>
       <c r="E55" t="n">
         <v>39381.25</v>
+      </c>
+      <c r="F55" t="n">
+        <v>24078.5</v>
       </c>
       <c r="G55" t="n">
         <v>-0.031834</v>
@@ -6521,7 +6752,7 @@
       <c r="D19" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Note on this section</t>
         </is>
@@ -7285,7 +7516,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>5. Weekly price series — LARGELY DONE: 54-week adjusted-close series for all 3 stocks + Nifty Energy parsed from Yahoo HTML files in the repo; returns, std-dev volatility and sector betas computed in Sheet 11. Outstanding: Nifty 50 (wrong page was saved — re-save the ^NSEI Historical Data page) and year-end FY19-FY26 prices for Sheet 2.</t>
+          <t>5. Weekly price series — DONE: 54-week adjusted-close series for all 3 stocks + Nifty 50 + Nifty Energy parsed from Yahoo HTML files in the repo; returns, volatility, and market &amp; sector betas computed in Sheet 11. Still open: year-end FY19-FY26 share prices for the Sheet 2 growth table (needs older price history).</t>
         </is>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -269,7 +269,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue / Total Income Trend, FY19-FY26 (₹ crore)</a:t>
+              <a:t>Revenue / Total Income Trend, FY22-FY26 (₹ crore)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -294,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$2:$A$9</f>
+              <f>'2b_Growth_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$B$2:$B$9</f>
+              <f>'2b_Growth_Chart_Data'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -318,12 +318,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$2:$A$9</f>
+              <f>'2b_Growth_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$C$2:$C$9</f>
+              <f>'2b_Growth_Chart_Data'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -342,12 +342,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$2:$A$9</f>
+              <f>'2b_Growth_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$D$2:$D$9</f>
+              <f>'2b_Growth_Chart_Data'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -429,7 +429,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Net Profit / PAT Trend, FY19-FY26 (₹ crore)</a:t>
+              <a:t>Net Profit / PAT Trend, FY22-FY26 (₹ crore)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -444,7 +444,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!B11</f>
+              <f>'2b_Growth_Chart_Data'!B8</f>
             </strRef>
           </tx>
           <spPr>
@@ -454,12 +454,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$12:$A$19</f>
+              <f>'2b_Growth_Chart_Data'!$A$9:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$B$12:$B$19</f>
+              <f>'2b_Growth_Chart_Data'!$B$9:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -468,7 +468,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!C11</f>
+              <f>'2b_Growth_Chart_Data'!C8</f>
             </strRef>
           </tx>
           <spPr>
@@ -478,12 +478,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$12:$A$19</f>
+              <f>'2b_Growth_Chart_Data'!$A$9:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$C$12:$C$19</f>
+              <f>'2b_Growth_Chart_Data'!$C$9:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -492,7 +492,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!D11</f>
+              <f>'2b_Growth_Chart_Data'!D8</f>
             </strRef>
           </tx>
           <spPr>
@@ -502,12 +502,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$12:$A$19</f>
+              <f>'2b_Growth_Chart_Data'!$A$9:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$D$12:$D$19</f>
+              <f>'2b_Growth_Chart_Data'!$D$9:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -589,7 +589,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Total Assets Trend, FY20-FY26 (₹ crore, consolidated)</a:t>
+              <a:t>Total Assets Trend, FY22-FY26 (₹ crore, consolidated)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -604,7 +604,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!B21</f>
+              <f>'2b_Growth_Chart_Data'!B15</f>
             </strRef>
           </tx>
           <spPr>
@@ -614,12 +614,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$22:$A$28</f>
+              <f>'2b_Growth_Chart_Data'!$A$16:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$B$22:$B$28</f>
+              <f>'2b_Growth_Chart_Data'!$B$16:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -628,7 +628,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!C21</f>
+              <f>'2b_Growth_Chart_Data'!C15</f>
             </strRef>
           </tx>
           <spPr>
@@ -638,12 +638,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$22:$A$28</f>
+              <f>'2b_Growth_Chart_Data'!$A$16:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$C$22:$C$28</f>
+              <f>'2b_Growth_Chart_Data'!$C$16:$C$20</f>
             </numRef>
           </val>
         </ser>
@@ -652,7 +652,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'2b_Growth_Chart_Data'!D21</f>
+              <f>'2b_Growth_Chart_Data'!D15</f>
             </strRef>
           </tx>
           <spPr>
@@ -662,12 +662,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$A$22:$A$28</f>
+              <f>'2b_Growth_Chart_Data'!$A$16:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'2b_Growth_Chart_Data'!$D$22:$D$28</f>
+              <f>'2b_Growth_Chart_Data'!$D$16:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -749,7 +749,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Segment Revenue Trends FY21-FY26 (₹ crore): Tata segments vs Adani Generation</a:t>
+              <a:t>Segment Revenue Trends FY22-FY26 (₹ crore): Tata segments vs Adani Generation</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -781,12 +781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$B$2:$B$7</f>
+              <f>'6b_Segment_Chart_Data'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -813,12 +813,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$C$2:$C$7</f>
+              <f>'6b_Segment_Chart_Data'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -845,12 +845,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$D$2:$D$7</f>
+              <f>'6b_Segment_Chart_Data'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -877,12 +877,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$A$2:$A$7</f>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'6b_Segment_Chart_Data'!$E$2:$E$7</f>
+              <f>'6b_Segment_Chart_Data'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -1304,92 +1304,17 @@
     <author>Research Agent</author>
   </authors>
   <commentList>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B16" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0" shapeId="0">
+    <comment ref="D10" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
     </comment>
     <comment ref="D16" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="G16" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B21" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="B22" authorId="0" shapeId="0">
-      <text>
-        <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
-      </text>
-    </comment>
-    <comment ref="C22" authorId="0" shapeId="0">
       <text>
         <t>Not independently verifiable via web search in this session — pull directly from screener.in / moneycontrol / NSE-BSE filings / the company's Annual Report before final submission.</t>
       </text>
@@ -1419,21 +1344,6 @@
         <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
-    <comment ref="G26" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="H26" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
     <comment ref="B27" authorId="0" shapeId="0">
       <text>
         <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
@@ -1459,21 +1369,6 @@
         <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="I27" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
         <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
@@ -1495,21 +1390,6 @@
       </text>
     </comment>
     <comment ref="F28" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="G28" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
-      <text>
-        <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
-      </text>
-    </comment>
-    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <t>Historical FY-end (31 March) closing prices were not retrievable via search in this session. Pull directly from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
       </text>
@@ -3417,7 +3297,7 @@
     <row r="21" ht="100" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>All three companies have been actively de-leveraging and improving credit ratings over the last five years — a sector-wide trend as thermal-generation cash flows normalized post-COVID and renewable capex was increasingly funded with cheaper, longer-tenor debt. Adani Power's improvement is the most dramatic in relative terms (net debt/EBITDA from ~4x to ~1.4x within two years), consistent with its swing from losses to strong profitability. Tata Power funded its FY20 deleveraging via a promoter-only preferential allotment rather than a public offering, keeping the raise off the open market. Torrent Power is notable for having gone ~30 years without a public equity raise before its Dec-2024 QIP — a signal of a more conservative, debt/promoter-funded capital structure historically, now shifting toward institutional equity to fund its large (₹80,000 cr) five-year capex programme.</t>
+          <t>All three companies have been actively de-leveraging and improving credit ratings over the last five years — a sector-wide trend as thermal-generation cash flows normalized post-COVID and renewable capex was increasingly funded with cheaper, longer-tenor debt. Adani Power's improvement is the most dramatic in relative terms (net debt/EBITDA from ~4x to ~1.4x within two years), consistent with its swing from losses to strong profitability. Tata Power funded its 2020 deleveraging via a promoter-only preferential allotment rather than a public offering, keeping the raise off the open market. Torrent Power is notable for having gone ~30 years without a public equity raise before its Dec-2024 QIP — a signal of a more conservative, debt/promoter-funded capital structure historically, now shifting toward institutional equity to fund its large (₹80,000 cr) five-year capex programme.</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7349,7 @@
     <row r="6" ht="115" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers not otherwise flagged therefore come from search-engine snippets of secondary coverage of those primary sources, not the primary documents themselves. UPDATE: the user subsequently uploaded the actual Integrated Annual Report PDFs covering — Adani Power FY20-21, FY22-23, FY23-24 (financials section), FY24-25 and FY25-26; Tata Power FY21-22, FY22-23, FY23-24, FY24-25 and FY25-26; Torrent Power FY20-21 through FY25-26 (all six). Using each report's current + prior-year comparative columns, the consolidated Revenue/Total Income, PAT and Total Assets series in Sheet 2 are now PRIMARY-VERIFIED for FY20-FY26 (Adani, Torrent) and FY21-FY26 (Tata), and standalone employee counts were extracted where disclosed. Only FY19 (all metrics beyond secondary-sourced revenue/PAT) and the share-price rows remain unverified/yellow. Segment tables, AOC-1 subsidiary lists and the Investments notes are IN these PDFs but not yet extracted into Sheets 6-9.</t>
+          <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers not otherwise flagged therefore come from search-engine snippets of secondary coverage of those primary sources, not the primary documents themselves. UPDATE: the user subsequently uploaded the companies' actual Integrated Annual Report PDFs, and the analysis window was then NARROWED TO FY22-FY26 (the last five fiscal years) at the user's request — earlier-year data has been removed from this workbook. Within FY22-FY26, the consolidated Revenue/Total Income, PAT and Total Assets series (Sheet 2), the Ind AS 108 segment tables (Sheet 6), the AOC-1 group structure (Sheets 7-8) and the Investments detail (Sheet 9) are all PRIMARY-VERIFIED from the audited Annual Reports stored in this repo. Only the FY-end share-price rows in Sheet 2 remain to be filled (from NSE/Yahoo historical data).</t>
         </is>
       </c>
     </row>
@@ -7488,35 +7368,35 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1. Year-end (31-Mar) share prices, FY19-FY26, all three companies — still not found for any year; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
+          <t>1. Year-end (31-Mar) share prices, FY22-FY26, all three companies — still not filled; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>2. Total Assets — now VERIFIED FY20-FY26 (Adani, Torrent) and FY21-FY26 (Tata) from the Annual Reports. Only FY19 (all 3) and Tata FY20 remain open (needs the FY19-20 Annual Reports).</t>
+          <t>2. Total Assets — DONE: fully VERIFIED FY22-FY26 for all three companies from the Annual Reports.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>3. Employee headcount — standalone-parent counts now VERIFIED where disclosed (Adani FY21/23/25/26; Tata FY22/23/25/26; Torrent FY21-FY26). Group-wide/consolidated headcount is still not disclosed anywhere and would be needed for a true cross-company Sales/Employee comparison.</t>
+          <t>3. Employee headcount — standalone-parent counts VERIFIED where disclosed (Adani FY23/25/26 — FY22/FY24 not disclosed in available reports; Tata FY22/23/25/26; Torrent FY22-FY26). Group-wide/consolidated headcount is not disclosed anywhere and would be needed for a true cross-company Sales/Employee comparison.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>4. Segment-wise (Ind AS 108) tables — DONE: Sheet 6 now carries verified segment revenue/results/assets for Adani Power (FY20-FY26, 2 segments) and Tata Power (FY21-FY26, 4 segments), plus the verified finding that Torrent Power reports NO segments under Ind AS 108 (single integrated business).</t>
+          <t>4. Segment-wise (Ind AS 108) tables — DONE: Sheet 6 carries verified segment revenue/results/assets for Adani Power and Tata Power (FY22-FY26), plus the verified finding that Torrent Power reports NO segments under Ind AS 108 (single integrated business).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>5. Weekly price series — DONE: 54-week adjusted-close series for all 3 stocks + Nifty 50 + Nifty Energy parsed from Yahoo HTML files in the repo; returns, volatility, and market &amp; sector betas computed in Sheet 11. Still open: year-end FY19-FY26 share prices for the Sheet 2 growth table (needs older price history).</t>
+          <t>5. Weekly price series — DONE: 54-week adjusted-close series for all 3 stocks + Nifty 50 + Nifty Energy parsed from Yahoo HTML files in the repo; returns, volatility, and market &amp; sector betas computed in Sheet 11. Still open: year-end FY22-FY26 share prices for the Sheet 2 growth table.</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7837,14 +7717,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>2. Growth Comparison: Sales, Assets, Profit, Market Price (FY19-FY26)</t>
+          <t>2. Growth Comparison: Sales, Assets, Profit, Market Price (FY22-FY26, last 5 years)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>₹ crore, Consolidated. FY24-FY26 columns VERIFIED from primary Annual Reports (uploaded). Yellow = still needs verification.</t>
+          <t>₹ crore, Consolidated. All columns VERIFIED from the audited Annual Reports in the repo. Yellow = still needs data.</t>
         </is>
       </c>
     </row>
@@ -7857,47 +7737,32 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>FY19</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>FY20</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>CAGR</t>
+          <t>4-yr CAGR</t>
         </is>
       </c>
     </row>
@@ -7908,31 +7773,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26362</v>
+        <v>31686.47</v>
       </c>
       <c r="C7" t="n">
-        <v>27841.81</v>
+        <v>43040.52</v>
       </c>
       <c r="D7" t="n">
-        <v>28149.68</v>
+        <v>60281.48</v>
       </c>
       <c r="E7" t="n">
-        <v>31686.47</v>
+        <v>58905.83</v>
       </c>
       <c r="F7" t="n">
-        <v>43040.52</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60281.48</v>
-      </c>
-      <c r="H7" t="n">
-        <v>58905.83</v>
-      </c>
-      <c r="I7" t="n">
         <v>57865.28</v>
       </c>
-      <c r="J7" s="12">
-        <f>IFERROR(IF(OR(B7="N/A",I7="N/A"),"N/A",(I7/B7)^(1/7)-1),"N/A")</f>
+      <c r="G7" s="12">
+        <f>IFERROR(IF(OR(B7="N/A",F7="N/A"),"N/A",(F7/B7)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -7943,31 +7799,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-984.4</v>
+        <v>4911.58</v>
       </c>
       <c r="C8" t="n">
-        <v>-2274.77</v>
+        <v>10726.64</v>
       </c>
       <c r="D8" t="n">
-        <v>1269.98</v>
+        <v>20828.79</v>
       </c>
       <c r="E8" t="n">
-        <v>4911.58</v>
+        <v>12749.61</v>
       </c>
       <c r="F8" t="n">
-        <v>10726.64</v>
-      </c>
-      <c r="G8" t="n">
-        <v>20828.79</v>
-      </c>
-      <c r="H8" t="n">
-        <v>12749.61</v>
-      </c>
-      <c r="I8" t="n">
         <v>12971.08</v>
       </c>
-      <c r="J8" s="12">
-        <f>IFERROR(IF(OR(B8="N/A",I8="N/A"),"N/A",(I8/B8)^(1/7)-1),"N/A")</f>
+      <c r="G8" s="12">
+        <f>IFERROR(IF(OR(B8="N/A",F8="N/A"),"N/A",(F8/B8)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -7977,34 +7824,23 @@
           <t>Adani Power — Total Assets (₹ cr)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" t="n">
+        <v>81981.02</v>
       </c>
       <c r="C9" t="n">
-        <v>75025</v>
+        <v>85821.27</v>
       </c>
       <c r="D9" t="n">
-        <v>78535.47</v>
+        <v>92324.77</v>
       </c>
       <c r="E9" t="n">
-        <v>81981.02</v>
+        <v>112917.57</v>
       </c>
       <c r="F9" t="n">
-        <v>85821.27</v>
-      </c>
-      <c r="G9" t="n">
-        <v>92324.77</v>
-      </c>
-      <c r="H9" t="n">
-        <v>112917.57</v>
-      </c>
-      <c r="I9" t="n">
         <v>142279.92</v>
       </c>
-      <c r="J9" s="12">
-        <f>IFERROR(IF(OR(B9="N/A",I9="N/A"),"N/A",(I9/B9)^(1/7)-1),"N/A")</f>
+      <c r="G9" s="12">
+        <f>IFERROR(IF(OR(B9="N/A",F9="N/A"),"N/A",(F9/B9)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8019,42 +7855,29 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="n">
+        <v>2805</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>84</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E10" t="n">
+        <v>4210</v>
       </c>
       <c r="F10" t="n">
-        <v>2805</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>4210</v>
-      </c>
-      <c r="I10" t="n">
         <v>3967</v>
       </c>
-      <c r="J10" s="12">
-        <f>IFERROR(IF(OR(B10="N/A",I10="N/A"),"N/A",(I10/B10)^(1/7)-1),"N/A")</f>
+      <c r="G10" s="12">
+        <f>IFERROR(IF(OR(B10="N/A",F10="N/A"),"N/A",(F10/B10)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>FY20-FY26 figures VERIFIED from Adani Power's audited Integrated Annual Reports (consolidated). FY19 revenue/PAT are secondary-source (Business Standard, May-2019 results coverage); FY19 Total Assets not available. Employees = STANDALONE permanent employees on Company rolls: FY21's count of just 84 reflects the pre-amalgamation structure — until 1-Oct-2021 the parent was largely a holding shell, with operating staff employed by the 6 subsidiaries merged in that year, so the series has a structural break and FY21 is NOT comparable to FY23+. FY24 PAT (₹20,829cr) was inflated by one-off other income (₹9,781cr incl. prior-period revenue recognition) vs FY25's normalised ₹12,750cr.</t>
+          <t>All figures VERIFIED from Adani Power's audited Integrated Annual Reports (consolidated). Employees = STANDALONE permanent employees on Company rolls; FY22 and FY24 counts not disclosed in the reports available (the FY21-22 Annual Report is not in the repo). FY24 PAT (₹20,829cr) was inflated by one-off other income (₹9,781cr incl. prior-period revenue recognition) vs FY25's normalised ₹12,750cr.</t>
         </is>
       </c>
     </row>
@@ -8065,31 +7888,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30743</v>
+        <v>42576</v>
       </c>
       <c r="C13" t="n">
-        <v>30350</v>
+        <v>56033</v>
       </c>
       <c r="D13" t="n">
-        <v>33239</v>
+        <v>63272.32</v>
       </c>
       <c r="E13" t="n">
-        <v>42576</v>
+        <v>66992.17</v>
       </c>
       <c r="F13" t="n">
-        <v>56033</v>
-      </c>
-      <c r="G13" t="n">
-        <v>63272.32</v>
-      </c>
-      <c r="H13" t="n">
-        <v>66992.17</v>
-      </c>
-      <c r="I13" t="n">
         <v>64171.66</v>
       </c>
-      <c r="J13" s="12">
-        <f>IFERROR(IF(OR(B13="N/A",I13="N/A"),"N/A",(I13/B13)^(1/7)-1),"N/A")</f>
+      <c r="G13" s="12">
+        <f>IFERROR(IF(OR(B13="N/A",F13="N/A"),"N/A",(F13/B13)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8099,36 +7913,23 @@
           <t>Tata Power — Net Profit / PAT (₹ cr)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2156</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3810</v>
       </c>
       <c r="D14" t="n">
-        <v>1439</v>
+        <v>4280</v>
       </c>
       <c r="E14" t="n">
-        <v>2156</v>
+        <v>4775</v>
       </c>
       <c r="F14" t="n">
-        <v>3810</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4280</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4775</v>
-      </c>
-      <c r="I14" t="n">
         <v>5118</v>
       </c>
-      <c r="J14" s="12">
-        <f>IFERROR(IF(OR(B14="N/A",I14="N/A"),"N/A",(I14/B14)^(1/7)-1),"N/A")</f>
+      <c r="G14" s="12">
+        <f>IFERROR(IF(OR(B14="N/A",F14="N/A"),"N/A",(F14/B14)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8138,36 +7939,23 @@
           <t>Tata Power — Total Assets (₹ cr)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B15" t="n">
+        <v>112884.59</v>
+      </c>
+      <c r="C15" t="n">
+        <v>128349.04</v>
       </c>
       <c r="D15" t="n">
-        <v>98838.86</v>
+        <v>139553.49</v>
       </c>
       <c r="E15" t="n">
-        <v>112884.59</v>
+        <v>156711.29</v>
       </c>
       <c r="F15" t="n">
-        <v>128349.04</v>
-      </c>
-      <c r="G15" t="n">
-        <v>139553.49</v>
-      </c>
-      <c r="H15" t="n">
-        <v>156711.29</v>
-      </c>
-      <c r="I15" t="n">
         <v>175171.78</v>
       </c>
-      <c r="J15" s="12">
-        <f>IFERROR(IF(OR(B15="N/A",I15="N/A"),"N/A",(I15/B15)^(1/7)-1),"N/A")</f>
+      <c r="G15" s="12">
+        <f>IFERROR(IF(OR(B15="N/A",F15="N/A"),"N/A",(F15/B15)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8177,47 +7965,32 @@
           <t>Tata Power — Employees (#)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="n">
+        <v>2815</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3071</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="E16" t="n">
-        <v>2815</v>
+        <v>3130</v>
       </c>
       <c r="F16" t="n">
-        <v>3071</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>3130</v>
-      </c>
-      <c r="I16" t="n">
         <v>3295</v>
       </c>
-      <c r="J16" s="12">
-        <f>IFERROR(IF(OR(B16="N/A",I16="N/A"),"N/A",(I16/B16)^(1/7)-1),"N/A")</f>
+      <c r="G16" s="12">
+        <f>IFERROR(IF(OR(B16="N/A",F16="N/A"),"N/A",(F16/B16)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>FY21-FY26 figures VERIFIED from Tata Power's Integrated Annual Reports (consolidated, reported basis): PAT FY21 ₹1,439cr / FY22 ₹2,156cr / FY23 ₹3,810cr replace earlier secondary-source variants (1,424/2,298/3,878, which were pre-exceptional or pre-minority-interest bases). Revenue FY21-23 (33,239/42,576/56,033) is the company's own highlights-basis series incl. regulatory income, now confirmed in the FY22/FY23 Annual Reports; as-reported P&amp;L 'Revenue from Operations' is slightly lower (32,703/42,816/55,109). FY19/FY20 figures remain secondary-source. Employees = STANDALONE parent only (~2,800-3,300) — most of the group workforce sits in subsidiaries (TPREL, discoms), so do not compare with consolidated revenue.</t>
+          <t>All figures VERIFIED from Tata Power's Integrated Annual Reports (consolidated, reported basis). Revenue FY22-23 (42,576/56,033) is the company's own highlights-basis series incl. regulatory income; as-reported P&amp;L 'Revenue from Operations' is slightly lower (42,816/55,109). Employees = STANDALONE parent only (~2,800-3,300) — most of the group workforce sits in subsidiaries (TPREL, discoms), so do not compare with consolidated revenue.</t>
         </is>
       </c>
     </row>
@@ -8227,34 +8000,23 @@
           <t>Torrent Power — Revenue / Total Income (₹ cr)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B19" t="n">
+        <v>14492.65</v>
       </c>
       <c r="C19" t="n">
-        <v>13818.22</v>
+        <v>26075.97</v>
       </c>
       <c r="D19" t="n">
-        <v>12314.47</v>
+        <v>27527.53</v>
       </c>
       <c r="E19" t="n">
-        <v>14492.65</v>
+        <v>29652.47</v>
       </c>
       <c r="F19" t="n">
-        <v>26075.97</v>
-      </c>
-      <c r="G19" t="n">
-        <v>27527.53</v>
-      </c>
-      <c r="H19" t="n">
-        <v>29652.47</v>
-      </c>
-      <c r="I19" t="n">
         <v>29288.92</v>
       </c>
-      <c r="J19" s="12">
-        <f>IFERROR(IF(OR(B19="N/A",I19="N/A"),"N/A",(I19/B19)^(1/7)-1),"N/A")</f>
+      <c r="G19" s="12">
+        <f>IFERROR(IF(OR(B19="N/A",F19="N/A"),"N/A",(F19/B19)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8264,34 +8026,23 @@
           <t>Torrent Power — Net Profit / PAT (₹ cr)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B20" t="n">
+        <v>458.7</v>
       </c>
       <c r="C20" t="n">
-        <v>1178.88</v>
+        <v>2164.67</v>
       </c>
       <c r="D20" t="n">
-        <v>1295.87</v>
+        <v>1896</v>
       </c>
       <c r="E20" t="n">
-        <v>458.7</v>
+        <v>3058.61</v>
       </c>
       <c r="F20" t="n">
-        <v>2164.67</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1896</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3058.61</v>
-      </c>
-      <c r="I20" t="n">
         <v>2469.36</v>
       </c>
-      <c r="J20" s="12">
-        <f>IFERROR(IF(OR(B20="N/A",I20="N/A"),"N/A",(I20/B20)^(1/7)-1),"N/A")</f>
+      <c r="G20" s="12">
+        <f>IFERROR(IF(OR(B20="N/A",F20="N/A"),"N/A",(F20/B20)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8301,34 +8052,23 @@
           <t>Torrent Power — Total Assets (₹ cr)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B21" t="n">
+        <v>25022.7</v>
       </c>
       <c r="C21" t="n">
-        <v>23623.04</v>
+        <v>29910.18</v>
       </c>
       <c r="D21" t="n">
-        <v>23538.72</v>
+        <v>33392.48</v>
       </c>
       <c r="E21" t="n">
-        <v>25022.7</v>
+        <v>36573.38</v>
       </c>
       <c r="F21" t="n">
-        <v>29910.18</v>
-      </c>
-      <c r="G21" t="n">
-        <v>33392.48</v>
-      </c>
-      <c r="H21" t="n">
-        <v>36573.38</v>
-      </c>
-      <c r="I21" t="n">
         <v>45193.28</v>
       </c>
-      <c r="J21" s="12">
-        <f>IFERROR(IF(OR(B21="N/A",I21="N/A"),"N/A",(I21/B21)^(1/7)-1),"N/A")</f>
+      <c r="G21" s="12">
+        <f>IFERROR(IF(OR(B21="N/A",F21="N/A"),"N/A",(F21/B21)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -8338,43 +8078,30 @@
           <t>Torrent Power — Employees (#)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B22" t="n">
+        <v>7603</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6992</v>
       </c>
       <c r="D22" t="n">
-        <v>7429</v>
+        <v>6987</v>
       </c>
       <c r="E22" t="n">
-        <v>7603</v>
+        <v>7213</v>
       </c>
       <c r="F22" t="n">
-        <v>6992</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6987</v>
-      </c>
-      <c r="H22" t="n">
-        <v>7213</v>
-      </c>
-      <c r="I22" t="n">
         <v>6687</v>
       </c>
-      <c r="J22" s="12">
-        <f>IFERROR(IF(OR(B22="N/A",I22="N/A"),"N/A",(I22/B22)^(1/7)-1),"N/A")</f>
+      <c r="G22" s="12">
+        <f>IFERROR(IF(OR(B22="N/A",F22="N/A"),"N/A",(F22/B22)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>FY20-FY26 figures VERIFIED from Torrent Power's Integrated Annual Reports (consolidated). Only FY19 remains unverified (no FY19-20 report uploaded). FY22 PAT (₹458.70cr) was depressed by a ~₹1,300cr DGEN plant impairment. Employees = standalone permanent employees on Company rolls (Rule 5(1) disclosure) — Torrent runs most operations in the parent entity, so this series is closer to a true group headcount than Adani/Tata's standalone counts.</t>
+          <t>All figures VERIFIED from Torrent Power's Integrated Annual Reports (consolidated). FY22 PAT (₹458.70cr) was depressed by a ~₹1,300cr DGEN plant impairment — treat FY22-base growth rates with care. Employees = standalone permanent employees on Company rolls (Rule 5(1) disclosure) — Torrent runs most operations in the parent entity, so this series is closer to a true group headcount than Adani/Tata's standalone counts.</t>
         </is>
       </c>
     </row>
@@ -8416,21 +8143,6 @@
           <t>TO FILL</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8463,21 +8175,6 @@
           <t>TO FILL</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8510,21 +8207,6 @@
           <t>TO FILL</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
@@ -8536,7 +8218,7 @@
     <row r="31" ht="100" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>SALES GROWTH: Adani Power's revenue rose from ₹27,842cr (FY20) to ₹57,865cr (FY26), ~13% CAGR, with the big jumps in FY23-FY24 driven by IBC acquisitions (Mahan, Korba) plus tariff/prior-period recoveries; FY25-FY26 revenue plateaued. Tata Power roughly doubled revenue FY20→FY26 (₹30,350cr→₹64,172cr), the FY22-23 surge reflecting the four Odisha discoms and high Mundra fuel pass-throughs. Torrent Power's revenue more than doubled (₹13,818cr→₹29,289cr), with the single biggest step in FY23 (+80%) from the DNH&amp;DD discom takeover and merchant gas sales. PROFIT GROWTH: Adani Power's swing is the most dramatic — from a ₹2,275cr loss (FY20) to ₹12,971cr PAT (FY26); FY24's ₹20,829cr spike was one-off-boosted and FY25/FY26 is the cleaner run-rate. Tata Power compounded PAT steadily every single year (₹1,439cr FY21 → ₹5,118cr FY26, ~29% CAGR) — the most consistent grower. Torrent is profitable but lumpy (FY22 impairment, FY25 peak, FY26 dip). ASSETS GROWTH: Adani Power's asset base compounded ~11% (₹75,025cr FY20 → ₹1,42,280cr FY26), accelerating sharply after FY24 as acquisitions/new capacity landed. Tata Power grew assets ~12% CAGR (₹98,839cr FY21 → ₹1,75,172cr FY26) — the largest absolute base. Torrent was static FY20-FY22 (~₹23-25,000cr) then accelerated to ₹45,193cr by FY26 (Nabha + capex cycle). MARKET PRICE: year-end share-price rows still need NSE/Yahoo data (yellow) to complete the fourth growth lens.</t>
+          <t>SALES GROWTH (FY22→FY26): Adani Power grew revenue ~83% (₹31,686cr → ₹57,865cr, ~16% CAGR), driven by IBC acquisitions (Mahan, Korba) and tariff/prior-period recoveries in FY23-FY24, before plateauing in FY25-FY26. Torrent Power doubled revenue (₹14,493cr → ₹29,289cr, ~19% CAGR) with the single biggest step in FY23 (+80%) from the DNH&amp;DD discom takeover and merchant gas sales. Tata Power grew ~51% (₹42,576cr → ₹64,172cr, ~11% CAGR). PROFIT GROWTH: Adani Power PAT rose from ₹4,912cr to ₹12,971cr (~27% CAGR); FY24's ₹20,829cr spike was one-off-boosted and FY25/FY26 is the cleaner run-rate. Tata Power compounded PAT steadily every single year (₹2,156cr → ₹5,118cr, ~24% CAGR) — the most consistent grower. Torrent is profitable but lumpy: FY22 was impairment-depressed (₹459cr), rebounding to ₹2,165-3,059cr, easing to ₹2,469cr in FY26. ASSETS GROWTH: Adani Power's asset base grew ~74% (₹81,981cr → ₹1,42,280cr), accelerating sharply after FY24 as acquisitions and new capacity landed. Tata Power grew ~55% to ₹1,75,172cr — the largest absolute base. Torrent grew ~81% (₹25,023cr → ₹45,193cr; Nabha Power + capex cycle) — the fastest in relative terms. MARKET PRICE: year-end share-price rows still need NSE/Yahoo historical data (yellow) to complete the fourth lens.</t>
         </is>
       </c>
     </row>
@@ -8546,12 +8228,12 @@
     <row r="35"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A31:J35"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G35"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8565,7 +8247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8593,397 +8275,284 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FY19</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26362</v>
+        <v>31686.47</v>
       </c>
       <c r="C2" t="n">
-        <v>30743</v>
+        <v>42576</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14492.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FY20</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27841.81</v>
+        <v>43040.52</v>
       </c>
       <c r="C3" t="n">
-        <v>30350</v>
+        <v>56033</v>
       </c>
       <c r="D3" t="n">
-        <v>13818.22</v>
+        <v>26075.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28149.68</v>
+        <v>60281.48</v>
       </c>
       <c r="C4" t="n">
-        <v>33239</v>
+        <v>63272.32</v>
       </c>
       <c r="D4" t="n">
-        <v>12314.47</v>
+        <v>27527.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31686.47</v>
+        <v>58905.83</v>
       </c>
       <c r="C5" t="n">
-        <v>42576</v>
+        <v>66992.17</v>
       </c>
       <c r="D5" t="n">
-        <v>14492.65</v>
+        <v>29652.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43040.52</v>
+        <v>57865.28</v>
       </c>
       <c r="C6" t="n">
-        <v>56033</v>
+        <v>64171.66</v>
       </c>
       <c r="D6" t="n">
-        <v>26075.97</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>60281.48</v>
-      </c>
-      <c r="C7" t="n">
-        <v>63272.32</v>
-      </c>
-      <c r="D7" t="n">
-        <v>27527.53</v>
+        <v>29288.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>58905.83</v>
-      </c>
-      <c r="C8" t="n">
-        <v>66992.17</v>
-      </c>
-      <c r="D8" t="n">
-        <v>29652.47</v>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adani Power PAT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tata Power PAT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Torrent Power PAT</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57865.28</v>
+        <v>4911.58</v>
       </c>
       <c r="C9" t="n">
-        <v>64171.66</v>
+        <v>2156</v>
       </c>
       <c r="D9" t="n">
-        <v>29288.92</v>
+        <v>458.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10726.64</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3810</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2164.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Adani Power PAT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Tata Power PAT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Torrent Power PAT</t>
-        </is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20828.79</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4280</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1896</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FY19</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-984.4</v>
+        <v>12749.61</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3058.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FY20</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2274.77</v>
+        <v>12971.08</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5118</v>
       </c>
       <c r="D13" t="n">
-        <v>1178.88</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FY21</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1269.98</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1439</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1295.87</v>
+        <v>2469.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FY22</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4911.58</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2156</v>
-      </c>
-      <c r="D15" t="n">
-        <v>458.7</v>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Adani Power Assets</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tata Power Assets</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Torrent Power Assets</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10726.64</v>
+        <v>81981.02</v>
       </c>
       <c r="C16" t="n">
-        <v>3810</v>
+        <v>112884.59</v>
       </c>
       <c r="D16" t="n">
-        <v>2164.67</v>
+        <v>25022.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20828.79</v>
+        <v>85821.27</v>
       </c>
       <c r="C17" t="n">
-        <v>4280</v>
+        <v>128349.04</v>
       </c>
       <c r="D17" t="n">
-        <v>1896</v>
+        <v>29910.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12749.61</v>
+        <v>92324.77</v>
       </c>
       <c r="C18" t="n">
-        <v>4775</v>
+        <v>139553.49</v>
       </c>
       <c r="D18" t="n">
-        <v>3058.61</v>
+        <v>33392.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>112917.57</v>
+      </c>
+      <c r="C19" t="n">
+        <v>156711.29</v>
+      </c>
+      <c r="D19" t="n">
+        <v>36573.38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>FY26</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>12971.08</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5118</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2469.36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Adani Power Assets</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tata Power Assets</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Torrent Power Assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>FY20</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>75025</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23623.04</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>FY21</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>78535.47</v>
-      </c>
-      <c r="C23" t="n">
-        <v>98838.86</v>
-      </c>
-      <c r="D23" t="n">
-        <v>23538.72</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>FY22</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>81981.02</v>
-      </c>
-      <c r="C24" t="n">
-        <v>112884.59</v>
-      </c>
-      <c r="D24" t="n">
-        <v>25022.7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FY23</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>85821.27</v>
-      </c>
-      <c r="C25" t="n">
-        <v>128349.04</v>
-      </c>
-      <c r="D25" t="n">
-        <v>29910.18</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>92324.77</v>
-      </c>
-      <c r="C26" t="n">
-        <v>139553.49</v>
-      </c>
-      <c r="D26" t="n">
-        <v>33392.48</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>112917.57</v>
-      </c>
-      <c r="C27" t="n">
-        <v>156711.29</v>
-      </c>
-      <c r="D27" t="n">
-        <v>36573.38</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+      <c r="B20" t="n">
         <v>142279.92</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C20" t="n">
         <v>175171.78</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D20" t="n">
         <v>45193.28</v>
       </c>
     </row>
@@ -8998,24 +8567,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>3. Sales per Rupee of Asset Deployed &amp; Sales per Employee</t>
+          <t>3. Sales per Rupee of Asset Deployed &amp; Sales per Employee (FY22-FY26)</t>
         </is>
       </c>
     </row>
@@ -9035,40 +8601,25 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>FY19</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>FY20</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>FY23</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
@@ -9100,18 +8651,6 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F7),ISTEXT('2_Growth_Comparison'!F9)),"N/A",'2_Growth_Comparison'!F7/'2_Growth_Comparison'!F9),"N/A")</f>
         <v/>
       </c>
-      <c r="G7" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G7),ISTEXT('2_Growth_Comparison'!G9)),"N/A",'2_Growth_Comparison'!G7/'2_Growth_Comparison'!G9),"N/A")</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H7),ISTEXT('2_Growth_Comparison'!H9)),"N/A",'2_Growth_Comparison'!H7/'2_Growth_Comparison'!H9),"N/A")</f>
-        <v/>
-      </c>
-      <c r="I7" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I7),ISTEXT('2_Growth_Comparison'!I9)),"N/A",'2_Growth_Comparison'!I7/'2_Growth_Comparison'!I9),"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9139,18 +8678,6 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F7),ISTEXT('2_Growth_Comparison'!F10)),"N/A",'2_Growth_Comparison'!F7*100/'2_Growth_Comparison'!F10),"N/A")</f>
         <v/>
       </c>
-      <c r="G8" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G7),ISTEXT('2_Growth_Comparison'!G10)),"N/A",'2_Growth_Comparison'!G7*100/'2_Growth_Comparison'!G10),"N/A")</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H7),ISTEXT('2_Growth_Comparison'!H10)),"N/A",'2_Growth_Comparison'!H7*100/'2_Growth_Comparison'!H10),"N/A")</f>
-        <v/>
-      </c>
-      <c r="I8" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I7),ISTEXT('2_Growth_Comparison'!I10)),"N/A",'2_Growth_Comparison'!I7*100/'2_Growth_Comparison'!I10),"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9178,18 +8705,6 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F13),ISTEXT('2_Growth_Comparison'!F15)),"N/A",'2_Growth_Comparison'!F13/'2_Growth_Comparison'!F15),"N/A")</f>
         <v/>
       </c>
-      <c r="G10" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G13),ISTEXT('2_Growth_Comparison'!G15)),"N/A",'2_Growth_Comparison'!G13/'2_Growth_Comparison'!G15),"N/A")</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H13),ISTEXT('2_Growth_Comparison'!H15)),"N/A",'2_Growth_Comparison'!H13/'2_Growth_Comparison'!H15),"N/A")</f>
-        <v/>
-      </c>
-      <c r="I10" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I13),ISTEXT('2_Growth_Comparison'!I15)),"N/A",'2_Growth_Comparison'!I13/'2_Growth_Comparison'!I15),"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9217,18 +8732,6 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F13),ISTEXT('2_Growth_Comparison'!F16)),"N/A",'2_Growth_Comparison'!F13*100/'2_Growth_Comparison'!F16),"N/A")</f>
         <v/>
       </c>
-      <c r="G11" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G13),ISTEXT('2_Growth_Comparison'!G16)),"N/A",'2_Growth_Comparison'!G13*100/'2_Growth_Comparison'!G16),"N/A")</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H13),ISTEXT('2_Growth_Comparison'!H16)),"N/A",'2_Growth_Comparison'!H13*100/'2_Growth_Comparison'!H16),"N/A")</f>
-        <v/>
-      </c>
-      <c r="I11" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I13),ISTEXT('2_Growth_Comparison'!I16)),"N/A",'2_Growth_Comparison'!I13*100/'2_Growth_Comparison'!I16),"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9256,18 +8759,6 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F19),ISTEXT('2_Growth_Comparison'!F21)),"N/A",'2_Growth_Comparison'!F19/'2_Growth_Comparison'!F21),"N/A")</f>
         <v/>
       </c>
-      <c r="G13" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G19),ISTEXT('2_Growth_Comparison'!G21)),"N/A",'2_Growth_Comparison'!G19/'2_Growth_Comparison'!G21),"N/A")</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H19),ISTEXT('2_Growth_Comparison'!H21)),"N/A",'2_Growth_Comparison'!H19/'2_Growth_Comparison'!H21),"N/A")</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I19),ISTEXT('2_Growth_Comparison'!I21)),"N/A",'2_Growth_Comparison'!I19/'2_Growth_Comparison'!I21),"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9295,18 +8786,6 @@
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F19),ISTEXT('2_Growth_Comparison'!F22)),"N/A",'2_Growth_Comparison'!F19*100/'2_Growth_Comparison'!F22),"N/A")</f>
         <v/>
       </c>
-      <c r="G14" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!G19),ISTEXT('2_Growth_Comparison'!G22)),"N/A",'2_Growth_Comparison'!G19*100/'2_Growth_Comparison'!G22),"N/A")</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!H19),ISTEXT('2_Growth_Comparison'!H22)),"N/A",'2_Growth_Comparison'!H19*100/'2_Growth_Comparison'!H22),"N/A")</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!I19),ISTEXT('2_Growth_Comparison'!I22)),"N/A",'2_Growth_Comparison'!I19*100/'2_Growth_Comparison'!I22),"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -9318,7 +8797,7 @@
     <row r="17" ht="130" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>SALES PER RUPEE OF ASSET (now computable FY20/FY21-FY26 from verified Annual Report data): Adani Power improved from ~0.37x (FY20, low utilisation/losses era) to a peak of ~0.65x (FY24), then fell back to ~0.41x (FY26) as its asset base ballooned ahead of revenue from new acquisitions still ramping up. Tata Power is stable in a ~0.34-0.45x band — typical of a regulated, asset-heavy integrated utility. Torrent Power is consistently the MOST asset-efficient of the three (~0.52-0.87x, peaking FY23 when DNH&amp;DD volumes hit a still-small asset base) — its regulated distribution business generates more revenue per rupee of assets than pure thermal generation does. SALES PER EMPLOYEE: comparable across time within Torrent (parent employs most staff: ~₹18-44 cr/employee trend) but NOT comparable across companies — Adani and Tata employee counts are standalone-parent only, while their revenue is consolidated (Tata's discoms/TPREL staff and Adani's pre-FY22 plant staff sit in subsidiaries). Adani's FY21 count of 84 (pre-amalgamation shell) makes that year's ratio meaningless and it is excluded from comment. Use the Torrent series as the benchmark and treat Adani/Tata Sales-per-Employee as indicative only, noting the basis in any write-up.</t>
+          <t>SALES PER RUPEE OF ASSET (all five years computed from verified Annual Report data): Adani Power improved from ~0.39x (FY22) to a peak of ~0.65x (FY24), then fell back to ~0.41x (FY26) as its asset base ballooned ahead of revenue from new acquisitions still ramping up. Tata Power is stable in a ~0.37-0.45x band — typical of a regulated, asset-heavy integrated utility. Torrent Power is consistently the MOST asset-efficient of the three (~0.58-0.87x, peaking FY23 when DNH&amp;DD volumes hit a still-small asset base) — its regulated distribution business generates more revenue per rupee of assets than pure thermal generation does. SALES PER EMPLOYEE: comparable across time within Torrent (parent employs most staff) but NOT comparable across companies — Adani and Tata employee counts are standalone-parent only, while their revenue is consolidated (Tata's discoms/TPREL staff sit in subsidiaries). Use the Torrent series as the benchmark and treat Adani/Tata Sales-per-Employee as indicative only, noting the basis in any write-up.</t>
         </is>
       </c>
     </row>
@@ -9331,9 +8810,9 @@
     <row r="24"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A17:I24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10370,7 +9849,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>₹ crore, consolidated. Extracted directly from the 'Segment Reporting' notes of each company's audited Annual Reports (FY21-FY26 reports uploaded by user).</t>
+          <t>₹ crore, consolidated, FY22-FY26. Extracted directly from the 'Segment Reporting' notes of each company's audited Annual Reports.</t>
         </is>
       </c>
     </row>
@@ -10390,35 +9869,25 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>FY20</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
@@ -10431,24 +9900,18 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>26005.92</v>
+        <v>27221.78</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>25870.6</v>
+        <v>37895.85</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>27221.78</v>
+        <v>50014.16</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>37895.85</v>
+        <v>56107.06</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>50014.16</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>56107.06</v>
-      </c>
-      <c r="H7" s="19" t="n">
         <v>54240.52</v>
       </c>
     </row>
@@ -10459,24 +9922,18 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>461.8</v>
+        <v>489.4</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>350.88</v>
+        <v>877.45</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>489.4</v>
+        <v>337.09</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>877.45</v>
+        <v>96.03</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>337.09</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>96.03</v>
-      </c>
-      <c r="H8" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10486,29 +9943,19 @@
           <t>Segment Results — Power Generation</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" s="19" t="n">
+        <v>6571.37</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>6957.13</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>6571.37</v>
+        <v>20557.22</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>6957.13</v>
+        <v>16540.39</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>20557.22</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>16540.39</v>
-      </c>
-      <c r="H9" s="19" t="n">
         <v>15757.55</v>
       </c>
     </row>
@@ -10518,29 +9965,19 @@
           <t>Segment Results — Trading/Investment/Other</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B10" s="19" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>717.5700000000001</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>5.76</v>
+        <v>234.29</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>717.5700000000001</v>
+        <v>-1.81</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>234.29</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="H10" s="19" t="n">
         <v>13.68</v>
       </c>
     </row>
@@ -10551,24 +9988,18 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>74847.53999999999</v>
+        <v>81888.09</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>77747</v>
+        <v>84364.22</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>81888.09</v>
+        <v>91378.85000000001</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>84364.22</v>
+        <v>111162.48</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>91378.85000000001</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>111162.48</v>
-      </c>
-      <c r="H11" s="19" t="n">
         <v>139777.31</v>
       </c>
     </row>
@@ -10579,31 +10010,25 @@
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>177.46</v>
+        <v>42.02</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>788.47</v>
+        <v>1134.26</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>42.02</v>
+        <v>203.86</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>1134.26</v>
+        <v>1328.18</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>203.86</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>1328.18</v>
-      </c>
-      <c r="H12" s="19" t="n">
         <v>1354.52</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>FY20/21 segment results shown as N/A because the FY21 report used a different basis ('profit before interest…', not comparable); FY22-23 results are as restated in the FY23 report after a CODM methodology change. FY26 Trading revenue was nil; segment results shown are pre-tax basis per each year's note.</t>
+          <t>FY22-23 results are as restated in the FY23 report after a CODM methodology change. FY26 Trading revenue was nil; segment results shown are pre-tax basis per each year's note.</t>
         </is>
       </c>
     </row>
@@ -10622,30 +10047,25 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
@@ -10658,21 +10078,18 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>13432.77</v>
+        <v>11211.03</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>11211.03</v>
+        <v>18211.35</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>18211.35</v>
+        <v>19613.61</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>19613.61</v>
+        <v>19739.07</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>19739.07</v>
-      </c>
-      <c r="G17" s="19" t="n">
         <v>11635.93</v>
       </c>
     </row>
@@ -10683,21 +10100,18 @@
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>5887.65</v>
+        <v>7748.9</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>7748.9</v>
+        <v>8196.91</v>
       </c>
       <c r="D18" s="19" t="n">
-        <v>8196.91</v>
+        <v>10175.29</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>10175.29</v>
+        <v>9876.360000000001</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>9876.360000000001</v>
-      </c>
-      <c r="G18" s="19" t="n">
         <v>15027.82</v>
       </c>
     </row>
@@ -10708,21 +10122,18 @@
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>16829.85</v>
+        <v>27493.17</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>27493.17</v>
+        <v>34529.36</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>34529.36</v>
+        <v>36205.82</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>36205.82</v>
+        <v>39120.52</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>39120.52</v>
-      </c>
-      <c r="G19" s="19" t="n">
         <v>41338.59</v>
       </c>
     </row>
@@ -10733,21 +10144,18 @@
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>262.16</v>
+        <v>317.8</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>317.8</v>
+        <v>413.56</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>413.56</v>
+        <v>430.62</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>430.62</v>
+        <v>431.04</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>431.04</v>
-      </c>
-      <c r="G20" s="19" t="n">
         <v>431.79</v>
       </c>
     </row>
@@ -10758,21 +10166,18 @@
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>2709.81</v>
+        <v>2632.75</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>2632.75</v>
+        <v>5092.16</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>5092.16</v>
+        <v>2569.61</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>2569.61</v>
+        <v>2878.91</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>2878.91</v>
-      </c>
-      <c r="G21" s="19" t="n">
         <v>1137.94</v>
       </c>
     </row>
@@ -10783,21 +10188,18 @@
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>1494.25</v>
+        <v>1923.57</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>1923.57</v>
+        <v>1932.01</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>1932.01</v>
+        <v>2147.1</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>2147.1</v>
+        <v>2880.68</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>2880.68</v>
-      </c>
-      <c r="G22" s="19" t="n">
         <v>4340.93</v>
       </c>
     </row>
@@ -10808,21 +10210,18 @@
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>1677.02</v>
+        <v>2138.49</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>2138.49</v>
+        <v>2197.68</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>2197.68</v>
+        <v>2418.22</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>2418.22</v>
+        <v>3128.27</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>3128.27</v>
-      </c>
-      <c r="G23" s="19" t="n">
         <v>4307.95</v>
       </c>
     </row>
@@ -10833,21 +10232,18 @@
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>83.16</v>
+        <v>-286.03</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>-286.03</v>
+        <v>-308.17</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>-308.17</v>
+        <v>105.38</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>105.38</v>
+        <v>112.8</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="G24" s="19" t="n">
         <v>104.72</v>
       </c>
     </row>
@@ -10858,21 +10254,18 @@
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>37717.32</v>
+        <v>38201.93</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>38201.93</v>
+        <v>41201.04</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>41201.04</v>
+        <v>39315.88</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>39315.88</v>
+        <v>39708.11</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>39708.11</v>
-      </c>
-      <c r="G25" s="19" t="n">
         <v>41697.31</v>
       </c>
     </row>
@@ -10883,21 +10276,18 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>22702.98</v>
+        <v>27589.28</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>27589.28</v>
+        <v>29744.49</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>29744.49</v>
+        <v>40459.25</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>40459.25</v>
+        <v>51355.61</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>51355.61</v>
-      </c>
-      <c r="G26" s="19" t="n">
         <v>56921.28</v>
       </c>
     </row>
@@ -10908,21 +10298,18 @@
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>25542.61</v>
+        <v>32411.34</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>32411.34</v>
+        <v>37477.26</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>37477.26</v>
+        <v>42059.9</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>42059.9</v>
+        <v>45707.75</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>45707.75</v>
-      </c>
-      <c r="G27" s="19" t="n">
         <v>53428.87</v>
       </c>
     </row>
@@ -10933,21 +10320,18 @@
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>12875.95</v>
+        <v>14682.04</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>14682.04</v>
+        <v>19926.25</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>19926.25</v>
+        <v>17718.46</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>17718.46</v>
+        <v>19939.82</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>19939.82</v>
-      </c>
-      <c r="G28" s="19" t="n">
         <v>23124.32</v>
       </c>
     </row>
@@ -10986,7 +10370,7 @@
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>GENERATION is the only segment where all three effectively compete, and the verified numbers show a stark contrast: Adani Power's generation segment grew revenue ~2.1x (₹26,006cr FY20 → ₹54,241cr FY26) with segment results of ₹15,758-20,557cr in FY24-26 — vastly more profitable than Tata Power's generation segment (results of only ₹1,138-2,879cr on ₹11,636-19,739cr revenue in the same years, dragged by the Mundra plant's fuel economics and eventual shutdown). Adani is unambiguously the generation winner. RENEWABLES: only Tata Power reports it separately, and it is now their growth engine — revenue up 2.6x (₹5,888cr FY21 → ₹15,028cr FY26), results up 2.9x (₹1,494cr → ₹4,341cr), and segment assets up 2.5x to ₹56,921cr, overtaking every other Tata segment. Adani Power has no renewables segment (that sits in sister company Adani Green). TRANSMISSION &amp; DISTRIBUTION: Tata Power's largest and steadiest segment — revenue grew ₹16,830cr → ₹41,339cr (FY21→FY26, boosted by the Odisha discoms) with consistently positive, regulated-return results (₹1,677cr → ₹4,308cr). Torrent's distribution business is economically similar (regulated, stable) but not separately reported. INDUSTRY CONTEXT: India's power demand grew ~7-8%/yr (CEA) over this period — Adani's generation growth (~13% CAGR) and Tata's renewables growth (~21% CAGR) both outpaced the sector, largely through acquisitions and capacity build-out respectively, while Tata's generation segment underperformed the sector.</t>
+          <t>GENERATION is the only segment where all three effectively compete, and the verified numbers show a stark contrast: Adani Power's generation segment grew revenue ~2.0x (₹27,222cr FY22 → ₹54,241cr FY26) with segment results of ₹15,758-20,557cr in FY24-26 — vastly more profitable than Tata Power's generation segment (results of only ₹1,138-2,879cr on ₹11,636-19,739cr revenue in the same years, dragged by the Mundra plant's fuel economics and eventual shutdown). Adani is unambiguously the generation winner. RENEWABLES: only Tata Power reports it separately, and it is now their growth engine — revenue up ~1.9x (₹7,749cr FY22 → ₹15,028cr FY26), results up 2.3x (₹1,924cr → ₹4,341cr), and segment assets up 2.1x to ₹56,921cr, overtaking every other Tata segment. Adani Power has no renewables segment (that sits in sister company Adani Green). TRANSMISSION &amp; DISTRIBUTION: Tata Power's largest and steadiest segment — revenue grew ₹27,493cr → ₹41,339cr (FY22→FY26, boosted by the Odisha discoms) with consistently positive, regulated-return results (₹2,138cr → ₹4,308cr). Torrent's distribution business is economically similar (regulated, stable) but not separately reported. INDUSTRY CONTEXT: India's power demand grew ~7-8%/yr (CEA) over this period — Adani's generation growth (~13% CAGR) and Tata's renewables growth (~21% CAGR) both outpaced the sector, largely through acquisitions and capacity build-out respectively, while Tata's generation segment underperformed the sector.</t>
         </is>
       </c>
     </row>
@@ -11018,7 +10402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11051,114 +10435,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13432.77</v>
+        <v>11211.03</v>
       </c>
       <c r="C2" t="n">
-        <v>5887.65</v>
+        <v>7748.9</v>
       </c>
       <c r="D2" t="n">
-        <v>16829.85</v>
+        <v>27493.17</v>
       </c>
       <c r="E2" t="n">
-        <v>25870.6</v>
+        <v>27221.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11211.03</v>
+        <v>18211.35</v>
       </c>
       <c r="C3" t="n">
-        <v>7748.9</v>
+        <v>8196.91</v>
       </c>
       <c r="D3" t="n">
-        <v>27493.17</v>
+        <v>34529.36</v>
       </c>
       <c r="E3" t="n">
-        <v>27221.78</v>
+        <v>37895.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18211.35</v>
+        <v>19613.61</v>
       </c>
       <c r="C4" t="n">
-        <v>8196.91</v>
+        <v>10175.29</v>
       </c>
       <c r="D4" t="n">
-        <v>34529.36</v>
+        <v>36205.82</v>
       </c>
       <c r="E4" t="n">
-        <v>37895.85</v>
+        <v>50014.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19613.61</v>
+        <v>19739.07</v>
       </c>
       <c r="C5" t="n">
-        <v>10175.29</v>
+        <v>9876.360000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>36205.82</v>
+        <v>39120.52</v>
       </c>
       <c r="E5" t="n">
-        <v>50014.16</v>
+        <v>56107.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19739.07</v>
+        <v>11635.93</v>
       </c>
       <c r="C6" t="n">
-        <v>9876.360000000001</v>
+        <v>15027.82</v>
       </c>
       <c r="D6" t="n">
-        <v>39120.52</v>
+        <v>41338.59</v>
       </c>
       <c r="E6" t="n">
-        <v>56107.06</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11635.93</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15027.82</v>
-      </c>
-      <c r="D7" t="n">
-        <v>41338.59</v>
-      </c>
-      <c r="E7" t="n">
         <v>54240.52</v>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -8,23 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1_Business_Overview" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2_Growth_Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2b_Growth_Chart_Data" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="3_Sales_per_Asset_Employee" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4_Acquisitions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5_Shareholding_Pattern" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="6_Business_Segments" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="6b_Segment_Chart_Data" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="7_Group_Structure" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="8_Associates_JVs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="9_Investments" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="10_Financing_Changes" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="11_Returns_Volatility" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Weekly_Price_Data" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="12_Major_Announcements" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="12b_Announcement_Chart_Data" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet name="13_Sources_and_Gaps" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FS_Extracts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1_Business_Overview" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2_Growth_Comparison" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2b_Growth_Chart_Data" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="3_Sales_per_Asset_Employee" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4_Acquisitions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5_Shareholding_Pattern" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6_Business_Segments" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6b_Segment_Chart_Data" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="7_Group_Structure" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="8_Associates_JVs" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="9_Investments" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="10_Financing_Changes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="11_Returns_Volatility" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Weekly_Price_Data" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="12_Major_Announcements" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="12b_Announcement_Chart_Data" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet name="13_Sources_and_Gaps" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,6 +78,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -87,20 +93,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="1"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00008000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -159,27 +160,27 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1925,89 +1926,96 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>1. Business Overview &amp; Market</t>
+          <t>FS Extracts — financial-statement trail (course requirement)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>2. Sales / Asset / Profit / Market-Price Growth (5-yr) — Comparison &amp; Chart</t>
+          <t>1. Business Overview &amp; Market</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>3. Sales per Rupee of Asset &amp; Sales per Employee</t>
+          <t>2. Sales / Asset / Profit / Market-Price Growth (5-yr) — Comparison &amp; Chart</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>4. Business Acquisitions &amp; Post-Acquisition Impact</t>
+          <t>3. Sales per Rupee of Asset &amp; Sales per Employee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>5. Shareholding Pattern (Promoters, FII, DII/MF, Pledge, Free Float)</t>
+          <t>4. Business Acquisitions &amp; Post-Acquisition Impact</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>6. Reportable Business Segments — 5-yr Trend &amp; Comparison</t>
+          <t>5. Shareholding Pattern (Promoters, FII, DII/MF, Pledge, Free Float)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>7. Group Structure — Subsidiaries</t>
+          <t>6. Reportable Business Segments — 5-yr Trend &amp; Comparison</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>8. Associates &amp; Joint Ventures</t>
+          <t>7. Group Structure — Subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>9. Other Investments (ex subs/associates/JVs) up to FY23</t>
+          <t>8. Associates &amp; Joint Ventures</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>10. Major Changes in Financing (5-yr)</t>
+          <t>9. Other Investments (ex subs/associates/JVs) up to FY23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>11. Share Price Return vs Sectoral &amp; Market Index (weekly, 1-yr) &amp; Volatility</t>
+          <t>10. Major Changes in Financing (5-yr)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>12. Major Announcements (last 1 year) &amp; Price Reaction — Chart</t>
+          <t>11. Share Price Return vs Sectoral &amp; Market Index (weekly, 1-yr) &amp; Volatility</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
+        <is>
+          <t>12. Major Announcements (last 1 year) &amp; Price Reaction — Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>13. Sources &amp; Data Gaps (READ FIRST)</t>
         </is>
@@ -2049,6 +2057,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tata Generation Rev</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tata Renewables Rev</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tata T&amp;D Rev</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Adani Generation Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11211.03</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7748.9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27493.17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27221.78</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18211.35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8196.91</v>
+      </c>
+      <c r="D3" t="n">
+        <v>34529.36</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37895.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>19613.61</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10175.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36205.82</v>
+      </c>
+      <c r="E4" t="n">
+        <v>50014.16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19739.07</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9876.360000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39120.52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>56107.06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11635.93</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15027.82</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41338.59</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54240.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2074,572 +2218,572 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Subsidiary</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>% Holding</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Mahan Energen Ltd (MEL)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>94% (per FY26 AOC-1 — earlier reported as 100%)</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>1,200+ MW coal thermal, MP; ex-Essar Power MP (CIRP, Mar 2022). FY26: turnover ₹3,614cr, PAT ₹784cr.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Korba Power Ltd (KPL, ex-Lanco Amarkantak)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>600 MW coal thermal, Chhattisgarh (CIRP, Sep 2024). FY26: turnover ₹1,552cr, PAT ₹354cr.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Moxie Power Generation Ltd (ex-Coastal Energen)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>49% — but consolidated as a SUBSIDIARY in AOC-1 Part A (control basis), not a JV</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>1,200 MW, Thoothukudi, Tamil Nadu. FY26: turnover ₹2,985cr, PAT ₹268cr. Listed in AOC-1 subsidiaries despite 49% equity — control established via arrangement with DAIT.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Vidarbha Industries Power Ltd (VIPL)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>100% (acquired 07-Jul-2025)</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>600 MW, Nagpur (CIRP). FY26: turnover ₹1,327cr, PAT ₹347cr.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Adani Power Dahej Ltd / Pench Thermal Energy (MP) Ltd / Kutchh Power Generation Ltd</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>100% each</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Greenfield thermal project SPVs (Dahej, Pench, Kutchh).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Anuppur Thermal Energy (MP) / Mirzapur Thermal Energy (UP) / Orrisa Thermal Energy</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>100% each (acquired/renamed 2024)</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>New thermal project SPVs for capacity expansion (Anuppur, Mirzapur, Odisha sites).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Mahan Fuel Management / Resurgent Fuel Management Ltd</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>100% each</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Fuel sourcing/management SPVs.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Alcedo / Chandenvalle / Emberiza Infra Park Ltd</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>100% each</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Infrastructure park SPVs.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Adani Atomic Energy Ltd (AAEL)</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>100% (incorporated 11-Feb-2026)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Nuclear power entry post SHANTI Act 2025.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Adani Power Middle East Ltd (AED) / Adani Power Global Pte Ltd (US$)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>100% each (incorporated 2024)</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Overseas ventures (Middle East; Singapore trading/holding).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Adani Power Resources Ltd</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Resource-related SPV (immaterial size).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>[TOTAL: 19 entities in FY26 AOC-1 Part A — fully verified]</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>The 6 operating cos (Adani Power Maharashtra/Rajasthan, Udupi, Raipur/Raigarh Energen, Adani Power (Mundra)) were amalgamated INTO the parent effective 1-Oct-2021 and no longer appear.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Tata Power Renewable Energy Ltd (TPREL)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>88.57% (per FY26 AOC-1 — VERIFIED; not ~100% as earlier assumed)</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Renewables arm (solar/wind/rooftop/EV charging). FY26: turnover ₹11,748cr, PAT ₹1,268cr. ~11.4% held by BlackRock-led consortium since FY23 equity raise.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Tata Power Delhi Distribution Ltd (Tata Power-DDL)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>51% (VERIFIED per FY26 AOC-1)</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>North Delhi discom (JV with Delhi Govt). FY26: turnover ₹10,426cr, PAT ₹1,299cr.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>TP Central / Western / Southern / Northern Odisha Distribution Ltds</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>51% each (VERIFIED)</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Four Odisha discoms (PPP, 2020-21). FY26 turnover: TPCODL ₹6,313cr, TPWODL ₹6,355cr, TPSODL ₹2,542cr, TPNODL ₹4,769cr; all PAT-positive.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Tata Power Solar Systems Ltd (TPSSL)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>In AOC-1 (100%, via TPREL structure)</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Solar cell/module manufacturing + EPC.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Coastal Gujarat Power Ltd (CGPL) — NOTE</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Merged into parent, 1-Apr-2020</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Mundra UMPP is now a direct Generation-segment asset, not a subsidiary.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>[TOTAL: ~113 entities in FY26 AOC-1 Part A]</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Includes dozens of renewable/transmission SPVs under TPREL and Resurgent Power Ventures; full list in FY26 Annual Report pg. 666+ (AOC-1).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Torrent Power Grid Ltd</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>74% (VERIFIED; PowerGrid Corp holds 26%)</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Interstate power transmission JV-structured subsidiary.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Transmission SPVs (Solapur Transmission Ltd &amp; 4 others at 74%)</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>74% each (per FY26 AOC-1)</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Intra/interstate transmission project SPVs.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Torrent Pipavav Generation Ltd</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>95% (VERIFIED)</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Power generation project, Pipavav.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Dadra &amp; Nagar Haveli and Daman &amp; Diu Power Distribution Corp Ltd</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>51% (VERIFIED)</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>UT power distribution licensee (acquired Apr 2022).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Nabha Power Ltd</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>100% (acquired Jun 2026)</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>2x700 MW supercritical coal plant, Punjab (from L&amp;T).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Torrent Solargen, Latur Renewable, Surya Vidyut, Torrent Akshay Urja, Jodhpur Wind Farms, MSKVY solar SPVs, Torrent Electricals, Newzone India, etc.</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>100% each</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Renewable generation SPVs (solar/wind incl. Maharashtra MSKVY series), cables/electricals, and other ventures.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>[TOTAL: ~60 entities in FY26 AOC-1 — 53 at 100%, 5 at 74%, 1 at 95%, 1 at 51%]</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Verified from the FY26 Annual Report AOC-1 statement.</t>
         </is>
@@ -2654,7 +2798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2681,154 +2825,154 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Associate / JV</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Wangchhu Hydroelectric Power Ltd (Bhutan)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>JV (per FY26 AOC-1 Part B — the Group's only listed associate/JV)</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>570 MW Wangchhu hydro project JV with Druk Green Power Corp (~₹6,000 cr); Shareholders Agreement Sep 2025; 'yet to commence operations' per AOC-1. VERIFIED.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Moxie Power Generation Ltd — RECLASSIFIED</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>49% equity but consolidated as SUBSIDIARY (see Sheet 7)</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>CORRECTION: earlier flagged as a JV; the FY26 AOC-1 lists it under Part A (Subsidiaries) — Adani has control despite 49% equity.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Jaiprakash Power Ventures Ltd (JPVL)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>24% (indirect, via resolution plan)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Adani Power as 'Implementing Entity'; NCLT-approved ~Mar 2026 (~₹14,535 cr). Not yet in FY26 AOC-1 Part B (transaction completing post year-end).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Tata Projects, Resurgent Power Ventures (26%), industrial JVs &amp; associates</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Various</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Tata Power holds numerous associates/JVs (share of profit ₹708cr FY26, ₹793cr FY25 per consolidated P&amp;L); full Part B list in FY26 Annual Report AOC-1.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Dorjilung Hydro Power Ltd (Bhutan)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Stake not disclosed in extract</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>1,125 MW hydro project under development with Druk Green.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Associates (2 per earlier AOC-1 references)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Not extracted</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Torrent's FY26 AOC-1 Part B not extracted in this pass — the Part A subsidiary data above is verified; pull Part B from the same annexure if associate detail is needed.</t>
         </is>
@@ -2843,7 +2987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2869,75 +3013,75 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Finding</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Data Quality</t>
         </is>
       </c>
     </row>
     <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>VERIFIED from FY23 consolidated Investments notes: NON-CURRENT — ₹42.51cr total as at 31-Mar-2023 (vs ₹0.01cr FY22), comprising ₹42.50cr of 0.001% Optionally Convertible Cumulative Debentures of Sal Technologies and Solutions Ltd (4.25cr units, new in FY23), a ₹0.01cr National Saving Certificate, and a negligible FVTOCI equity stake in Adani Naval Defence Systems &amp; Technologies Ltd. CURRENT — ₹611.54cr in unquoted mutual funds (SBI Liquid Fund ₹608.42cr + SBI Overnight Fund ₹3.12cr) vs ₹183.24cr (FY22, SBI Overnight only). Pattern: treasury parked in liquid MFs, scale rising with cash generation; almost no discretionary long-term securities portfolio.</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>VERIFIED (FY23 Annual Report)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>VERIFIED from FY23 consolidated Investments note: non-current investments OTHER than associates/JVs totalled ₹1,301.21cr as at 31-Mar-2023 (vs ₹1,169.81cr FY22), comprising equity shares carried at FVTOCI/FVTPL and Government Securities (unquoted) of ₹128.10cr (FY22: ₹124.26cr). The earlier secondary-source figure of '~₹12,064cr non-current investments' conflated investments in associates/JVs (equity-method carrying values) with this third-party portfolio — use ₹1,301cr for the ex-subsidiary/associate/JV basis the assignment asks for.</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>VERIFIED (FY23 Annual Report) — replaces earlier unverified figure</t>
         </is>
       </c>
     </row>
     <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>VERIFIED from FY23 consolidated Investments notes: NON-CURRENT — quoted investments (incl. Government of India bonds held as the GERC Multi-Year-Tariff-mandated 'contingency reserve' for its Gujarat distribution licences) of ~₹15.94cr market value ₹15.70cr as at 31-Mar-2023 (down from ₹132.82cr FY22 as bonds matured/were reclassified). CURRENT — ₹682.31cr total (vs ₹253.27cr FY22): unquoted mutual funds ₹656.03cr + statutory contingency-reserve investments ₹1.93cr + other ₹24.35cr. The GoI-bond holdings are regulatory-mandated (usable only for GERC-specified purposes), not discretionary treasury.</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>VERIFIED (FY23 Annual Report)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>All three companies' figures above are now extracted directly from the consolidated 'Investments' notes of the FY2022-23 Annual Reports uploaded to the repo. Common pattern: all three park treasury cash in liquid/overnight mutual funds; Torrent additionally holds regulatory-mandated GoI bonds (GERC contingency reserve); none runs a material discretionary securities portfolio.</t>
         </is>
@@ -2953,7 +3097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2980,322 +3124,322 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Amount (₹ cr)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Jan 2024</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>CRISIL upgraded bank-facility rating to AA-/Stable from A/Stable</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Feb 2025</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>CRISIL upgraded to AA/Stable from AA-/Positive on ₹38,000 cr long-term bank facilities; assigned AA/Stable to proposed NCDs</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>38,000 (facilities); 11,000 (proposed NCDs)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>FY22→FY24</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Deleveraging: net debt/EBITDA fell from ~4.0x (Mar-22) to 3.3x (Mar-23) to 1.4x (Mar-24)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Net debt ~26,270-26,545 (Q4 FY24)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>FY24→FY25</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Shareholders' funds grew from ₹43,145 cr (31-Mar-24) to ₹56,347 cr (31-Mar-25)</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>+13,202</t>
         </is>
       </c>
     </row>
     <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>1-Aug-2025 / 22-Sep-2025</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>1:5 stock split announced / effective (face value ₹10 → ₹2) — capital structure change, not a capital raise</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>30-Jul-2020</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>₹2,600 cr preferential allotment of ~49.06 cr shares to promoter Tata Sons at ₹53/share, to cut debt &amp; fund capex; raised promoter stake 35.27%→45.21%</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Apr-2024</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>CRISIL upgraded to AA+/Stable from AA/Positive, citing improved generation/distribution profitability</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="55" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>FY22→FY24</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Deleveraging: net debt/EBITDA fell from ~4.5x (FY22) to 3.8x (FY23), sustained &lt;4.0x through FY24; debtor days improved from &gt;150 to ~102 days</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="55" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Dec-2024</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Maiden QIP — ₹3,500 cr raised at ₹1,503/share (~2.32 cr shares); first Torrent Group equity raise in ~3 decades; ~4x oversubscribed (bids ~₹14,000 cr)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
       </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Apr-2022</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Series 8 NCDs — ₹600 cr (coupons 6.20%-7.45% across tenors)</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
     </row>
     <row r="16" ht="55" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>NCD issuance, 8/9/10-yr tenor</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Jun-2026</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>NCDs across 4 tranches (3-10yr, coupons 8.10%-8.20%); board also sanctioned up to ₹10,000 cr NCD private placement tied to an ₹80,000 cr 5-yr capex plan</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>3,800 (allotted); up to 10,000 (sanctioned)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="55" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Dec-2023 / Feb-2024 / Feb-2025</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>CRISIL reaffirmed AA+/Stable (LT) and A1+ (ST) at each review; net debt/EBITDA improved 2.20x (FY24) → 1.40x (FY25)</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="21" ht="100" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>All three companies have been actively de-leveraging and improving credit ratings over the last five years — a sector-wide trend as thermal-generation cash flows normalized post-COVID and renewable capex was increasingly funded with cheaper, longer-tenor debt. Adani Power's improvement is the most dramatic in relative terms (net debt/EBITDA from ~4x to ~1.4x within two years), consistent with its swing from losses to strong profitability. Tata Power funded its 2020 deleveraging via a promoter-only preferential allotment rather than a public offering, keeping the raise off the open market. Torrent Power is notable for having gone ~30 years without a public equity raise before its Dec-2024 QIP — a signal of a more conservative, debt/promoter-funded capital structure historically, now shifting toward institutional equity to fund its large (₹80,000 cr) five-year capex programme.</t>
         </is>
@@ -3317,7 +3461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3350,366 +3494,366 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Nifty Energy (sector)</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Nifty 50 (market)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Price at start (14-Jul-2025, adj)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>118.93</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>405.39</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>1,349.89</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>36,231.65</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>24,968.40</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Price at end (15-Jul-2026)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>218.97</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>380.90</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>1,441.10</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>39,381.25</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>24,078.50</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>52-week weekly-close range</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>113.40 - 243.37</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>343.12 - 441.81</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>1,204.41 - 1,730.01</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>33,098.30 - 40,878.00</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>22,713.10 - 26,328.55</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>1-year return (COMPUTED)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>+84.1%</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>-6.0%</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>+6.8%</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>+8.7%</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>-3.6%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Weekly return std dev (COMPUTED)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>4.95%</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>2.90%</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>4.55%</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>2.30%</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Annualized volatility = sd x sqrt(52)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>35.7%</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>20.9%</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>32.8%</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>16.6%</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>12.3%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Beta vs Nifty 50 / market (COMPUTED)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Beta vs Nifty Energy / sector (COMPUTED)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Return vs market (stock - Nifty 50)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>+87.7 pts</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>-2.5 pts</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>+10.3 pts</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>+12.3 pts</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Return vs sector (stock - Nifty Energy)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>+75.4 pts</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>-14.7 pts</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>-1.9 pts</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Data note</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>COMPLETE: all five series (3 stocks + Nifty 50 + Nifty Energy) parsed from the Yahoo Finance Historical Data pages saved in the repo (54 weekly adjusted-close points each, 14-Jul-2025 to 15-Jul-2026, split-adjusted). Weekly returns, standard deviations, annualized volatility, and betas computed from this data - see the Weekly_Price_Data sheet for the full series and the rebased performance chart below.</t>
         </is>
@@ -3718,14 +3862,14 @@
     <row r="19"/>
     <row r="20"/>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Comments — which share is most volatile?</t>
         </is>
       </c>
     </row>
     <row r="23" ht="130" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ANSWER (computed from 54 weekly observations, split-adjusted): ADANI POWER is the most volatile of the three — weekly-return standard deviation 4.95% (annualized ~36%), vs Torrent Power 4.55% (~33%) and Tata Power 2.90% (~21%). The sector index (Nifty Energy) sat at 2.30% weekly (~17% annualized) — all three stocks were roughly 1.3-2.2x as volatile as their sector index. RETURNS: Adani Power massively outperformed (+84% vs the sector's +9%), Torrent Power roughly tracked the sector (+6.8%), and Tata Power underperformed (-6.0%). Note the LOW computed betas vs Nifty Energy (0.03-0.54): Nifty Energy is dominated by Reliance/ONGC (oil &amp; gas), so these power stocks move on company-specific news far more than on the 'sector' index — high volatility with low index correlation. Interpret beta accordingly. VS THE MARKET: Nifty 50 fell -3.6% over the window, so all three power stocks outperformed the broad market (Adani by ~88 points); market betas vs Nifty 50 are 1.13 (Adani), 0.62 (Tata) and 1.46 (Torrent).</t>
         </is>
@@ -3750,7 +3894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6315,7 +6459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6346,300 +6490,300 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Date (approx.)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Announcement</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Reported Price Reaction</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Nearest known price (₹)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>07-Jul-2025</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Completed acquisition of Vidarbha Industries Power Ltd (600 MW) — total capacity to 18,150 MW</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Not quantified in sources found</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr"/>
+      <c r="D6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>01-Aug-2025</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Q1 FY26 results: PAT ₹3,305 cr (down 15.5% YoY); 1:5 stock split announced</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr"/>
+      <c r="D7" s="16" t="inlineStr"/>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Sep-2025</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Adani Power–Druk Green (Bhutan) Shareholders Agreement — 570 MW Wangchhu hydro (~₹6,000 cr)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>22-Sep-2025</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>1:5 stock split effective (face value ₹10→₹2)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Mechanical price adjustment (~1/5th), not a market reaction</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr"/>
+      <c r="D9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>30-Oct-2025</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Q2 FY26 results: PAT ~₹2,906-2,953 cr (down ~11-12% YoY); secured 4.5 GW new long-term PPAs</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>14-Nov-2025</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Letter of Award — 3,200 MW Assam UMPP (~₹48,000 cr investment, DBFOO)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>'Share price surge reported' (source did not quantify %)</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr"/>
+      <c r="D11" s="16" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Nov-2025</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>24% stake in Jaiprakash Power Ventures via ₹14,535 cr resolution plan — creditors approved (89% votes)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>JP Power (the target) stock jumped ~29% in two days — Adani Power's own reaction not quantified in sources found</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr"/>
+      <c r="D12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>05-Jan-2026</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>News coverage: stock up ~40% over trailing 12 months</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>+40% (12-mo, as reported that day)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>146.20</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>11-Feb-2026</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Incorporation of Adani Atomic Energy Ltd — entry into nuclear power</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr"/>
+      <c r="D14" s="16" t="inlineStr"/>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>~Mar-2026</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>NCLT approval of Jaiprakash Power Ventures resolution plan</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>29-Apr-2026</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Q4/FY26 results: Q4 PAT ₹4,271 cr (+64% YoY); FY26 PAT ₹12,971 cr vs ₹12,750 cr FY25</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr"/>
+      <c r="D16" s="16" t="inlineStr"/>
     </row>
     <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Stock hits 52-week high, intraday</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Record high reached</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>234.35</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>22-May-2026</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Profit-booking reported post ~100% 1-year return</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>~6% off high; ~100% 1-yr return cited that day</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>~220.00</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>13-Jul-2026</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Filing on encumbrance/non-disposal undertaking re: Jaiprakash Power shares (in role as JPVL implementing entity)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Not quantified</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr"/>
+      <c r="D19" s="16" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Note on this section</t>
         </is>
       </c>
     </row>
     <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Most individual-announcement price reactions (in %) were NOT disclosed in the secondary news sources found via search — only a few data points (the 40% 12-month move reported 5-Jan-2026, the 52-week high of ₹234.35 on 5-May-2026, and the ~100% 1-yr return cited 22-May-2026) could be tied to a specific date and price. For a proper event-study chart (price in a window around each announcement date), pull the daily closing price for the 5 days before/after each announcement from NSE historical data and compute the % reaction — the chart below plots the sparse real data points we do have as a starting frame; extend it once you have the daily series.</t>
         </is>
@@ -6659,7 +6803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7315,7 +7459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7340,14 +7484,14 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Methodology</t>
         </is>
       </c>
     </row>
     <row r="6" ht="115" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>This workbook was built using automated web search (news wires, brokerage research notes, exchange press releases, and secondary financial-data aggregators such as Trendlyne, ScanX, HDFC Sky, Business Standard, BusinessToday, Equitymaster) inside a sandboxed research session. Direct scripted/API access to the PRIMARY sources you were asked to use — screener.in, moneycontrol.com, NSE India (nseindia.com), BSE India (bseindia.com), and the companies' own Annual Report PDFs (adanipower.com, tatapower.com, torrentpower.com) — was blocked (HTTP 403) for automated fetches in this environment. All numbers not otherwise flagged therefore come from search-engine snippets of secondary coverage of those primary sources, not the primary documents themselves. UPDATE: the user subsequently uploaded the companies' actual Integrated Annual Report PDFs, and the analysis window was then NARROWED TO FY22-FY26 (the last five fiscal years) at the user's request — earlier-year data has been removed from this workbook. Within FY22-FY26, the consolidated Revenue/Total Income, PAT and Total Assets series (Sheet 2), the Ind AS 108 segment tables (Sheet 6), the AOC-1 group structure (Sheets 7-8) and the Investments detail (Sheet 9) are all PRIMARY-VERIFIED from the audited Annual Reports stored in this repo. Only the FY-end share-price rows in Sheet 2 remain to be filled (from NSE/Yahoo historical data).</t>
         </is>
@@ -7359,140 +7503,140 @@
     <row r="10"/>
     <row r="11"/>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Priority list — verify these before submission</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>1. Year-end (31-Mar) share prices, FY22-FY26, all three companies — still not filled; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>2. Total Assets — DONE: fully VERIFIED FY22-FY26 for all three companies from the Annual Reports.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>3. Employee headcount — standalone-parent counts VERIFIED where disclosed (Adani FY23/25/26 — FY22/FY24 not disclosed in available reports; Tata FY22/23/25/26; Torrent FY22-FY26). Group-wide/consolidated headcount is not disclosed anywhere and would be needed for a true cross-company Sales/Employee comparison.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>4. Segment-wise (Ind AS 108) tables — DONE: Sheet 6 carries verified segment revenue/results/assets for Adani Power and Tata Power (FY22-FY26), plus the verified finding that Torrent Power reports NO segments under Ind AS 108 (single integrated business).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>5. Weekly price series — DONE: 54-week adjusted-close series for all 3 stocks + Nifty 50 + Nifty Energy parsed from Yahoo HTML files in the repo; returns, volatility, and market &amp; sector betas computed in Sheet 11. Still open: year-end FY22-FY26 share prices for the Sheet 2 growth table.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>6. Shareholding pattern — Promoter %, promoter pledge (nil, all 3), and the single largest non-promoter &gt;5% holder are now VERIFIED as at 31-Mar-2026 from the Annual Reports for all three companies (Sheet 5). FII/DII category-level % breakdowns are still secondary-source/unverified — pull the full SHP table from each PDF or BSE/NSE XBRL filing if needed.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>7. Subsidiary lists — DONE: Sheets 7-8 now carry the verified FY26 AOC-1 data (Adani 19 entities incl. Mahan at 94% and Moxie consolidated at 49%; Tata ~113 entities incl. TPREL at 88.57%; Torrent ~60 entities). Only Torrent's associates (Part B) remain unextracted.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>8. Investments (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — DONE: Sheet 9 now carries verified figures from all three FY23 Annual Reports (Adani ₹42.51cr non-current + ₹611.54cr MFs; Tata ₹1,301.21cr; Torrent ₹15.94cr bonds + ₹682.31cr current).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>9. Promoter pledge status — now VERIFIED as NIL for all three companies as at FY26 (Sheet 5), from the Annual Reports.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>10. Exact announcement dates + daily price reaction for Adani Power's major events (Sheet 12) — cross-check against BSE corporate announcements page.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Key sources cited across this workbook (non-exhaustive)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Business Standard (business-standard.com) — quarterly results coverage, all 3 companies</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>BusinessToday (businesstoday.in) — results, stock-move coverage</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Equitymaster (equitymaster.com) — annual report analyses (Torrent Power, Tata Power)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>CRISIL Ratings (crisil.com) — rating rationales for all 3 companies</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Trendlyne, ScanX, HDFC Sky, Kotak Neo, ICICI Direct, Groww — shareholding, price, beta/volatility snapshots</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Mercom India, Saurenergy, PV Magazine India — renewable/PPA/project news</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>NSE India, BSE India (nseindia.com, bseindia.com) — REFERENCED but not directly fetchable in this session; primary source for final verification</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>screener.in, moneycontrol.com — REFERENCED but not directly fetchable in this session; primary source for financial-statement data</t>
         </is>
@@ -7532,6 +7676,496 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Financial Statement Extracts (Consolidated), FY22-FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Key lines from each company's audited Consolidated Financial Statements, extracted from the Annual Report PDFs stored in this repository. These are the 'trail' for every figure used in Sheets 2, 3 and 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>ADANI POWER LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Line item (₹ crore, consolidated)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Revenue from Operations</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>27711.18</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>38773.3</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>50351.25</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>56203.09</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>54240.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>31686.47</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>43040.52</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>60281.48</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>58905.83</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>57865.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Profit Before Tax (before deferred tax adj.)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>6577.13</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>7674.7</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>20791.51</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>16359.51</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>15499.51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Total Tax Expense / (Credit)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>1744.8</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>-3267.37</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>-37.28</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>3609.9</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>2528.43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>4911.58</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>10726.64</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>20828.79</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>12749.61</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>12971.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>81981.02</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>85821.27</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>92324.77</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>112917.57</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>142279.92</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Source PDFs in repo: AR_22088_ADANIPOWER_2022_2023 (FY22 &amp; FY23), AR_24072_ADANIPOWER_2023_2024 (FY24), ADANIPOWER-2025 / AR_26476 (FY25), AR_29298_ADANIPOWER_2025_2026 (FY26) — Consolidated Statement of P&amp;L and Balance Sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>THE TATA POWER COMPANY LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Line item (₹ crore, consolidated)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Revenue from Operations (as reported P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>42815.67</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>55109.08</v>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>65478.24</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Total Income (highlights basis, incl. regulatory)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>42576</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>56033</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>63272.32</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>66992.17</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>64171.66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT, reported)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>2156</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>3810</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>4280</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>4775</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>5118</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>112884.59</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>128349.04</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>139553.49</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>156711.29</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>175171.78</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Source PDFs in repo: AR_20052_TATAPOWER_2021_2022 (FY22), AR_2022_2023 (FY23), AR_24164_TATAPOWER_2023_2024 (FY24), AR_26536 (FY25), AR_29380 (FY26) — Consolidated Statement of P&amp;L and Balance Sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TORRENT POWER LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Line item (₹ crore, consolidated)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>14492.65</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>26075.97</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>27527.53</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>29652.47</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>29288.92</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>2164.67</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1896</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>3058.61</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>2469.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>25022.7</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>29910.18</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>33392.48</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>36573.38</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>45193.28</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Source PDFs in repo: AR_20392_TORNTPOWER_2021_2022 (FY22), AR_22356 (FY23), AR_24323 (FY24), AR_26840 (FY25), AR_29704 (FY26) — Consolidated Statement of P&amp;L and Balance Sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Trail note</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Every Revenue/Total Income, PAT and Total Assets figure in Sheet 2 equals the corresponding line above; Sheet 3 ratios are formulas over Sheet 2 cells; Sheet 6 segment figures come from the Segment Reporting (Ind AS 108) note of the same consolidated financial statements. The full audited financial statements are contained in the Annual Report PDFs submitted alongside this workbook in the same repository/folder, satisfying the course requirement that the file contain the financial statements with calculation trails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A31:F34"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7557,128 +8191,128 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr"/>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Adani Power Ltd (Target)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Tata Power Company Ltd (Competitor)</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Torrent Power Ltd (Competitor)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Positioning</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>India's largest PRIVATE thermal (base-load) power producer; part of the Adani Group.</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>India's largest vertically integrated power company (generation + transmission + distribution).</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Leading integrated power utility; part of Torrent Group (also pharma &amp; city-gas distribution).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Core products/services</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Thermal power generation (subcritical to ultra-supercritical); sold via long-term &amp; short-term PPAs and merchant sales on power exchanges.</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Generation (thermal+hydro), Transmission, Distribution (regulated discoms); shifting toward 100% renewable generation; new-age products (solar rooftop, EV charging).</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Generation (gas, coal, solar, wind), Transmission (~1,340 ckm HV lines), Distribution (licensed + franchise).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Market / geographic footprint</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>12 plants across 8 states (Gujarat, Maharashtra, Karnataka, Rajasthan, Chhattisgarh, MP, Jharkhand, Tamil Nadu); ~7.3% of India's coal-based generation capacity; exports power to Bangladesh via Godda plant.</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Pan-India: Mumbai &amp; Delhi discoms, 4 Odisha discoms, Ajmer discom; ~12.6 million distribution customers; renewable assets nationwide; expanding into Bhutan hydro &amp; nuclear.</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Gujarat (Ahmedabad, Surat, Dahej), Dadra &amp; Nagar Haveli/Daman &amp; Diu, franchise areas Agra (UP) &amp; Bhiwandi (Maharashtra); ~4.3 million customers p.a.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Installed capacity (approx., 2025-26)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>~18,150 MW (post Vidarbha acquisition, Jul 2025), all thermal.</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>~11.6 GW renewable identified/under TPREL alone + thermal (Mundra 4 GW+) + hydro + distribution licenses covering 12.6mn customers.</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>~2,730 MW gas + 362 MW coal + ~663 MW solar + ~1,220 MW wind (as of FY23/Jan-24 disclosures); Nabha Power (2x700MW coal) added June 2026.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Strategic direction</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Capacity expansion via IBC/CIRP acquisitions (Mahan, Korba, Moxie, Vidarbha, JPVL); new Assam UMPP (3,200 MW, ~₹48,000 cr); entry into nuclear power (Adani Atomic Energy Ltd, Feb 2026); Bhutan hydro JV with Druk Green.</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Targeting ₹1 lakh crore revenue &amp; ₹10,000 cr PAT by 2030; nuclear, battery storage, solar manufacturing (Odisha); pumped hydro storage (Bhivpuri, Shirawta); Bhutan hydro portfolio (5,033 MW identified).</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>₹80,000 crore 5-yr capex plan: +3 GW thermal (incl. Nabha), ~3.96 GW renewables, ~3 GW pumped storage; exploring Green Hydrogen/Ammonia.</t>
         </is>
@@ -7693,7 +8327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7730,37 +8364,37 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company / Metric</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>FY22</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>4-yr CAGR</t>
         </is>
@@ -7787,7 +8421,7 @@
       <c r="F7" t="n">
         <v>57865.28</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="17">
         <f>IFERROR(IF(OR(B7="N/A",F7="N/A"),"N/A",(F7/B7)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -7813,7 +8447,7 @@
       <c r="F8" t="n">
         <v>12971.08</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="17">
         <f>IFERROR(IF(OR(B8="N/A",F8="N/A"),"N/A",(F8/B8)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -7839,7 +8473,7 @@
       <c r="F9" t="n">
         <v>142279.92</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="17">
         <f>IFERROR(IF(OR(B9="N/A",F9="N/A"),"N/A",(F9/B9)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -7869,13 +8503,13 @@
       <c r="F10" t="n">
         <v>3967</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="17">
         <f>IFERROR(IF(OR(B10="N/A",F10="N/A"),"N/A",(F10/B10)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>All figures VERIFIED from Adani Power's audited Integrated Annual Reports (consolidated). Employees = STANDALONE permanent employees on Company rolls; FY22 and FY24 counts not disclosed in the reports available (the FY21-22 Annual Report is not in the repo). FY24 PAT (₹20,829cr) was inflated by one-off other income (₹9,781cr incl. prior-period revenue recognition) vs FY25's normalised ₹12,750cr.</t>
         </is>
@@ -7902,7 +8536,7 @@
       <c r="F13" t="n">
         <v>64171.66</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="17">
         <f>IFERROR(IF(OR(B13="N/A",F13="N/A"),"N/A",(F13/B13)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -7928,7 +8562,7 @@
       <c r="F14" t="n">
         <v>5118</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="17">
         <f>IFERROR(IF(OR(B14="N/A",F14="N/A"),"N/A",(F14/B14)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -7954,7 +8588,7 @@
       <c r="F15" t="n">
         <v>175171.78</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="17">
         <f>IFERROR(IF(OR(B15="N/A",F15="N/A"),"N/A",(F15/B15)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -7982,13 +8616,13 @@
       <c r="F16" t="n">
         <v>3295</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="17">
         <f>IFERROR(IF(OR(B16="N/A",F16="N/A"),"N/A",(F16/B16)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>All figures VERIFIED from Tata Power's Integrated Annual Reports (consolidated, reported basis). Revenue FY22-23 (42,576/56,033) is the company's own highlights-basis series incl. regulatory income; as-reported P&amp;L 'Revenue from Operations' is slightly lower (42,816/55,109). Employees = STANDALONE parent only (~2,800-3,300) — most of the group workforce sits in subsidiaries (TPREL, discoms), so do not compare with consolidated revenue.</t>
         </is>
@@ -8015,7 +8649,7 @@
       <c r="F19" t="n">
         <v>29288.92</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="17">
         <f>IFERROR(IF(OR(B19="N/A",F19="N/A"),"N/A",(F19/B19)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -8041,7 +8675,7 @@
       <c r="F20" t="n">
         <v>2469.36</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="17">
         <f>IFERROR(IF(OR(B20="N/A",F20="N/A"),"N/A",(F20/B20)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -8067,7 +8701,7 @@
       <c r="F21" t="n">
         <v>45193.28</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="17">
         <f>IFERROR(IF(OR(B21="N/A",F21="N/A"),"N/A",(F21/B21)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
@@ -8093,20 +8727,20 @@
       <c r="F22" t="n">
         <v>6687</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="17">
         <f>IFERROR(IF(OR(B22="N/A",F22="N/A"),"N/A",(F22/B22)^(1/4)-1),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>All figures VERIFIED from Torrent Power's Integrated Annual Reports (consolidated). FY22 PAT (₹458.70cr) was depressed by a ~₹1,300cr DGEN plant impairment — treat FY22-base growth rates with care. Employees = standalone permanent employees on Company rolls (Rule 5(1) disclosure) — Torrent runs most operations in the parent entity, so this series is closer to a true group headcount than Adani/Tata's standalone counts.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Market price per share (₹, year-end 31-Mar)</t>
         </is>
@@ -8209,14 +8843,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="31" ht="100" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>SALES GROWTH (FY22→FY26): Adani Power grew revenue ~83% (₹31,686cr → ₹57,865cr, ~16% CAGR), driven by IBC acquisitions (Mahan, Korba) and tariff/prior-period recoveries in FY23-FY24, before plateauing in FY25-FY26. Torrent Power doubled revenue (₹14,493cr → ₹29,289cr, ~19% CAGR) with the single biggest step in FY23 (+80%) from the DNH&amp;DD discom takeover and merchant gas sales. Tata Power grew ~51% (₹42,576cr → ₹64,172cr, ~11% CAGR). PROFIT GROWTH: Adani Power PAT rose from ₹4,912cr to ₹12,971cr (~27% CAGR); FY24's ₹20,829cr spike was one-off-boosted and FY25/FY26 is the cleaner run-rate. Tata Power compounded PAT steadily every single year (₹2,156cr → ₹5,118cr, ~24% CAGR) — the most consistent grower. Torrent is profitable but lumpy: FY22 was impairment-depressed (₹459cr), rebounding to ₹2,165-3,059cr, easing to ₹2,469cr in FY26. ASSETS GROWTH: Adani Power's asset base grew ~74% (₹81,981cr → ₹1,42,280cr), accelerating sharply after FY24 as acquisitions and new capacity landed. Tata Power grew ~55% to ₹1,75,172cr — the largest absolute base. Torrent grew ~81% (₹25,023cr → ₹45,193cr; Nabha Power + capex cycle) — the fastest in relative terms. MARKET PRICE: year-end share-price rows still need NSE/Yahoo historical data (yellow) to complete the fourth lens.</t>
         </is>
@@ -8241,7 +8875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8561,7 +9195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8594,32 +9228,32 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company / Metric</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>FY22</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
@@ -8631,23 +9265,23 @@
           <t>Adani Power — Sales / Total Assets (x)</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!B7),ISTEXT('2_Growth_Comparison'!B9)),"N/A",'2_Growth_Comparison'!B7/'2_Growth_Comparison'!B9),"N/A")</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!C7),ISTEXT('2_Growth_Comparison'!C9)),"N/A",'2_Growth_Comparison'!C7/'2_Growth_Comparison'!C9),"N/A")</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!D7),ISTEXT('2_Growth_Comparison'!D9)),"N/A",'2_Growth_Comparison'!D7/'2_Growth_Comparison'!D9),"N/A")</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!E7),ISTEXT('2_Growth_Comparison'!E9)),"N/A",'2_Growth_Comparison'!E7/'2_Growth_Comparison'!E9),"N/A")</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F7),ISTEXT('2_Growth_Comparison'!F9)),"N/A",'2_Growth_Comparison'!F7/'2_Growth_Comparison'!F9),"N/A")</f>
         <v/>
       </c>
@@ -8658,23 +9292,23 @@
           <t>Adani Power — Sales / Employee (₹ lakh)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!B7),ISTEXT('2_Growth_Comparison'!B10)),"N/A",'2_Growth_Comparison'!B7*100/'2_Growth_Comparison'!B10),"N/A")</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!C7),ISTEXT('2_Growth_Comparison'!C10)),"N/A",'2_Growth_Comparison'!C7*100/'2_Growth_Comparison'!C10),"N/A")</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!D7),ISTEXT('2_Growth_Comparison'!D10)),"N/A",'2_Growth_Comparison'!D7*100/'2_Growth_Comparison'!D10),"N/A")</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!E7),ISTEXT('2_Growth_Comparison'!E10)),"N/A",'2_Growth_Comparison'!E7*100/'2_Growth_Comparison'!E10),"N/A")</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F7),ISTEXT('2_Growth_Comparison'!F10)),"N/A",'2_Growth_Comparison'!F7*100/'2_Growth_Comparison'!F10),"N/A")</f>
         <v/>
       </c>
@@ -8685,23 +9319,23 @@
           <t>Tata Power — Sales / Total Assets (x)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!B13),ISTEXT('2_Growth_Comparison'!B15)),"N/A",'2_Growth_Comparison'!B13/'2_Growth_Comparison'!B15),"N/A")</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!C13),ISTEXT('2_Growth_Comparison'!C15)),"N/A",'2_Growth_Comparison'!C13/'2_Growth_Comparison'!C15),"N/A")</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!D13),ISTEXT('2_Growth_Comparison'!D15)),"N/A",'2_Growth_Comparison'!D13/'2_Growth_Comparison'!D15),"N/A")</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!E13),ISTEXT('2_Growth_Comparison'!E15)),"N/A",'2_Growth_Comparison'!E13/'2_Growth_Comparison'!E15),"N/A")</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F13),ISTEXT('2_Growth_Comparison'!F15)),"N/A",'2_Growth_Comparison'!F13/'2_Growth_Comparison'!F15),"N/A")</f>
         <v/>
       </c>
@@ -8712,23 +9346,23 @@
           <t>Tata Power — Sales / Employee (₹ lakh)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!B13),ISTEXT('2_Growth_Comparison'!B16)),"N/A",'2_Growth_Comparison'!B13*100/'2_Growth_Comparison'!B16),"N/A")</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!C13),ISTEXT('2_Growth_Comparison'!C16)),"N/A",'2_Growth_Comparison'!C13*100/'2_Growth_Comparison'!C16),"N/A")</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!D13),ISTEXT('2_Growth_Comparison'!D16)),"N/A",'2_Growth_Comparison'!D13*100/'2_Growth_Comparison'!D16),"N/A")</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!E13),ISTEXT('2_Growth_Comparison'!E16)),"N/A",'2_Growth_Comparison'!E13*100/'2_Growth_Comparison'!E16),"N/A")</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F13),ISTEXT('2_Growth_Comparison'!F16)),"N/A",'2_Growth_Comparison'!F13*100/'2_Growth_Comparison'!F16),"N/A")</f>
         <v/>
       </c>
@@ -8739,23 +9373,23 @@
           <t>Torrent Power — Sales / Total Assets (x)</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!B19),ISTEXT('2_Growth_Comparison'!B21)),"N/A",'2_Growth_Comparison'!B19/'2_Growth_Comparison'!B21),"N/A")</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!C19),ISTEXT('2_Growth_Comparison'!C21)),"N/A",'2_Growth_Comparison'!C19/'2_Growth_Comparison'!C21),"N/A")</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!D19),ISTEXT('2_Growth_Comparison'!D21)),"N/A",'2_Growth_Comparison'!D19/'2_Growth_Comparison'!D21),"N/A")</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!E19),ISTEXT('2_Growth_Comparison'!E21)),"N/A",'2_Growth_Comparison'!E19/'2_Growth_Comparison'!E21),"N/A")</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F19),ISTEXT('2_Growth_Comparison'!F21)),"N/A",'2_Growth_Comparison'!F19/'2_Growth_Comparison'!F21),"N/A")</f>
         <v/>
       </c>
@@ -8766,36 +9400,36 @@
           <t>Torrent Power — Sales / Employee (₹ lakh)</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!B19),ISTEXT('2_Growth_Comparison'!B22)),"N/A",'2_Growth_Comparison'!B19*100/'2_Growth_Comparison'!B22),"N/A")</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!C19),ISTEXT('2_Growth_Comparison'!C22)),"N/A",'2_Growth_Comparison'!C19*100/'2_Growth_Comparison'!C22),"N/A")</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!D19),ISTEXT('2_Growth_Comparison'!D22)),"N/A",'2_Growth_Comparison'!D19*100/'2_Growth_Comparison'!D22),"N/A")</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!E19),ISTEXT('2_Growth_Comparison'!E22)),"N/A",'2_Growth_Comparison'!E19*100/'2_Growth_Comparison'!E22),"N/A")</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="19">
         <f>IFERROR(IF(OR(ISTEXT('2_Growth_Comparison'!F19),ISTEXT('2_Growth_Comparison'!F22)),"N/A",'2_Growth_Comparison'!F19*100/'2_Growth_Comparison'!F22),"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="17" ht="130" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>SALES PER RUPEE OF ASSET (all five years computed from verified Annual Report data): Adani Power improved from ~0.39x (FY22) to a peak of ~0.65x (FY24), then fell back to ~0.41x (FY26) as its asset base ballooned ahead of revenue from new acquisitions still ramping up. Tata Power is stable in a ~0.37-0.45x band — typical of a regulated, asset-heavy integrated utility. Torrent Power is consistently the MOST asset-efficient of the three (~0.58-0.87x, peaking FY23 when DNH&amp;DD volumes hit a still-small asset base) — its regulated distribution business generates more revenue per rupee of assets than pure thermal generation does. SALES PER EMPLOYEE: comparable across time within Torrent (parent employs most staff) but NOT comparable across companies — Adani and Tata employee counts are standalone-parent only, while their revenue is consolidated (Tata's discoms/TPREL staff sit in subsidiaries). Use the Torrent series as the benchmark and treat Adani/Tata Sales-per-Employee as indicative only, noting the basis in any write-up.</t>
         </is>
@@ -8818,7 +9452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8852,680 +9486,680 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Target / Deal</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Deal Size (₹ cr)</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Impact on Sales/Profit/CFO post-acquisition</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Essar Power MP → Mahan Energen Ltd (1,200 MW, MP)</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>&gt;4,250</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Lifted total operating capacity; management cites new-acquisition depreciation as a near-term drag on PBT, but capacity/EBITDA growth outweighs it. No standalone P&amp;L attribution disclosed publicly.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Feb 2023</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>DB Power (1,200 MW, Chhattisgarh)</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>7,017 (deal signed)</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>LAPSED — long-stop date expired unconsummated</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Negotiated M&amp;A</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>None — deal did not close.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Lanco Amarkantak → Korba Power Ltd (600 MW, Chhattisgarh)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>4,101</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>NCLT-approved, completed</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Contributed to capacity growth to 17,550 MW (Q1 FY26); no standalone P&amp;L split disclosed.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Aug 2024</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Coastal Energen → Moxie Power Generation Ltd (1,200 MW, Tamil Nadu) — 49% JV with DAIT</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>~3,335 (to creditors)</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>NCLT-approved, completed</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP (JV, Adani 49%)</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Adds south-India footprint; equity-accounted as JV, so full revenue not consolidated line-by-line.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Jul 2025</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Vidarbha Industries Power Ltd (600 MW, Nagpur)</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Took total operating capacity to 18,150 MW.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>~Mar 2026</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Jaiprakash Power Ventures Ltd — 24% stake via resolution plan (thermal + hydro assets)</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>~14,535</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>NCLT approved</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP (implementing entity)</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Too recent for post-acquisition P&amp;L data; JP Power stock jumped ~29% in 2 days on the news.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Dec 2025 (bid)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>GVK Energy — Alaknanda hydro (330 MW, Uttarakhand)</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>~3,000-4,000 (bid range)</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Frontrunner reported; completion unconfirmed</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP (bidding)</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Not yet completed as of research date — verify current status.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>2024 (bid)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>KSK Mahanadi Power (1,800 MW, Chhattisgarh)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>~27,000 (bid)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Completion status unconfirmed</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>IBC/CIRP (bidding)</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Verify current status directly.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Mar 2021</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>NESCO → TP Northern Odisha Distribution Ltd (TPNODL) — 51%</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>PPP discom privatization</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Part of a wave of 4 Odisha discom acquisitions (2020-21) that materially grew the T&amp;D segment's customer base (12.6mn customers) and revenue.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>2020-21</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>TP Central/Western/Southern Odisha Distribution Ltds (TPCODL/TPWODL/TPSODL) — 51% each</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>PPP discom privatization</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>See above — combined Odisha discom impact drove T&amp;D revenue growth through FY22-24.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Resurgent Power Ventures — NRSS XXXVI Transmission Ltd &amp; South East UP Power Transmission Co Ltd (transmission SPVs)</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>M&amp;A (transmission assets)</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Expands regulated transmission asset base; no standalone P&amp;L disclosed.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Dorjilung Hydro Power Ltd stake (Bhutan, 1,125 MW project)</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>In development</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>JV/equity stake</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>Development-stage; no revenue contribution yet.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>Ryapte Power (transmission SPV) — Letter of Intent</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>LOI stage</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Too recent — no impact data.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Apr 2022 (LoI Feb 2021)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>51% stake, Dadra &amp; Nagar Haveli and Daman &amp; Diu (DNH&amp;DD) Power Distribution Corp Ltd</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>~555 (bid)</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Completed (after litigation delay)</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>PPP discom privatization</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Distribution electricity-purchase volume +63.2% YoY in FY23 (30,037 MU vs 18,405 MU) — a major driver of the FY23 revenue jump to ₹26,076 cr.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Jul 2022</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Wind Two Renergy — 100% stake</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>~4.1 (US$ mn, i.e. ~₹34 cr)</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>Adds wind capacity; no standalone P&amp;L disclosed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>~2022-23</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Visual Percept Solar Projects (25 MW solar, Gujarat)</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>25-year PPA signed; incremental to solar segment.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Jun 2026 (SPA Feb 2026)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Nabha Power Ltd — 100% (2x700 MW coal, Punjab), from L&amp;T Power Development</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>~3,632-3,661</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Lifts total generation capacity from ~5 GW to ~6.4 GW; stock rose ~39% in Apr 2026 partly on this news (pre-completion announcement effect).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="25" ht="100" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>All three companies have grown primarily through IBC/CIRP-route or PPP-route acquisitions rather than open-market M&amp;A, reflecting the sector's history of stressed/under-construction assets (Adani Power, Tata Power distribution) and government discom-privatization programmes (Tata Power's Odisha discoms, Torrent Power's DNH&amp;DD). Adani Power has been the most acquisitive by deal count and value (five completed + two pending IBC deals since 2022, plus a 24% stake in Jaiprakash Power via a ~₹14,535 cr resolution plan), consistent with its capacity nearly doubling since FY22. None of the three companies publicly disclose acquisition-specific post-deal P&amp;L/cash-flow attribution — this had to be inferred qualitatively from capacity growth and management commentary; a precise before/after contribution analysis would require the acquired entities' standalone financial statements (available via MCA/ROC filings) cross-referenced against the parent's segment note.</t>
         </is>
@@ -9547,7 +10181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9579,226 +10213,226 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Adani Power</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Tata Power</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Torrent Power</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Promoter holding (%)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>74.96% (Promoter &amp; Promoter Group, per FY26 Annual Report shareholding table)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>46.86% total promoter group; Tata Sons Pvt Ltd alone = 45.21% (per FY26 Annual Report)</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>51.09% — Torrent Investments Ltd (formerly Torrent Investments Pvt Ltd), unchanged FY25→FY26 (per FY26 Annual Report)</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>VERIFIED from FY25-26 Annual Reports (uploaded).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Promoter pledge</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>No pledge of promoter shares disclosed in the FY26 Annual Report (only routine subsidiary-loan security pledges by the Company, unrelated to promoter shareholding).</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>'Company has not raised loans during the year on the pledge of securities held in its subsidiaries, joint ventures...' — no promoter share pledge disclosed.</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>No pledge of promoter shares disclosed in the FY26 Annual Report.</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>VERIFIED (nil promoter pledge) from FY25-26 Annual Reports for all three.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>FII / FPI holding (%)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>11.74% (secondary-source snapshot; not separately re-verified in the Annual Report text extract)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>~10.0-10.04% (secondary-source snapshot)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>8.4%-14.2% (conflicting across sources/dates)</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Category-wise FII/DII % not captured from the Annual Report's shareholding table in this pass — cross-check the full SHP table in each PDF if needed.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>DII / Mutual Fund holding (%)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>3.69% (DII, secondary-source snapshot)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>8.64% (DII, one source) vs 18.28% (DII, another) — MFs alone ~8.89-9.63%</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>SBI Mutual Fund confirmed at 8.57% (FY26, up from 7.95% FY25) — VERIFIED from Annual Report top-10-shareholders table.</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>6-month change for SBI MF in Torrent Power (7.95%→8.57%) is now VERIFIED; other DII figures remain secondary-source.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Public / Retail (%)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>9.62% (secondary-source snapshot)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>~21.5-25.6% (free float, incl. FII+DII+public)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>~9.3-17.68% (conflicting by source/date)</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr"/>
+      <c r="E10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Free float (100% - promoter%)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>~25.04%</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>~53.14%</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>~48.91%</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Approx.; = 100% - promoter%.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Named shareholder(s) holding &gt;5%</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>NONE currently &gt;5% besides promoter group — GQG Partners (Goldman Sachs Trust II - Goldman Sachs GQG Partner) now holds only 3.30% as of FY26 (down from ~7.7-8.1% in 2023), per the FY26 Annual Report's top-10-shareholders table. No other non-promoter holder exceeds 5%.</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Life Insurance Corporation of India (LIC) — 5.18% as at 31-Mar-2026 (up from 2.96% at 31-Mar-2025), crossing the 5% threshold during FY26 — VERIFIED from the FY26 Annual Report's 'shareholders holding more than 5%' table.</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Gujarat Urja Vikas Nigam Ltd (GUVNL, Gujarat's state power utility) — 6.95%, unchanged FY25→FY26 — VERIFIED from the FY26 Annual Report's top-10-shareholders table. (Earlier flagged 'Aditya Birla Group ~6.34%' claim was NOT found in the primary source and should be disregarded.)</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>All three figures in this row are now VERIFIED from primary Annual Reports, replacing prior unconfirmed secondary-source claims.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="15" ht="100" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Adani Power has by far the highest promoter concentration (~75%) of the three, leaving the smallest free float (~25%) — typical of Adani Group listed entities, and a legacy of tightened promoter control after the 2023 Hindenburg-report episode (with an emphasis on 'zero pledge' messaging across group companies since). Tata Power's promoter stake (Tata Sons, ~47%) is the lowest of the three, giving it the widest institutional/public float and closest to the SEBI minimum public shareholding norms. Torrent Power sits in between (~51% promoter). Shareholding figures pulled from secondary aggregators showed real inconsistencies across sources/dates for FII/DII splits at all three companies — before using these in the final submission, pull ONE consistent-quarter shareholding-pattern XBRL filing per company directly from BSE/NSE (each company files this quarterly) rather than mixing snapshots from different dates.</t>
         </is>
@@ -9820,7 +10454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9855,502 +10489,502 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>ADANI POWER — 2 segments: 'Power Generation &amp; related activities' + 'Trading, Investment &amp; other activities'</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Particulars</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>FY22</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Segment Revenue — Power Generation</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="11" t="n">
         <v>27221.78</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="11" t="n">
         <v>37895.85</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="11" t="n">
         <v>50014.16</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="11" t="n">
         <v>56107.06</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="11" t="n">
         <v>54240.52</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Segment Revenue — Trading/Investment/Other</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="11" t="n">
         <v>489.4</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="11" t="n">
         <v>877.45</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="11" t="n">
         <v>337.09</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="11" t="n">
         <v>96.03</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Segment Results — Power Generation</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="11" t="n">
         <v>6571.37</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="11" t="n">
         <v>6957.13</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="11" t="n">
         <v>20557.22</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="11" t="n">
         <v>16540.39</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="11" t="n">
         <v>15757.55</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Segment Results — Trading/Investment/Other</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="11" t="n">
         <v>5.76</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="11" t="n">
         <v>717.5700000000001</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="11" t="n">
         <v>234.29</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="11" t="n">
         <v>-1.81</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="11" t="n">
         <v>13.68</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Segment Assets — Power Generation</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="11" t="n">
         <v>81888.09</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="11" t="n">
         <v>84364.22</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="11" t="n">
         <v>91378.85000000001</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="11" t="n">
         <v>111162.48</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="11" t="n">
         <v>139777.31</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Segment Assets — Trading/Investment/Other</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="11" t="n">
         <v>42.02</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="11" t="n">
         <v>1134.26</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="11" t="n">
         <v>203.86</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="11" t="n">
         <v>1328.18</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="11" t="n">
         <v>1354.52</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>FY22-23 results are as restated in the FY23 report after a CODM methodology change. FY26 Trading revenue was nil; segment results shown are pre-tax basis per each year's note.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>TATA POWER — 4 segments: Generation (Thermal &amp; Hydro), Renewables, Transmission &amp; Distribution, Others</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Particulars</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>FY22</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Segment Revenue — Generation/Thermal &amp; Hydro</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="11" t="n">
         <v>11211.03</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="11" t="n">
         <v>18211.35</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="11" t="n">
         <v>19613.61</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="11" t="n">
         <v>19739.07</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="11" t="n">
         <v>11635.93</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Segment Revenue — Renewables</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="11" t="n">
         <v>7748.9</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="11" t="n">
         <v>8196.91</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="11" t="n">
         <v>10175.29</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="11" t="n">
         <v>9876.360000000001</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="11" t="n">
         <v>15027.82</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Segment Revenue — Transmission &amp; Distribution</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="11" t="n">
         <v>27493.17</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="11" t="n">
         <v>34529.36</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="11" t="n">
         <v>36205.82</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="11" t="n">
         <v>39120.52</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="11" t="n">
         <v>41338.59</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Segment Revenue — Others</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="11" t="n">
         <v>317.8</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="11" t="n">
         <v>413.56</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="11" t="n">
         <v>430.62</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="11" t="n">
         <v>431.04</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="11" t="n">
         <v>431.79</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Segment Results — Generation/Thermal &amp; Hydro</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="11" t="n">
         <v>2632.75</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="11" t="n">
         <v>5092.16</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="11" t="n">
         <v>2569.61</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="11" t="n">
         <v>2878.91</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="11" t="n">
         <v>1137.94</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Segment Results — Renewables</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="11" t="n">
         <v>1923.57</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="11" t="n">
         <v>1932.01</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="11" t="n">
         <v>2147.1</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="11" t="n">
         <v>2880.68</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="11" t="n">
         <v>4340.93</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Segment Results — Transmission &amp; Distribution</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="11" t="n">
         <v>2138.49</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="11" t="n">
         <v>2197.68</v>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="11" t="n">
         <v>2418.22</v>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="11" t="n">
         <v>3128.27</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="11" t="n">
         <v>4307.95</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Segment Results — Others</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="11" t="n">
         <v>-286.03</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="11" t="n">
         <v>-308.17</v>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="11" t="n">
         <v>105.38</v>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="11" t="n">
         <v>112.8</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="11" t="n">
         <v>104.72</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Segment Assets — Generation/Thermal &amp; Hydro</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="11" t="n">
         <v>38201.93</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="11" t="n">
         <v>41201.04</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="11" t="n">
         <v>39315.88</v>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="11" t="n">
         <v>39708.11</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="11" t="n">
         <v>41697.31</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Segment Assets — Renewables</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="11" t="n">
         <v>27589.28</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="11" t="n">
         <v>29744.49</v>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="11" t="n">
         <v>40459.25</v>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="11" t="n">
         <v>51355.61</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="11" t="n">
         <v>56921.28</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Segment Assets — Transmission &amp; Distribution</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="11" t="n">
         <v>32411.34</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="11" t="n">
         <v>37477.26</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="11" t="n">
         <v>42059.9</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="11" t="n">
         <v>45707.75</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="11" t="n">
         <v>53428.87</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Segment Assets — Others + Unallocable</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="11" t="n">
         <v>14682.04</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="11" t="n">
         <v>19926.25</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="11" t="n">
         <v>17718.46</v>
       </c>
-      <c r="E28" s="19" t="n">
+      <c r="E28" s="11" t="n">
         <v>19939.82</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="11" t="n">
         <v>23124.32</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Revenue shown gross (before inter-segment eliminations of ~₹4,000-5,400cr/yr, mostly Generation→T&amp;D coal/power sales). 'Generation' was renamed 'Thermal &amp; Hydro' from the FY25 report. FY23 Generation result of ₹5,092cr was later restated in the FY24 report to ₹1,528cr segment result + ₹3,564cr exceptional; the as-originally-reported figure is shown here. FY26 Thermal &amp; Hydro result derived as total-minus-other-segments (₹9,891.54cr total). FY26 revenue drop in Thermal &amp; Hydro reflects the Mundra shutdown; Renewables surged on new capacity.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>TORRENT POWER — NO reportable segments under Ind AS 108</t>
         </is>
       </c>
     </row>
     <row r="32" ht="95" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Per Note 53/54 ('Operating Segments') of Torrent Power's FY23 Annual Report (and equivalent notes in other years): "the Group does not have any reportable segment as per Ind AS-108 'Operating Segments'" — the CODM manages Generation, Transmission and Distribution as ONE integrated electricity business, and the cable business is immaterial (below reportable thresholds for revenue, profit and assets). This is an important verified correction: earlier drafts of this sheet assumed 3 reportable segments (Generation/Transmission/Distribution) from the MD&amp;A's business description — the MD&amp;A discusses those businesses operationally, but the statutory segment note reports a single segment. Any segment-level financial comparison for Torrent must therefore rely on MD&amp;A operating metrics (e.g., FY23 distribution electricity purchases +63.2% YoY to 30,037 MU after the DNH&amp;DD takeover), not audited segment P&amp;L data, because none is published.</t>
         </is>
@@ -10361,14 +10995,14 @@
     <row r="35"/>
     <row r="36"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Comparative analysis — who is doing well in which segment?</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>GENERATION is the only segment where all three effectively compete, and the verified numbers show a stark contrast: Adani Power's generation segment grew revenue ~2.0x (₹27,222cr FY22 → ₹54,241cr FY26) with segment results of ₹15,758-20,557cr in FY24-26 — vastly more profitable than Tata Power's generation segment (results of only ₹1,138-2,879cr on ₹11,636-19,739cr revenue in the same years, dragged by the Mundra plant's fuel economics and eventual shutdown). Adani is unambiguously the generation winner. RENEWABLES: only Tata Power reports it separately, and it is now their growth engine — revenue up ~1.9x (₹7,749cr FY22 → ₹15,028cr FY26), results up 2.3x (₹1,924cr → ₹4,341cr), and segment assets up 2.1x to ₹56,921cr, overtaking every other Tata segment. Adani Power has no renewables segment (that sits in sister company Adani Green). TRANSMISSION &amp; DISTRIBUTION: Tata Power's largest and steadiest segment — revenue grew ₹27,493cr → ₹41,339cr (FY22→FY26, boosted by the Odisha discoms) with consistently positive, regulated-return results (₹2,138cr → ₹4,308cr). Torrent's distribution business is economically similar (regulated, stable) but not separately reported. INDUSTRY CONTEXT: India's power demand grew ~7-8%/yr (CEA) over this period — Adani's generation growth (~13% CAGR) and Tata's renewables growth (~21% CAGR) both outpaced the sector, largely through acquisitions and capacity build-out respectively, while Tata's generation segment underperformed the sector.</t>
         </is>
@@ -10394,140 +11028,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Tata Generation Rev</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tata Renewables Rev</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Tata T&amp;D Rev</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Adani Generation Rev</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>FY22</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>11211.03</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7748.9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27493.17</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27221.78</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FY23</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>18211.35</v>
-      </c>
-      <c r="C3" t="n">
-        <v>8196.91</v>
-      </c>
-      <c r="D3" t="n">
-        <v>34529.36</v>
-      </c>
-      <c r="E3" t="n">
-        <v>37895.85</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>19613.61</v>
-      </c>
-      <c r="C4" t="n">
-        <v>10175.29</v>
-      </c>
-      <c r="D4" t="n">
-        <v>36205.82</v>
-      </c>
-      <c r="E4" t="n">
-        <v>50014.16</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>19739.07</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9876.360000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>39120.52</v>
-      </c>
-      <c r="E5" t="n">
-        <v>56107.06</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>11635.93</v>
-      </c>
-      <c r="C6" t="n">
-        <v>15027.82</v>
-      </c>
-      <c r="D6" t="n">
-        <v>41338.59</v>
-      </c>
-      <c r="E6" t="n">
-        <v>54240.52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -37,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +103,11 @@
       <b val="1"/>
       <color rgb="00008000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -148,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +187,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3071,12 +3077,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>VERIFIED from FY23 consolidated Investments notes: NON-CURRENT — quoted investments (incl. Government of India bonds held as the GERC Multi-Year-Tariff-mandated 'contingency reserve' for its Gujarat distribution licences) of ~₹15.94cr market value ₹15.70cr as at 31-Mar-2023 (down from ₹132.82cr FY22 as bonds matured/were reclassified). CURRENT — ₹682.31cr total (vs ₹253.27cr FY22): unquoted mutual funds ₹656.03cr + statutory contingency-reserve investments ₹1.93cr + other ₹24.35cr. The GoI-bond holdings are regulatory-mandated (usable only for GERC-specified purposes), not discretionary treasury.</t>
+          <t>VERIFIED from Note 10 (Other Investments) and Note 16 (Current Investments) of the CONSOLIDATED Financial Statements, FY23 Annual Report ('Notes forming part of the consolidated financial statements for the year ended March 31, 2023'): NON-CURRENT — ₹15.94cr as at 31-Mar-2023 (down from ₹132.82cr FY22), comprising Government of India bonds ₹15.89cr (the GERC Multi-Year-Tariff-mandated 'contingency reserve' for its Gujarat distribution licences) + ₹0.05cr equity in UNM Foundation. CURRENT — ₹787.75cr total (vs ₹273.70cr FY22): unquoted mutual funds ₹785.82cr + statutory contingency-reserve investments ₹1.93cr. CORRECTION: an earlier pass of this sheet had pulled the STANDALONE (parent-only) figures for current investments (₹682.31cr) by mistake — the consolidated figure is ₹787.75cr, ~₹105cr higher because subsidiaries hold additional mutual fund investments. Non-current figure is unchanged (identical at both levels). The GoI-bond holdings are regulatory-mandated (usable only for GERC-specified purposes), not discretionary treasury.</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>VERIFIED (FY23 Annual Report)</t>
+          <t>VERIFIED CONSOLIDATED (FY23 Annual Report) — corrected from standalone</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7503,168 +7509,192 @@
     <row r="10"/>
     <row r="11"/>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Priority list — verify these before submission</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Consolidated-vs-Standalone audit (line-by-line re-verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="190" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>1. Year-end (31-Mar) share prices, FY22-FY26, all three companies — still not filled; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>2. Total Assets — DONE: fully VERIFIED FY22-FY26 for all three companies from the Annual Reports.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>3. Employee headcount — standalone-parent counts VERIFIED where disclosed (Adani FY23/25/26 — FY22/FY24 not disclosed in available reports; Tata FY22/23/25/26; Torrent FY22-FY26). Group-wide/consolidated headcount is not disclosed anywhere and would be needed for a true cross-company Sales/Employee comparison.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>4. Segment-wise (Ind AS 108) tables — DONE: Sheet 6 carries verified segment revenue/results/assets for Adani Power and Tata Power (FY22-FY26), plus the verified finding that Torrent Power reports NO segments under Ind AS 108 (single integrated business).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>5. Weekly price series — DONE: 54-week adjusted-close series for all 3 stocks + Nifty 50 + Nifty Energy parsed from Yahoo HTML files in the repo; returns, volatility, and market &amp; sector betas computed in Sheet 11. Still open: year-end FY22-FY26 share prices for the Sheet 2 growth table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>6. Shareholding pattern — Promoter %, promoter pledge (nil, all 3), and the single largest non-promoter &gt;5% holder are now VERIFIED as at 31-Mar-2026 from the Annual Reports for all three companies (Sheet 5). FII/DII category-level % breakdowns are still secondary-source/unverified — pull the full SHP table from each PDF or BSE/NSE XBRL filing if needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>7. Subsidiary lists — DONE: Sheets 7-8 now carry the verified FY26 AOC-1 data (Adani 19 entities incl. Mahan at 94% and Moxie consolidated at 49%; Tata ~113 entities incl. TPREL at 88.57%; Torrent ~60 entities). Only Torrent's associates (Part B) remain unextracted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>8. Investments (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — DONE: Sheet 9 now carries verified figures from all three FY23 Annual Reports (Adani ₹42.51cr non-current + ₹611.54cr MFs; Tata ₹1,301.21cr; Torrent ₹15.94cr bonds + ₹682.31cr current).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>9. Promoter pledge status — now VERIFIED as NIL for all three companies as at FY26 (Sheet 5), from the Annual Reports.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>10. Exact announcement dates + daily price reaction for Adani Power's major events (Sheet 12) — cross-check against BSE corporate announcements page.</t>
-        </is>
-      </c>
-    </row>
+          <t>Every Revenue/Total Income, PAT and Total Assets figure in Sheet 2 (all 3 companies, FY22-FY26) and every Segment Revenue/Results/Assets figure in Sheet 6 was individually re-traced to its source PDF and confirmed to sit under an explicit 'Consolidated Balance Sheet' / 'Consolidated Statement of Profit and Loss' / 'Notes to (the) Consolidated Financial Statements' heading (not standalone) — verified via direct text search for these headings immediately preceding each figure in the extracted PDF text. ONE ERROR WAS FOUND AND FIXED in this pass: Sheet 9's Torrent Power current-investments figure had been pulled from the STANDALONE balance sheet notes (₹682.31cr) instead of the consolidated notes (₹787.75cr, ~₹105cr higher due to subsidiary-level mutual fund holdings) — this has been corrected. Adani Power and Tata Power's Sheet 9 figures were already confirmed consolidated. Two categories of data are DELIBERATELY standalone/parent-only, clearly labelled as such, and this is unavoidable (none of the three companies discloses these on a consolidated/group-wide basis anywhere in their Annual Reports): (1) Employee headcount rows in Sheet 2/3 — sourced from each company's Rule 5(1)/BRSR 'permanent employees on the rolls of the Company' disclosure, which is a standalone-entity statutory disclosure by definition; (2) Shareholding pattern in Sheet 5 — shareholding is inherently reported at the standalone listed-entity level for all Indian companies (there is no such thing as a 'consolidated' shareholding pattern). Sheets 4 (Acquisitions), 5 (Shareholding %s beyond promoter/pledge/named holders), 10 (Financing/credit-rating narrative) and 11-12 (share price/announcements) draw on recognized secondary sources (CRISIL/ICRA rating rationales, exchange filings summarized by Business Standard/BusinessToday, Yahoo Finance historical price data) rather than the Annual Report PDFs themselves, since this information (deal narratives, credit actions, daily prices) is not disclosed inside the audited financial statements — these are flagged inline where not yet independently cross-verified against a primary filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
+          <t>Priority list — verify these before submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>1. Year-end (31-Mar) share prices, FY22-FY26, all three companies — still not filled; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>2. Total Assets — DONE: fully VERIFIED FY22-FY26 for all three companies from the Annual Reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>3. Employee headcount — standalone-parent counts VERIFIED where disclosed (Adani FY23/25/26 — FY22/FY24 not disclosed in available reports; Tata FY22/23/25/26; Torrent FY22-FY26). Group-wide/consolidated headcount is not disclosed anywhere and would be needed for a true cross-company Sales/Employee comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>4. Segment-wise (Ind AS 108) tables — DONE: Sheet 6 carries verified segment revenue/results/assets for Adani Power and Tata Power (FY22-FY26), plus the verified finding that Torrent Power reports NO segments under Ind AS 108 (single integrated business).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>5. Weekly price series — DONE: 54-week adjusted-close series for all 3 stocks + Nifty 50 + Nifty Energy parsed from Yahoo HTML files in the repo; returns, volatility, and market &amp; sector betas computed in Sheet 11. Still open: year-end FY22-FY26 share prices for the Sheet 2 growth table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>6. Shareholding pattern — Promoter %, promoter pledge (nil, all 3), and the single largest non-promoter &gt;5% holder are now VERIFIED as at 31-Mar-2026 from the Annual Reports for all three companies (Sheet 5). FII/DII category-level % breakdowns are still secondary-source/unverified — pull the full SHP table from each PDF or BSE/NSE XBRL filing if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>7. Subsidiary lists — DONE: Sheets 7-8 now carry the verified FY26 AOC-1 data (Adani 19 entities incl. Mahan at 94% and Moxie consolidated at 49%; Tata ~113 entities incl. TPREL at 88.57%; Torrent ~60 entities). Only Torrent's associates (Part B) remain unextracted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>8. Investments (ex subsidiaries/associates/JVs) as at 31-Mar-2023 — DONE: Sheet 9 now carries verified figures from all three FY23 Annual Reports (Adani ₹42.51cr non-current + ₹611.54cr MFs; Tata ₹1,301.21cr; Torrent ₹15.94cr bonds + ₹682.31cr current).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>9. Promoter pledge status — now VERIFIED as NIL for all three companies as at FY26 (Sheet 5), from the Annual Reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>10. Exact announcement dates + daily price reaction for Adani Power's major events (Sheet 12) — cross-check against BSE corporate announcements page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
           <t>Key sources cited across this workbook (non-exhaustive)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Business Standard (business-standard.com) — quarterly results coverage, all 3 companies</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>BusinessToday (businesstoday.in) — results, stock-move coverage</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Equitymaster (equitymaster.com) — annual report analyses (Torrent Power, Tata Power)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>CRISIL Ratings (crisil.com) — rating rationales for all 3 companies</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Trendlyne, ScanX, HDFC Sky, Kotak Neo, ICICI Direct, Groww — shareholding, price, beta/volatility snapshots</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Mercom India, Saurenergy, PV Magazine India — renewable/PPA/project news</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>NSE India, BSE India (nseindia.com, bseindia.com) — REFERENCED but not directly fetchable in this session; primary source for final verification</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>screener.in, moneycontrol.com — REFERENCED but not directly fetchable in this session; primary source for financial-statement data</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A6:B11"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A14:B23"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -26,6 +26,12 @@
     <sheet name="12_Major_Announcements" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="12b_Announcement_Chart_Data" sheetId="18" state="hidden" r:id="rId18"/>
     <sheet name="13_Sources_and_Gaps" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Adani_BS_Consolidated" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Adani_PL_Consolidated" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Tata_BS_Consolidated" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Tata_PL_Consolidated" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Torrent_BS_Consolidated" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Torrent_PL_Consolidated" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +43,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +114,18 @@
       <color rgb="00008000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +140,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +209,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1846,7 +1880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D33"/>
+  <dimension ref="B2:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2082,27 @@
     <row r="31"/>
     <row r="32"/>
     <row r="33"/>
+    <row r="35">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Detailed per-company Consolidated Financial Statements (6 sheets):</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Adani_BS_Consolidated, Adani_PL_Consolidated, Tata_BS_Consolidated, Tata_PL_Consolidated, Torrent_BS_Consolidated, Torrent_PL_Consolidated</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>(replaces earlier draft sheets that mixed in mislabeled standalone Adani Power data)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B26:D33"/>
@@ -8190,6 +8245,3809 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ADANI POWER LIMITED — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Source: Adani Power Ltd FY2022-23 Integrated Annual Report, 'Consolidated Balance Sheet as at 31st March, 2023' (repo file: AR_22088_ADANIPOWER_2022_2023). NOTE: an earlier draft sheet in this workbook ('Sheet5') showed Adani Power's STANDALONE balance sheet mislabeled — this sheet replaces it with the genuine consolidated figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>As at 31-Mar-2023</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>As at 31-Mar-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>ASSETS</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Property, Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>50543.8</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>53071.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Capital Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>12879.54</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>10269.74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Investment Property</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>704.9400000000001</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>190.61</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>190.61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Non-current)</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Non-current)</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>779.71</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>856.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>1115.13</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>1352.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>66268.27</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>65752.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>3075.2</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>2258.27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Current)</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>611.54</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>183.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Trade Receivables</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>11529.36</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>9560.92</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Cash and Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>349.23</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>782.37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Bank Balances other than above</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>1524.42</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>1582.31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Loans (Current)</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Current)</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>557.5</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>308.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>1902.56</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <v>1545.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n">
+        <v>19553</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <v>16228.07</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n">
+        <v>85821.27</v>
+      </c>
+      <c r="C26" s="31" t="n">
+        <v>81981.02</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Unsecured Perpetual Securities</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n">
+        <v>13215</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Other Equity</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n">
+        <v>12803.72</v>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>1631.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Equity attributable to equity holders of the parent</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>29875.66</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>18703.44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>Non-Controlling Interests</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="n">
+        <v>29875.66</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>18703.44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Non-current)</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>33702.6</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>37871.32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>94.36</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>960.37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Non-current)</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="n">
+        <v>226.95</v>
+      </c>
+      <c r="C38" s="30" t="n">
+        <v>220.87</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <v>2499.78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>4183.15</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>4487.21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>38201.02</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>46133.91</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Current)</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>8549.450000000001</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>10924.36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="C44" s="30" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables — micro/small enterprises</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="C45" s="30" t="n">
+        <v>57.59</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables — other creditors</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>2983.69</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>3450.62</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>2461.58</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>1167.32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n">
+        <v>3622.82</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>861.36</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Current)</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>28.71</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>645.3200000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n">
+        <v>17744.59</v>
+      </c>
+      <c r="C51" s="31" t="n">
+        <v>17143.67</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="n">
+        <v>55945.61</v>
+      </c>
+      <c r="C52" s="31" t="n">
+        <v>63277.58</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="n">
+        <v>85821.27</v>
+      </c>
+      <c r="C53" s="31" t="n">
+        <v>81981.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ADANI POWER LIMITED — Consolidated Statement of Profit and Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Source: Adani Power Ltd FY2022-23 Integrated Annual Report, 'Consolidated Statement of Profit and Loss for the year ended 31st March, 2023' (repo file: AR_22088_ADANIPOWER_2022_2023). NOTE: replaces an earlier draft sheet ('Consolidated Profit and loss st...') that was mislabeled and actually contained Adani Power's STANDALONE figures (PAT ₹10,246.15cr FY23) — the genuine consolidated PAT is ₹10,726.64cr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Year ended 31-Mar-2023</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Year ended 31-Mar-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Revenue from Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>38773.3</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>27711.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>4267.22</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>3975.29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n">
+        <v>43040.52</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>31686.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Fuel Cost</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>25480.85</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>14762.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Purchase of Stock-in-trade / Power for resale</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>214.14</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>545.5599999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Transmission Charges</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>519.61</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>642.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Employee Benefits Expense</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>569.99</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>470.31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Finance Costs (net)</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>3333.5</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>4094.78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Depreciation and Amortisation Expense</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>3303.68</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>3117.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>1944.05</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>1476.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>35365.82</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>25109.34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Profit before tax and deferred tax (adj.)/recoverable from future tariff</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>7674.7</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>6577.13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>768.34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Tax credit adjusted relating to earlier years</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>-768.1799999999999</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax (credit)/charge (incl. earlier-year adj.)</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>-2499.77</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>976.5700000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Total Tax (Credit)/Expense</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n">
+        <v>-3267.37</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>1744.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Add: Deferred tax (adj.)/recoverable from future tariff (net of tax)</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>-215.43</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>79.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT)</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="n">
+        <v>10726.64</v>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>4911.58</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income, net of tax</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>43.63</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Total Comprehensive Income for the Year</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n">
+        <v>10760.38</v>
+      </c>
+      <c r="C26" s="31" t="n">
+        <v>4955.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>THE TATA POWER COMPANY LIMITED — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Sources: Tata Power Integrated Annual Reports FY21-22 (AR_20052), FY23-24 (AR_24164) and FY25-26 (AR_29380) — 'Consolidated Balance Sheet' as at each year-end. Fills the FY24/FY25 gaps left blank in the team's original 'Tata Power' draft sheet; FY22/23/26 figures cross-checked and match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2024</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2023</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>ASSETS</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Property, Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>78870.53999999999</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>70261.38</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>59624.06</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>54524.96</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>50502.96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Right of Use Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>5525.44</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>5089.89</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>4368.75</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>3982.05</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>3661.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Capital Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>14595.13</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>12678.87</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>11561.31</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>5376.36</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>4635.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>1651.46</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>1651.46</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>1757.46</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>1858.31</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>1858.31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>1245.25</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>1371.7</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>1459.29</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>1381.34</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>1366.18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Investments accounted for using Equity Method</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>13549.05</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>12894.22</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>12983.51</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>14218.88</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>12580</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Other Investments (Non-current)</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>1669.37</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>2119.75</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>1854.59</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>1301.21</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>1169.81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Trade Receivables (Non-current)</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>1599.35</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>1223.02</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>273.29</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>359.63</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>685.78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Loans (Non-current)</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Finance Lease Receivables (Non-current)</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>837.84</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>526.98</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>561.66</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>567.22</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>588.6900000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Non-current)</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>3522.62</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>2168.98</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>2084.5</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>1726.66</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>1684.53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Non-current Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>960.96</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>745.78</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>585.89</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>739.0700000000001</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>520.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>607.54</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>517.99</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>499.09</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>334.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>10635.84</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>8393.799999999999</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>5173.57</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>2532.46</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>1849.82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>135307.53</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>119645.82</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>102789.45</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>88824.03999999999</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>81441.75999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>5107.64</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>4571.82</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>4419.63</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>3942.88</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>4231.52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Current)</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>1356.12</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <v>1302.42</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>1477.89</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>1149.6</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>410.52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Trade Receivables (Current)</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="n">
+        <v>4423.96</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>5709.78</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>7401.69</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>6952.15</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>5979.74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Unbilled Revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="n">
+        <v>2842.63</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>2737.06</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>2552.23</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>2456.71</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>2285.57</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Cash and Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="n">
+        <v>4409.67</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>4862.47</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>3324.34</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>4189.76</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>3077.24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Bank Balances other than above</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>9234.33</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>6888.51</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>5827.57</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>7016.77</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <v>3563.46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Loans (Current)</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="F29" s="30" t="n">
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Finance Lease Receivables (Current)</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>74.47</v>
+      </c>
+      <c r="D30" s="30" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F30" s="30" t="n">
+        <v>46.91</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Current)</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>1316.67</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>656.48</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>471.48</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>688.3</v>
+      </c>
+      <c r="F31" s="30" t="n">
+        <v>501.45</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>1773.58</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>1941.3</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>1704.3</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>1328.72</v>
+      </c>
+      <c r="F33" s="30" t="n">
+        <v>1479.67</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="n">
+        <v>30571.05</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>28756.65</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>27264.39</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>27791.63</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>21585.43</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Assets Classified as Held For Sale</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>1153.75</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>1145.21</v>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>1200.99</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>3299.94</v>
+      </c>
+      <c r="F35" s="30" t="n">
+        <v>3046.83</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Total Assets before Regulatory Deferral Account</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n">
+        <v>167032.33</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <v>149547.68</v>
+      </c>
+      <c r="D36" s="31" t="n">
+        <v>131254.83</v>
+      </c>
+      <c r="E36" s="31" t="n">
+        <v>119915.61</v>
+      </c>
+      <c r="F36" s="31" t="n">
+        <v>106074.02</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Regulatory Deferral Account — Assets</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>8139.45</v>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>7163.61</v>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>8298.66</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>8433.43</v>
+      </c>
+      <c r="F37" s="30" t="n">
+        <v>6810.57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="n">
+        <v>175171.78</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>156711.29</v>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>139553.49</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>128349.04</v>
+      </c>
+      <c r="F38" s="31" t="n">
+        <v>112884.59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="F40" s="30" t="n">
+        <v>319.56</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>Other Equity</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="n">
+        <v>39147.65</v>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>35521.11</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>32035.73</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>28467.87</v>
+      </c>
+      <c r="F41" s="30" t="n">
+        <v>22122</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>Equity attributable to Shareholders of Parent</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>39467.21</v>
+      </c>
+      <c r="C42" s="30" t="n">
+        <v>35840.67</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>32355.29</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>28787.43</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>22441.56</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>Non-controlling Interests</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>8070.86</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>6765.37</v>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>5977.48</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>5416.69</v>
+      </c>
+      <c r="F43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>47538.07</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>42606.04</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>38332.77</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>34204.12</v>
+      </c>
+      <c r="F44" s="32" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Non-current)</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>61608.57</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>44129.72</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>37392.25</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>30708.49</v>
+      </c>
+      <c r="F46" s="11" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>4549.94</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>4196.21</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>3742.48</v>
+      </c>
+      <c r="E47" s="30" t="n">
+        <v>3510.7</v>
+      </c>
+      <c r="F47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n">
+        <v>694.64</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>674.12</v>
+      </c>
+      <c r="D48" s="30" t="n">
+        <v>1507.55</v>
+      </c>
+      <c r="E48" s="30" t="n">
+        <v>1410.4</v>
+      </c>
+      <c r="F48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Non-current)</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>3213.85</v>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>2548.69</v>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>1865.08</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>1420.02</v>
+      </c>
+      <c r="F49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="n">
+        <v>4807.88</v>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>4104.12</v>
+      </c>
+      <c r="D50" s="30" t="n">
+        <v>2772.33</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>1919.37</v>
+      </c>
+      <c r="F50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>13411.97</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <v>12930.57</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>11973.08</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>9847.82</v>
+      </c>
+      <c r="F51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="n">
+        <v>88286.85000000001</v>
+      </c>
+      <c r="C52" s="31" t="n">
+        <v>68583.42999999999</v>
+      </c>
+      <c r="D52" s="31" t="n">
+        <v>59252.77</v>
+      </c>
+      <c r="E52" s="31" t="n">
+        <v>48816.8</v>
+      </c>
+      <c r="F52" s="32" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Current)</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="n">
+        <v>9513.82</v>
+      </c>
+      <c r="C54" s="30" t="n">
+        <v>14015.84</v>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>12087.56</v>
+      </c>
+      <c r="E54" s="30" t="n">
+        <v>18265.94</v>
+      </c>
+      <c r="F54" s="11" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>468.94</v>
+      </c>
+      <c r="C55" s="30" t="n">
+        <v>524.03</v>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>467.16</v>
+      </c>
+      <c r="E55" s="30" t="n">
+        <v>437.87</v>
+      </c>
+      <c r="F55" s="11" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables — micro/small enterprises</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="n">
+        <v>809.84</v>
+      </c>
+      <c r="C56" s="30" t="n">
+        <v>784.21</v>
+      </c>
+      <c r="D56" s="30" t="n">
+        <v>870</v>
+      </c>
+      <c r="E56" s="30" t="n">
+        <v>537.6</v>
+      </c>
+      <c r="F56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables — other creditors</t>
+        </is>
+      </c>
+      <c r="B57" s="30" t="n">
+        <v>6328.39</v>
+      </c>
+      <c r="C57" s="30" t="n">
+        <v>8070.34</v>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>8451.370000000001</v>
+      </c>
+      <c r="E57" s="30" t="n">
+        <v>6869.6</v>
+      </c>
+      <c r="F57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="n">
+        <v>13897.6</v>
+      </c>
+      <c r="C58" s="30" t="n">
+        <v>12427.03</v>
+      </c>
+      <c r="D58" s="30" t="n">
+        <v>14796.16</v>
+      </c>
+      <c r="E58" s="30" t="n">
+        <v>13150.77</v>
+      </c>
+      <c r="F58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Current)</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>680.4400000000001</v>
+      </c>
+      <c r="C59" s="30" t="n">
+        <v>437.56</v>
+      </c>
+      <c r="D59" s="30" t="n">
+        <v>294.34</v>
+      </c>
+      <c r="E59" s="30" t="n">
+        <v>311.07</v>
+      </c>
+      <c r="F59" s="11" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>185.42</v>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="D60" s="30" t="n">
+        <v>291.54</v>
+      </c>
+      <c r="E60" s="30" t="n">
+        <v>217.96</v>
+      </c>
+      <c r="F60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="n">
+        <v>3691.15</v>
+      </c>
+      <c r="C61" s="30" t="n">
+        <v>3672.38</v>
+      </c>
+      <c r="D61" s="30" t="n">
+        <v>3879.84</v>
+      </c>
+      <c r="E61" s="30" t="n">
+        <v>4188.41</v>
+      </c>
+      <c r="F61" s="11" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="n">
+        <v>39223.57</v>
+      </c>
+      <c r="C62" s="31" t="n">
+        <v>45269.52</v>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>41137.97</v>
+      </c>
+      <c r="E62" s="31" t="n">
+        <v>43979.22</v>
+      </c>
+      <c r="F62" s="32" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Liabilities re: Assets Held For Sale</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="n">
+        <v>114.24</v>
+      </c>
+      <c r="C63" s="30" t="n">
+        <v>113.56</v>
+      </c>
+      <c r="D63" s="30" t="n">
+        <v>113.56</v>
+      </c>
+      <c r="E63" s="30" t="n">
+        <v>113.56</v>
+      </c>
+      <c r="F63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>Regulatory Deferral Account — Liability</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="C64" s="30" t="n">
+        <v>138.74</v>
+      </c>
+      <c r="D64" s="30" t="n">
+        <v>716.42</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>1235.34</v>
+      </c>
+      <c r="F64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B65" s="31" t="n">
+        <v>175171.78</v>
+      </c>
+      <c r="C65" s="31" t="n">
+        <v>156711.29</v>
+      </c>
+      <c r="D65" s="31" t="n">
+        <v>139553.49</v>
+      </c>
+      <c r="E65" s="31" t="n">
+        <v>128349.04</v>
+      </c>
+      <c r="F65" s="31" t="n">
+        <v>112884.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>THE TATA POWER COMPANY LIMITED — Consolidated Statement of Profit and Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Sources: Tata Power Integrated Annual Reports FY21-22, FY23-24 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. Extends the team's original sheet (which only had FY22/23) to the full FY22-FY26 window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2025-26</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2024-25</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2023-24</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2022-23</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2021-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Revenue from Operations</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>62428.59</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>65478.24</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>61448.9</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>55109.08</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>42815.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>1743.07</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>1513.93</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>1823.42</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>1438.02</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>919.96</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>64171.66</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>66992.17</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>63272.32</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>56547.1</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>43735.63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Cost of Power Purchased</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>19647.25</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>20523.61</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>20014.46</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>19062.67</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>14640.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Cost of Fuel</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>7498.39</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>13918.47</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>14130.47</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>13763.59</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>8290.92</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Transmission Charges</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>1467.98</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>1277.81</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>1168.69</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>1194.95</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>1018.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Raw Material Consumed / Construction Cost</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>8618.4</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>4921.46</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>5439.86</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>3882.3</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>3832.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Purchase of Finished Goods and Spares</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>49.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>(Increase)/Decrease in Stock-in-Trade &amp; WIP</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>-84.11</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>-440.76</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>-51.78</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>-199.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Employee Benefits Expense</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>4693.73</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>4372.92</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>4036.09</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>3624.26</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>3611.63</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Finance Costs</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>5256.79</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>4702.44</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>4633.22</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>4371.65</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>3859.02</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Depreciation and Amortisation Expense</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>4811.09</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>4116.86</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>3786.37</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>3439.2</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>3122.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>7449.54</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>6943.02</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>5887.39</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>5775.31</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>4060.42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>59401.41</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>60367.67</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>59084.66</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>55213.61</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>42285.72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Profit before Regulatory Deferral, Exceptional Items &amp; Assoc./JV share</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>4770.25</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>6624.5</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>4187.66</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>1333.49</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>1449.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Net Movement in Regulatory Deferral Balances (incl. earlier years, net tax)</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>1252.04</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>-976.16</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>93.43000000000001</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>924.05</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>-239.47</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Profit Before Exceptional Items, Tax &amp; Assoc./JV Share</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n">
+        <v>6022.29</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>5648.34</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>4281.09</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>2257.54</v>
+      </c>
+      <c r="F22" s="31" t="n">
+        <v>1210.44</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Share of Net Profit of Associates and JVs (Equity Method)</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>707.87</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>793.33</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>1177.57</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>3199.46</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>1942.83</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Profit Before Exceptional Items and Tax</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="n">
+        <v>6730.16</v>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>6441.67</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>5458.66</v>
+      </c>
+      <c r="E24" s="31" t="n">
+        <v>5457</v>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>3153.27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Exceptional Items (net)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="30" t="n">
+        <v>273.36</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>-150.27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Profit Before Tax</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>5732.02</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>5457</v>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Total Tax Expense/(Credit)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="30" t="n">
+        <v>1451.92</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>1647.33</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>379.56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT, consolidated)</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="n">
+        <v>5117.56</v>
+      </c>
+      <c r="C28" s="31" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>4280.1</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>3809.67</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>2623.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TORRENT POWER LIMITED — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Sources: Torrent Power Integrated Annual Reports FY21-22 (AR_20392) through FY25-26 (AR_29704) — 'Consolidated Balance Sheet' as at each year-end. Fills the FY22/FY21 gap left blank in the team's original 'Consolidated Balance Sheet Summ[ary]' sheet; FY23-26 figures cross-checked and match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2024</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2023</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2022</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Property, Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="30" t="n">
+        <v>16759.39</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>17129.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="30" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>178.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Capital Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>6961.53</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>2249.81</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>2472.36</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>2624.69</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>1297.27</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>837.73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-Current Assets (incl. intangibles/investments/loans)</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>4791.5</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>2675.23</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>1760.08</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>874.3099999999999</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>1525.68</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>748.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>35953.86</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>27953.33</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>24886.12</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>21894</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>19796.94</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>18894.31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>9239.42</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>8620.049999999999</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>8506.360000000001</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>8016.18</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>5225.76</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <v>4644.41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n">
+        <v>45193.28</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>36573.38</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>33392.48</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>29910.18</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>25022.7</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>23538.72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>EQUITY &amp; LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>503.9</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>503.9</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>480.62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Other Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>18571.43</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>17111.41</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>11581.09</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>10529</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>9462.559999999999</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>9703.620000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Net Worth (Attributable to Owners)</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>19075.33</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>17615.31</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>12061.71</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>11009.62</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>9943.18</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>10184.24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Non-Controlling Interests</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>633.42</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>600.47</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>535.79</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>446.33</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>36.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n">
+        <v>19708.75</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>18215.78</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>12597.5</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>11455.95</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>9979.110000000001</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <v>10220.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Non-current Liabilities (Borrowings, provisions, deferred tax etc.)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="30" t="n">
+        <v>8895.92</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>8508.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Current Liabilities (Borrowings, trade payables etc.)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="30" t="n">
+        <v>6147.67</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>4809.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>45193.28</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>36573.38</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>33392.48</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>29910.18</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>25022.7</v>
+      </c>
+      <c r="G21" s="31" t="n">
+        <v>23538.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TORRENT POWER LIMITED — Consolidated Statement of Profit and Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Sources: Torrent Power Integrated Annual Reports FY21-22 through FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. Extends the team's original sheet (FY23-26 only) back to include FY22 and FY21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2025-26</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2024-25</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2023-24</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2022-23</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2021-22</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2020-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Revenue from Operations</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>28966.31</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>29165.26</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>27183.21</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>25694.12</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>14257.61</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>12172.66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>322.61</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>487.21</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>344.32</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>235.04</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>141.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="n">
+        <v>29288.92</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>29652.47</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>27527.53</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>26075.97</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>14492.65</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>12314.47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Electrical Energy Purchased</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>15053.7</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>15289.81</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>13743.27</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>14440.53</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>5116.39</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>3358.36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Fuel Cost</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>3944.21</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>4877.69</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>5647.95</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>2508.23</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>3403.4</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>3610.55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Cost of Materials Consumed</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="30" t="n">
+        <v>213.46</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>406.5</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>334.81</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>262.64</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>104.21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Employee Benefits Expense</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>705.8</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>689.96</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>611.1900000000001</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>578.25</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>533.54</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>538.9400000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Finance Costs</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>934.47</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>1044.87</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>943.4</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>818.2</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>628.21</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>775.73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>1612.75</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>1497.12</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>1377.5</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>1280.96</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>1333.86</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>1279.55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>2127.55</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>1682.96</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>1504.14</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>1223.56</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>1055.76</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>1038.26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>25972.15</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>26399.89</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>24944.93</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>23034.61</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>12628.68</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>10762.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Profit Before Exceptional Items and Tax</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>3316.77</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>3252.58</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>2582.6</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>3041.36</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>1863.97</v>
+      </c>
+      <c r="G17" s="31" t="n">
+        <v>1551.77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Exceptional Items (DGEN plant impairment, FY22)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="30" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Profit Before Tax</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="31" t="n">
+        <v>563.97</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>1551.77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Total Tax Expense</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="30" t="n">
+        <v>105.27</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>255.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT, consolidated)</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>2469.36</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>3058.61</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>1896</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>2164.67</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>458.7</v>
+      </c>
+      <c r="G21" s="31" t="n">
+        <v>1295.87</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8893,8 +12751,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G35"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A31:G35"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A23:G23"/>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -8251,1006 +8251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>ADANI POWER LIMITED — Consolidated Balance Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Source: Adani Power Ltd FY2022-23 Integrated Annual Report, 'Consolidated Balance Sheet as at 31st March, 2023' (repo file: AR_22088_ADANIPOWER_2022_2023). NOTE: an earlier draft sheet in this workbook ('Sheet5') showed Adani Power's STANDALONE balance sheet mislabeled — this sheet replaces it with the genuine consolidated figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>Particulars (₹ crore)</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>As at 31-Mar-2023</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>As at 31-Mar-2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>ASSETS</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>Non-current Assets</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Property, Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="n">
-        <v>50543.8</v>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>53071.62</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Capital Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n">
-        <v>12879.54</v>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>10269.74</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Investment Property</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="n">
-        <v>704.9400000000001</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="n">
-        <v>190.61</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>190.61</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Other Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="n">
-        <v>12.03</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>11.98</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>Investments (Non-current)</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n">
-        <v>42.51</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>Other Financial Assets (Non-current)</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="n">
-        <v>779.71</v>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>856.04</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>Other Non-current Assets</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>1115.13</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>1352.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Total Non-current Assets</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="n">
-        <v>66268.27</v>
-      </c>
-      <c r="C15" s="31" t="n">
-        <v>65752.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>Inventories</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="n">
-        <v>3075.2</v>
-      </c>
-      <c r="C17" s="30" t="n">
-        <v>2258.27</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>Investments (Current)</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="n">
-        <v>611.54</v>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>183.24</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>Trade Receivables</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="n">
-        <v>11529.36</v>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>9560.92</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>Cash and Cash Equivalents</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="n">
-        <v>349.23</v>
-      </c>
-      <c r="C20" s="30" t="n">
-        <v>782.37</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>Bank Balances other than above</t>
-        </is>
-      </c>
-      <c r="B21" s="30" t="n">
-        <v>1524.42</v>
-      </c>
-      <c r="C21" s="30" t="n">
-        <v>1582.31</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>Loans (Current)</t>
-        </is>
-      </c>
-      <c r="B22" s="30" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="C22" s="30" t="n">
-        <v>7.62</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>Other Financial Assets (Current)</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="n">
-        <v>557.5</v>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>308.28</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>Other Current Assets</t>
-        </is>
-      </c>
-      <c r="B24" s="30" t="n">
-        <v>1902.56</v>
-      </c>
-      <c r="C24" s="30" t="n">
-        <v>1545.06</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Total Current Assets</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="n">
-        <v>19553</v>
-      </c>
-      <c r="C25" s="31" t="n">
-        <v>16228.07</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL ASSETS</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="n">
-        <v>85821.27</v>
-      </c>
-      <c r="C26" s="31" t="n">
-        <v>81981.02</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>EQUITY AND LIABILITIES</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>Equity Share Capital</t>
-        </is>
-      </c>
-      <c r="B28" s="30" t="n">
-        <v>3856.94</v>
-      </c>
-      <c r="C28" s="30" t="n">
-        <v>3856.94</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="29" t="inlineStr">
-        <is>
-          <t>Unsecured Perpetual Securities</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="n">
-        <v>13215</v>
-      </c>
-      <c r="C29" s="30" t="n">
-        <v>13215</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>Other Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="n">
-        <v>12803.72</v>
-      </c>
-      <c r="C30" s="30" t="n">
-        <v>1631.5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>Equity attributable to equity holders of the parent</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="n">
-        <v>29875.66</v>
-      </c>
-      <c r="C31" s="30" t="n">
-        <v>18703.44</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>Non-Controlling Interests</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
-        <v>29875.66</v>
-      </c>
-      <c r="C33" s="31" t="n">
-        <v>18703.44</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>Non-current Liabilities</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>Borrowings (Non-current)</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="n">
-        <v>33702.6</v>
-      </c>
-      <c r="C35" s="30" t="n">
-        <v>37871.32</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="29" t="inlineStr">
-        <is>
-          <t>Lease Liabilities (Non-current)</t>
-        </is>
-      </c>
-      <c r="B36" s="30" t="n">
-        <v>88.31999999999999</v>
-      </c>
-      <c r="C36" s="30" t="n">
-        <v>94.36</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="29" t="inlineStr">
-        <is>
-          <t>Other Financial Liabilities (Non-current)</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="30" t="n">
-        <v>960.37</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="29" t="inlineStr">
-        <is>
-          <t>Provisions (Non-current)</t>
-        </is>
-      </c>
-      <c r="B38" s="30" t="n">
-        <v>226.95</v>
-      </c>
-      <c r="C38" s="30" t="n">
-        <v>220.87</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="29" t="inlineStr">
-        <is>
-          <t>Deferred Tax Liabilities (Net)</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="30" t="n">
-        <v>2499.78</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>Other Non-current Liabilities</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="n">
-        <v>4183.15</v>
-      </c>
-      <c r="C40" s="30" t="n">
-        <v>4487.21</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Total Non-current Liabilities</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>38201.02</v>
-      </c>
-      <c r="C41" s="31" t="n">
-        <v>46133.91</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="28" t="inlineStr">
-        <is>
-          <t>Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="29" t="inlineStr">
-        <is>
-          <t>Borrowings (Current)</t>
-        </is>
-      </c>
-      <c r="B43" s="30" t="n">
-        <v>8549.450000000001</v>
-      </c>
-      <c r="C43" s="30" t="n">
-        <v>10924.36</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>Lease Liabilities (Current)</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="C44" s="30" t="n">
-        <v>8.390000000000001</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>Trade Payables — micro/small enterprises</t>
-        </is>
-      </c>
-      <c r="B45" s="30" t="n">
-        <v>95.76000000000001</v>
-      </c>
-      <c r="C45" s="30" t="n">
-        <v>57.59</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>Trade Payables — other creditors</t>
-        </is>
-      </c>
-      <c r="B46" s="30" t="n">
-        <v>2983.69</v>
-      </c>
-      <c r="C46" s="30" t="n">
-        <v>3450.62</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="29" t="inlineStr">
-        <is>
-          <t>Other Financial Liabilities (Current)</t>
-        </is>
-      </c>
-      <c r="B47" s="30" t="n">
-        <v>2461.58</v>
-      </c>
-      <c r="C47" s="30" t="n">
-        <v>1167.32</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="29" t="inlineStr">
-        <is>
-          <t>Other Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B48" s="30" t="n">
-        <v>3622.82</v>
-      </c>
-      <c r="C48" s="30" t="n">
-        <v>861.36</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>Provisions (Current)</t>
-        </is>
-      </c>
-      <c r="B49" s="30" t="n">
-        <v>21.64</v>
-      </c>
-      <c r="C49" s="30" t="n">
-        <v>28.71</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="29" t="inlineStr">
-        <is>
-          <t>Current Tax Liabilities (Net)</t>
-        </is>
-      </c>
-      <c r="B50" s="30" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="C50" s="30" t="n">
-        <v>645.3200000000001</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Total Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="n">
-        <v>17744.59</v>
-      </c>
-      <c r="C51" s="31" t="n">
-        <v>17143.67</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="n">
-        <v>55945.61</v>
-      </c>
-      <c r="C52" s="31" t="n">
-        <v>63277.58</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL EQUITY AND LIABILITIES</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="n">
-        <v>85821.27</v>
-      </c>
-      <c r="C53" s="31" t="n">
-        <v>81981.02</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>ADANI POWER LIMITED — Consolidated Statement of Profit and Loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Source: Adani Power Ltd FY2022-23 Integrated Annual Report, 'Consolidated Statement of Profit and Loss for the year ended 31st March, 2023' (repo file: AR_22088_ADANIPOWER_2022_2023). NOTE: replaces an earlier draft sheet ('Consolidated Profit and loss st...') that was mislabeled and actually contained Adani Power's STANDALONE figures (PAT ₹10,246.15cr FY23) — the genuine consolidated PAT is ₹10,726.64cr.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>Particulars (₹ crore)</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Year ended 31-Mar-2023</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>Year ended 31-Mar-2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Revenue from Operations</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="n">
-        <v>38773.3</v>
-      </c>
-      <c r="C6" s="30" t="n">
-        <v>27711.18</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="n">
-        <v>4267.22</v>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>3975.29</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Total Income</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="n">
-        <v>43040.52</v>
-      </c>
-      <c r="C8" s="31" t="n">
-        <v>31686.47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Fuel Cost</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="n">
-        <v>25480.85</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>14762.21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Purchase of Stock-in-trade / Power for resale</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="n">
-        <v>214.14</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>545.5599999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>Transmission Charges</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n">
-        <v>519.61</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>642.77</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>Employee Benefits Expense</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="n">
-        <v>569.99</v>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>470.31</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>Finance Costs (net)</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>3333.5</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>4094.78</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>Depreciation and Amortisation Expense</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="n">
-        <v>3303.68</v>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>3117.54</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>Other Expenses</t>
-        </is>
-      </c>
-      <c r="B16" s="30" t="n">
-        <v>1944.05</v>
-      </c>
-      <c r="C16" s="30" t="n">
-        <v>1476.17</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="n">
-        <v>35365.82</v>
-      </c>
-      <c r="C17" s="31" t="n">
-        <v>25109.34</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>Profit before tax and deferred tax (adj.)/recoverable from future tariff</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="n">
-        <v>7674.7</v>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>6577.13</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>Current Tax</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>768.34</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>Tax credit adjusted relating to earlier years</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="n">
-        <v>-768.1799999999999</v>
-      </c>
-      <c r="C20" s="30" t="n">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>Deferred Tax (credit)/charge (incl. earlier-year adj.)</t>
-        </is>
-      </c>
-      <c r="B21" s="30" t="n">
-        <v>-2499.77</v>
-      </c>
-      <c r="C21" s="30" t="n">
-        <v>976.5700000000001</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Total Tax (Credit)/Expense</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="n">
-        <v>-3267.37</v>
-      </c>
-      <c r="C22" s="31" t="n">
-        <v>1744.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>Add: Deferred tax (adj.)/recoverable from future tariff (net of tax)</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="n">
-        <v>-215.43</v>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>79.25</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Profit for the Year (PAT)</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="n">
-        <v>10726.64</v>
-      </c>
-      <c r="C24" s="31" t="n">
-        <v>4911.58</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t>Other Comprehensive Income, net of tax</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="n">
-        <v>33.74</v>
-      </c>
-      <c r="C25" s="30" t="n">
-        <v>43.63</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Total Comprehensive Income for the Year</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="n">
-        <v>10760.38</v>
-      </c>
-      <c r="C26" s="31" t="n">
-        <v>4955.21</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -9264,14 +8265,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>THE TATA POWER COMPANY LIMITED — Consolidated Balance Sheet</t>
+          <t>ADANI POWER LIMITED — Consolidated Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Sources: Tata Power Integrated Annual Reports FY21-22 (AR_20052), FY23-24 (AR_24164) and FY25-26 (AR_29380) — 'Consolidated Balance Sheet' as at each year-end. Fills the FY24/FY25 gaps left blank in the team's original 'Tata Power' draft sheet; FY22/23/26 figures cross-checked and match.</t>
+          <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23 (AR_22088), FY23-24 (AR_24072), FY24-25 (ADANIPOWER-2025) and FY25-26 (AR_29298) — 'Consolidated Balance Sheet' as at each year-end. NOTE: an earlier draft sheet in this workbook ('Sheet5') showed Adani Power's STANDALONE balance sheet mislabeled as consolidated — this sheet replaces it with genuine consolidated figures across the full FY22-FY26 window.</t>
         </is>
       </c>
     </row>
@@ -9338,6 +8339,1666 @@
         </is>
       </c>
       <c r="B7" s="30" t="n">
+        <v>66814.60000000001</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>66707.23</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>62812.71</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>50543.8</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>53071.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>2261.28</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>2319.82</v>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Capital Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>35053.46</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>12104.42</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>925.12</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>12879.54</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>10269.74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Investment Property</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>704.9400000000001</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>190.61</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>190.61</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>190.61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Non-current)</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Loans (Non-current)</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Non-current)</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>690.36</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>691.41</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>636.2</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>779.71</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>856.04</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Non-current Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>192.06</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>216.55</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>365.72</v>
+      </c>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>811.39</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>376.34</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>7410.97</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>4219</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>1418.95</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>1115.13</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>1352.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>113591.84</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>86588.34</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>66738.19</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>66268.27</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>65752.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>3623.48</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>3317.28</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>4142.1</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>3075.2</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>2258.27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Current)</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>1491.35</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <v>1037.7</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>611.54</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>183.24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Trade Receivables</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>11791.37</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>13022.07</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>11677.48</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>11529.36</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>9560.92</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Cash and Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>927.88</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <v>319.86</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>1136.25</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>349.23</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>782.37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Bank Balances other than above</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="n">
+        <v>5998.44</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>5800.02</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>6075.51</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>1524.42</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>1582.31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Loans (Current)</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Current)</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="n">
+        <v>2161.97</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>887.51</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>435.82</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>557.5</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>308.28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n">
+        <v>2682.6</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>1725.78</v>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>1742.43</v>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>1902.56</v>
+      </c>
+      <c r="F29" s="30" t="n">
+        <v>1545.06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n">
+        <v>28688.08</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>26313.45</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>25586.58</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>19553</v>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>16228.07</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Assets Classified as Held for Sale</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n">
+        <v>142279.92</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>112917.57</v>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>92324.77</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>85821.27</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>81981.02</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+      <c r="C34" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+      <c r="D34" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+      <c r="F34" s="30" t="n">
+        <v>3856.94</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Instrument entirely Equity in nature / Unsecured Perpetual Securities</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>3056.92</v>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>7315</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>13215</v>
+      </c>
+      <c r="F35" s="30" t="n">
+        <v>13215</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Other Equity</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="n">
+        <v>61079.94</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>49433.23</v>
+      </c>
+      <c r="D36" s="30" t="n">
+        <v>31973.09</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>12803.72</v>
+      </c>
+      <c r="F36" s="30" t="n">
+        <v>1631.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Equity attributable to equity holders of the parent</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>64936.88</v>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>56347.09</v>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>43145.03</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>29875.66</v>
+      </c>
+      <c r="F37" s="30" t="n">
+        <v>18703.44</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Non-Controlling Interests</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="n">
+        <v>1465.04</v>
+      </c>
+      <c r="C38" s="30" t="n">
+        <v>1326.47</v>
+      </c>
+      <c r="D38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="n">
+        <v>66401.92</v>
+      </c>
+      <c r="C39" s="31" t="n">
+        <v>57673.56</v>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>43145.03</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>29875.66</v>
+      </c>
+      <c r="F39" s="31" t="n">
+        <v>18703.44</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Non-current)</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="n">
+        <v>42829.6</v>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>27646.96</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>26595.01</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>33702.6</v>
+      </c>
+      <c r="F41" s="30" t="n">
+        <v>37871.32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>1049.27</v>
+      </c>
+      <c r="C42" s="30" t="n">
+        <v>1094.04</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>143.11</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>94.36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>185.69</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>960.37</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Non-current)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="C44" s="30" t="n">
+        <v>339.64</v>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>237.45</v>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>226.95</v>
+      </c>
+      <c r="F44" s="30" t="n">
+        <v>220.87</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="n">
+        <v>5827.15</v>
+      </c>
+      <c r="C45" s="30" t="n">
+        <v>4022.73</v>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="E45" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="30" t="n">
+        <v>2499.78</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>5298.18</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>5698.48</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>6098.63</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>4183.15</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>4487.21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>55549.79</v>
+      </c>
+      <c r="C47" s="31" t="n">
+        <v>38803.02</v>
+      </c>
+      <c r="D47" s="31" t="n">
+        <v>33391.07</v>
+      </c>
+      <c r="E47" s="31" t="n">
+        <v>38201.02</v>
+      </c>
+      <c r="F47" s="31" t="n">
+        <v>46133.91</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Current)</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>10725.94</v>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>10687.92</v>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>7861.85</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>8549.450000000001</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>10924.36</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="D50" s="30" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables — micro/small enterprises</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>183.98</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <v>215.73</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>141.93</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>57.59</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables — other creditors</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="n">
+        <v>2656.55</v>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>2761.93</v>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>3494.37</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>2983.69</v>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>3450.62</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="n">
+        <v>4049.65</v>
+      </c>
+      <c r="C53" s="30" t="n">
+        <v>1230.62</v>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>2089.8</v>
+      </c>
+      <c r="E53" s="30" t="n">
+        <v>2461.58</v>
+      </c>
+      <c r="F53" s="30" t="n">
+        <v>1167.32</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="n">
+        <v>994.38</v>
+      </c>
+      <c r="C54" s="30" t="n">
+        <v>1348.74</v>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>2159.44</v>
+      </c>
+      <c r="E54" s="30" t="n">
+        <v>3622.82</v>
+      </c>
+      <c r="F54" s="30" t="n">
+        <v>861.36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Current)</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>96.95999999999999</v>
+      </c>
+      <c r="C55" s="30" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="E55" s="30" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="F55" s="30" t="n">
+        <v>28.71</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="n">
+        <v>1555.27</v>
+      </c>
+      <c r="C56" s="30" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="D56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F56" s="30" t="n">
+        <v>645.3200000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="n">
+        <v>20328.21</v>
+      </c>
+      <c r="C57" s="31" t="n">
+        <v>16440.99</v>
+      </c>
+      <c r="D57" s="31" t="n">
+        <v>15788.67</v>
+      </c>
+      <c r="E57" s="31" t="n">
+        <v>17744.59</v>
+      </c>
+      <c r="F57" s="31" t="n">
+        <v>17143.67</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="n">
+        <v>75878</v>
+      </c>
+      <c r="C58" s="31" t="n">
+        <v>55244.01</v>
+      </c>
+      <c r="D58" s="31" t="n">
+        <v>49179.74</v>
+      </c>
+      <c r="E58" s="31" t="n">
+        <v>55945.61</v>
+      </c>
+      <c r="F58" s="31" t="n">
+        <v>63277.58</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY AND LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B59" s="31" t="n">
+        <v>142279.92</v>
+      </c>
+      <c r="C59" s="31" t="n">
+        <v>112917.57</v>
+      </c>
+      <c r="D59" s="31" t="n">
+        <v>92324.77</v>
+      </c>
+      <c r="E59" s="31" t="n">
+        <v>85821.27</v>
+      </c>
+      <c r="F59" s="31" t="n">
+        <v>81981.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ADANI POWER LIMITED — Consolidated Statement of Profit and Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23, FY23-24, FY24-25 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. NOTE: replaces an earlier draft sheet ('Consolidated Profit and loss st...') that was mislabeled and actually contained Adani Power's STANDALONE figures (PAT ₹10,246.15cr FY23) — the genuine consolidated PAT is ₹10,726.64cr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2025-26</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2024-25</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2023-24</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2022-23</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>FY 2021-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Revenue from Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>54240.52</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>56203.09</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>50351.25</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>38773.3</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>27711.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>3624.76</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>2702.74</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>9930.23</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>4267.22</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>3975.29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n">
+        <v>57865.28</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>58905.83</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>60281.48</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>43040.52</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>31686.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Fuel Cost</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>29168.02</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>30273.25</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>28452.64</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>25480.85</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>14762.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Purchase of Stock-in-trade / Power for resale</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>222.26</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>214.14</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>545.5599999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Transmission Charges</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>557.42</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>459.09</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>503.99</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>519.61</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>642.77</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Employee Benefits Expense</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>855.1799999999999</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>784.4</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>643.7</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>569.99</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>470.31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Finance Costs (net)</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>3366.83</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>3339.79</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>3388.09</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>3333.5</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>4094.78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Depreciation and Amortisation Expense</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>4564.53</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>4308.88</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>3931.33</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>3303.68</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>3117.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>3644.13</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>3023.92</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>2347.96</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>1944.05</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>1476.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n">
+        <v>42365.77</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>42546.32</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>39489.97</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>35365.82</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>25109.34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Profit before share of JV profit and tax</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>15499.51</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>16359.51</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>20791.51</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>7674.7</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>6577.13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Total Tax Expense/(Credit)</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>2528.43</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>3609.9</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>-37.28</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>-3267.37</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>1744.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Add: Deferred tax (adj.)/recoverable from future tariff (net of tax)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>-215.43</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>79.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Profit for the Year (PAT, consolidated)</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="n">
+        <v>12971.08</v>
+      </c>
+      <c r="C21" s="31" t="n">
+        <v>12749.61</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>20828.79</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>10726.64</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>4911.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income, net of tax</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>-27.49</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>43.63</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Total Comprehensive Income for the Year</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="n">
+        <v>12990.75</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>12746.92</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>20801.3</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>10760.38</v>
+      </c>
+      <c r="F23" s="31" t="n">
+        <v>4955.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>THE TATA POWER COMPANY LIMITED — Consolidated Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Sources: Tata Power Integrated Annual Reports FY21-22 (AR_20052), FY23-24 (AR_24164) and FY25-26 (AR_29380) — 'Consolidated Balance Sheet' as at each year-end. Fills the FY24/FY25 gaps left blank in the team's original 'Tata Power' draft sheet; FY22/23/26 figures cross-checked and match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Particulars (₹ crore)</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2024</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2023</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>Mar-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>ASSETS</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Property, Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
         <v>78870.53999999999</v>
       </c>
       <c r="C7" s="30" t="n">
@@ -10121,7 +10782,9 @@
       <c r="E43" s="30" t="n">
         <v>5416.69</v>
       </c>
-      <c r="F43" s="11" t="n"/>
+      <c r="F43" s="30" t="n">
+        <v>3586.9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -10141,7 +10804,9 @@
       <c r="E44" s="31" t="n">
         <v>34204.12</v>
       </c>
-      <c r="F44" s="32" t="n"/>
+      <c r="F44" s="31" t="n">
+        <v>26028.46</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="28" t="inlineStr">
@@ -10173,7 +10838,9 @@
       <c r="E46" s="30" t="n">
         <v>30708.49</v>
       </c>
-      <c r="F46" s="11" t="n"/>
+      <c r="F46" s="30" t="n">
+        <v>32729.7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
@@ -10193,359 +10860,419 @@
       <c r="E47" s="30" t="n">
         <v>3510.7</v>
       </c>
-      <c r="F47" s="11" t="n"/>
+      <c r="F47" s="30" t="n">
+        <v>3207.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
         <is>
-          <t>Other Financial Liabilities (Non-current)</t>
-        </is>
-      </c>
-      <c r="B48" s="30" t="n">
-        <v>694.64</v>
-      </c>
-      <c r="C48" s="30" t="n">
-        <v>674.12</v>
-      </c>
-      <c r="D48" s="30" t="n">
-        <v>1507.55</v>
-      </c>
-      <c r="E48" s="30" t="n">
-        <v>1410.4</v>
-      </c>
-      <c r="F48" s="11" t="n"/>
+          <t>Trade Payables (Non-current)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>Provisions (Non-current)</t>
+          <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
       <c r="B49" s="30" t="n">
-        <v>3213.85</v>
+        <v>694.64</v>
       </c>
       <c r="C49" s="30" t="n">
-        <v>2548.69</v>
+        <v>674.12</v>
       </c>
       <c r="D49" s="30" t="n">
-        <v>1865.08</v>
+        <v>1507.55</v>
       </c>
       <c r="E49" s="30" t="n">
-        <v>1420.02</v>
-      </c>
-      <c r="F49" s="11" t="n"/>
+        <v>1410.4</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>1156.56</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>Deferred Tax Liabilities (Net)</t>
-        </is>
-      </c>
-      <c r="B50" s="30" t="n">
-        <v>4807.88</v>
-      </c>
-      <c r="C50" s="30" t="n">
-        <v>4104.12</v>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>2772.33</v>
-      </c>
-      <c r="E50" s="30" t="n">
-        <v>1919.37</v>
-      </c>
-      <c r="F50" s="11" t="n"/>
+          <t>Non-current Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="30" t="n">
+        <v>3.03</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="29" t="inlineStr">
         <is>
+          <t>Provisions (Non-current)</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>3213.85</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <v>2548.69</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>1865.08</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>1420.02</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>1218.18</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="n">
+        <v>4807.88</v>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>4104.12</v>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>2772.33</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>1919.37</v>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>1033.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B51" s="30" t="n">
+      <c r="B53" s="30" t="n">
         <v>13411.97</v>
       </c>
-      <c r="C51" s="30" t="n">
+      <c r="C53" s="30" t="n">
         <v>12930.57</v>
       </c>
-      <c r="D51" s="30" t="n">
+      <c r="D53" s="30" t="n">
         <v>11973.08</v>
       </c>
-      <c r="E51" s="30" t="n">
+      <c r="E53" s="30" t="n">
         <v>9847.82</v>
       </c>
-      <c r="F51" s="11" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="F53" s="30" t="n">
+        <v>8139.29</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B52" s="31" t="n">
+      <c r="B54" s="31" t="n">
         <v>88286.85000000001</v>
       </c>
-      <c r="C52" s="31" t="n">
+      <c r="C54" s="31" t="n">
         <v>68583.42999999999</v>
       </c>
-      <c r="D52" s="31" t="n">
+      <c r="D54" s="31" t="n">
         <v>59252.77</v>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E54" s="31" t="n">
         <v>48816.8</v>
       </c>
-      <c r="F52" s="32" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="28" t="inlineStr">
+      <c r="F54" s="31" t="n">
+        <v>47487.85</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>Borrowings (Current)</t>
-        </is>
-      </c>
-      <c r="B54" s="30" t="n">
-        <v>9513.82</v>
-      </c>
-      <c r="C54" s="30" t="n">
-        <v>14015.84</v>
-      </c>
-      <c r="D54" s="30" t="n">
-        <v>12087.56</v>
-      </c>
-      <c r="E54" s="30" t="n">
-        <v>18265.94</v>
-      </c>
-      <c r="F54" s="11" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="29" t="inlineStr">
-        <is>
-          <t>Lease Liabilities (Current)</t>
-        </is>
-      </c>
-      <c r="B55" s="30" t="n">
-        <v>468.94</v>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>524.03</v>
-      </c>
-      <c r="D55" s="30" t="n">
-        <v>467.16</v>
-      </c>
-      <c r="E55" s="30" t="n">
-        <v>437.87</v>
-      </c>
+      <c r="B55" s="11" t="n"/>
+      <c r="C55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
       <c r="F55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>Trade Payables — micro/small enterprises</t>
+          <t>Borrowings (Current)</t>
         </is>
       </c>
       <c r="B56" s="30" t="n">
-        <v>809.84</v>
+        <v>9513.82</v>
       </c>
       <c r="C56" s="30" t="n">
-        <v>784.21</v>
+        <v>14015.84</v>
       </c>
       <c r="D56" s="30" t="n">
-        <v>870</v>
+        <v>12087.56</v>
       </c>
       <c r="E56" s="30" t="n">
-        <v>537.6</v>
-      </c>
-      <c r="F56" s="11" t="n"/>
+        <v>18265.94</v>
+      </c>
+      <c r="F56" s="30" t="n">
+        <v>14860.3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>Trade Payables — other creditors</t>
+          <t>Lease Liabilities (Current)</t>
         </is>
       </c>
       <c r="B57" s="30" t="n">
-        <v>6328.39</v>
+        <v>468.94</v>
       </c>
       <c r="C57" s="30" t="n">
-        <v>8070.34</v>
+        <v>524.03</v>
       </c>
       <c r="D57" s="30" t="n">
-        <v>8451.370000000001</v>
+        <v>467.16</v>
       </c>
       <c r="E57" s="30" t="n">
-        <v>6869.6</v>
-      </c>
-      <c r="F57" s="11" t="n"/>
+        <v>437.87</v>
+      </c>
+      <c r="F57" s="30" t="n">
+        <v>397.33</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>Other Financial Liabilities (Current)</t>
+          <t>Trade Payables — micro/small enterprises</t>
         </is>
       </c>
       <c r="B58" s="30" t="n">
-        <v>13897.6</v>
+        <v>809.84</v>
       </c>
       <c r="C58" s="30" t="n">
-        <v>12427.03</v>
+        <v>784.21</v>
       </c>
       <c r="D58" s="30" t="n">
-        <v>14796.16</v>
+        <v>870</v>
       </c>
       <c r="E58" s="30" t="n">
-        <v>13150.77</v>
+        <v>537.6</v>
       </c>
       <c r="F58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>Provisions (Current)</t>
+          <t>Trade Payables — other creditors / total</t>
         </is>
       </c>
       <c r="B59" s="30" t="n">
-        <v>680.4400000000001</v>
+        <v>6328.39</v>
       </c>
       <c r="C59" s="30" t="n">
-        <v>437.56</v>
+        <v>8070.34</v>
       </c>
       <c r="D59" s="30" t="n">
-        <v>294.34</v>
+        <v>8451.370000000001</v>
       </c>
       <c r="E59" s="30" t="n">
-        <v>311.07</v>
-      </c>
-      <c r="F59" s="11" t="n"/>
+        <v>6869.6</v>
+      </c>
+      <c r="F59" s="30" t="n">
+        <v>10459.6</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>Current Tax Liabilities (Net)</t>
+          <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
       <c r="B60" s="30" t="n">
-        <v>185.42</v>
+        <v>13897.6</v>
       </c>
       <c r="C60" s="30" t="n">
-        <v>208.2</v>
+        <v>12427.03</v>
       </c>
       <c r="D60" s="30" t="n">
-        <v>291.54</v>
+        <v>14796.16</v>
       </c>
       <c r="E60" s="30" t="n">
-        <v>217.96</v>
-      </c>
-      <c r="F60" s="11" t="n"/>
+        <v>13150.77</v>
+      </c>
+      <c r="F60" s="30" t="n">
+        <v>9631.959999999999</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>Other Current Liabilities</t>
+          <t>Provisions (Current)</t>
         </is>
       </c>
       <c r="B61" s="30" t="n">
-        <v>3691.15</v>
+        <v>680.4400000000001</v>
       </c>
       <c r="C61" s="30" t="n">
-        <v>3672.38</v>
+        <v>437.56</v>
       </c>
       <c r="D61" s="30" t="n">
-        <v>3879.84</v>
+        <v>294.34</v>
       </c>
       <c r="E61" s="30" t="n">
-        <v>4188.41</v>
-      </c>
-      <c r="F61" s="11" t="n"/>
+        <v>311.07</v>
+      </c>
+      <c r="F61" s="30" t="n">
+        <v>344.82</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
-        <is>
-          <t>Total Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
-        <v>39223.57</v>
-      </c>
-      <c r="C62" s="31" t="n">
-        <v>45269.52</v>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>41137.97</v>
-      </c>
-      <c r="E62" s="31" t="n">
-        <v>43979.22</v>
-      </c>
-      <c r="F62" s="32" t="n"/>
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="n">
+        <v>185.42</v>
+      </c>
+      <c r="C62" s="30" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="D62" s="30" t="n">
+        <v>291.54</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>217.96</v>
+      </c>
+      <c r="F62" s="30" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="n">
+        <v>3691.15</v>
+      </c>
+      <c r="C63" s="30" t="n">
+        <v>3672.38</v>
+      </c>
+      <c r="D63" s="30" t="n">
+        <v>3879.84</v>
+      </c>
+      <c r="E63" s="30" t="n">
+        <v>4188.41</v>
+      </c>
+      <c r="F63" s="30" t="n">
+        <v>2779.08</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n">
+        <v>39223.57</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>45269.52</v>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>41137.97</v>
+      </c>
+      <c r="E64" s="31" t="n">
+        <v>43979.22</v>
+      </c>
+      <c r="F64" s="31" t="n">
+        <v>38620.09</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
           <t>Liabilities re: Assets Held For Sale</t>
         </is>
       </c>
-      <c r="B63" s="30" t="n">
+      <c r="B65" s="30" t="n">
         <v>114.24</v>
       </c>
-      <c r="C63" s="30" t="n">
+      <c r="C65" s="30" t="n">
         <v>113.56</v>
       </c>
-      <c r="D63" s="30" t="n">
+      <c r="D65" s="30" t="n">
         <v>113.56</v>
       </c>
-      <c r="E63" s="30" t="n">
+      <c r="E65" s="30" t="n">
         <v>113.56</v>
       </c>
-      <c r="F63" s="11" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+      <c r="F65" s="30" t="n">
+        <v>113.56</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Liability</t>
         </is>
       </c>
-      <c r="B64" s="30" t="n">
+      <c r="B66" s="30" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="C64" s="30" t="n">
+      <c r="C66" s="30" t="n">
         <v>138.74</v>
       </c>
-      <c r="D64" s="30" t="n">
+      <c r="D66" s="30" t="n">
         <v>716.42</v>
       </c>
-      <c r="E64" s="30" t="n">
+      <c r="E66" s="30" t="n">
         <v>1235.34</v>
       </c>
-      <c r="F64" s="11" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="F66" s="30" t="n">
+        <v>634.63</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B65" s="31" t="n">
+      <c r="B67" s="31" t="n">
         <v>175171.78</v>
       </c>
-      <c r="C65" s="31" t="n">
+      <c r="C67" s="31" t="n">
         <v>156711.29</v>
       </c>
-      <c r="D65" s="31" t="n">
+      <c r="D67" s="31" t="n">
         <v>139553.49</v>
       </c>
-      <c r="E65" s="31" t="n">
+      <c r="E67" s="31" t="n">
         <v>128349.04</v>
       </c>
-      <c r="F65" s="31" t="n">
+      <c r="F67" s="31" t="n">
         <v>112884.59</v>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -11312,7 +11312,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Sources: Tata Power Integrated Annual Reports FY21-22, FY23-24 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. Extends the team's original sheet (which only had FY22/23) to the full FY22-FY26 window.</t>
+          <t>Sources: Tata Power Integrated Annual Reports FY21-22, FY23-24 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. Extends the team's original sheet (which only had FY22/23) to the full FY22-FY26 window, including the Exceptional Items / Profit Before Tax / Total Tax Expense rows for FY25 and FY26.</t>
         </is>
       </c>
     </row>
@@ -11784,8 +11784,12 @@
           <t>Exceptional Items (net)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
+      <c r="B25" s="30" t="n">
+        <v>-94.17</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>-122.05</v>
+      </c>
       <c r="D25" s="30" t="n">
         <v>273.36</v>
       </c>
@@ -11802,8 +11806,12 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
+      <c r="B26" s="31" t="n">
+        <v>6635.99</v>
+      </c>
+      <c r="C26" s="31" t="n">
+        <v>6319.62</v>
+      </c>
       <c r="D26" s="31" t="n">
         <v>5732.02</v>
       </c>
@@ -11820,8 +11828,12 @@
           <t>Total Tax Expense/(Credit)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
+      <c r="B27" s="30" t="n">
+        <v>1518.43</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>1544.25</v>
+      </c>
       <c r="D27" s="30" t="n">
         <v>1451.92</v>
       </c>
@@ -11842,7 +11854,7 @@
         <v>5117.56</v>
       </c>
       <c r="C28" s="31" t="n">
-        <v>4775</v>
+        <v>4775.37</v>
       </c>
       <c r="D28" s="31" t="n">
         <v>4280.1</v>
@@ -11869,7 +11881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -11891,7 +11903,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Sources: Torrent Power Integrated Annual Reports FY21-22 (AR_20392) through FY25-26 (AR_29704) — 'Consolidated Balance Sheet' as at each year-end. Fills the FY22/FY21 gap left blank in the team's original 'Consolidated Balance Sheet Summ[ary]' sheet; FY23-26 figures cross-checked and match.</t>
+          <t>Sources: Torrent Power Integrated Annual Reports FY21-22 (AR_20392) through FY25-26 (AR_29704) — 'Consolidated Balance Sheet' as at each year-end. Full line-item detail (Property Plant &amp; Equipment, Right-of-use Assets, etc.) now extracted for every year FY21-FY26; all totals cross-checked and tie out.</t>
         </is>
       </c>
     </row>
@@ -11951,10 +11963,18 @@
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
+      <c r="B6" s="30" t="n">
+        <v>24200.83</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>23028.29</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>20653.68</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>18115.94</v>
+      </c>
       <c r="F6" s="30" t="n">
         <v>16759.39</v>
       </c>
@@ -11968,10 +11988,18 @@
           <t>Right-of-use Assets</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
+      <c r="B7" s="30" t="n">
+        <v>585.35</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>259.07</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>216.46</v>
+      </c>
       <c r="F7" s="30" t="n">
         <v>214.6</v>
       </c>
@@ -12007,297 +12035,1070 @@
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Other Non-Current Assets (incl. intangibles/investments/loans)</t>
+          <t>Investment Property</t>
         </is>
       </c>
       <c r="B9" s="30" t="n">
-        <v>4791.5</v>
+        <v>0.37</v>
       </c>
       <c r="C9" s="30" t="n">
-        <v>2675.23</v>
+        <v>0.37</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>1760.08</v>
+        <v>0</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>874.3099999999999</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <v>1525.68</v>
-      </c>
-      <c r="G9" s="30" t="n">
-        <v>748.98</v>
-      </c>
+        <v>9.390000000000001</v>
+      </c>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Total Non-current Assets</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>35953.86</v>
-      </c>
-      <c r="C10" s="31" t="n">
-        <v>27953.33</v>
-      </c>
-      <c r="D10" s="31" t="n">
-        <v>24886.12</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>21894</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>19796.94</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>18894.31</v>
-      </c>
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>171.07</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>171.07</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>171.07</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>171.07</v>
+      </c>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>9239.42</v>
-      </c>
-      <c r="C11" s="31" t="n">
-        <v>8620.049999999999</v>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>8506.360000000001</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>8016.18</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>5225.76</v>
-      </c>
-      <c r="G11" s="31" t="n">
-        <v>4644.41</v>
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>653.66</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>687.46</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>718.46</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>756.33</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>123.29</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>18.44</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL ASSETS</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="n">
-        <v>45193.28</v>
-      </c>
-      <c r="C12" s="31" t="n">
-        <v>36573.38</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>33392.48</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>29910.18</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>25022.7</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>23538.72</v>
-      </c>
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Intangible Assets Under Development</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>EQUITY &amp; LIABILITIES</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Non-current)</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>132.82</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>124.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>Equity Share Capital</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>503.9</v>
-      </c>
-      <c r="C14" s="30" t="n">
-        <v>503.9</v>
-      </c>
-      <c r="D14" s="30" t="n">
-        <v>480.62</v>
-      </c>
+          <t>Loans (Non-current)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
       <c r="E14" s="30" t="n">
-        <v>480.62</v>
+        <v>0</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>480.62</v>
+        <v>121.87</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>480.62</v>
+        <v>155.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>Other Equity</t>
+          <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
       <c r="B15" s="30" t="n">
-        <v>18571.43</v>
+        <v>349.43</v>
       </c>
       <c r="C15" s="30" t="n">
-        <v>17111.41</v>
+        <v>105.75</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>11581.09</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="E15" s="30" t="n">
-        <v>10529</v>
+        <v>135.38</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>9462.559999999999</v>
+        <v>101.55</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>9703.620000000001</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Net Worth (Attributable to Owners)</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="n">
-        <v>19075.33</v>
-      </c>
-      <c r="C16" s="31" t="n">
-        <v>17615.31</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>12061.71</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>11009.62</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>9943.18</v>
-      </c>
-      <c r="G16" s="31" t="n">
-        <v>10184.24</v>
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Assets (Net)</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>148.21</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>114.67</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>24.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Non-Controlling Interests</t>
+          <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
       <c r="B17" s="30" t="n">
-        <v>633.42</v>
+        <v>18.85</v>
       </c>
       <c r="C17" s="30" t="n">
-        <v>600.47</v>
+        <v>16.27</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>535.79</v>
+        <v>12.64</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>446.33</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>35.93</v>
+        <v>10.56</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>36.36</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="n">
-        <v>19708.75</v>
-      </c>
-      <c r="C18" s="31" t="n">
-        <v>18215.78</v>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>12597.5</v>
-      </c>
-      <c r="E18" s="31" t="n">
-        <v>11455.95</v>
-      </c>
-      <c r="F18" s="31" t="n">
-        <v>9979.110000000001</v>
-      </c>
-      <c r="G18" s="31" t="n">
-        <v>10220.6</v>
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>2837.21</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>1158.63</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>420.76</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>1000.47</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>337.48</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>Non-current Liabilities (Borrowings, provisions, deferred tax etc.)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="30" t="n">
-        <v>8895.92</v>
-      </c>
-      <c r="G19" s="30" t="n">
-        <v>8508.27</v>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Assets</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>35953.86</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>27953.33</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>24886.12</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>22457.39</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>19796.94</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>18894.31</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>Current Liabilities (Borrowings, trade payables etc.)</t>
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="B20" s="11" t="n"/>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>507.18</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>658.02</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>800.45</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>820.28</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>537.5700000000001</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>450.35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Investments (Current)</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>1507.19</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <v>873.03</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>937.37</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>787.75</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>341.58</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Trade Receivables</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>2329.76</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>2362.25</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>2190.86</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>2246.33</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>1602.7</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>1420.29</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Cash and Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>766.61</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <v>289.11</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>188.23</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>289.41</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>107.28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Bank Balances other than above</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>67.91</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>155.29</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>95.14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Loans (Current)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="30" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G26" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Assets (Current)</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="n">
+        <v>3516.62</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>4188.37</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>3989.23</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>3111.4</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>2298.81</v>
+      </c>
+      <c r="G27" s="30" t="n">
+        <v>2153.41</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>547.24</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>158.38</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>169.71</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>143.51</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <v>140.74</v>
+      </c>
+      <c r="G28" s="30" t="n">
+        <v>76.36</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n">
+        <v>9239.42</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>8620.049999999999</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>8506.360000000001</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>7452.79</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <v>5225.76</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>4644.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n">
+        <v>45193.28</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>36573.38</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>33392.48</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>29910.18</v>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>25022.7</v>
+      </c>
+      <c r="G30" s="31" t="n">
+        <v>23538.72</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>EQUITY &amp; LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>Equity Share Capital</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>503.9</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>503.9</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>480.62</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>480.62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Other Equity</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>18571.43</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>17111.41</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>11581.09</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>10529</v>
+      </c>
+      <c r="F33" s="30" t="n">
+        <v>9462.559999999999</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>9703.620000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Net Worth (Attributable to Owners)</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="n">
+        <v>19075.33</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>17615.31</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>12061.71</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>11010</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>9943.18</v>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>10184.24</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Non-Controlling Interests</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>633.42</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>600.47</v>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>535.79</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>476.65</v>
+      </c>
+      <c r="F35" s="30" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="G35" s="30" t="n">
+        <v>36.36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n">
+        <v>19708.75</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <v>18215.78</v>
+      </c>
+      <c r="D36" s="31" t="n">
+        <v>12597.5</v>
+      </c>
+      <c r="E36" s="31" t="n">
+        <v>11486.65</v>
+      </c>
+      <c r="F36" s="31" t="n">
+        <v>9979.110000000001</v>
+      </c>
+      <c r="G36" s="31" t="n">
+        <v>10220.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Non-current)</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="n">
+        <v>11871.42</v>
+      </c>
+      <c r="C38" s="30" t="n">
+        <v>7310.21</v>
+      </c>
+      <c r="D38" s="30" t="n">
+        <v>9916.4</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>8902.32</v>
+      </c>
+      <c r="F38" s="30" t="n">
+        <v>7099.15</v>
+      </c>
+      <c r="G38" s="30" t="n">
+        <v>6672.18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>219.83</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="D39" s="30" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="F39" s="30" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>30.96</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables (Non-current)</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>210.61</v>
+      </c>
+      <c r="F40" s="30" t="n">
+        <v>150.46</v>
+      </c>
+      <c r="G40" s="30" t="n">
+        <v>116.11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Non-current)</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G41" s="30" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>1628.57</v>
+      </c>
+      <c r="C42" s="30" t="n">
+        <v>1352.21</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>1233.65</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>968.79</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>345.21</v>
+      </c>
+      <c r="G42" s="30" t="n">
+        <v>527.51</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>Other Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n">
+        <v>1689.43</v>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>1623.6</v>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>1445.68</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>1372.46</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>1261.67</v>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>1160.34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Total Non-current Liabilities</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>15771.44</v>
+      </c>
+      <c r="C44" s="31" t="n">
+        <v>10768.11</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>12981.89</v>
+      </c>
+      <c r="E44" s="31" t="n">
+        <v>11493.5</v>
+      </c>
+      <c r="F44" s="31" t="n">
+        <v>8895.92</v>
+      </c>
+      <c r="G44" s="31" t="n">
+        <v>8508.27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>Borrowings (Current)</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>1861.51</v>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>1426.47</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>1668.63</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>1593.75</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>1999.27</v>
+      </c>
+      <c r="G46" s="30" t="n">
+        <v>1108.37</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Lease Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="E47" s="30" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="F47" s="30" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="G47" s="30" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>Trade Payables (Current)</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n">
+        <v>1879.23</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <v>1824.13</v>
+      </c>
+      <c r="D48" s="30" t="n">
+        <v>1811.92</v>
+      </c>
+      <c r="E48" s="30" t="n">
+        <v>1522.67</v>
+      </c>
+      <c r="F48" s="30" t="n">
+        <v>1111.13</v>
+      </c>
+      <c r="G48" s="30" t="n">
+        <v>974.79</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Other Financial Liabilities (Current)</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>4771.06</v>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>3409.61</v>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>3264.67</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>2687.72</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>2021.51</v>
+      </c>
+      <c r="G49" s="30" t="n">
+        <v>1799.77</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="n">
+        <v>921.02</v>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>689.74</v>
+      </c>
+      <c r="D50" s="30" t="n">
+        <v>735.0599999999999</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>677.24</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>613.5599999999999</v>
+      </c>
+      <c r="G50" s="30" t="n">
+        <v>542.02</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>Provisions (Current)</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="n">
+        <v>226.37</v>
+      </c>
+      <c r="C51" s="30" t="n">
+        <v>198.17</v>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>201.74</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>264.06</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="G51" s="30" t="n">
+        <v>335.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Current Tax Liabilities (Net)</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="C52" s="30" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>178.57</v>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>122.54</v>
+      </c>
+      <c r="G52" s="30" t="n">
+        <v>44.55</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="n">
+        <v>9713.09</v>
+      </c>
+      <c r="C53" s="31" t="n">
+        <v>7589.49</v>
+      </c>
+      <c r="D53" s="31" t="n">
+        <v>7813.09</v>
+      </c>
+      <c r="E53" s="31" t="n">
+        <v>6930.03</v>
+      </c>
+      <c r="F53" s="31" t="n">
         <v>6147.67</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G53" s="31" t="n">
         <v>4809.85</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B54" s="31" t="n">
         <v>45193.28</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C54" s="31" t="n">
         <v>36573.38</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D54" s="31" t="n">
         <v>33392.48</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E54" s="31" t="n">
         <v>29910.18</v>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="F54" s="31" t="n">
         <v>25022.7</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G54" s="31" t="n">
         <v>23538.72</v>
       </c>
     </row>
@@ -12316,7 +13117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12338,7 +13139,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Sources: Torrent Power Integrated Annual Reports FY21-22 through FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. Extends the team's original sheet (FY23-26 only) back to include FY22 and FY21.</t>
+          <t>Sources: Torrent Power Integrated Annual Reports FY21-22 through FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. Exceptional items, Profit Before Tax and the Current/Deferred Tax split are now shown for every year FY21-FY26; only FY22 had an exceptional item (the ~Rs 1,300cr DGEN plant impairment) — all other years are genuinely nil, not missing data.</t>
         </is>
       </c>
     </row>
@@ -12693,13 +13494,21 @@
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Exceptional Items (DGEN plant impairment, FY22)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
+          <t>Exceptional Items (DGEN plant impairment, FY22 only)</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" s="30" t="n">
         <v>1300</v>
       </c>
@@ -12713,10 +13522,18 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
+      <c r="B19" s="31" t="n">
+        <v>3316.77</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>3252.58</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>2582.6</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>3041.36</v>
+      </c>
       <c r="F19" s="31" t="n">
         <v>563.97</v>
       </c>
@@ -12727,42 +13544,100 @@
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
+          <t>Current Tax</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>728.15</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>600.47</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>445.07</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>672.8200000000001</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>287.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Deferred Tax</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>119.26</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>-406.5</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>241.53</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>203.87</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>-267.21</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>-31.95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
           <t>Total Tax Expense</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="30" t="n">
+      <c r="B22" s="31" t="n">
+        <v>847.41</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>193.97</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>686.6</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>876.6900000000001</v>
+      </c>
+      <c r="F22" s="31" t="n">
         <v>105.27</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G22" s="31" t="n">
         <v>255.9</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B23" s="31" t="n">
         <v>2469.36</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C23" s="31" t="n">
         <v>3058.61</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D23" s="31" t="n">
         <v>1896</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E23" s="31" t="n">
         <v>2164.67</v>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="F23" s="31" t="n">
         <v>458.7</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G23" s="31" t="n">
         <v>1295.87</v>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -1428,22 +1428,22 @@
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>NOT FOUND in any Annual Report available in this repo for this company/year. TO SOURCE IT: go to finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history (tickers: ADANIPOWER, TATAPOWER, TORNTPOWER), set the date range to cover 31-March of the target year, and read off the 'Close' (or 'Adj Close') for the last trading day on/before 31-March. Equivalent primary source: nseindia.com -&gt; Market Data -&gt; Historical Data -&gt; Equities, select the symbol and exact date. NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025 (face value ₹10 -&gt; ₹2) — for a like-for-like series with the FY26 figure below, divide any pre-split Adani Power price by 5.</t>
       </text>
     </comment>
     <comment ref="C26" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>NOT FOUND as a single closing price in repo sources. Adani Power's FY22-23 AR (Corporate Governance Report, section (h) 'Market Price Data') gives only the March-2023 monthly range — BSE High/Low ₹187.60/₹115.50, NSE High/Low ₹217.35/₹152.15 (extremely wide because of the Jan-2023 Hindenburg-report volatility) — not a single closing price. TO GET THE EXACT FIGURE: NSE 'Historical Data' for ADANIPOWER, date 31-Mar-2023 (nseindia.com -&gt; Market Data -&gt; Historical Data -&gt; Equities, or finance.yahoo.com/quote/ADANIPOWER.NS/history).</t>
       </text>
     </comment>
     <comment ref="D26" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>NOT FOUND in any Annual Report available in this repo for this company/year. TO SOURCE IT: go to finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history (tickers: ADANIPOWER, TATAPOWER, TORNTPOWER), set the date range to cover 31-March of the target year, and read off the 'Close' (or 'Adj Close') for the last trading day on/before 31-March. Equivalent primary source: nseindia.com -&gt; Market Data -&gt; Historical Data -&gt; Equities, select the symbol and exact date. NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025 (face value ₹10 -&gt; ₹2) — for a like-for-like series with the FY26 figure below, divide any pre-split Adani Power price by 5.</t>
       </text>
     </comment>
     <comment ref="E26" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>DERIVED: Market capitalisation ₹1,96,395.33 cr (Adani Power Integrated AR 2024-25, 'Investors' stakeholder-engagement infographic) ÷ 3,85,69,38,941 equity shares outstanding at 31-Mar-2025 (Note on Share Capital, same AR; face value ₹10, PRE stock-split) = ₹509.19/share (pre-split terms). On a post 1:5-split, ₹2-face-value basis (to match the FY26 figure), this is ₹101.84/share equivalent.</t>
       </text>
     </comment>
     <comment ref="F26" authorId="0" shapeId="0">
@@ -1453,22 +1453,22 @@
     </comment>
     <comment ref="B27" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>DERIVED: Market capitalisation ₹76,321 cr 'as on Mar 31, 2022' (Tata Power Integrated AR 2021-22, Outputs/Outcomes infographic) ÷ 319.70 cr paid-up equity shares (Note on Share Capital, same AR) = ₹238.79/share. Cross-checked: falls inside the disclosed March-2022 BSE/NSE monthly trading range of ₹216.20-241.70 (Corporate Governance Report, Market Price Data table).</t>
       </text>
     </comment>
     <comment ref="C27" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>DERIVED: Market capitalisation ₹60,775 cr 'as on Mar 31, 2023' (Tata Power Integrated AR 2022-23, same infographic) ÷ 319.70 cr shares = ₹190.10/share. Cross-checked: falls inside the disclosed March-2023 range of ₹183.95-211.25 (same AR, Market Price Data table).</t>
       </text>
     </comment>
     <comment ref="D27" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>NOT FOUND in any Annual Report available in this repo for this company/year. TO SOURCE IT: go to finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history (tickers: ADANIPOWER, TATAPOWER, TORNTPOWER), set the date range to cover 31-March of the target year, and read off the 'Close' (or 'Adj Close') for the last trading day on/before 31-March. Equivalent primary source: nseindia.com -&gt; Market Data -&gt; Historical Data -&gt; Equities, select the symbol and exact date. NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025 (face value ₹10 -&gt; ₹2) — for a like-for-like series with the FY26 figure below, divide any pre-split Adani Power price by 5.</t>
       </text>
     </comment>
     <comment ref="E27" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>DERIVED (approximate): Market capitalisation stated only as '₹1.20 lakh crore (as on Mar 31, 2025)' — rounded to 3 significant figures — in the Tata Power Integrated AR 2024-25 infographic, ÷ 319.70 cr shares ≈ ₹375/share. Because the source rounds to the nearest ₹100 cr of market cap, this derived price could be off by roughly ±₹0.3 — treat as an approximation and replace with an exact NSE/BSE closing price if precision matters.</t>
       </text>
     </comment>
     <comment ref="F27" authorId="0" shapeId="0">
@@ -1478,22 +1478,22 @@
     </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>VERIFIED — exact quote: 'Closing market price of equity shares on March 31, 2022 was ₹491.90 on BSE and ₹491.85 on NSE' (Torrent Power Integrated AR 2021-22, Report on Corporate Governance, section (e) 'Market price data'). NSE figure used for consistency with the other rows.</t>
       </text>
     </comment>
     <comment ref="C28" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>VERIFIED — exact quote: 'Closing market price of equity shares on March 31, 2023 was ₹509.50 on BSE and ₹510.40 on NSE' (Torrent Power Integrated AR 2022-23, same section).</t>
       </text>
     </comment>
     <comment ref="D28" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>VERIFIED — exact quote: 'Closing market price of equity shares on March 31, 2024 was ₹1,354.75 on BSE and ₹1,357.95 on NSE' (Torrent Power Integrated AR 2023-24, same section).</t>
       </text>
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>FY-end (31 March) closing prices for FY22-FY25 are outside the 1-year weekly price window downloaded to this repo. Pull from NSE historical data / Yahoo Finance (finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history) — NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025, so use SPLIT-ADJUSTED prices for a like-for-like series.</t>
+        <t>NOT FOUND in any Annual Report available in this repo for this company/year. TO SOURCE IT: go to finance.yahoo.com/quote/&lt;TICKER&gt;.NS/history (tickers: ADANIPOWER, TATAPOWER, TORNTPOWER), set the date range to cover 31-March of the target year, and read off the 'Close' (or 'Adj Close') for the last trading day on/before 31-March. Equivalent primary source: nseindia.com -&gt; Market Data -&gt; Historical Data -&gt; Equities, select the symbol and exact date. NOTE: Adani Power did a 1:5 stock split effective 22-Sep-2025 (face value ₹10 -&gt; ₹2) — for a like-for-like series with the FY26 figure below, divide any pre-split Adani Power price by 5.</t>
       </text>
     </comment>
     <comment ref="F28" authorId="0" shapeId="0">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Associates (2 per earlier AOC-1 references)</t>
+          <t>NONE — zero associates or JVs as of 31-Mar-2026</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Not extracted</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Torrent's FY26 AOC-1 Part B not extracted in this pass — the Part A subsidiary data above is verified; pull Part B from the same annexure if associate detail is needed.</t>
+          <t>VERIFIED: the FY26 AOC-1 'Form AOC-1, (b) Associates and Joint Ventures' annexure (Integrated Annual Report 2025-26) has NO rows at all — Torrent Power Limited holds no associate or JV interest as of 31-Mar-2026. History: through FY24-25, the only entity ever listed in Part B was UNM Foundation, a Section-8 (not-for-profit) company whose profits cannot legally flow to members — explicitly EXCLUDED from consolidation for that reason (per its own FY24-25 AOC-1 footnote), so it was never really a commercial associate. On 30-Mar-2026 Torrent Power transferred its 50,000 UNM Foundation shares to Torrent Investments Ltd (the parent holding company), per the FY26 AOC-1 footnote — leaving Part B empty.</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>1. Year-end (31-Mar) share prices, FY22-FY26, all three companies — still not filled; pull from NSE historical data or Yahoo Finance (split-adjust Adani Power for its Sep-2025 1:5 split).</t>
+          <t>1. Year-end (31-Mar) share prices — FY26 (all 3) DONE from weekly price data; FY22-FY25 now mostly VERIFIED or DERIVED directly from each company's own Annual Report (Sheet 2, with per-cell source comments). Still genuinely missing (no primary source found in this repo): Adani Power FY22/FY23/FY24 and Tata Power FY24 — see the flagged-cell comments in Sheet 2 for exact NSE/Yahoo lookup instructions.</t>
         </is>
       </c>
     </row>
@@ -8440,14 +8440,14 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>6. Shareholding pattern — Promoter %, promoter pledge (nil, all 3), and the single largest non-promoter &gt;5% holder are now VERIFIED as at 31-Mar-2026 from the Annual Reports for all three companies (Sheet 5). FII/DII category-level % breakdowns are still secondary-source/unverified — pull the full SHP table from each PDF or BSE/NSE XBRL filing if needed.</t>
+          <t>6. Shareholding pattern — Promoter %, promoter pledge (nil, all 3), the single largest non-promoter &gt;5% holder, AND the full FII/DII/Public category breakdown are now ALL VERIFIED as at 31-Mar-2026 from each company's own statutory 'Category-wise shareholding' table in its Annual Report (Sheet 5) — ties out exactly to the free-float row for all three.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>7. Subsidiary lists — DONE: Sheets 7-8 now carry the verified FY26 AOC-1 data (Adani 19 entities incl. Mahan at 94% and Moxie consolidated at 49%; Tata ~113 entities incl. TPREL at 88.57%; Torrent ~60 entities). Only Torrent's associates (Part B) remain unextracted.</t>
+          <t>7. Subsidiary lists — DONE: Sheets 7-8 now carry the verified FY26 AOC-1 data (Adani 19 entities incl. Mahan at 94% and Moxie consolidated at 49%; Tata ~113 entities incl. TPREL at 88.57%; Torrent ~60 entities). Torrent's Part B (Associates/JVs) is now also VERIFIED as empty — zero associates/JVs as of 31-Mar-2026 (see Sheet 8 note).</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9219,7 +9219,7 @@
     <row r="11" ht="68" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Shareholding pattern, &gt;5% holders, promoter pledge (Sheet 5)</t>
+          <t>Shareholding pattern, &gt;5% holders, promoter pledge, FII/DII/Public split (Sheet 5)</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -9229,51 +9229,51 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Corporate Governance Report / Notes to financial statements — shareholding pattern table, 'shareholders holding more than 5%' note, promoter shareholding table; FII/DII category splits cross-checked with Trendlyne/exchange aggregator snapshots (secondary)</t>
+          <t>Report on Corporate Governance — 'Category-wise shareholding as on March 31, 2026' (Adani)/'By category of Members' (Torrent)/Table 23 'Category-wise shareholding' (Tata) statutory tables, plus the 'shareholders holding more than 5%' note and promoter shareholding table</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Primary (promoter/&gt;5%/pledge); secondary (FII/DII splits)</t>
+          <t>VERIFIED primary — all rows, incl. FII/DII/Public splits</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Subsidiaries, associates, JVs (Sheets 7-8)</t>
+          <t>Year-end (31-Mar) share price, FY22-FY25 (Sheet 2)</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>FY25-26 Annual Reports (all 3)</t>
+          <t>Torrent: AR_20392 (FY22 AR)/AR_22356 (FY23 AR)/AR_24323 (FY24 AR). Tata: AR_20052 (FY22 AR)/AR_2022_2023 (FY23 AR)/AR_26536 (FY25 AR). Adani: ADANIPOWER-2025 (FY25 AR).</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Form AOC-1 annexure (statement of salient features of financial statements of subsidiaries/associates/JVs) — entity names, % holdings, turnover and PAT per entity</t>
+          <t>Torrent: Report on Corporate Governance, 'Market price data', explicit 'Closing market price ... on March 31, 20XX' statement. Tata/Adani: 'Market capitalisation (as on Mar 31, 20XX)' infographic ÷ Note on Share Capital's paid-up shares outstanding (DERIVED, cross-checked against disclosed monthly High/Low range where available).</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>VERIFIED primary</t>
+          <t>VERIFIED (Torrent FY22-24); DERIVED from primary data (Tata FY22/23/25, Adani FY25); NOT FOUND in repo sources (Adani FY22/23/24, Tata FY24) — see Sheet 2 cell comments for exact manual-lookup instructions</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Investments other than subs/assoc/JVs (Sheet 9)</t>
+          <t>Subsidiaries, associates, JVs (Sheets 7-8)</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>FY22-23 Annual Reports (all 3)</t>
+          <t>FY25-26 Annual Reports (all 3)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Notes to Consolidated Financial Statements — Non-current Investments and Current Investments notes (e.g. Torrent Notes 10 &amp; 16; Adani Notes 5 &amp; 9)</t>
+          <t>Form AOC-1 annexure (statement of salient features of financial statements of subsidiaries/associates/JVs) — entity names, % holdings, turnover and PAT per entity</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -9285,126 +9285,148 @@
     <row r="14" ht="68" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Acquisitions &amp; deal values (Sheet 4)</t>
+          <t>Investments other than subs/assoc/JVs (Sheet 9)</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Directors' Reports in the Annual Report PDFs (deal completion/status) + financial press</t>
+          <t>FY22-23 Annual Reports (all 3)</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Directors' Report M&amp;A discussion; deal values from Business Standard, BusinessToday, Mercom India, PIB releases, NCLT/CCI filings as reported; each row states its basis</t>
+          <t>Notes to Consolidated Financial Statements — Non-current Investments and Current Investments notes (e.g. Torrent Notes 10 &amp; 16; Adani Notes 5 &amp; 9)</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Primary + named secondary</t>
+          <t>VERIFIED primary</t>
         </is>
       </c>
     </row>
     <row r="15" ht="68" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Financing changes, credit ratings (Sheet 10)</t>
+          <t>Acquisitions &amp; deal values (Sheet 4)</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>CRISIL / ICRA / India Ratings rating rationales; company press releases; exchange filings via financial press</t>
+          <t>Directors' Reports in the Annual Report PDFs (deal completion/status) + financial press</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>crisil.com rating rationale pages (Adani Power Feb-2025 upgrade, Tata Power Apr-2024 upgrade, Torrent reaffirmations); QIP/NCD details from Business Standard/exchange-filing coverage</t>
+          <t>Directors' Report M&amp;A discussion; deal values from Business Standard, BusinessToday, Mercom India, PIB releases, NCLT/CCI filings as reported; each row states its basis</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>Named secondary (recognized rating agencies/press)</t>
+          <t>Primary + named secondary</t>
         </is>
       </c>
     </row>
     <row r="16" ht="68" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Weekly share prices, returns, volatility, beta (Sheets 11, Weekly_Price_Data)</t>
+          <t>Financing changes, credit ratings (Sheet 10)</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Yahoo Finance Historical Data pages saved in this repo: ADANIPOWER_weekly.htm, TATAPOWER_weekly.htm, TORRENTPOWER_weekly.htm, NIFTYENERGY_weekly.htm, NIFTY50_weeklyreal.htm</t>
+          <t>CRISIL / ICRA / India Ratings rating rationales; company press releases; exchange filings via financial press</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Weekly adjusted-close tables, 14-Jul-2025 to 15-Jul-2026, split-adjusted; 53 dates common to all 5 series; all stats are live Excel formulas (STDEV/SLOPE) over these prices</t>
+          <t>crisil.com rating rationale pages (Adani Power Feb-2025 upgrade, Tata Power Apr-2024 upgrade, Torrent reaffirmations); QIP/NCD details from Business Standard/exchange-filing coverage</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Primary data files in repo; computations auditable in-cell</t>
+          <t>Named secondary (recognized rating agencies/press)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="68" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Major announcements &amp; price reaction (Sheet 12)</t>
+          <t>Weekly share prices, returns, volatility, beta (Sheets 11, Weekly_Price_Data)</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Company press releases / exchange announcements as covered by Business Standard, BusinessToday, PSU Connect + the weekly price series above</t>
+          <t>Yahoo Finance Historical Data pages saved in this repo: ADANIPOWER_weekly.htm, TATAPOWER_weekly.htm, TORRENTPOWER_weekly.htm, NIFTYENERGY_weekly.htm, NIFTY50_weeklyreal.htm</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Each announcement row lists the event; price overlay from Weekly_Price_Data; exact filing dates should be cross-checked on BSE corporate announcements page before an event-study</t>
+          <t>Weekly adjusted-close tables, 14-Jul-2025 to 15-Jul-2026, split-adjusted; 53 dates common to all 5 series; all stats are live Excel formulas (STDEV/SLOPE) over these prices</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Named secondary + repo price data</t>
+          <t>Primary data files in repo; computations auditable in-cell</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
+          <t>Major announcements &amp; price reaction (Sheet 12)</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Company press releases / exchange announcements as covered by Business Standard, BusinessToday, PSU Connect + the weekly price series above</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Each announcement row lists the event; price overlay from Weekly_Price_Data; exact filing dates should be cross-checked on BSE corporate announcements page before an event-study</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Named secondary + repo price data</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="68" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
           <t>Course requirements (structure of this file)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>FADM_(1).pdf (course plan, in this repo)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Project Schedule table — Session-6 'Part-1' deliverable list; 'file must contain the financial statements... trails to the FSs' requirement</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Note on verifiability: every Annual Report PDF and Yahoo Finance price file cited above is included in the same repository/folder as this workbook, so any figure can be traced end-to-end: workbook cell → FS_Extracts / detail sheet → named statement or note → source PDF. Items marked 'named secondary' (credit ratings, deal values, announcement dates) come from recognized public sources (rating agencies, national financial press, government releases) because that information is not disclosed inside audited financial statements.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A20:D22"/>
+    <mergeCell ref="A21:D23"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15698,7 +15720,7 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>Market price per share (₹, adj. close, year-end 31-Mar)</t>
+          <t>Market price per share (₹, year-end 31-Mar, as actually quoted)</t>
         </is>
       </c>
     </row>
@@ -15723,10 +15745,8 @@
           <t>TO FILL</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
+      <c r="E26" s="19" t="n">
+        <v>509.19</v>
       </c>
       <c r="F26" s="19" t="n">
         <v>159.97</v>
@@ -15738,25 +15758,19 @@
           <t>Tata Power — Year-end share price</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="19" t="n">
+        <v>238.79</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>TO FILL</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
+      <c r="E27" s="19" t="n">
+        <v>375.35</v>
       </c>
       <c r="F27" s="19" t="n">
         <v>382.63</v>
@@ -15768,20 +15782,14 @@
           <t>Torrent Power — Year-end share price</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>TO FILL</t>
-        </is>
+      <c r="B28" s="19" t="n">
+        <v>491.85</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>510.4</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>1357.95</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -17251,22 +17259,22 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>11.74% (secondary-source snapshot; not separately re-verified in the Annual Report text extract)</t>
+          <t>11.73% — 'Foreign Institutional Investors/Portfolio Investor', 2,26,30,86,903 shares (FY26 Annual Report, 'Category-wise shareholding as on March 31, 2026' table)</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>~10.0-10.04% (secondary-source snapshot)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>8.4%-14.2% (conflicting across sources/dates)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Category-wise FII/DII % not captured from the Annual Report's shareholding table in this pass — cross-check the full SHP table in each PDF if needed.</t>
+          <t>10.04% — 'Foreign Portfolio Investors – Corporate' (FY26 Annual Report, Table 23 'Category-wise shareholding'). 5-yr trend (same AR's Institutional Holding Pattern chart): FY22 10.83%, FY23 9.46%, FY24 9.45%, FY25 9.39%, FY26 10.04%.</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>8.40% — 'Foreign Portfolio Investors', 4,23,31,239 shares (FY26 Annual Report, 'By category of Members' table)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>VERIFIED for all three from each company's own FY25-26 'Category-wise shareholding'/'By category of Members' statutory table (Report on Corporate Governance). This resolves the prior conflicting ranges — the low end of each range was correct; higher figures quoted by secondary sources could not be traced to any primary filing and should be disregarded.</t>
         </is>
       </c>
     </row>
@@ -17278,22 +17286,22 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>3.69% (DII, secondary-source snapshot)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>8.64% (DII, one source) vs 18.28% (DII, another) — MFs alone ~8.89-9.63%</t>
+          <t>3.65% = Insurance Companies (0.03%) + Mutual Funds/Banks/Financial Institutions (3.62%) — VERIFIED, same FY26 category-wise shareholding table.</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>9.15% Mutual Funds/UTI alone (Table 23); company's own 'Domestic Institutional Investors' summary category (broader, includes other domestic institutions) = 10.51% FY26. Insurance Companies is reported separately at 7.77% FY26. Insurance + DII = 18.28% — this exactly matches one of the two previously-conflicting figures, confirming it was correct (labelled 'DII alone', it should have read 'DII + Insurance'). SBI Mutual Fund alone (a Torrent Power holding, not Tata) is a different figure — see Torrent column.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>SBI Mutual Fund confirmed at 8.57% (FY26, up from 7.95% FY25) — VERIFIED from Annual Report top-10-shareholders table.</t>
+          <t>21.06% = Mutual Funds (15.67%) + Insurance Companies (5.31%) + Financial Institutions &amp; Banks (0.08%) — VERIFIED, FY26 'By category of Members' table. SBI Mutual Fund alone = 8.57% (FY26, up from 7.95% FY25), within this total — VERIFIED from the top-10-shareholders table.</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>6-month change for SBI MF in Torrent Power (7.95%→8.57%) is now VERIFIED; other DII figures remain secondary-source.</t>
+          <t>All three VERIFIED from the FY25-26 Annual Reports' statutory category-wise shareholding tables; ties out exactly against the Free-float row below for all three companies (strong internal consistency check).</t>
         </is>
       </c>
     </row>
@@ -17305,20 +17313,24 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>9.62% (secondary-source snapshot)</t>
+          <t>9.66% = Indian Public &amp; others (5.24%) + Bodies Corporate (0.45%) + NRI/Foreign Nationals (0.19%) + Others (3.78%) — VERIFIED, same FY26 table.</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>~21.5-25.6% (free float, incl. FII+DII+public)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>~9.3-17.68% (conflicting by source/date)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr"/>
+          <t>26.19% = Resident Individuals &amp; HUF (22.01%) + Non-Resident Indians (1.30%) + Others (2.88%) — VERIFIED, FY26 Table 23.</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>11.10% = Non-Institutional Individuals (5.51%) + Body Corporates (2.77%) + Others (2.82%) — VERIFIED, FY26 'By category of Members' table.</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>All non-promoter, non-FII, non-DII categories combined; VERIFIED from the same FY26 statutory tables as the two rows above.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -17328,23 +17340,22 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>~25.04%</t>
+          <t>25.04% (= FII 11.73% + DII 3.65% + Public 9.66%, ties out exactly)</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>~53.14%</t>
+          <t>53.14% (≈ FII 10.04% + Insurance 7.77% + MF/UTI 9.15% + Public 26.19% = 53.15%, rounding)</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>~48.91%</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Approx.; = 100% - promoter%.</t>
-        </is>
+          <t>48.91% (= FII 8.40% + DII 21.06% + Central/State Govt 8.35% + Public 11.10%, ties out exactly)</t>
+        </is>
+      </c>
+      <c r="E11" s="16">
+        <f> 100% - promoter%; now cross-checked line-by-line against the FII/DII/Public rows above for all three companies.</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
@@ -17384,7 +17395,7 @@
     <row r="15" ht="100" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Adani Power has by far the highest promoter concentration (~75%) of the three, leaving the smallest free float (~25%) — typical of Adani Group listed entities, and a legacy of tightened promoter control after the 2023 Hindenburg-report episode (with an emphasis on 'zero pledge' messaging across group companies since). Tata Power's promoter stake (Tata Sons, ~47%) is the lowest of the three, giving it the widest institutional/public float and closest to the SEBI minimum public shareholding norms. Torrent Power sits in between (~51% promoter). Shareholding figures pulled from secondary aggregators showed real inconsistencies across sources/dates for FII/DII splits at all three companies — before using these in the final submission, pull ONE consistent-quarter shareholding-pattern XBRL filing per company directly from BSE/NSE (each company files this quarterly) rather than mixing snapshots from different dates.</t>
+          <t>Adani Power has by far the highest promoter concentration (~75%) of the three, leaving the smallest free float (~25%) — typical of Adani Group listed entities, and a legacy of tightened promoter control after the 2023 Hindenburg-report episode (with an emphasis on 'zero pledge' messaging across group companies since). Tata Power's promoter stake (Tata Sons, ~47%) is the lowest of the three, giving it the widest institutional/public float and closest to the SEBI minimum public shareholding norms. Torrent Power sits in between (~51% promoter). FII/DII/Public splits (previously flagged as conflicting across secondary sources) are now VERIFIED from each company's own FY25-26 Annual Report statutory shareholding table and tie out exactly to the free-float row for all three — Adani Power has the lowest FII+DII institutional ownership (~15.4% combined) of the three despite its high overall market cap, consistent with its concentrated promoter/retail-skewed float; Tata Power has the most balanced institutional base (FII ~10%, Insurance+DII ~18%); Torrent Power's free float includes a notable ~8.4% held by Central/State Government entities (chiefly GUVNL), on top of ~29.5% FII+DII.</t>
         </is>
       </c>
     </row>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -203,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,6 +261,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -281,7 +284,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -862,7 +864,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Segment Revenue Trends FY22-FY26 (₹ crore): Tata segments vs Adani Generation</a:t>
+              <a:t>Segment Revenue Trends FY22-FY26 (₹ crore): Tata segments vs Adani/Torrent Generation</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -996,6 +998,38 @@
           <val>
             <numRef>
               <f>'6b_Segment_Chart_Data'!$E$2:$E$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'6b_Segment_Chart_Data'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'6b_Segment_Chart_Data'!$F$2:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -1635,7 +1669,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4680000"/>
@@ -2237,7 +2271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2756,14 +2790,14 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>TORRENT POWER — NO reportable segments under Ind AS 108</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="95" customHeight="1">
+          <t>TORRENT POWER — Generation, Transmission &amp; Distribution, Renewables (reportable from FY23-24 onward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="100" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Per Note 53/54 ('Operating Segments') of Torrent Power's FY23 Annual Report (and equivalent notes in other years): "the Group does not have any reportable segment as per Ind AS-108 'Operating Segments'" — the CODM manages Generation, Transmission and Distribution as ONE integrated electricity business, and the cable business is immaterial (below reportable thresholds for revenue, profit and assets). This is an important verified correction: earlier drafts of this sheet assumed 3 reportable segments (Generation/Transmission/Distribution) from the MD&amp;A's business description — the MD&amp;A discusses those businesses operationally, but the statutory segment note reports a single segment. Any segment-level financial comparison for Torrent must therefore rely on MD&amp;A operating metrics (e.g., FY23 distribution electricity purchases +63.2% YoY to 30,037 MU after the DNH&amp;DD takeover), not audited segment P&amp;L data, because none is published.</t>
+          <t>VERIFIED CORRECTION: an earlier pass of this workbook found Torrent Power to have 'no reportable segments,' sourced from the FY22-23 Annual Report's Operating Segments note, which is genuinely correct FOR THAT YEAR — Note 53/54 of the FY22-23 AR states "the Group does not have any reportable segment as per Ind AS-108". However, the FY23-24 Annual Report's Note 52 explicitly states: "During the current year, in line with the reassessment for reporting financial information to the entity's chief operating decision maker (CODM), the Group has presented its segment information..." — i.e. Torrent Power's CODM reassessed segment reportability and started disclosing THREE segments (Generation, Transmission &amp; Distribution, Renewables) from FY23-24 onward, most likely because Renewables crossed the Ind AS 108 materiality threshold as it scaled. This is confirmed in the FY24-25 and FY25-26 Annual Reports too (same three segments, same wording). Only FY24-FY26 segment-level data is therefore available (no FY22/FY23 comparative, since no segment note existed then).</t>
         </is>
       </c>
     </row>
@@ -2774,30 +2808,310 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
+          <t>TORRENT POWER — Segment Trend, FY24-FY26 (Consolidated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Generation</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>7978.69</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>8180.99</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>7585.36</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>24391.25</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>25178.12</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>24764.42</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Segment Revenue — Renewables</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>1149.92</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>1066.3</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>1241.14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Segment Results — Generation</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>1147.5</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>1563.1</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>1319.73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Segment Results — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>2871.57</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>3359.68</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>3792.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>Segment Results — Renewables</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>1001.65</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>887.22</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>1012.42</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>Segment Assets — Generation</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>4806</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>4272.59</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>4425.56</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>Segment Assets — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>20169.02</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>21503.5</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>22202.29</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>Segment Assets — Renewables</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>8073.37</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>11786.11</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>17110.96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Profit Before Tax — Generation</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>1126.42</v>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>1011.37</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>Profit Before Tax — Transmission &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>1779.19</v>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>2177.01</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>Profit Before Tax — Renewables</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>114.19</v>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Revenue/Results/Assets from Note 52/53/54 'Operating Segments', Torrent Power Consolidated Financial Statements, AR FY23-24 (FY24 col.)/FY24-25 (FY25 col.)/FY25-26 (FY26 col.). Segment PBT (a separate reconciliation line in the same note) was not cleanly extractable for FY25 in this pass — flagged N/A rather than estimated. Revenue shown gross before inter-segment eliminations; T&amp;D also included the Power Cable business up to 16-Oct-2024 (since divested/discontinued).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Segment growth rate vs. industry growth rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="65" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Industry growth benchmarks (India, per CEA/CREA data, most recent available): overall electricity generation growth slowed to just ~3% YoY in Q4 FY26 (slowest in six years); renewable electricity generation grew ~20% in calendar 2025 (solar +24%, wind +11-28%); coal-fired generation actually FELL ~3.2% in 2025 amid muted demand growth and renewable curtailment pressures (≈27 GW solar and ≈4 GW wind directly curtailed in Q4 FY26 alone). Renewables' share of India's generation mix rose from 22.06% (FY25) to 25.86% (FY26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
           <t>Comparative analysis — who is doing well in which segment?</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>GENERATION is the only segment where all three effectively compete, and the verified numbers show a stark contrast: Adani Power's generation segment grew revenue ~2.0x (₹27,222cr FY22 → ₹54,241cr FY26) with segment results of ₹15,758-20,557cr in FY24-26 — vastly more profitable than Tata Power's generation segment (results of only ₹1,138-2,879cr on ₹11,636-19,739cr revenue in the same years, dragged by the Mundra plant's fuel economics and eventual shutdown). Adani is unambiguously the generation winner. RENEWABLES: only Tata Power reports it separately, and it is now their growth engine — revenue up ~1.9x (₹7,749cr FY22 → ₹15,028cr FY26), results up 2.3x (₹1,924cr → ₹4,341cr), and segment assets up 2.1x to ₹56,921cr, overtaking every other Tata segment. Adani Power has no renewables segment (that sits in sister company Adani Green). TRANSMISSION &amp; DISTRIBUTION: Tata Power's largest and steadiest segment — revenue grew ₹27,493cr → ₹41,339cr (FY22→FY26, boosted by the Odisha discoms) with consistently positive, regulated-return results (₹2,138cr → ₹4,308cr). Torrent's distribution business is economically similar (regulated, stable) but not separately reported. INDUSTRY CONTEXT: India's power demand grew ~7-8%/yr (CEA) over this period — Adani's generation growth (~13% CAGR) and Tata's renewables growth (~21% CAGR) both outpaced the sector, largely through acquisitions and capacity build-out respectively, while Tata's generation segment underperformed the sector.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
+    <row r="60" ht="130" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>GENERATION (comparable across all three — Adani Power's whole business, Tata Power's 'Thermal &amp; Hydro', Torrent's 'Generation'): Adani Power's generation revenue grew explosively in FY23-FY24 (+39.2%, +32.0%) as newly acquired/commissioned capacity ramped up — far outpacing the other two and the broader industry — before decelerating sharply to +12.2% (FY25) and turning NEGATIVE -3.3% (FY26). Torrent's Generation segment also declined -7.3% in FY26 (after a modest +2.5% in FY25). Tata Power's Thermal &amp; Hydro segment was essentially flat (+0.6%) FY24→FY25. All three companies' generation growth has converged toward — or fallen below — the industry-wide ~3% generation growth rate and the outright decline in coal generation, consistent with the sector-wide pattern of renewables displacing thermal dispatch. On PROFITABILITY, Adani Power's Generation segment is far larger in absolute PBT (₹15,757.55 Cr FY26) than either peer's comparable segment, reflecting its much larger scale, though its margin trajectory has also decelerated in step with revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="65" ht="130" customHeight="1">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>TRANSMISSION &amp; DISTRIBUTION (Tata Power vs. Torrent Power only — Adani Power has no T&amp;D segment): Tata Power's T&amp;D segment grew revenue +8.1% (FY24→FY25), notably faster than Torrent's +3.2% (FY24→FY25), and Torrent's T&amp;D revenue then DECLINED -1.6% in FY26. On segment RESULTS (profit), however, Torrent's T&amp;D segment results grew faster in relative terms — from ₹2,871.57 Cr (FY24) to ₹3,792.80 Cr (FY26), a ~32% cumulative increase over two years — versus Tata Power's T&amp;D results growing from ₹2,418.22 Cr (FY24) to ₹4,307.95 Cr (FY26), roughly ~78% cumulative. Tata Power's T&amp;D segment is also larger in absolute segment assets (₹53,428.87 Cr FY26 vs Torrent's ₹22,202.29 Cr), consistent with Tata Power's much larger discom footprint (Mumbai, Delhi JV, Odisha, Ajmer) versus Torrent's more concentrated Ahmedabad/Surat/Bhiwandi/Agra franchise areas. On a PROFIT-TO-ASSETS basis, though, Torrent's T&amp;D segment is notably more capital-efficient (segment results ~17% of segment assets in FY26, vs. Tata Power's ~8%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="70" ht="130" customHeight="1">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>RENEWABLES (Tata Power vs. Torrent Power only): the most dynamic segment for both peers. Tata Power's renewables SEGMENT ASSETS are far larger in absolute terms (₹56,921.28 Cr FY26) but grew only +10.8% (FY25→FY26); Torrent's renewables segment assets, while much smaller in absolute terms, grew far FASTER in relative terms — +46.0% (FY24→FY25) and +45.2% (FY25→FY26), more than doubling over two years (₹8,073 Cr → ₹17,111 Cr) — indicating Torrent is scaling its renewables capacity much more aggressively on a percentage basis, even as Tata Power remains the larger renewables player overall. On REVENUE, both companies' renewables segments actually underperformed the ~20-24% industry-wide renewable generation growth rate: Tata Power's renewables revenue DECLINED -2.9% (FY24→FY25) while Torrent's swung from -7.3% (FY25) to +16.4% (FY26) — the latter closer to, but still short of, the industry benchmark. This gap between strong ASSET/capacity growth and weaker REVENUE growth across both companies is consistent with the industry-wide renewable curtailment problem flagged by CREA (solar/wind capacity growing faster than the grid's ability to absorb and pay for that generation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="75" ht="130" customHeight="1">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>OVERALL: Torrent Power is the standout performer on relative (percentage) growth and capital efficiency across segments — especially in scaling Renewables assets — despite being the smallest of the three companies in absolute scale. Tata Power remains the largest and most diversified generator-cum-distributor, with the largest absolute Renewables and T&amp;D asset bases, but slower relative growth in the most recent year. Adani Power's single dominant Generation segment shows the most dramatic historical growth (driven by acquisitions) but is now the most exposed to the industry-wide deceleration in thermal generation, having no T&amp;D or standalone Renewables segment to diversify into for now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="A75:H78"/>
+    <mergeCell ref="A70:H73"/>
+    <mergeCell ref="A65:H68"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A60:H63"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A39:H47"/>
+    <mergeCell ref="A55:H57"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A32:H36"/>
     <mergeCell ref="A1:H1"/>
@@ -2813,7 +3127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2842,6 +3156,11 @@
           <t>Adani Generation Rev</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Torrent Generation Rev</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2899,6 +3218,9 @@
       <c r="E4" t="n">
         <v>50014.16</v>
       </c>
+      <c r="F4" t="n">
+        <v>7978.69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2918,6 +3240,9 @@
       <c r="E5" t="n">
         <v>56107.06</v>
       </c>
+      <c r="F5" t="n">
+        <v>8180.99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2936,6 +3261,9 @@
       </c>
       <c r="E6" t="n">
         <v>54240.52</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7585.36</v>
       </c>
     </row>
   </sheetData>
@@ -3837,7 +4165,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>All three companies' figures above are now extracted directly from the consolidated 'Investments' notes of the FY2022-23 Annual Reports uploaded to the repo. Common pattern: all three park treasury cash in liquid/overnight mutual funds; Torrent additionally holds regulatory-mandated GoI bonds (GERC contingency reserve); none runs a material discretionary securities portfolio.</t>
         </is>
@@ -4287,23 +4615,23 @@
           <t>Price at start (14-Jul-2025, adj)</t>
         </is>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="37">
         <f>'Weekly_Price_Data'!B2</f>
         <v/>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="37">
         <f>'Weekly_Price_Data'!C2</f>
         <v/>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="37">
         <f>'Weekly_Price_Data'!D2</f>
         <v/>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="37">
         <f>'Weekly_Price_Data'!E2</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="37">
         <f>'Weekly_Price_Data'!F2</f>
         <v/>
       </c>
@@ -4314,23 +4642,23 @@
           <t>Price at end (15-Jul-2026)</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="37">
         <f>'Weekly_Price_Data'!B54</f>
         <v/>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="37">
         <f>'Weekly_Price_Data'!C54</f>
         <v/>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="37">
         <f>'Weekly_Price_Data'!D54</f>
         <v/>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="37">
         <f>'Weekly_Price_Data'!E54</f>
         <v/>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="37">
         <f>'Weekly_Price_Data'!F54</f>
         <v/>
       </c>
@@ -4341,23 +4669,23 @@
           <t>52-week weekly-close range</t>
         </is>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="38">
         <f>MIN('Weekly_Price_Data'!B2:B54)&amp;" - "&amp;MAX('Weekly_Price_Data'!B2:B54)</f>
         <v/>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="38">
         <f>MIN('Weekly_Price_Data'!C2:C54)&amp;" - "&amp;MAX('Weekly_Price_Data'!C2:C54)</f>
         <v/>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="38">
         <f>MIN('Weekly_Price_Data'!D2:D54)&amp;" - "&amp;MAX('Weekly_Price_Data'!D2:D54)</f>
         <v/>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="38">
         <f>MIN('Weekly_Price_Data'!E2:E54)&amp;" - "&amp;MAX('Weekly_Price_Data'!E2:E54)</f>
         <v/>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="38">
         <f>MIN('Weekly_Price_Data'!F2:F54)&amp;" - "&amp;MAX('Weekly_Price_Data'!F2:F54)</f>
         <v/>
       </c>
@@ -4368,23 +4696,23 @@
           <t>1-year return (COMPUTED)</t>
         </is>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="39">
         <f>'Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1</f>
         <v/>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="39">
         <f>'Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1</f>
         <v/>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="39">
         <f>'Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1</f>
         <v/>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="39">
         <f>'Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1</f>
         <v/>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="39">
         <f>'Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1</f>
         <v/>
       </c>
@@ -4395,23 +4723,23 @@
           <t>Weekly return std dev (COMPUTED)</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="40">
         <f>STDEV('Weekly_Price_Data'!G3:G54)</f>
         <v/>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="40">
         <f>STDEV('Weekly_Price_Data'!H3:H54)</f>
         <v/>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="40">
         <f>STDEV('Weekly_Price_Data'!I3:I54)</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="40">
         <f>STDEV('Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="40">
         <f>STDEV('Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
@@ -4422,23 +4750,23 @@
           <t>Annualized volatility = sd x sqrt(52)</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="39">
         <f>STDEV('Weekly_Price_Data'!G3:G54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="39">
         <f>STDEV('Weekly_Price_Data'!H3:H54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="39">
         <f>STDEV('Weekly_Price_Data'!I3:I54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="39">
         <f>STDEV('Weekly_Price_Data'!J3:J54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="39">
         <f>STDEV('Weekly_Price_Data'!K3:K54)*SQRT(52)</f>
         <v/>
       </c>
@@ -4449,23 +4777,23 @@
           <t>Beta vs Nifty 50 / market (COMPUTED)</t>
         </is>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="37">
         <f>SLOPE('Weekly_Price_Data'!G3:G54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="37">
         <f>SLOPE('Weekly_Price_Data'!H3:H54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="37">
         <f>SLOPE('Weekly_Price_Data'!I3:I54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="37">
         <f>SLOPE('Weekly_Price_Data'!J3:J54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="37">
         <f>1</f>
         <v/>
       </c>
@@ -4476,23 +4804,23 @@
           <t>Beta vs Nifty Energy / sector (COMPUTED)</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="37">
         <f>SLOPE('Weekly_Price_Data'!G3:G54,'Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="37">
         <f>SLOPE('Weekly_Price_Data'!H3:H54,'Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="37">
         <f>SLOPE('Weekly_Price_Data'!I3:I54,'Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="37">
         <f>1</f>
         <v/>
       </c>
-      <c r="F13" s="38" t="n"/>
+      <c r="F13" s="41" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -4500,23 +4828,23 @@
           <t>Return vs market (stock - Nifty 50)</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="39">
         <f>('Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="39">
         <f>('Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="39">
         <f>('Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="39">
         <f>('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="F14" s="39" t="n"/>
+      <c r="F14" s="42" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -4524,23 +4852,23 @@
           <t>Return vs sector (stock - Nifty Energy)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="39">
         <f>('Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
         <v/>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="39">
         <f>('Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="39">
         <f>('Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
         <v/>
       </c>
-      <c r="E15" s="39" t="n"/>
-      <c r="F15" s="39" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Data note</t>
         </is>
@@ -4760,23 +5088,23 @@
       <c r="F3" t="n">
         <v>24837</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="35">
         <f>B3/B2-1</f>
         <v/>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="35">
         <f>C3/C2-1</f>
         <v/>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="35">
         <f>D3/D2-1</f>
         <v/>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="35">
         <f>E3/E2-1</f>
         <v/>
       </c>
-      <c r="K3" s="41">
+      <c r="K3" s="35">
         <f>F3/F2-1</f>
         <v/>
       </c>
@@ -4822,23 +5150,23 @@
       <c r="F4" t="n">
         <v>24565.35</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="35">
         <f>B4/B3-1</f>
         <v/>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="35">
         <f>C4/C3-1</f>
         <v/>
       </c>
-      <c r="I4" s="41">
+      <c r="I4" s="35">
         <f>D4/D3-1</f>
         <v/>
       </c>
-      <c r="J4" s="41">
+      <c r="J4" s="35">
         <f>E4/E3-1</f>
         <v/>
       </c>
-      <c r="K4" s="41">
+      <c r="K4" s="35">
         <f>F4/F3-1</f>
         <v/>
       </c>
@@ -4884,23 +5212,23 @@
       <c r="F5" t="n">
         <v>24363.3</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="35">
         <f>B5/B4-1</f>
         <v/>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="35">
         <f>C5/C4-1</f>
         <v/>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="35">
         <f>D5/D4-1</f>
         <v/>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="35">
         <f>E5/E4-1</f>
         <v/>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="35">
         <f>F5/F4-1</f>
         <v/>
       </c>
@@ -4946,23 +5274,23 @@
       <c r="F6" t="n">
         <v>24631.3</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="35">
         <f>B6/B5-1</f>
         <v/>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="35">
         <f>C6/C5-1</f>
         <v/>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="35">
         <f>D6/D5-1</f>
         <v/>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="35">
         <f>E6/E5-1</f>
         <v/>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="35">
         <f>F6/F5-1</f>
         <v/>
       </c>
@@ -5008,23 +5336,23 @@
       <c r="F7" t="n">
         <v>24870.1</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="35">
         <f>B7/B6-1</f>
         <v/>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="35">
         <f>C7/C6-1</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="35">
         <f>D7/D6-1</f>
         <v/>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="35">
         <f>E7/E6-1</f>
         <v/>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="35">
         <f>F7/F6-1</f>
         <v/>
       </c>
@@ -5070,23 +5398,23 @@
       <c r="F8" t="n">
         <v>24426.85</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="35">
         <f>B8/B7-1</f>
         <v/>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="35">
         <f>C8/C7-1</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="35">
         <f>D8/D7-1</f>
         <v/>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="35">
         <f>E8/E7-1</f>
         <v/>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="35">
         <f>F8/F7-1</f>
         <v/>
       </c>
@@ -5132,23 +5460,23 @@
       <c r="F9" t="n">
         <v>24741</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="35">
         <f>B9/B8-1</f>
         <v/>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="35">
         <f>C9/C8-1</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="35">
         <f>D9/D8-1</f>
         <v/>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="35">
         <f>E9/E8-1</f>
         <v/>
       </c>
-      <c r="K9" s="41">
+      <c r="K9" s="35">
         <f>F9/F8-1</f>
         <v/>
       </c>
@@ -5194,23 +5522,23 @@
       <c r="F10" t="n">
         <v>25114</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="35">
         <f>B10/B9-1</f>
         <v/>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="35">
         <f>C10/C9-1</f>
         <v/>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="35">
         <f>D10/D9-1</f>
         <v/>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="35">
         <f>E10/E9-1</f>
         <v/>
       </c>
-      <c r="K10" s="41">
+      <c r="K10" s="35">
         <f>F10/F9-1</f>
         <v/>
       </c>
@@ -5256,23 +5584,23 @@
       <c r="F11" t="n">
         <v>25327.05</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="35">
         <f>B11/B10-1</f>
         <v/>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="35">
         <f>C11/C10-1</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="35">
         <f>D11/D10-1</f>
         <v/>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="35">
         <f>E11/E10-1</f>
         <v/>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="35">
         <f>F11/F10-1</f>
         <v/>
       </c>
@@ -5318,23 +5646,23 @@
       <c r="F12" t="n">
         <v>24654.7</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="35">
         <f>B12/B11-1</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="35">
         <f>C12/C11-1</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="35">
         <f>D12/D11-1</f>
         <v/>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="35">
         <f>E12/E11-1</f>
         <v/>
       </c>
-      <c r="K12" s="41">
+      <c r="K12" s="35">
         <f>F12/F11-1</f>
         <v/>
       </c>
@@ -5380,23 +5708,23 @@
       <c r="F13" t="n">
         <v>24894.25</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="35">
         <f>B13/B12-1</f>
         <v/>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="35">
         <f>C13/C12-1</f>
         <v/>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="35">
         <f>D13/D12-1</f>
         <v/>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="35">
         <f>E13/E12-1</f>
         <v/>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="35">
         <f>F13/F12-1</f>
         <v/>
       </c>
@@ -5442,23 +5770,23 @@
       <c r="F14" t="n">
         <v>25285.35</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="35">
         <f>B14/B13-1</f>
         <v/>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="35">
         <f>C14/C13-1</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="35">
         <f>D14/D13-1</f>
         <v/>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="35">
         <f>E14/E13-1</f>
         <v/>
       </c>
-      <c r="K14" s="41">
+      <c r="K14" s="35">
         <f>F14/F13-1</f>
         <v/>
       </c>
@@ -5504,23 +5832,23 @@
       <c r="F15" t="n">
         <v>25709.85</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="35">
         <f>B15/B14-1</f>
         <v/>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="35">
         <f>C15/C14-1</f>
         <v/>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="35">
         <f>D15/D14-1</f>
         <v/>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="35">
         <f>E15/E14-1</f>
         <v/>
       </c>
-      <c r="K15" s="41">
+      <c r="K15" s="35">
         <f>F15/F14-1</f>
         <v/>
       </c>
@@ -5566,23 +5894,23 @@
       <c r="F16" t="n">
         <v>25795.15</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="35">
         <f>B16/B15-1</f>
         <v/>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="35">
         <f>C16/C15-1</f>
         <v/>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="35">
         <f>D16/D15-1</f>
         <v/>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="35">
         <f>E16/E15-1</f>
         <v/>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="35">
         <f>F16/F15-1</f>
         <v/>
       </c>
@@ -5628,23 +5956,23 @@
       <c r="F17" t="n">
         <v>25722.1</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="35">
         <f>B17/B16-1</f>
         <v/>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="35">
         <f>C17/C16-1</f>
         <v/>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="35">
         <f>D17/D16-1</f>
         <v/>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="35">
         <f>E17/E16-1</f>
         <v/>
       </c>
-      <c r="K17" s="41">
+      <c r="K17" s="35">
         <f>F17/F16-1</f>
         <v/>
       </c>
@@ -5690,23 +6018,23 @@
       <c r="F18" t="n">
         <v>25492.3</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="35">
         <f>B18/B17-1</f>
         <v/>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="35">
         <f>C18/C17-1</f>
         <v/>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="35">
         <f>D18/D17-1</f>
         <v/>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="35">
         <f>E18/E17-1</f>
         <v/>
       </c>
-      <c r="K18" s="41">
+      <c r="K18" s="35">
         <f>F18/F17-1</f>
         <v/>
       </c>
@@ -5752,23 +6080,23 @@
       <c r="F19" t="n">
         <v>25910.05</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="35">
         <f>B19/B18-1</f>
         <v/>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="35">
         <f>C19/C18-1</f>
         <v/>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="35">
         <f>D19/D18-1</f>
         <v/>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="35">
         <f>E19/E18-1</f>
         <v/>
       </c>
-      <c r="K19" s="41">
+      <c r="K19" s="35">
         <f>F19/F18-1</f>
         <v/>
       </c>
@@ -5814,23 +6142,23 @@
       <c r="F20" t="n">
         <v>26068.15</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="35">
         <f>B20/B19-1</f>
         <v/>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="35">
         <f>C20/C19-1</f>
         <v/>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="35">
         <f>D20/D19-1</f>
         <v/>
       </c>
-      <c r="J20" s="41">
+      <c r="J20" s="35">
         <f>E20/E19-1</f>
         <v/>
       </c>
-      <c r="K20" s="41">
+      <c r="K20" s="35">
         <f>F20/F19-1</f>
         <v/>
       </c>
@@ -5876,23 +6204,23 @@
       <c r="F21" t="n">
         <v>26202.95</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="35">
         <f>B21/B20-1</f>
         <v/>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="35">
         <f>C21/C20-1</f>
         <v/>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="35">
         <f>D21/D20-1</f>
         <v/>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="35">
         <f>E21/E20-1</f>
         <v/>
       </c>
-      <c r="K21" s="41">
+      <c r="K21" s="35">
         <f>F21/F20-1</f>
         <v/>
       </c>
@@ -5938,23 +6266,23 @@
       <c r="F22" t="n">
         <v>26186.45</v>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="35">
         <f>B22/B21-1</f>
         <v/>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="35">
         <f>C22/C21-1</f>
         <v/>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="35">
         <f>D22/D21-1</f>
         <v/>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="35">
         <f>E22/E21-1</f>
         <v/>
       </c>
-      <c r="K22" s="41">
+      <c r="K22" s="35">
         <f>F22/F21-1</f>
         <v/>
       </c>
@@ -6000,23 +6328,23 @@
       <c r="F23" t="n">
         <v>26046.95</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="35">
         <f>B23/B22-1</f>
         <v/>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="35">
         <f>C23/C22-1</f>
         <v/>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="35">
         <f>D23/D22-1</f>
         <v/>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="35">
         <f>E23/E22-1</f>
         <v/>
       </c>
-      <c r="K23" s="41">
+      <c r="K23" s="35">
         <f>F23/F22-1</f>
         <v/>
       </c>
@@ -6062,23 +6390,23 @@
       <c r="F24" t="n">
         <v>25966.4</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="35">
         <f>B24/B23-1</f>
         <v/>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="35">
         <f>C24/C23-1</f>
         <v/>
       </c>
-      <c r="I24" s="41">
+      <c r="I24" s="35">
         <f>D24/D23-1</f>
         <v/>
       </c>
-      <c r="J24" s="41">
+      <c r="J24" s="35">
         <f>E24/E23-1</f>
         <v/>
       </c>
-      <c r="K24" s="41">
+      <c r="K24" s="35">
         <f>F24/F23-1</f>
         <v/>
       </c>
@@ -6124,23 +6452,23 @@
       <c r="F25" t="n">
         <v>26042.3</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="35">
         <f>B25/B24-1</f>
         <v/>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="35">
         <f>C25/C24-1</f>
         <v/>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="35">
         <f>D25/D24-1</f>
         <v/>
       </c>
-      <c r="J25" s="41">
+      <c r="J25" s="35">
         <f>E25/E24-1</f>
         <v/>
       </c>
-      <c r="K25" s="41">
+      <c r="K25" s="35">
         <f>F25/F24-1</f>
         <v/>
       </c>
@@ -6186,23 +6514,23 @@
       <c r="F26" t="n">
         <v>26328.55</v>
       </c>
-      <c r="G26" s="41">
+      <c r="G26" s="35">
         <f>B26/B25-1</f>
         <v/>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="35">
         <f>C26/C25-1</f>
         <v/>
       </c>
-      <c r="I26" s="41">
+      <c r="I26" s="35">
         <f>D26/D25-1</f>
         <v/>
       </c>
-      <c r="J26" s="41">
+      <c r="J26" s="35">
         <f>E26/E25-1</f>
         <v/>
       </c>
-      <c r="K26" s="41">
+      <c r="K26" s="35">
         <f>F26/F25-1</f>
         <v/>
       </c>
@@ -6248,23 +6576,23 @@
       <c r="F27" t="n">
         <v>25683.3</v>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="35">
         <f>B27/B26-1</f>
         <v/>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="35">
         <f>C27/C26-1</f>
         <v/>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="35">
         <f>D27/D26-1</f>
         <v/>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="35">
         <f>E27/E26-1</f>
         <v/>
       </c>
-      <c r="K27" s="41">
+      <c r="K27" s="35">
         <f>F27/F26-1</f>
         <v/>
       </c>
@@ -6310,23 +6638,23 @@
       <c r="F28" t="n">
         <v>25694.35</v>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="35">
         <f>B28/B27-1</f>
         <v/>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="35">
         <f>C28/C27-1</f>
         <v/>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="35">
         <f>D28/D27-1</f>
         <v/>
       </c>
-      <c r="J28" s="41">
+      <c r="J28" s="35">
         <f>E28/E27-1</f>
         <v/>
       </c>
-      <c r="K28" s="41">
+      <c r="K28" s="35">
         <f>F28/F27-1</f>
         <v/>
       </c>
@@ -6372,23 +6700,23 @@
       <c r="F29" t="n">
         <v>25048.65</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="35">
         <f>B29/B28-1</f>
         <v/>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="35">
         <f>C29/C28-1</f>
         <v/>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="35">
         <f>D29/D28-1</f>
         <v/>
       </c>
-      <c r="J29" s="41">
+      <c r="J29" s="35">
         <f>E29/E28-1</f>
         <v/>
       </c>
-      <c r="K29" s="41">
+      <c r="K29" s="35">
         <f>F29/F28-1</f>
         <v/>
       </c>
@@ -6434,23 +6762,23 @@
       <c r="F30" t="n">
         <v>24825.45</v>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="35">
         <f>B30/B29-1</f>
         <v/>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="35">
         <f>C30/C29-1</f>
         <v/>
       </c>
-      <c r="I30" s="41">
+      <c r="I30" s="35">
         <f>D30/D29-1</f>
         <v/>
       </c>
-      <c r="J30" s="41">
+      <c r="J30" s="35">
         <f>E30/E29-1</f>
         <v/>
       </c>
-      <c r="K30" s="41">
+      <c r="K30" s="35">
         <f>F30/F29-1</f>
         <v/>
       </c>
@@ -6496,23 +6824,23 @@
       <c r="F31" t="n">
         <v>25693.7</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="35">
         <f>B31/B30-1</f>
         <v/>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="35">
         <f>C31/C30-1</f>
         <v/>
       </c>
-      <c r="I31" s="41">
+      <c r="I31" s="35">
         <f>D31/D30-1</f>
         <v/>
       </c>
-      <c r="J31" s="41">
+      <c r="J31" s="35">
         <f>E31/E30-1</f>
         <v/>
       </c>
-      <c r="K31" s="41">
+      <c r="K31" s="35">
         <f>F31/F30-1</f>
         <v/>
       </c>
@@ -6558,23 +6886,23 @@
       <c r="F32" t="n">
         <v>25471.1</v>
       </c>
-      <c r="G32" s="41">
+      <c r="G32" s="35">
         <f>B32/B31-1</f>
         <v/>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="35">
         <f>C32/C31-1</f>
         <v/>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="35">
         <f>D32/D31-1</f>
         <v/>
       </c>
-      <c r="J32" s="41">
+      <c r="J32" s="35">
         <f>E32/E31-1</f>
         <v/>
       </c>
-      <c r="K32" s="41">
+      <c r="K32" s="35">
         <f>F32/F31-1</f>
         <v/>
       </c>
@@ -6620,23 +6948,23 @@
       <c r="F33" t="n">
         <v>25571.25</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="35">
         <f>B33/B32-1</f>
         <v/>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="35">
         <f>C33/C32-1</f>
         <v/>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="35">
         <f>D33/D32-1</f>
         <v/>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="35">
         <f>E33/E32-1</f>
         <v/>
       </c>
-      <c r="K33" s="41">
+      <c r="K33" s="35">
         <f>F33/F32-1</f>
         <v/>
       </c>
@@ -6682,23 +7010,23 @@
       <c r="F34" t="n">
         <v>25178.65</v>
       </c>
-      <c r="G34" s="41">
+      <c r="G34" s="35">
         <f>B34/B33-1</f>
         <v/>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="35">
         <f>C34/C33-1</f>
         <v/>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="35">
         <f>D34/D33-1</f>
         <v/>
       </c>
-      <c r="J34" s="41">
+      <c r="J34" s="35">
         <f>E34/E33-1</f>
         <v/>
       </c>
-      <c r="K34" s="41">
+      <c r="K34" s="35">
         <f>F34/F33-1</f>
         <v/>
       </c>
@@ -6744,23 +7072,23 @@
       <c r="F35" t="n">
         <v>24450.45</v>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="35">
         <f>B35/B34-1</f>
         <v/>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="35">
         <f>C35/C34-1</f>
         <v/>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="35">
         <f>D35/D34-1</f>
         <v/>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="35">
         <f>E35/E34-1</f>
         <v/>
       </c>
-      <c r="K35" s="41">
+      <c r="K35" s="35">
         <f>F35/F34-1</f>
         <v/>
       </c>
@@ -6806,23 +7134,23 @@
       <c r="F36" t="n">
         <v>23151.1</v>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="35">
         <f>B36/B35-1</f>
         <v/>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="35">
         <f>C36/C35-1</f>
         <v/>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="35">
         <f>D36/D35-1</f>
         <v/>
       </c>
-      <c r="J36" s="41">
+      <c r="J36" s="35">
         <f>E36/E35-1</f>
         <v/>
       </c>
-      <c r="K36" s="41">
+      <c r="K36" s="35">
         <f>F36/F35-1</f>
         <v/>
       </c>
@@ -6868,23 +7196,23 @@
       <c r="F37" t="n">
         <v>23114.5</v>
       </c>
-      <c r="G37" s="41">
+      <c r="G37" s="35">
         <f>B37/B36-1</f>
         <v/>
       </c>
-      <c r="H37" s="41">
+      <c r="H37" s="35">
         <f>C37/C36-1</f>
         <v/>
       </c>
-      <c r="I37" s="41">
+      <c r="I37" s="35">
         <f>D37/D36-1</f>
         <v/>
       </c>
-      <c r="J37" s="41">
+      <c r="J37" s="35">
         <f>E37/E36-1</f>
         <v/>
       </c>
-      <c r="K37" s="41">
+      <c r="K37" s="35">
         <f>F37/F36-1</f>
         <v/>
       </c>
@@ -6930,23 +7258,23 @@
       <c r="F38" t="n">
         <v>22819.6</v>
       </c>
-      <c r="G38" s="41">
+      <c r="G38" s="35">
         <f>B38/B37-1</f>
         <v/>
       </c>
-      <c r="H38" s="41">
+      <c r="H38" s="35">
         <f>C38/C37-1</f>
         <v/>
       </c>
-      <c r="I38" s="41">
+      <c r="I38" s="35">
         <f>D38/D37-1</f>
         <v/>
       </c>
-      <c r="J38" s="41">
+      <c r="J38" s="35">
         <f>E38/E37-1</f>
         <v/>
       </c>
-      <c r="K38" s="41">
+      <c r="K38" s="35">
         <f>F38/F37-1</f>
         <v/>
       </c>
@@ -6992,23 +7320,23 @@
       <c r="F39" t="n">
         <v>22713.1</v>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="35">
         <f>B39/B38-1</f>
         <v/>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="35">
         <f>C39/C38-1</f>
         <v/>
       </c>
-      <c r="I39" s="41">
+      <c r="I39" s="35">
         <f>D39/D38-1</f>
         <v/>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="35">
         <f>E39/E38-1</f>
         <v/>
       </c>
-      <c r="K39" s="41">
+      <c r="K39" s="35">
         <f>F39/F38-1</f>
         <v/>
       </c>
@@ -7054,23 +7382,23 @@
       <c r="F40" t="n">
         <v>24050.6</v>
       </c>
-      <c r="G40" s="41">
+      <c r="G40" s="35">
         <f>B40/B39-1</f>
         <v/>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="35">
         <f>C40/C39-1</f>
         <v/>
       </c>
-      <c r="I40" s="41">
+      <c r="I40" s="35">
         <f>D40/D39-1</f>
         <v/>
       </c>
-      <c r="J40" s="41">
+      <c r="J40" s="35">
         <f>E40/E39-1</f>
         <v/>
       </c>
-      <c r="K40" s="41">
+      <c r="K40" s="35">
         <f>F40/F39-1</f>
         <v/>
       </c>
@@ -7116,23 +7444,23 @@
       <c r="F41" t="n">
         <v>24353.55</v>
       </c>
-      <c r="G41" s="41">
+      <c r="G41" s="35">
         <f>B41/B40-1</f>
         <v/>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="35">
         <f>C41/C40-1</f>
         <v/>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="35">
         <f>D41/D40-1</f>
         <v/>
       </c>
-      <c r="J41" s="41">
+      <c r="J41" s="35">
         <f>E41/E40-1</f>
         <v/>
       </c>
-      <c r="K41" s="41">
+      <c r="K41" s="35">
         <f>F41/F40-1</f>
         <v/>
       </c>
@@ -7178,23 +7506,23 @@
       <c r="F42" t="n">
         <v>23897.95</v>
       </c>
-      <c r="G42" s="41">
+      <c r="G42" s="35">
         <f>B42/B41-1</f>
         <v/>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="35">
         <f>C42/C41-1</f>
         <v/>
       </c>
-      <c r="I42" s="41">
+      <c r="I42" s="35">
         <f>D42/D41-1</f>
         <v/>
       </c>
-      <c r="J42" s="41">
+      <c r="J42" s="35">
         <f>E42/E41-1</f>
         <v/>
       </c>
-      <c r="K42" s="41">
+      <c r="K42" s="35">
         <f>F42/F41-1</f>
         <v/>
       </c>
@@ -7240,23 +7568,23 @@
       <c r="F43" t="n">
         <v>23997.55</v>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="35">
         <f>B43/B42-1</f>
         <v/>
       </c>
-      <c r="H43" s="41">
+      <c r="H43" s="35">
         <f>C43/C42-1</f>
         <v/>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="35">
         <f>D43/D42-1</f>
         <v/>
       </c>
-      <c r="J43" s="41">
+      <c r="J43" s="35">
         <f>E43/E42-1</f>
         <v/>
       </c>
-      <c r="K43" s="41">
+      <c r="K43" s="35">
         <f>F43/F42-1</f>
         <v/>
       </c>
@@ -7302,23 +7630,23 @@
       <c r="F44" t="n">
         <v>24176.15</v>
       </c>
-      <c r="G44" s="41">
+      <c r="G44" s="35">
         <f>B44/B43-1</f>
         <v/>
       </c>
-      <c r="H44" s="41">
+      <c r="H44" s="35">
         <f>C44/C43-1</f>
         <v/>
       </c>
-      <c r="I44" s="41">
+      <c r="I44" s="35">
         <f>D44/D43-1</f>
         <v/>
       </c>
-      <c r="J44" s="41">
+      <c r="J44" s="35">
         <f>E44/E43-1</f>
         <v/>
       </c>
-      <c r="K44" s="41">
+      <c r="K44" s="35">
         <f>F44/F43-1</f>
         <v/>
       </c>
@@ -7364,23 +7692,23 @@
       <c r="F45" t="n">
         <v>23643.5</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="35">
         <f>B45/B44-1</f>
         <v/>
       </c>
-      <c r="H45" s="41">
+      <c r="H45" s="35">
         <f>C45/C44-1</f>
         <v/>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="35">
         <f>D45/D44-1</f>
         <v/>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="35">
         <f>E45/E44-1</f>
         <v/>
       </c>
-      <c r="K45" s="41">
+      <c r="K45" s="35">
         <f>F45/F44-1</f>
         <v/>
       </c>
@@ -7426,23 +7754,23 @@
       <c r="F46" t="n">
         <v>23719.3</v>
       </c>
-      <c r="G46" s="41">
+      <c r="G46" s="35">
         <f>B46/B45-1</f>
         <v/>
       </c>
-      <c r="H46" s="41">
+      <c r="H46" s="35">
         <f>C46/C45-1</f>
         <v/>
       </c>
-      <c r="I46" s="41">
+      <c r="I46" s="35">
         <f>D46/D45-1</f>
         <v/>
       </c>
-      <c r="J46" s="41">
+      <c r="J46" s="35">
         <f>E46/E45-1</f>
         <v/>
       </c>
-      <c r="K46" s="41">
+      <c r="K46" s="35">
         <f>F46/F45-1</f>
         <v/>
       </c>
@@ -7488,23 +7816,23 @@
       <c r="F47" t="n">
         <v>23547.75</v>
       </c>
-      <c r="G47" s="41">
+      <c r="G47" s="35">
         <f>B47/B46-1</f>
         <v/>
       </c>
-      <c r="H47" s="41">
+      <c r="H47" s="35">
         <f>C47/C46-1</f>
         <v/>
       </c>
-      <c r="I47" s="41">
+      <c r="I47" s="35">
         <f>D47/D46-1</f>
         <v/>
       </c>
-      <c r="J47" s="41">
+      <c r="J47" s="35">
         <f>E47/E46-1</f>
         <v/>
       </c>
-      <c r="K47" s="41">
+      <c r="K47" s="35">
         <f>F47/F46-1</f>
         <v/>
       </c>
@@ -7550,23 +7878,23 @@
       <c r="F48" t="n">
         <v>23366.7</v>
       </c>
-      <c r="G48" s="41">
+      <c r="G48" s="35">
         <f>B48/B47-1</f>
         <v/>
       </c>
-      <c r="H48" s="41">
+      <c r="H48" s="35">
         <f>C48/C47-1</f>
         <v/>
       </c>
-      <c r="I48" s="41">
+      <c r="I48" s="35">
         <f>D48/D47-1</f>
         <v/>
       </c>
-      <c r="J48" s="41">
+      <c r="J48" s="35">
         <f>E48/E47-1</f>
         <v/>
       </c>
-      <c r="K48" s="41">
+      <c r="K48" s="35">
         <f>F48/F47-1</f>
         <v/>
       </c>
@@ -7612,23 +7940,23 @@
       <c r="F49" t="n">
         <v>23622.9</v>
       </c>
-      <c r="G49" s="41">
+      <c r="G49" s="35">
         <f>B49/B48-1</f>
         <v/>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="35">
         <f>C49/C48-1</f>
         <v/>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="35">
         <f>D49/D48-1</f>
         <v/>
       </c>
-      <c r="J49" s="41">
+      <c r="J49" s="35">
         <f>E49/E48-1</f>
         <v/>
       </c>
-      <c r="K49" s="41">
+      <c r="K49" s="35">
         <f>F49/F48-1</f>
         <v/>
       </c>
@@ -7674,23 +8002,23 @@
       <c r="F50" t="n">
         <v>24013.1</v>
       </c>
-      <c r="G50" s="41">
+      <c r="G50" s="35">
         <f>B50/B49-1</f>
         <v/>
       </c>
-      <c r="H50" s="41">
+      <c r="H50" s="35">
         <f>C50/C49-1</f>
         <v/>
       </c>
-      <c r="I50" s="41">
+      <c r="I50" s="35">
         <f>D50/D49-1</f>
         <v/>
       </c>
-      <c r="J50" s="41">
+      <c r="J50" s="35">
         <f>E50/E49-1</f>
         <v/>
       </c>
-      <c r="K50" s="41">
+      <c r="K50" s="35">
         <f>F50/F49-1</f>
         <v/>
       </c>
@@ -7736,23 +8064,23 @@
       <c r="F51" t="n">
         <v>24056</v>
       </c>
-      <c r="G51" s="41">
+      <c r="G51" s="35">
         <f>B51/B50-1</f>
         <v/>
       </c>
-      <c r="H51" s="41">
+      <c r="H51" s="35">
         <f>C51/C50-1</f>
         <v/>
       </c>
-      <c r="I51" s="41">
+      <c r="I51" s="35">
         <f>D51/D50-1</f>
         <v/>
       </c>
-      <c r="J51" s="41">
+      <c r="J51" s="35">
         <f>E51/E50-1</f>
         <v/>
       </c>
-      <c r="K51" s="41">
+      <c r="K51" s="35">
         <f>F51/F50-1</f>
         <v/>
       </c>
@@ -7798,23 +8126,23 @@
       <c r="F52" t="n">
         <v>24270.85</v>
       </c>
-      <c r="G52" s="41">
+      <c r="G52" s="35">
         <f>B52/B51-1</f>
         <v/>
       </c>
-      <c r="H52" s="41">
+      <c r="H52" s="35">
         <f>C52/C51-1</f>
         <v/>
       </c>
-      <c r="I52" s="41">
+      <c r="I52" s="35">
         <f>D52/D51-1</f>
         <v/>
       </c>
-      <c r="J52" s="41">
+      <c r="J52" s="35">
         <f>E52/E51-1</f>
         <v/>
       </c>
-      <c r="K52" s="41">
+      <c r="K52" s="35">
         <f>F52/F51-1</f>
         <v/>
       </c>
@@ -7860,23 +8188,23 @@
       <c r="F53" t="n">
         <v>24206.9</v>
       </c>
-      <c r="G53" s="41">
+      <c r="G53" s="35">
         <f>B53/B52-1</f>
         <v/>
       </c>
-      <c r="H53" s="41">
+      <c r="H53" s="35">
         <f>C53/C52-1</f>
         <v/>
       </c>
-      <c r="I53" s="41">
+      <c r="I53" s="35">
         <f>D53/D52-1</f>
         <v/>
       </c>
-      <c r="J53" s="41">
+      <c r="J53" s="35">
         <f>E53/E52-1</f>
         <v/>
       </c>
-      <c r="K53" s="41">
+      <c r="K53" s="35">
         <f>F53/F52-1</f>
         <v/>
       </c>
@@ -7922,23 +8250,23 @@
       <c r="F54" t="n">
         <v>24078.5</v>
       </c>
-      <c r="G54" s="41">
+      <c r="G54" s="35">
         <f>B54/B53-1</f>
         <v/>
       </c>
-      <c r="H54" s="41">
+      <c r="H54" s="35">
         <f>C54/C53-1</f>
         <v/>
       </c>
-      <c r="I54" s="41">
+      <c r="I54" s="35">
         <f>D54/D53-1</f>
         <v/>
       </c>
-      <c r="J54" s="41">
+      <c r="J54" s="35">
         <f>E54/E53-1</f>
         <v/>
       </c>
-      <c r="K54" s="41">
+      <c r="K54" s="35">
         <f>F54/F53-1</f>
         <v/>
       </c>
@@ -9492,7 +9820,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>Consolidated-vs-Standalone audit (line-by-line re-verification)</t>
         </is>
@@ -10087,309 +10415,309 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23 (AR_22088), FY23-24 (AR_24072), FY24-25 (ADANIPOWER-2025) and FY25-26 (AR_29298) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them — click any total to see exactly what it adds up.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n"/>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n"/>
-      <c r="C6" s="47" t="n"/>
-      <c r="D6" s="47" t="n"/>
-      <c r="E6" s="47" t="n"/>
-      <c r="F6" s="47" t="n"/>
+      <c r="B6" s="49" t="n"/>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>66814.60000000001</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="49" t="n">
         <v>66707.23</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="49" t="n">
         <v>62812.71</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="49" t="n">
         <v>50543.8</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="49" t="n">
         <v>53071.62</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Right-of-use Assets</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="49" t="n">
         <v>2261.28</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="49" t="n">
         <v>2319.82</v>
       </c>
-      <c r="D8" s="47" t="n"/>
-      <c r="E8" s="47" t="n"/>
-      <c r="F8" s="47" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>35053.46</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="49" t="n">
         <v>12104.42</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="49" t="n">
         <v>925.12</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="49" t="n">
         <v>12879.54</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="49" t="n">
         <v>10269.74</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Investment Property</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>92.25</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>48.69</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>704.9400000000001</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>204.52</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="49" t="n">
         <v>204.52</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="49" t="n">
         <v>190.61</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="49" t="n">
         <v>190.61</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="49" t="n">
         <v>190.61</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>28.81</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>17.19</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="49" t="n">
         <v>12.53</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="49" t="n">
         <v>12.03</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="49" t="n">
         <v>11.98</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Investments (Non-current)</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>24.64</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="49" t="n">
         <v>59.51</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="49" t="n">
         <v>0.01</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="49" t="n">
         <v>42.51</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="49" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="49" t="n">
         <v>7.5</v>
       </c>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="E14" s="47" t="n"/>
-      <c r="F14" s="47" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>690.36</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="49" t="n">
         <v>691.41</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="49" t="n">
         <v>636.2</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="49" t="n">
         <v>779.71</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="49" t="n">
         <v>856.04</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="49" t="n">
         <v>192.06</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="49" t="n">
         <v>216.55</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="49" t="n">
         <v>365.72</v>
       </c>
-      <c r="E16" s="47" t="n"/>
-      <c r="F16" s="47" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="49" t="n">
         <v>811.39</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="49" t="n">
         <v>376.34</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="47" t="n"/>
+      <c r="F17" s="49" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n">
+      <c r="B18" s="49" t="n">
         <v>7410.97</v>
       </c>
-      <c r="C18" s="47" t="n">
+      <c r="C18" s="49" t="n">
         <v>4219</v>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="49" t="n">
         <v>1418.95</v>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="49" t="n">
         <v>1115.13</v>
       </c>
-      <c r="F18" s="47" t="n">
+      <c r="F18" s="49" t="n">
         <v>1352.95</v>
       </c>
     </row>
@@ -10399,230 +10727,230 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="51">
         <f>B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="51">
         <f>C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="51">
         <f>D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="51">
         <f>E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="51">
         <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="49" t="n">
         <v>3623.48</v>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="49" t="n">
         <v>3317.28</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="49" t="n">
         <v>4142.1</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="49" t="n">
         <v>3075.2</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="F21" s="49" t="n">
         <v>2258.27</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
+      <c r="B22" s="49" t="n">
         <v>1491.35</v>
       </c>
-      <c r="C22" s="47" t="n">
+      <c r="C22" s="49" t="n">
         <v>1037.7</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="49" t="n">
         <v>373.5</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="49" t="n">
         <v>611.54</v>
       </c>
-      <c r="F22" s="47" t="n">
+      <c r="F22" s="49" t="n">
         <v>183.24</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>Trade Receivables</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
+      <c r="B23" s="49" t="n">
         <v>11791.37</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="49" t="n">
         <v>13022.07</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="49" t="n">
         <v>11677.48</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="49" t="n">
         <v>11529.36</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="49" t="n">
         <v>9560.92</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
+      <c r="B24" s="49" t="n">
         <v>927.88</v>
       </c>
-      <c r="C24" s="47" t="n">
+      <c r="C24" s="49" t="n">
         <v>319.86</v>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="49" t="n">
         <v>1136.25</v>
       </c>
-      <c r="E24" s="47" t="n">
+      <c r="E24" s="49" t="n">
         <v>349.23</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="F24" s="49" t="n">
         <v>782.37</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
       </c>
-      <c r="B25" s="47" t="n">
+      <c r="B25" s="49" t="n">
         <v>5998.44</v>
       </c>
-      <c r="C25" s="47" t="n">
+      <c r="C25" s="49" t="n">
         <v>5800.02</v>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="49" t="n">
         <v>6075.51</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="49" t="n">
         <v>1524.42</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="49" t="n">
         <v>1582.31</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
       </c>
-      <c r="B26" s="47" t="n">
+      <c r="B26" s="49" t="n">
         <v>10.99</v>
       </c>
-      <c r="C26" s="47" t="n">
+      <c r="C26" s="49" t="n">
         <v>6.82</v>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="49" t="n">
         <v>3.49</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="49" t="n">
         <v>3.19</v>
       </c>
-      <c r="F26" s="47" t="n">
+      <c r="F26" s="49" t="n">
         <v>7.62</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="49" t="n">
         <v>2161.97</v>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C27" s="49" t="n">
         <v>887.51</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="49" t="n">
         <v>435.82</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="49" t="n">
         <v>557.5</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="49" t="n">
         <v>308.28</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C28" s="49" t="n">
         <v>196.41</v>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="47" t="n"/>
-      <c r="F28" s="47" t="n"/>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="49" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="49" t="n">
         <v>2682.6</v>
       </c>
-      <c r="C29" s="47" t="n">
+      <c r="C29" s="49" t="n">
         <v>1725.78</v>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="49" t="n">
         <v>1742.43</v>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="49" t="n">
         <v>1902.56</v>
       </c>
-      <c r="F29" s="47" t="n">
+      <c r="F29" s="49" t="n">
         <v>1545.06</v>
       </c>
     </row>
@@ -10632,44 +10960,44 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B30" s="49">
+      <c r="B30" s="51">
         <f>B21+B22+B23+B24+B25+B26+B27+B28+B29</f>
         <v/>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="51">
         <f>C21+C22+C23+C24+C25+C26+C27+C28+C29</f>
         <v/>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="51">
         <f>D21+D22+D23+D24+D25+D26+D27+D28+D29</f>
         <v/>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="51">
         <f>E21+E22+E23+E24+E25+E26+E27+E28+E29</f>
         <v/>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="51">
         <f>F21+F22+F23+F24+F25+F26+F27+F28+F29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>Assets Classified as Held for Sale</t>
         </is>
       </c>
-      <c r="B31" s="47" t="n">
+      <c r="B31" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="47" t="n">
+      <c r="C31" s="49" t="n">
         <v>15.78</v>
       </c>
-      <c r="D31" s="47" t="n">
+      <c r="D31" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="47" t="n"/>
-      <c r="F31" s="47" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
@@ -10677,102 +11005,102 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B32" s="49">
+      <c r="B32" s="51">
         <f>B19+B30+B31</f>
         <v/>
       </c>
-      <c r="C32" s="49">
+      <c r="C32" s="51">
         <f>C19+C30+C31</f>
         <v/>
       </c>
-      <c r="D32" s="49">
+      <c r="D32" s="51">
         <f>D19+D30+D31</f>
         <v/>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="51">
         <f>E19+E30+E31</f>
         <v/>
       </c>
-      <c r="F32" s="49">
+      <c r="F32" s="51">
         <f>F19+F30+F31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="46" t="inlineStr">
+      <c r="A33" s="48" t="inlineStr">
         <is>
           <t>EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B33" s="47" t="n"/>
-      <c r="C33" s="47" t="n"/>
-      <c r="D33" s="47" t="n"/>
-      <c r="E33" s="47" t="n"/>
-      <c r="F33" s="47" t="n"/>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="48" t="inlineStr">
+      <c r="A34" s="50" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="49" t="n">
         <v>3856.94</v>
       </c>
-      <c r="C34" s="47" t="n">
+      <c r="C34" s="49" t="n">
         <v>3856.94</v>
       </c>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="49" t="n">
         <v>3856.94</v>
       </c>
-      <c r="E34" s="47" t="n">
+      <c r="E34" s="49" t="n">
         <v>3856.94</v>
       </c>
-      <c r="F34" s="47" t="n">
+      <c r="F34" s="49" t="n">
         <v>3856.94</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>Instrument entirely Equity in nature / Unsecured Perpetual Securities</t>
         </is>
       </c>
-      <c r="B35" s="47" t="n">
+      <c r="B35" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="47" t="n">
+      <c r="C35" s="49" t="n">
         <v>3056.92</v>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="49" t="n">
         <v>7315</v>
       </c>
-      <c r="E35" s="47" t="n">
+      <c r="E35" s="49" t="n">
         <v>13215</v>
       </c>
-      <c r="F35" s="47" t="n">
+      <c r="F35" s="49" t="n">
         <v>13215</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="50" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
       </c>
-      <c r="B36" s="47" t="n">
+      <c r="B36" s="49" t="n">
         <v>61079.94</v>
       </c>
-      <c r="C36" s="47" t="n">
+      <c r="C36" s="49" t="n">
         <v>49433.23</v>
       </c>
-      <c r="D36" s="47" t="n">
+      <c r="D36" s="49" t="n">
         <v>31973.09</v>
       </c>
-      <c r="E36" s="47" t="n">
+      <c r="E36" s="49" t="n">
         <v>12803.72</v>
       </c>
-      <c r="F36" s="47" t="n">
+      <c r="F36" s="49" t="n">
         <v>1631.5</v>
       </c>
     </row>
@@ -10782,46 +11110,46 @@
           <t>Equity attributable to equity holders of the parent</t>
         </is>
       </c>
-      <c r="B37" s="49">
+      <c r="B37" s="51">
         <f>B34+B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="49">
+      <c r="C37" s="51">
         <f>C34+C35+C36</f>
         <v/>
       </c>
-      <c r="D37" s="49">
+      <c r="D37" s="51">
         <f>D34+D35+D36</f>
         <v/>
       </c>
-      <c r="E37" s="49">
+      <c r="E37" s="51">
         <f>E34+E35+E36</f>
         <v/>
       </c>
-      <c r="F37" s="49">
+      <c r="F37" s="51">
         <f>F34+F35+F36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="48" t="inlineStr">
+      <c r="A38" s="50" t="inlineStr">
         <is>
           <t>Non-Controlling Interests</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="49" t="n">
         <v>1465.04</v>
       </c>
-      <c r="C38" s="47" t="n">
+      <c r="C38" s="49" t="n">
         <v>1326.47</v>
       </c>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="47" t="n">
+      <c r="E38" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="47" t="n">
+      <c r="F38" s="49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10831,168 +11159,168 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B39" s="49">
+      <c r="B39" s="51">
         <f>B37+B38</f>
         <v/>
       </c>
-      <c r="C39" s="49">
+      <c r="C39" s="51">
         <f>C37+C38</f>
         <v/>
       </c>
-      <c r="D39" s="49">
+      <c r="D39" s="51">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E39" s="49">
+      <c r="E39" s="51">
         <f>E37+E38</f>
         <v/>
       </c>
-      <c r="F39" s="49">
+      <c r="F39" s="51">
         <f>F37+F38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="46" t="inlineStr">
+      <c r="A40" s="48" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n"/>
-      <c r="C40" s="47" t="n"/>
-      <c r="D40" s="47" t="n"/>
-      <c r="E40" s="47" t="n"/>
-      <c r="F40" s="47" t="n"/>
+      <c r="B40" s="49" t="n"/>
+      <c r="C40" s="49" t="n"/>
+      <c r="D40" s="49" t="n"/>
+      <c r="E40" s="49" t="n"/>
+      <c r="F40" s="49" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
       </c>
-      <c r="B41" s="47" t="n">
+      <c r="B41" s="49" t="n">
         <v>42829.6</v>
       </c>
-      <c r="C41" s="47" t="n">
+      <c r="C41" s="49" t="n">
         <v>27646.96</v>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="49" t="n">
         <v>26595.01</v>
       </c>
-      <c r="E41" s="47" t="n">
+      <c r="E41" s="49" t="n">
         <v>33702.6</v>
       </c>
-      <c r="F41" s="47" t="n">
+      <c r="F41" s="49" t="n">
         <v>37871.32</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="50" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B42" s="47" t="n">
+      <c r="B42" s="49" t="n">
         <v>1049.27</v>
       </c>
-      <c r="C42" s="47" t="n">
+      <c r="C42" s="49" t="n">
         <v>1094.04</v>
       </c>
-      <c r="D42" s="47" t="n">
+      <c r="D42" s="49" t="n">
         <v>143.11</v>
       </c>
-      <c r="E42" s="47" t="n">
+      <c r="E42" s="49" t="n">
         <v>88.31999999999999</v>
       </c>
-      <c r="F42" s="47" t="n">
+      <c r="F42" s="49" t="n">
         <v>94.36</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="50" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B43" s="47" t="n">
+      <c r="B43" s="49" t="n">
         <v>185.69</v>
       </c>
-      <c r="C43" s="47" t="n">
+      <c r="C43" s="49" t="n">
         <v>1.17</v>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="49" t="n">
         <v>1.07</v>
       </c>
-      <c r="E43" s="47" t="n">
+      <c r="E43" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="47" t="n">
+      <c r="F43" s="49" t="n">
         <v>960.37</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="48" t="inlineStr">
+      <c r="A44" s="50" t="inlineStr">
         <is>
           <t>Provisions (Non-current)</t>
         </is>
       </c>
-      <c r="B44" s="47" t="n">
+      <c r="B44" s="49" t="n">
         <v>359.9</v>
       </c>
-      <c r="C44" s="47" t="n">
+      <c r="C44" s="49" t="n">
         <v>339.64</v>
       </c>
-      <c r="D44" s="47" t="n">
+      <c r="D44" s="49" t="n">
         <v>237.45</v>
       </c>
-      <c r="E44" s="47" t="n">
+      <c r="E44" s="49" t="n">
         <v>226.95</v>
       </c>
-      <c r="F44" s="47" t="n">
+      <c r="F44" s="49" t="n">
         <v>220.87</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="48" t="inlineStr">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B45" s="47" t="n">
+      <c r="B45" s="49" t="n">
         <v>5827.15</v>
       </c>
-      <c r="C45" s="47" t="n">
+      <c r="C45" s="49" t="n">
         <v>4022.73</v>
       </c>
-      <c r="D45" s="47" t="n">
+      <c r="D45" s="49" t="n">
         <v>315.8</v>
       </c>
-      <c r="E45" s="47" t="n">
+      <c r="E45" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="47" t="n">
+      <c r="F45" s="49" t="n">
         <v>2499.78</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="48" t="inlineStr">
+      <c r="A46" s="50" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B46" s="47" t="n">
+      <c r="B46" s="49" t="n">
         <v>5298.18</v>
       </c>
-      <c r="C46" s="47" t="n">
+      <c r="C46" s="49" t="n">
         <v>5698.48</v>
       </c>
-      <c r="D46" s="47" t="n">
+      <c r="D46" s="49" t="n">
         <v>6098.63</v>
       </c>
-      <c r="E46" s="47" t="n">
+      <c r="E46" s="49" t="n">
         <v>4183.15</v>
       </c>
-      <c r="F46" s="47" t="n">
+      <c r="F46" s="49" t="n">
         <v>4487.21</v>
       </c>
     </row>
@@ -11002,212 +11330,212 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B47" s="49">
+      <c r="B47" s="51">
         <f>B41+B42+B43+B44+B45+B46</f>
         <v/>
       </c>
-      <c r="C47" s="49">
+      <c r="C47" s="51">
         <f>C41+C42+C43+C44+C45+C46</f>
         <v/>
       </c>
-      <c r="D47" s="49">
+      <c r="D47" s="51">
         <f>D41+D42+D43+D44+D45+D46</f>
         <v/>
       </c>
-      <c r="E47" s="49">
+      <c r="E47" s="51">
         <f>E41+E42+E43+E44+E45+E46</f>
         <v/>
       </c>
-      <c r="F47" s="49">
+      <c r="F47" s="51">
         <f>F41+F42+F43+F44+F45+F46</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="48" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B48" s="47" t="n"/>
-      <c r="C48" s="47" t="n"/>
-      <c r="D48" s="47" t="n"/>
-      <c r="E48" s="47" t="n"/>
-      <c r="F48" s="47" t="n"/>
+      <c r="B48" s="49" t="n"/>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="48" t="inlineStr">
+      <c r="A49" s="50" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
       </c>
-      <c r="B49" s="47" t="n">
+      <c r="B49" s="49" t="n">
         <v>10725.94</v>
       </c>
-      <c r="C49" s="47" t="n">
+      <c r="C49" s="49" t="n">
         <v>10687.92</v>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="49" t="n">
         <v>7861.85</v>
       </c>
-      <c r="E49" s="47" t="n">
+      <c r="E49" s="49" t="n">
         <v>8549.450000000001</v>
       </c>
-      <c r="F49" s="47" t="n">
+      <c r="F49" s="49" t="n">
         <v>10924.36</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="48" t="inlineStr">
+      <c r="A50" s="50" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B50" s="47" t="n">
+      <c r="B50" s="49" t="n">
         <v>65.48</v>
       </c>
-      <c r="C50" s="47" t="n">
+      <c r="C50" s="49" t="n">
         <v>65.95</v>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="49" t="n">
         <v>15.59</v>
       </c>
-      <c r="E50" s="47" t="n">
+      <c r="E50" s="49" t="n">
         <v>9.16</v>
       </c>
-      <c r="F50" s="47" t="n">
+      <c r="F50" s="49" t="n">
         <v>8.390000000000001</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="48" t="inlineStr">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>Trade Payables — micro/small enterprises</t>
         </is>
       </c>
-      <c r="B51" s="47" t="n">
+      <c r="B51" s="49" t="n">
         <v>183.98</v>
       </c>
-      <c r="C51" s="47" t="n">
+      <c r="C51" s="49" t="n">
         <v>215.73</v>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="49" t="n">
         <v>141.93</v>
       </c>
-      <c r="E51" s="47" t="n">
+      <c r="E51" s="49" t="n">
         <v>95.76000000000001</v>
       </c>
-      <c r="F51" s="47" t="n">
+      <c r="F51" s="49" t="n">
         <v>57.59</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="48" t="inlineStr">
+      <c r="A52" s="50" t="inlineStr">
         <is>
           <t>Trade Payables — other creditors</t>
         </is>
       </c>
-      <c r="B52" s="47" t="n">
+      <c r="B52" s="49" t="n">
         <v>2656.55</v>
       </c>
-      <c r="C52" s="47" t="n">
+      <c r="C52" s="49" t="n">
         <v>2761.93</v>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="49" t="n">
         <v>3494.37</v>
       </c>
-      <c r="E52" s="47" t="n">
+      <c r="E52" s="49" t="n">
         <v>2983.69</v>
       </c>
-      <c r="F52" s="47" t="n">
+      <c r="F52" s="49" t="n">
         <v>3450.62</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="48" t="inlineStr">
+      <c r="A53" s="50" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B53" s="47" t="n">
+      <c r="B53" s="49" t="n">
         <v>4049.65</v>
       </c>
-      <c r="C53" s="47" t="n">
+      <c r="C53" s="49" t="n">
         <v>1230.62</v>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="49" t="n">
         <v>2089.8</v>
       </c>
-      <c r="E53" s="47" t="n">
+      <c r="E53" s="49" t="n">
         <v>2461.58</v>
       </c>
-      <c r="F53" s="47" t="n">
+      <c r="F53" s="49" t="n">
         <v>1167.32</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="48" t="inlineStr">
+      <c r="A54" s="50" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B54" s="47" t="n">
+      <c r="B54" s="49" t="n">
         <v>994.38</v>
       </c>
-      <c r="C54" s="47" t="n">
+      <c r="C54" s="49" t="n">
         <v>1348.74</v>
       </c>
-      <c r="D54" s="47" t="n">
+      <c r="D54" s="49" t="n">
         <v>2159.44</v>
       </c>
-      <c r="E54" s="47" t="n">
+      <c r="E54" s="49" t="n">
         <v>3622.82</v>
       </c>
-      <c r="F54" s="47" t="n">
+      <c r="F54" s="49" t="n">
         <v>861.36</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="48" t="inlineStr">
+      <c r="A55" s="50" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
       </c>
-      <c r="B55" s="47" t="n">
+      <c r="B55" s="49" t="n">
         <v>96.95999999999999</v>
       </c>
-      <c r="C55" s="47" t="n">
+      <c r="C55" s="49" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="49" t="n">
         <v>25.69</v>
       </c>
-      <c r="E55" s="47" t="n">
+      <c r="E55" s="49" t="n">
         <v>21.64</v>
       </c>
-      <c r="F55" s="47" t="n">
+      <c r="F55" s="49" t="n">
         <v>28.71</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="48" t="inlineStr">
+      <c r="A56" s="50" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B56" s="47" t="n">
+      <c r="B56" s="49" t="n">
         <v>1555.27</v>
       </c>
-      <c r="C56" s="47" t="n">
+      <c r="C56" s="49" t="n">
         <v>59.86</v>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="47" t="n">
+      <c r="E56" s="49" t="n">
         <v>0.49</v>
       </c>
-      <c r="F56" s="47" t="n">
+      <c r="F56" s="49" t="n">
         <v>645.3200000000001</v>
       </c>
     </row>
@@ -11217,23 +11545,23 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B57" s="49">
+      <c r="B57" s="51">
         <f>B49+B50+B51+B52+B53+B54+B55+B56</f>
         <v/>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="51">
         <f>C49+C50+C51+C52+C53+C54+C55+C56</f>
         <v/>
       </c>
-      <c r="D57" s="49">
+      <c r="D57" s="51">
         <f>D49+D50+D51+D52+D53+D54+D55+D56</f>
         <v/>
       </c>
-      <c r="E57" s="49">
+      <c r="E57" s="51">
         <f>E49+E50+E51+E52+E53+E54+E55+E56</f>
         <v/>
       </c>
-      <c r="F57" s="49">
+      <c r="F57" s="51">
         <f>F49+F50+F51+F52+F53+F54+F55+F56</f>
         <v/>
       </c>
@@ -11244,23 +11572,23 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B58" s="49">
+      <c r="B58" s="51">
         <f>B47+B57</f>
         <v/>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="51">
         <f>C47+C57</f>
         <v/>
       </c>
-      <c r="D58" s="49">
+      <c r="D58" s="51">
         <f>D47+D57</f>
         <v/>
       </c>
-      <c r="E58" s="49">
+      <c r="E58" s="51">
         <f>E47+E57</f>
         <v/>
       </c>
-      <c r="F58" s="49">
+      <c r="F58" s="51">
         <f>F47+F57</f>
         <v/>
       </c>
@@ -11271,23 +11599,23 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B59" s="49">
+      <c r="B59" s="51">
         <f>B39+B58</f>
         <v/>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="51">
         <f>C39+C58</f>
         <v/>
       </c>
-      <c r="D59" s="49">
+      <c r="D59" s="51">
         <f>D39+D58</f>
         <v/>
       </c>
-      <c r="E59" s="49">
+      <c r="E59" s="51">
         <f>E39+E58</f>
         <v/>
       </c>
-      <c r="F59" s="49">
+      <c r="F59" s="51">
         <f>F39+F58</f>
         <v/>
       </c>
@@ -11326,97 +11654,97 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23, FY23-24, FY24-25 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n"/>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>54240.52</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="49" t="n">
         <v>56203.09</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="49" t="n">
         <v>50351.25</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="49" t="n">
         <v>38773.3</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="49" t="n">
         <v>27711.18</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>3624.76</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="49" t="n">
         <v>2702.74</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="49" t="n">
         <v>9930.23</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="49" t="n">
         <v>4267.22</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="49" t="n">
         <v>3975.29</v>
       </c>
     </row>
@@ -11426,190 +11754,190 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B8" s="49">
+      <c r="B8" s="51">
         <f>B6+B7</f>
         <v/>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="51">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="51">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="51">
         <f>E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="51">
         <f>F6+F7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n"/>
-      <c r="C9" s="47" t="n"/>
-      <c r="D9" s="47" t="n"/>
-      <c r="E9" s="47" t="n"/>
-      <c r="F9" s="47" t="n"/>
+      <c r="B9" s="49" t="n"/>
+      <c r="C9" s="49" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="49" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>29168.02</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>30273.25</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>28452.64</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>25480.85</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="49" t="n">
         <v>14762.21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Purchase of Stock-in-trade / Power for resale</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>209.66</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="49" t="n">
         <v>356.99</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="49" t="n">
         <v>222.26</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="49" t="n">
         <v>214.14</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="49" t="n">
         <v>545.5599999999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Transmission Charges</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>557.42</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>459.09</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="49" t="n">
         <v>503.99</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="49" t="n">
         <v>519.61</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="49" t="n">
         <v>642.77</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>855.1799999999999</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="49" t="n">
         <v>784.4</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="49" t="n">
         <v>643.7</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="49" t="n">
         <v>569.99</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="49" t="n">
         <v>470.31</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Finance Costs (net)</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="49" t="n">
         <v>3366.83</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="49" t="n">
         <v>3339.79</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="49" t="n">
         <v>3388.09</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="49" t="n">
         <v>3333.5</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="F14" s="49" t="n">
         <v>4094.78</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Depreciation and Amortisation Expense</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>4564.53</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="49" t="n">
         <v>4308.88</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="49" t="n">
         <v>3931.33</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="49" t="n">
         <v>3303.68</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="49" t="n">
         <v>3117.54</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="49" t="n">
         <v>3644.13</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="49" t="n">
         <v>3023.92</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="49" t="n">
         <v>2347.96</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="49" t="n">
         <v>1944.05</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="49" t="n">
         <v>1476.17</v>
       </c>
     </row>
@@ -11619,23 +11947,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B17" s="49">
+      <c r="B17" s="51">
         <f>B10+B11+B12+B13+B14+B15+B16</f>
         <v/>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="51">
         <f>C10+C11+C12+C13+C14+C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="51">
         <f>D10+D11+D12+D13+D14+D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="51">
         <f>E10+E11+E12+E13+E14+E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="51">
         <f>F10+F11+F12+F13+F14+F15+F16</f>
         <v/>
       </c>
@@ -11646,64 +11974,64 @@
           <t>Profit before share of JV profit and tax</t>
         </is>
       </c>
-      <c r="B18" s="49">
+      <c r="B18" s="51">
         <f>B8-B17</f>
         <v/>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="51">
         <f>C8-C17</f>
         <v/>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="51">
         <f>D8-D17</f>
         <v/>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="51">
         <f>E8-E17</f>
         <v/>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="51">
         <f>F8-F17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>Total Tax Expense/(Credit)</t>
         </is>
       </c>
-      <c r="B19" s="47" t="n">
+      <c r="B19" s="49" t="n">
         <v>2528.43</v>
       </c>
-      <c r="C19" s="47" t="n">
+      <c r="C19" s="49" t="n">
         <v>3609.9</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="49" t="n">
         <v>-37.28</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="49" t="n">
         <v>-3267.37</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="49" t="n">
         <v>1744.8</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>Add: Deferred tax (adj.)/recoverable from future tariff (net of tax)</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n">
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="49" t="n">
         <v>-215.43</v>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="F20" s="49" t="n">
         <v>79.25</v>
       </c>
     </row>
@@ -11713,46 +12041,46 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="51">
         <f>B18-B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="51">
         <f>C18-C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="49">
+      <c r="D21" s="51">
         <f>D18-D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="51">
         <f>E18-E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="51">
         <f>F18-F19+F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Other Comprehensive Income, net of tax</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
+      <c r="B22" s="49" t="n">
         <v>19.67</v>
       </c>
-      <c r="C22" s="47" t="n">
+      <c r="C22" s="49" t="n">
         <v>-2.69</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="49" t="n">
         <v>-27.49</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="49" t="n">
         <v>33.74</v>
       </c>
-      <c r="F22" s="47" t="n">
+      <c r="F22" s="49" t="n">
         <v>43.63</v>
       </c>
     </row>
@@ -11762,23 +12090,23 @@
           <t>Total Comprehensive Income for the Year</t>
         </is>
       </c>
-      <c r="B23" s="49">
+      <c r="B23" s="51">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="49">
+      <c r="C23" s="51">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="49">
+      <c r="D23" s="51">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="51">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="51">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -11817,373 +12145,373 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Sources: Tata Power Integrated Annual Reports FY21-22 (AR_20052), FY23-24 (AR_24164) and FY25-26 (AR_29380) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n"/>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n"/>
-      <c r="C6" s="47" t="n"/>
-      <c r="D6" s="47" t="n"/>
-      <c r="E6" s="47" t="n"/>
-      <c r="F6" s="47" t="n"/>
+      <c r="B6" s="49" t="n"/>
+      <c r="C6" s="49" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>78870.53999999999</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="49" t="n">
         <v>70261.38</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="49" t="n">
         <v>59624.06</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="49" t="n">
         <v>54524.96</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="49" t="n">
         <v>50502.96</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Right of Use Assets</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="49" t="n">
         <v>5525.44</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="49" t="n">
         <v>5089.89</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="49" t="n">
         <v>4368.75</v>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="49" t="n">
         <v>3982.05</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="49" t="n">
         <v>3661.99</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>14595.13</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="49" t="n">
         <v>12678.87</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="49" t="n">
         <v>11561.31</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="49" t="n">
         <v>5376.36</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="49" t="n">
         <v>4635.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>1651.46</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>1651.46</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>1757.46</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>1858.31</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="49" t="n">
         <v>1858.31</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>1245.25</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="49" t="n">
         <v>1371.7</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="49" t="n">
         <v>1459.29</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="49" t="n">
         <v>1381.34</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="49" t="n">
         <v>1366.18</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Investments accounted for using Equity Method</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>13549.05</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>12894.22</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="49" t="n">
         <v>12983.51</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="49" t="n">
         <v>14218.88</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="49" t="n">
         <v>12580</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Other Investments (Non-current)</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>1669.37</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="49" t="n">
         <v>2119.75</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="49" t="n">
         <v>1854.59</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="49" t="n">
         <v>1301.21</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="49" t="n">
         <v>1169.81</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Trade Receivables (Non-current)</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="49" t="n">
         <v>1599.35</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="49" t="n">
         <v>1223.02</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="49" t="n">
         <v>273.29</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="49" t="n">
         <v>359.63</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="F14" s="49" t="n">
         <v>685.78</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>37.14</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="49" t="n">
         <v>2.48</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="49" t="n">
         <v>2.99</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="49" t="n">
         <v>3.45</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Finance Lease Receivables (Non-current)</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="49" t="n">
         <v>837.84</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="49" t="n">
         <v>526.98</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="49" t="n">
         <v>561.66</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="49" t="n">
         <v>567.22</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="49" t="n">
         <v>588.6900000000001</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="49" t="n">
         <v>3522.62</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="49" t="n">
         <v>2168.98</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="49" t="n">
         <v>2084.5</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="49" t="n">
         <v>1726.66</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="49" t="n">
         <v>1684.53</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n">
+      <c r="B18" s="49" t="n">
         <v>960.96</v>
       </c>
-      <c r="C18" s="47" t="n">
+      <c r="C18" s="49" t="n">
         <v>745.78</v>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="49" t="n">
         <v>585.89</v>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="49" t="n">
         <v>739.0700000000001</v>
       </c>
-      <c r="F18" s="47" t="n">
+      <c r="F18" s="49" t="n">
         <v>520.54</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B19" s="47" t="n">
+      <c r="B19" s="49" t="n">
         <v>607.54</v>
       </c>
-      <c r="C19" s="47" t="n">
+      <c r="C19" s="49" t="n">
         <v>517.99</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="49" t="n">
         <v>499.09</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="49" t="n">
         <v>252.9</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="49" t="n">
         <v>334.6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="49" t="n">
         <v>10635.84</v>
       </c>
-      <c r="C20" s="47" t="n">
+      <c r="C20" s="49" t="n">
         <v>8393.799999999999</v>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="49" t="n">
         <v>5173.57</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="49" t="n">
         <v>2532.46</v>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="F20" s="49" t="n">
         <v>1849.82</v>
       </c>
     </row>
@@ -12193,278 +12521,278 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="51">
         <f>B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="51">
         <f>C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="49">
+      <c r="D21" s="51">
         <f>D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="51">
         <f>E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18+E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="51">
         <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18+F19+F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n"/>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
-      <c r="F22" s="47" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
+      <c r="B23" s="49" t="n">
         <v>5107.64</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="49" t="n">
         <v>4571.82</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="49" t="n">
         <v>4419.63</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="49" t="n">
         <v>3942.88</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="49" t="n">
         <v>4231.52</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
+      <c r="B24" s="49" t="n">
         <v>1356.12</v>
       </c>
-      <c r="C24" s="47" t="n">
+      <c r="C24" s="49" t="n">
         <v>1302.42</v>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="49" t="n">
         <v>1477.89</v>
       </c>
-      <c r="E24" s="47" t="n">
+      <c r="E24" s="49" t="n">
         <v>1149.6</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="F24" s="49" t="n">
         <v>410.52</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Trade Receivables (Current)</t>
         </is>
       </c>
-      <c r="B25" s="47" t="n">
+      <c r="B25" s="49" t="n">
         <v>4423.96</v>
       </c>
-      <c r="C25" s="47" t="n">
+      <c r="C25" s="49" t="n">
         <v>5709.78</v>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="49" t="n">
         <v>7401.69</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="49" t="n">
         <v>6952.15</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="49" t="n">
         <v>5979.74</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>Unbilled Revenue</t>
         </is>
       </c>
-      <c r="B26" s="47" t="n">
+      <c r="B26" s="49" t="n">
         <v>2842.63</v>
       </c>
-      <c r="C26" s="47" t="n">
+      <c r="C26" s="49" t="n">
         <v>2737.06</v>
       </c>
-      <c r="D26" s="47" t="n">
+      <c r="D26" s="49" t="n">
         <v>2552.23</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="49" t="n">
         <v>2456.71</v>
       </c>
-      <c r="F26" s="47" t="n">
+      <c r="F26" s="49" t="n">
         <v>2285.57</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="49" t="n">
         <v>4409.67</v>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C27" s="49" t="n">
         <v>4862.47</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="49" t="n">
         <v>3324.34</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="49" t="n">
         <v>4189.76</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="49" t="n">
         <v>3077.24</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="49" t="n">
         <v>9234.33</v>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C28" s="49" t="n">
         <v>6888.51</v>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="49" t="n">
         <v>5827.57</v>
       </c>
-      <c r="E28" s="47" t="n">
+      <c r="E28" s="49" t="n">
         <v>7016.77</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="F28" s="49" t="n">
         <v>3563.46</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="50" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="49" t="n">
         <v>19.8</v>
       </c>
-      <c r="C29" s="47" t="n">
+      <c r="C29" s="49" t="n">
         <v>12.34</v>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="49" t="n">
         <v>11.14</v>
       </c>
-      <c r="E29" s="47" t="n">
+      <c r="E29" s="49" t="n">
         <v>11.55</v>
       </c>
-      <c r="F29" s="47" t="n">
+      <c r="F29" s="49" t="n">
         <v>9.34</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="inlineStr">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>Finance Lease Receivables (Current)</t>
         </is>
       </c>
-      <c r="B30" s="47" t="n">
+      <c r="B30" s="49" t="n">
         <v>86.65000000000001</v>
       </c>
-      <c r="C30" s="47" t="n">
+      <c r="C30" s="49" t="n">
         <v>74.47</v>
       </c>
-      <c r="D30" s="47" t="n">
+      <c r="D30" s="49" t="n">
         <v>65.92</v>
       </c>
-      <c r="E30" s="47" t="n">
+      <c r="E30" s="49" t="n">
         <v>54.5</v>
       </c>
-      <c r="F30" s="47" t="n">
+      <c r="F30" s="49" t="n">
         <v>46.91</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
       </c>
-      <c r="B31" s="47" t="n">
+      <c r="B31" s="49" t="n">
         <v>1316.67</v>
       </c>
-      <c r="C31" s="47" t="n">
+      <c r="C31" s="49" t="n">
         <v>656.48</v>
       </c>
-      <c r="D31" s="47" t="n">
+      <c r="D31" s="49" t="n">
         <v>471.48</v>
       </c>
-      <c r="E31" s="47" t="n">
+      <c r="E31" s="49" t="n">
         <v>688.3</v>
       </c>
-      <c r="F31" s="47" t="n">
+      <c r="F31" s="49" t="n">
         <v>501.45</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>Current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B32" s="47" t="n">
+      <c r="B32" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="47" t="n">
+      <c r="C32" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="47" t="n">
+      <c r="D32" s="49" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E32" s="47" t="n">
+      <c r="E32" s="49" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="F32" s="47" t="n">
+      <c r="F32" s="49" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B33" s="47" t="n">
+      <c r="B33" s="49" t="n">
         <v>1773.58</v>
       </c>
-      <c r="C33" s="47" t="n">
+      <c r="C33" s="49" t="n">
         <v>1941.3</v>
       </c>
-      <c r="D33" s="47" t="n">
+      <c r="D33" s="49" t="n">
         <v>1704.3</v>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E33" s="49" t="n">
         <v>1328.72</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="49" t="n">
         <v>1479.67</v>
       </c>
     </row>
@@ -12474,46 +12802,46 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B34" s="49">
+      <c r="B34" s="51">
         <f>B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="51">
         <f>C23+C24+C25+C26+C27+C28+C29+C30+C31+C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="49">
+      <c r="D34" s="51">
         <f>D23+D24+D25+D26+D27+D28+D29+D30+D31+D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="51">
         <f>E23+E24+E25+E26+E27+E28+E29+E30+E31+E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="51">
         <f>F23+F24+F25+F26+F27+F28+F29+F30+F31+F32+F33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>Assets Classified as Held For Sale</t>
         </is>
       </c>
-      <c r="B35" s="47" t="n">
+      <c r="B35" s="49" t="n">
         <v>1153.75</v>
       </c>
-      <c r="C35" s="47" t="n">
+      <c r="C35" s="49" t="n">
         <v>1145.21</v>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="49" t="n">
         <v>1200.99</v>
       </c>
-      <c r="E35" s="47" t="n">
+      <c r="E35" s="49" t="n">
         <v>3299.94</v>
       </c>
-      <c r="F35" s="47" t="n">
+      <c r="F35" s="49" t="n">
         <v>3046.83</v>
       </c>
     </row>
@@ -12523,46 +12851,46 @@
           <t>Total Assets before Regulatory Deferral Account</t>
         </is>
       </c>
-      <c r="B36" s="49">
+      <c r="B36" s="51">
         <f>B21+B34+B35</f>
         <v/>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="51">
         <f>C21+C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="49">
+      <c r="D36" s="51">
         <f>D21+D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="51">
         <f>E21+E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="49">
+      <c r="F36" s="51">
         <f>F21+F34+F35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="50" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Assets</t>
         </is>
       </c>
-      <c r="B37" s="47" t="n">
+      <c r="B37" s="49" t="n">
         <v>8139.45</v>
       </c>
-      <c r="C37" s="47" t="n">
+      <c r="C37" s="49" t="n">
         <v>7163.61</v>
       </c>
-      <c r="D37" s="47" t="n">
+      <c r="D37" s="49" t="n">
         <v>8298.66</v>
       </c>
-      <c r="E37" s="47" t="n">
+      <c r="E37" s="49" t="n">
         <v>8433.43</v>
       </c>
-      <c r="F37" s="47" t="n">
+      <c r="F37" s="49" t="n">
         <v>6810.57</v>
       </c>
     </row>
@@ -12572,80 +12900,80 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B38" s="49">
+      <c r="B38" s="51">
         <f>B36+B37</f>
         <v/>
       </c>
-      <c r="C38" s="49">
+      <c r="C38" s="51">
         <f>C36+C37</f>
         <v/>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="51">
         <f>D36+D37</f>
         <v/>
       </c>
-      <c r="E38" s="49">
+      <c r="E38" s="51">
         <f>E36+E37</f>
         <v/>
       </c>
-      <c r="F38" s="49">
+      <c r="F38" s="51">
         <f>F36+F37</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="46" t="inlineStr">
+      <c r="A39" s="48" t="inlineStr">
         <is>
           <t>EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B39" s="47" t="n"/>
-      <c r="C39" s="47" t="n"/>
-      <c r="D39" s="47" t="n"/>
-      <c r="E39" s="47" t="n"/>
-      <c r="F39" s="47" t="n"/>
+      <c r="B39" s="49" t="n"/>
+      <c r="C39" s="49" t="n"/>
+      <c r="D39" s="49" t="n"/>
+      <c r="E39" s="49" t="n"/>
+      <c r="F39" s="49" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="50" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
+      <c r="B40" s="49" t="n">
         <v>319.56</v>
       </c>
-      <c r="C40" s="47" t="n">
+      <c r="C40" s="49" t="n">
         <v>319.56</v>
       </c>
-      <c r="D40" s="47" t="n">
+      <c r="D40" s="49" t="n">
         <v>319.56</v>
       </c>
-      <c r="E40" s="47" t="n">
+      <c r="E40" s="49" t="n">
         <v>319.56</v>
       </c>
-      <c r="F40" s="47" t="n">
+      <c r="F40" s="49" t="n">
         <v>319.56</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
       </c>
-      <c r="B41" s="47" t="n">
+      <c r="B41" s="49" t="n">
         <v>39147.65</v>
       </c>
-      <c r="C41" s="47" t="n">
+      <c r="C41" s="49" t="n">
         <v>35521.11</v>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="49" t="n">
         <v>32035.73</v>
       </c>
-      <c r="E41" s="47" t="n">
+      <c r="E41" s="49" t="n">
         <v>28467.87</v>
       </c>
-      <c r="F41" s="47" t="n">
+      <c r="F41" s="49" t="n">
         <v>22122</v>
       </c>
     </row>
@@ -12655,46 +12983,46 @@
           <t>Equity attributable to Shareholders of Parent</t>
         </is>
       </c>
-      <c r="B42" s="49">
+      <c r="B42" s="51">
         <f>B40+B41</f>
         <v/>
       </c>
-      <c r="C42" s="49">
+      <c r="C42" s="51">
         <f>C40+C41</f>
         <v/>
       </c>
-      <c r="D42" s="49">
+      <c r="D42" s="51">
         <f>D40+D41</f>
         <v/>
       </c>
-      <c r="E42" s="49">
+      <c r="E42" s="51">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F42" s="49">
+      <c r="F42" s="51">
         <f>F40+F41</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="50" t="inlineStr">
         <is>
           <t>Non-controlling Interests</t>
         </is>
       </c>
-      <c r="B43" s="47" t="n">
+      <c r="B43" s="49" t="n">
         <v>8070.86</v>
       </c>
-      <c r="C43" s="47" t="n">
+      <c r="C43" s="49" t="n">
         <v>6765.37</v>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="49" t="n">
         <v>5977.48</v>
       </c>
-      <c r="E43" s="47" t="n">
+      <c r="E43" s="49" t="n">
         <v>5416.69</v>
       </c>
-      <c r="F43" s="47" t="n">
+      <c r="F43" s="49" t="n">
         <v>3586.9</v>
       </c>
     </row>
@@ -12704,196 +13032,196 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B44" s="49">
+      <c r="B44" s="51">
         <f>B42+B43</f>
         <v/>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="51">
         <f>C42+C43</f>
         <v/>
       </c>
-      <c r="D44" s="49">
+      <c r="D44" s="51">
         <f>D42+D43</f>
         <v/>
       </c>
-      <c r="E44" s="49">
+      <c r="E44" s="51">
         <f>E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="49">
+      <c r="F44" s="51">
         <f>F42+F43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="48" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B45" s="47" t="n"/>
-      <c r="C45" s="47" t="n"/>
-      <c r="D45" s="47" t="n"/>
-      <c r="E45" s="47" t="n"/>
-      <c r="F45" s="47" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="48" t="inlineStr">
+      <c r="A46" s="50" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
       </c>
-      <c r="B46" s="47" t="n">
+      <c r="B46" s="49" t="n">
         <v>61608.57</v>
       </c>
-      <c r="C46" s="47" t="n">
+      <c r="C46" s="49" t="n">
         <v>44129.72</v>
       </c>
-      <c r="D46" s="47" t="n">
+      <c r="D46" s="49" t="n">
         <v>37392.25</v>
       </c>
-      <c r="E46" s="47" t="n">
+      <c r="E46" s="49" t="n">
         <v>30708.49</v>
       </c>
-      <c r="F46" s="47" t="n">
+      <c r="F46" s="49" t="n">
         <v>32729.7</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="48" t="inlineStr">
+      <c r="A47" s="50" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B47" s="47" t="n">
+      <c r="B47" s="49" t="n">
         <v>4549.94</v>
       </c>
-      <c r="C47" s="47" t="n">
+      <c r="C47" s="49" t="n">
         <v>4196.21</v>
       </c>
-      <c r="D47" s="47" t="n">
+      <c r="D47" s="49" t="n">
         <v>3742.48</v>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="49" t="n">
         <v>3510.7</v>
       </c>
-      <c r="F47" s="47" t="n">
+      <c r="F47" s="49" t="n">
         <v>3207.79</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="48" t="inlineStr">
+      <c r="A48" s="50" t="inlineStr">
         <is>
           <t>Trade Payables (Non-current)</t>
         </is>
       </c>
-      <c r="B48" s="47" t="n"/>
-      <c r="C48" s="47" t="n"/>
-      <c r="D48" s="47" t="n"/>
-      <c r="E48" s="47" t="n"/>
-      <c r="F48" s="47" t="n">
+      <c r="B48" s="49" t="n"/>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="48" t="inlineStr">
+      <c r="A49" s="50" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B49" s="47" t="n">
+      <c r="B49" s="49" t="n">
         <v>694.64</v>
       </c>
-      <c r="C49" s="47" t="n">
+      <c r="C49" s="49" t="n">
         <v>674.12</v>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="49" t="n">
         <v>1507.55</v>
       </c>
-      <c r="E49" s="47" t="n">
+      <c r="E49" s="49" t="n">
         <v>1410.4</v>
       </c>
-      <c r="F49" s="47" t="n">
+      <c r="F49" s="49" t="n">
         <v>1156.56</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="48" t="inlineStr">
+      <c r="A50" s="50" t="inlineStr">
         <is>
           <t>Non-current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B50" s="47" t="n"/>
-      <c r="C50" s="47" t="n"/>
-      <c r="D50" s="47" t="n"/>
-      <c r="E50" s="47" t="n"/>
-      <c r="F50" s="47" t="n">
+      <c r="B50" s="49" t="n"/>
+      <c r="C50" s="49" t="n"/>
+      <c r="D50" s="49" t="n"/>
+      <c r="E50" s="49" t="n"/>
+      <c r="F50" s="49" t="n">
         <v>3.03</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="48" t="inlineStr">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>Provisions (Non-current)</t>
         </is>
       </c>
-      <c r="B51" s="47" t="n">
+      <c r="B51" s="49" t="n">
         <v>3213.85</v>
       </c>
-      <c r="C51" s="47" t="n">
+      <c r="C51" s="49" t="n">
         <v>2548.69</v>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="49" t="n">
         <v>1865.08</v>
       </c>
-      <c r="E51" s="47" t="n">
+      <c r="E51" s="49" t="n">
         <v>1420.02</v>
       </c>
-      <c r="F51" s="47" t="n">
+      <c r="F51" s="49" t="n">
         <v>1218.18</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="48" t="inlineStr">
+      <c r="A52" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B52" s="47" t="n">
+      <c r="B52" s="49" t="n">
         <v>4807.88</v>
       </c>
-      <c r="C52" s="47" t="n">
+      <c r="C52" s="49" t="n">
         <v>4104.12</v>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="49" t="n">
         <v>2772.33</v>
       </c>
-      <c r="E52" s="47" t="n">
+      <c r="E52" s="49" t="n">
         <v>1919.37</v>
       </c>
-      <c r="F52" s="47" t="n">
+      <c r="F52" s="49" t="n">
         <v>1033.3</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="48" t="inlineStr">
+      <c r="A53" s="50" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B53" s="47" t="n">
+      <c r="B53" s="49" t="n">
         <v>13411.97</v>
       </c>
-      <c r="C53" s="47" t="n">
+      <c r="C53" s="49" t="n">
         <v>12930.57</v>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="49" t="n">
         <v>11973.08</v>
       </c>
-      <c r="E53" s="47" t="n">
+      <c r="E53" s="49" t="n">
         <v>9847.82</v>
       </c>
-      <c r="F53" s="47" t="n">
+      <c r="F53" s="49" t="n">
         <v>8139.29</v>
       </c>
     </row>
@@ -12903,226 +13231,226 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B54" s="49">
+      <c r="B54" s="51">
         <f>B46+B47+B48+B49+B50+B51+B52+B53</f>
         <v/>
       </c>
-      <c r="C54" s="49">
+      <c r="C54" s="51">
         <f>C46+C47+C48+C49+C50+C51+C52+C53</f>
         <v/>
       </c>
-      <c r="D54" s="49">
+      <c r="D54" s="51">
         <f>D46+D47+D48+D49+D50+D51+D52+D53</f>
         <v/>
       </c>
-      <c r="E54" s="49">
+      <c r="E54" s="51">
         <f>E46+E47+E48+E49+E50+E51+E52+E53</f>
         <v/>
       </c>
-      <c r="F54" s="49">
+      <c r="F54" s="51">
         <f>F46+F47+F48+F49+F50+F51+F52+F53</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="48" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B55" s="47" t="n"/>
-      <c r="C55" s="47" t="n"/>
-      <c r="D55" s="47" t="n"/>
-      <c r="E55" s="47" t="n"/>
-      <c r="F55" s="47" t="n"/>
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="49" t="n"/>
+      <c r="D55" s="49" t="n"/>
+      <c r="E55" s="49" t="n"/>
+      <c r="F55" s="49" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="48" t="inlineStr">
+      <c r="A56" s="50" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
       </c>
-      <c r="B56" s="47" t="n">
+      <c r="B56" s="49" t="n">
         <v>9513.82</v>
       </c>
-      <c r="C56" s="47" t="n">
+      <c r="C56" s="49" t="n">
         <v>14015.84</v>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="49" t="n">
         <v>12087.56</v>
       </c>
-      <c r="E56" s="47" t="n">
+      <c r="E56" s="49" t="n">
         <v>18265.94</v>
       </c>
-      <c r="F56" s="47" t="n">
+      <c r="F56" s="49" t="n">
         <v>14860.3</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="48" t="inlineStr">
+      <c r="A57" s="50" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B57" s="47" t="n">
+      <c r="B57" s="49" t="n">
         <v>468.94</v>
       </c>
-      <c r="C57" s="47" t="n">
+      <c r="C57" s="49" t="n">
         <v>524.03</v>
       </c>
-      <c r="D57" s="47" t="n">
+      <c r="D57" s="49" t="n">
         <v>467.16</v>
       </c>
-      <c r="E57" s="47" t="n">
+      <c r="E57" s="49" t="n">
         <v>437.87</v>
       </c>
-      <c r="F57" s="47" t="n">
+      <c r="F57" s="49" t="n">
         <v>397.33</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="48" t="inlineStr">
+      <c r="A58" s="50" t="inlineStr">
         <is>
           <t>Acceptances (Current)</t>
         </is>
       </c>
-      <c r="B58" s="47" t="n">
+      <c r="B58" s="49" t="n">
         <v>3647.97</v>
       </c>
-      <c r="C58" s="47" t="n">
+      <c r="C58" s="49" t="n">
         <v>5129.93</v>
       </c>
-      <c r="D58" s="47" t="n"/>
-      <c r="E58" s="47" t="n"/>
-      <c r="F58" s="47" t="n"/>
+      <c r="D58" s="49" t="n"/>
+      <c r="E58" s="49" t="n"/>
+      <c r="F58" s="49" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="48" t="inlineStr">
+      <c r="A59" s="50" t="inlineStr">
         <is>
           <t>Trade Payables — micro/small enterprises</t>
         </is>
       </c>
-      <c r="B59" s="47" t="n">
+      <c r="B59" s="49" t="n">
         <v>809.84</v>
       </c>
-      <c r="C59" s="47" t="n">
+      <c r="C59" s="49" t="n">
         <v>784.21</v>
       </c>
-      <c r="D59" s="47" t="n">
+      <c r="D59" s="49" t="n">
         <v>870</v>
       </c>
-      <c r="E59" s="47" t="n">
+      <c r="E59" s="49" t="n">
         <v>537.6</v>
       </c>
-      <c r="F59" s="47" t="n"/>
+      <c r="F59" s="49" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="48" t="inlineStr">
+      <c r="A60" s="50" t="inlineStr">
         <is>
           <t>Trade Payables — other creditors / total</t>
         </is>
       </c>
-      <c r="B60" s="47" t="n">
+      <c r="B60" s="49" t="n">
         <v>6328.39</v>
       </c>
-      <c r="C60" s="47" t="n">
+      <c r="C60" s="49" t="n">
         <v>8070.34</v>
       </c>
-      <c r="D60" s="47" t="n">
+      <c r="D60" s="49" t="n">
         <v>8451.370000000001</v>
       </c>
-      <c r="E60" s="47" t="n">
+      <c r="E60" s="49" t="n">
         <v>6869.6</v>
       </c>
-      <c r="F60" s="47" t="n">
+      <c r="F60" s="49" t="n">
         <v>10459.6</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="48" t="inlineStr">
+      <c r="A61" s="50" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B61" s="47" t="n">
+      <c r="B61" s="49" t="n">
         <v>13897.6</v>
       </c>
-      <c r="C61" s="47" t="n">
+      <c r="C61" s="49" t="n">
         <v>12427.03</v>
       </c>
-      <c r="D61" s="47" t="n">
+      <c r="D61" s="49" t="n">
         <v>14796.16</v>
       </c>
-      <c r="E61" s="47" t="n">
+      <c r="E61" s="49" t="n">
         <v>13150.77</v>
       </c>
-      <c r="F61" s="47" t="n">
+      <c r="F61" s="49" t="n">
         <v>9631.959999999999</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="48" t="inlineStr">
+      <c r="A62" s="50" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
       </c>
-      <c r="B62" s="47" t="n">
+      <c r="B62" s="49" t="n">
         <v>680.4400000000001</v>
       </c>
-      <c r="C62" s="47" t="n">
+      <c r="C62" s="49" t="n">
         <v>437.56</v>
       </c>
-      <c r="D62" s="47" t="n">
+      <c r="D62" s="49" t="n">
         <v>294.34</v>
       </c>
-      <c r="E62" s="47" t="n">
+      <c r="E62" s="49" t="n">
         <v>311.07</v>
       </c>
-      <c r="F62" s="47" t="n">
+      <c r="F62" s="49" t="n">
         <v>344.82</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="48" t="inlineStr">
+      <c r="A63" s="50" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B63" s="47" t="n">
+      <c r="B63" s="49" t="n">
         <v>185.42</v>
       </c>
-      <c r="C63" s="47" t="n">
+      <c r="C63" s="49" t="n">
         <v>208.2</v>
       </c>
-      <c r="D63" s="47" t="n">
+      <c r="D63" s="49" t="n">
         <v>291.54</v>
       </c>
-      <c r="E63" s="47" t="n">
+      <c r="E63" s="49" t="n">
         <v>217.96</v>
       </c>
-      <c r="F63" s="47" t="n">
+      <c r="F63" s="49" t="n">
         <v>147</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="48" t="inlineStr">
+      <c r="A64" s="50" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B64" s="47" t="n">
+      <c r="B64" s="49" t="n">
         <v>3691.15</v>
       </c>
-      <c r="C64" s="47" t="n">
+      <c r="C64" s="49" t="n">
         <v>3672.38</v>
       </c>
-      <c r="D64" s="47" t="n">
+      <c r="D64" s="49" t="n">
         <v>3879.84</v>
       </c>
-      <c r="E64" s="47" t="n">
+      <c r="E64" s="49" t="n">
         <v>4188.41</v>
       </c>
-      <c r="F64" s="47" t="n">
+      <c r="F64" s="49" t="n">
         <v>2779.08</v>
       </c>
     </row>
@@ -13132,68 +13460,68 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B65" s="49">
+      <c r="B65" s="51">
         <f>B56+B57+B58+B59+B60+B61+B62+B63+B64</f>
         <v/>
       </c>
-      <c r="C65" s="49">
+      <c r="C65" s="51">
         <f>C56+C57+C58+C59+C60+C61+C62+C63+C64</f>
         <v/>
       </c>
-      <c r="D65" s="49">
+      <c r="D65" s="51">
         <f>D56+D57+D58+D59+D60+D61+D62+D63+D64</f>
         <v/>
       </c>
-      <c r="E65" s="49">
+      <c r="E65" s="51">
         <f>E56+E57+E58+E59+E60+E61+E62+E63+E64</f>
         <v/>
       </c>
-      <c r="F65" s="49">
+      <c r="F65" s="51">
         <f>F56+F57+F58+F59+F60+F61+F62+F63+F64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="48" t="inlineStr">
+      <c r="A66" s="50" t="inlineStr">
         <is>
           <t>Liabilities re: Assets Held For Sale</t>
         </is>
       </c>
-      <c r="B66" s="47" t="n">
+      <c r="B66" s="49" t="n">
         <v>114.24</v>
       </c>
-      <c r="C66" s="47" t="n">
+      <c r="C66" s="49" t="n">
         <v>113.56</v>
       </c>
-      <c r="D66" s="47" t="n">
+      <c r="D66" s="49" t="n">
         <v>113.56</v>
       </c>
-      <c r="E66" s="47" t="n">
+      <c r="E66" s="49" t="n">
         <v>113.56</v>
       </c>
-      <c r="F66" s="47" t="n">
+      <c r="F66" s="49" t="n">
         <v>113.56</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="48" t="inlineStr">
+      <c r="A67" s="50" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Liability</t>
         </is>
       </c>
-      <c r="B67" s="47" t="n">
+      <c r="B67" s="49" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="C67" s="47" t="n">
+      <c r="C67" s="49" t="n">
         <v>138.74</v>
       </c>
-      <c r="D67" s="47" t="n">
+      <c r="D67" s="49" t="n">
         <v>716.42</v>
       </c>
-      <c r="E67" s="47" t="n">
+      <c r="E67" s="49" t="n">
         <v>1235.34</v>
       </c>
-      <c r="F67" s="47" t="n">
+      <c r="F67" s="49" t="n">
         <v>634.63</v>
       </c>
     </row>
@@ -13203,23 +13531,23 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B68" s="49">
+      <c r="B68" s="51">
         <f>B44+B54+B65+B66+B67</f>
         <v/>
       </c>
-      <c r="C68" s="49">
+      <c r="C68" s="51">
         <f>C44+C54+C65+C66+C67</f>
         <v/>
       </c>
-      <c r="D68" s="49">
+      <c r="D68" s="51">
         <f>D44+D54+D65+D66+D67</f>
         <v/>
       </c>
-      <c r="E68" s="49">
+      <c r="E68" s="51">
         <f>E44+E54+E65+E66+E67</f>
         <v/>
       </c>
-      <c r="F68" s="49">
+      <c r="F68" s="51">
         <f>F44+F54+F65+F66+F67</f>
         <v/>
       </c>
@@ -13258,85 +13586,85 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Sources: Tata Power Integrated Annual Reports FY21-22, FY23-24 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="49" t="n">
         <v>62428.59</v>
       </c>
-      <c r="C5" s="47" t="n">
+      <c r="C5" s="49" t="n">
         <v>65478.24</v>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="49" t="n">
         <v>61448.9</v>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="49" t="n">
         <v>55109.08</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="49" t="n">
         <v>42815.67</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>1743.07</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="49" t="n">
         <v>1513.93</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="49" t="n">
         <v>1823.42</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="49" t="n">
         <v>1438.02</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="49" t="n">
         <v>919.96</v>
       </c>
     </row>
@@ -13346,256 +13674,256 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="51">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="51">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="51">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="51">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="51">
         <f>F5+F6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n"/>
-      <c r="C8" s="47" t="n"/>
-      <c r="D8" s="47" t="n"/>
-      <c r="E8" s="47" t="n"/>
-      <c r="F8" s="47" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Cost of Power Purchased</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>19647.25</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="49" t="n">
         <v>20523.61</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="49" t="n">
         <v>20014.46</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="49" t="n">
         <v>19062.67</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="49" t="n">
         <v>14640.62</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Cost of Fuel</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>7498.39</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>13918.47</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>14130.47</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>13763.59</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="49" t="n">
         <v>8290.92</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Transmission Charges</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>1467.98</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="49" t="n">
         <v>1277.81</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="49" t="n">
         <v>1168.69</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="49" t="n">
         <v>1194.95</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="49" t="n">
         <v>1018.19</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Raw Material Consumed / Construction Cost</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>8618.4</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>4921.46</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="49" t="n">
         <v>5439.86</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="49" t="n">
         <v>3882.3</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="49" t="n">
         <v>3832.83</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Purchase of Finished Goods and Spares</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>42.35</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="49" t="n">
         <v>31.84</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="49" t="n">
         <v>39.89</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="49" t="n">
         <v>56.15</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="49" t="n">
         <v>49.11</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>(Increase)/Decrease in Stock-in-Trade &amp; WIP</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="49" t="n">
         <v>-84.11</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="49" t="n">
         <v>-440.76</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="49" t="n">
         <v>-51.78</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="49" t="n">
         <v>43.53</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="F14" s="49" t="n">
         <v>-199.22</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>4693.73</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="49" t="n">
         <v>4372.92</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="49" t="n">
         <v>4036.09</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="49" t="n">
         <v>3624.26</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="49" t="n">
         <v>3611.63</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Finance Costs</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="49" t="n">
         <v>5256.79</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="49" t="n">
         <v>4702.44</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="49" t="n">
         <v>4633.22</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="49" t="n">
         <v>4371.65</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="49" t="n">
         <v>3859.02</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Depreciation and Amortisation Expense</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="49" t="n">
         <v>4811.09</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="49" t="n">
         <v>4116.86</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="49" t="n">
         <v>3786.37</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="49" t="n">
         <v>3439.2</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="49" t="n">
         <v>3122.2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n">
+      <c r="B18" s="49" t="n">
         <v>7449.54</v>
       </c>
-      <c r="C18" s="47" t="n">
+      <c r="C18" s="49" t="n">
         <v>6943.02</v>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="49" t="n">
         <v>5887.39</v>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="49" t="n">
         <v>5775.31</v>
       </c>
-      <c r="F18" s="47" t="n">
+      <c r="F18" s="49" t="n">
         <v>4060.42</v>
       </c>
     </row>
@@ -13605,23 +13933,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="51">
         <f>B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="51">
         <f>C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="51">
         <f>D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="51">
         <f>E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="51">
         <f>F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
@@ -13632,46 +13960,46 @@
           <t>Profit before Regulatory Deferral, Exceptional Items &amp; Assoc./JV share</t>
         </is>
       </c>
-      <c r="B20" s="49">
+      <c r="B20" s="51">
         <f>B7-B19</f>
         <v/>
       </c>
-      <c r="C20" s="49">
+      <c r="C20" s="51">
         <f>C7-C19</f>
         <v/>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="51">
         <f>D7-D19</f>
         <v/>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="51">
         <f>E7-E19</f>
         <v/>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="51">
         <f>F7-F19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>Net Movement in Regulatory Deferral Balances (incl. earlier years, net tax)</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="49" t="n">
         <v>1252.04</v>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="49" t="n">
         <v>-976.16</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="49" t="n">
         <v>93.43000000000001</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="49" t="n">
         <v>924.05</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="F21" s="49" t="n">
         <v>-239.47</v>
       </c>
     </row>
@@ -13681,46 +14009,46 @@
           <t>Profit Before Exceptional Items, Tax &amp; Assoc./JV Share</t>
         </is>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="51">
         <f>B20+B21</f>
         <v/>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="51">
         <f>C20+C21</f>
         <v/>
       </c>
-      <c r="D22" s="49">
+      <c r="D22" s="51">
         <f>D20+D21</f>
         <v/>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="51">
         <f>E20+E21</f>
         <v/>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="51">
         <f>F20+F21</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>Share of Net Profit of Associates and JVs (Equity Method)</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
+      <c r="B23" s="49" t="n">
         <v>707.87</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="49" t="n">
         <v>793.33</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="49" t="n">
         <v>1177.57</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="49" t="n">
         <v>3199.46</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="49" t="n">
         <v>1942.83</v>
       </c>
     </row>
@@ -13730,46 +14058,46 @@
           <t>Profit Before Exceptional Items and Tax</t>
         </is>
       </c>
-      <c r="B24" s="49">
+      <c r="B24" s="51">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="51">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="49">
+      <c r="D24" s="51">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="51">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="51">
         <f>F22+F23</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Exceptional Items (net)</t>
         </is>
       </c>
-      <c r="B25" s="47" t="n">
+      <c r="B25" s="49" t="n">
         <v>-94.17</v>
       </c>
-      <c r="C25" s="47" t="n">
+      <c r="C25" s="49" t="n">
         <v>-122.05</v>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="49" t="n">
         <v>273.36</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="49" t="n">
         <v>-150.27</v>
       </c>
     </row>
@@ -13779,46 +14107,46 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B26" s="49">
+      <c r="B26" s="51">
         <f>B24+B25</f>
         <v/>
       </c>
-      <c r="C26" s="49">
+      <c r="C26" s="51">
         <f>C24+C25</f>
         <v/>
       </c>
-      <c r="D26" s="49">
+      <c r="D26" s="51">
         <f>D24+D25</f>
         <v/>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="51">
         <f>E24+E25</f>
         <v/>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="51">
         <f>F24+F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Total Tax Expense/(Credit)</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="49" t="n">
         <v>1518.43</v>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C27" s="49" t="n">
         <v>1544.25</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="49" t="n">
         <v>1451.92</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="49" t="n">
         <v>1647.33</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="49" t="n">
         <v>379.56</v>
       </c>
     </row>
@@ -13828,23 +14156,23 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B28" s="49">
+      <c r="B28" s="51">
         <f>B26-B27</f>
         <v/>
       </c>
-      <c r="C28" s="49">
+      <c r="C28" s="51">
         <f>C26-C27</f>
         <v/>
       </c>
-      <c r="D28" s="49">
+      <c r="D28" s="51">
         <f>D26-D27</f>
         <v/>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="51">
         <f>E26-E27</f>
         <v/>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="51">
         <f>F26-F27</f>
         <v/>
       </c>
@@ -13884,360 +14212,360 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Sources: Torrent Power Integrated Annual Reports FY21-22 (AR_20392) through FY25-26 (AR_29704) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>Mar-2021</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n"/>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
-      <c r="G5" s="47" t="n"/>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="49" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>24200.83</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="49" t="n">
         <v>23028.29</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="49" t="n">
         <v>20653.68</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="49" t="n">
         <v>18115.94</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="49" t="n">
         <v>16759.39</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="49" t="n">
         <v>17129.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>Right-of-use Assets</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="49" t="n">
         <v>585.35</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="49" t="n">
         <v>398.86</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="49" t="n">
         <v>259.07</v>
       </c>
-      <c r="E7" s="47" t="n">
+      <c r="E7" s="49" t="n">
         <v>216.46</v>
       </c>
-      <c r="F7" s="47" t="n">
+      <c r="F7" s="49" t="n">
         <v>214.6</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="49" t="n">
         <v>178.35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="49" t="n">
         <v>6961.53</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="49" t="n">
         <v>2249.81</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="49" t="n">
         <v>2472.36</v>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="49" t="n">
         <v>2624.69</v>
       </c>
-      <c r="F8" s="47" t="n">
+      <c r="F8" s="49" t="n">
         <v>1297.27</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="49" t="n">
         <v>837.73</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Investment Property</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>0.37</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="49" t="n">
         <v>0.37</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="49" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="F9" s="47" t="n"/>
-      <c r="G9" s="47" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>171.07</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>171.07</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>171.07</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>171.07</v>
       </c>
-      <c r="F10" s="47" t="n"/>
-      <c r="G10" s="47" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="49" t="n">
         <v>653.66</v>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="49" t="n">
         <v>687.46</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="49" t="n">
         <v>718.46</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="49" t="n">
         <v>756.33</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="49" t="n">
         <v>123.29</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="49" t="n">
         <v>18.44</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Intangible Assets Under Development</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>3.25</v>
       </c>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
-      <c r="E12" s="47" t="n"/>
-      <c r="F12" s="47" t="n"/>
-      <c r="G12" s="47" t="n"/>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Investments (Non-current)</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>24.1</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="49" t="n">
         <v>22.15</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="49" t="n">
         <v>17.02</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="49" t="n">
         <v>15.94</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="49" t="n">
         <v>132.82</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="49" t="n">
         <v>124.2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="E14" s="47" t="n">
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="F14" s="49" t="n">
         <v>121.87</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="49" t="n">
         <v>155.7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>349.43</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="49" t="n">
         <v>105.75</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="49" t="n">
         <v>94.68000000000001</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="49" t="n">
         <v>135.38</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="49" t="n">
         <v>101.55</v>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="49" t="n">
         <v>75.83</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="49" t="n">
         <v>148.21</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="49" t="n">
         <v>114.67</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="49" t="n">
         <v>66.38</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="49" t="n">
         <v>38.65</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="49" t="n">
         <v>35.12</v>
       </c>
-      <c r="G16" s="47" t="n">
+      <c r="G16" s="49" t="n">
         <v>24.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="49" t="n">
         <v>18.85</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="49" t="n">
         <v>16.27</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="49" t="n">
         <v>12.64</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="49" t="n">
         <v>12.5</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="49" t="n">
         <v>10.56</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="49" t="n">
         <v>12.83</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
       </c>
-      <c r="B18" s="47" t="n">
+      <c r="B18" s="49" t="n">
         <v>2837.21</v>
       </c>
-      <c r="C18" s="47" t="n">
+      <c r="C18" s="49" t="n">
         <v>1158.63</v>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="49" t="n">
         <v>420.76</v>
       </c>
-      <c r="E18" s="47" t="n">
+      <c r="E18" s="49" t="n">
         <v>361.04</v>
       </c>
-      <c r="F18" s="47" t="n">
+      <c r="F18" s="49" t="n">
         <v>1000.47</v>
       </c>
-      <c r="G18" s="47" t="n">
+      <c r="G18" s="49" t="n">
         <v>337.48</v>
       </c>
     </row>
@@ -14247,233 +14575,233 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="51">
         <f>B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="51">
         <f>C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="51">
         <f>D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="51">
         <f>E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="51">
         <f>F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="51">
         <f>G6+G7+G8+G9+G10+G11+G12+G13+G14+G15+G16+G17+G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="47" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="49" t="n">
         <v>507.18</v>
       </c>
-      <c r="C21" s="47" t="n">
+      <c r="C21" s="49" t="n">
         <v>658.02</v>
       </c>
-      <c r="D21" s="47" t="n">
+      <c r="D21" s="49" t="n">
         <v>800.45</v>
       </c>
-      <c r="E21" s="47" t="n">
+      <c r="E21" s="49" t="n">
         <v>820.28</v>
       </c>
-      <c r="F21" s="47" t="n">
+      <c r="F21" s="49" t="n">
         <v>537.5700000000001</v>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="49" t="n">
         <v>450.35</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
+      <c r="B22" s="49" t="n">
         <v>1507.19</v>
       </c>
-      <c r="C22" s="47" t="n">
+      <c r="C22" s="49" t="n">
         <v>873.03</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="49" t="n">
         <v>937.37</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="49" t="n">
         <v>787.75</v>
       </c>
-      <c r="F22" s="47" t="n">
+      <c r="F22" s="49" t="n">
         <v>273.7</v>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="49" t="n">
         <v>341.58</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>Trade Receivables</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
+      <c r="B23" s="49" t="n">
         <v>2329.76</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="49" t="n">
         <v>2362.25</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="49" t="n">
         <v>2190.86</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="49" t="n">
         <v>2246.33</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="49" t="n">
         <v>1602.7</v>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="49" t="n">
         <v>1420.29</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="inlineStr">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
+      <c r="B24" s="49" t="n">
         <v>766.61</v>
       </c>
-      <c r="C24" s="47" t="n">
+      <c r="C24" s="49" t="n">
         <v>289.11</v>
       </c>
-      <c r="D24" s="47" t="n">
+      <c r="D24" s="49" t="n">
         <v>350.83</v>
       </c>
-      <c r="E24" s="47" t="n">
+      <c r="E24" s="49" t="n">
         <v>188.23</v>
       </c>
-      <c r="F24" s="47" t="n">
+      <c r="F24" s="49" t="n">
         <v>289.41</v>
       </c>
-      <c r="G24" s="47" t="n">
+      <c r="G24" s="49" t="n">
         <v>107.28</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
       </c>
-      <c r="B25" s="47" t="n">
+      <c r="B25" s="49" t="n">
         <v>64.81999999999999</v>
       </c>
-      <c r="C25" s="47" t="n">
+      <c r="C25" s="49" t="n">
         <v>90.89</v>
       </c>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="49" t="n">
         <v>67.91</v>
       </c>
-      <c r="E25" s="47" t="n">
+      <c r="E25" s="49" t="n">
         <v>155.29</v>
       </c>
-      <c r="F25" s="47" t="n">
+      <c r="F25" s="49" t="n">
         <v>62.93</v>
       </c>
-      <c r="G25" s="47" t="n">
+      <c r="G25" s="49" t="n">
         <v>95.14</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
       </c>
-      <c r="B26" s="47" t="n"/>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="47" t="n"/>
-      <c r="F26" s="47" t="n">
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n">
         <v>19.9</v>
       </c>
-      <c r="G26" s="47" t="n">
+      <c r="G26" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="50" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="49" t="n">
         <v>3516.62</v>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C27" s="49" t="n">
         <v>4188.37</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="49" t="n">
         <v>3989.23</v>
       </c>
-      <c r="E27" s="47" t="n">
+      <c r="E27" s="49" t="n">
         <v>3111.4</v>
       </c>
-      <c r="F27" s="47" t="n">
+      <c r="F27" s="49" t="n">
         <v>2298.81</v>
       </c>
-      <c r="G27" s="47" t="n">
+      <c r="G27" s="49" t="n">
         <v>2153.41</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="49" t="n">
         <v>547.24</v>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C28" s="49" t="n">
         <v>158.38</v>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="49" t="n">
         <v>169.71</v>
       </c>
-      <c r="E28" s="47" t="n">
+      <c r="E28" s="49" t="n">
         <v>143.51</v>
       </c>
-      <c r="F28" s="47" t="n">
+      <c r="F28" s="49" t="n">
         <v>140.74</v>
       </c>
-      <c r="G28" s="47" t="n">
+      <c r="G28" s="49" t="n">
         <v>76.36</v>
       </c>
     </row>
@@ -14483,27 +14811,27 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B29" s="49">
+      <c r="B29" s="51">
         <f>B21+B22+B23+B24+B25+B26+B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="51">
         <f>C21+C22+C23+C24+C25+C26+C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="49">
+      <c r="D29" s="51">
         <f>D21+D22+D23+D24+D25+D26+D27+D28</f>
         <v/>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="51">
         <f>E21+E22+E23+E24+E25+E26+E27+E28</f>
         <v/>
       </c>
-      <c r="F29" s="49">
+      <c r="F29" s="51">
         <f>F21+F22+F23+F24+F25+F26+F27+F28</f>
         <v/>
       </c>
-      <c r="G29" s="49">
+      <c r="G29" s="51">
         <f>G21+G22+G23+G24+G25+G26+G27+G28</f>
         <v/>
       </c>
@@ -14514,91 +14842,91 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B30" s="49">
+      <c r="B30" s="51">
         <f>B19+B29</f>
         <v/>
       </c>
-      <c r="C30" s="49">
+      <c r="C30" s="51">
         <f>C19+C29</f>
         <v/>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="51">
         <f>D19+D29</f>
         <v/>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="51">
         <f>E19+E29</f>
         <v/>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="51">
         <f>F19+F29</f>
         <v/>
       </c>
-      <c r="G30" s="49">
+      <c r="G30" s="51">
         <f>G19+G29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="46" t="inlineStr">
+      <c r="A31" s="48" t="inlineStr">
         <is>
           <t>EQUITY &amp; LIABILITIES</t>
         </is>
       </c>
-      <c r="B31" s="47" t="n"/>
-      <c r="C31" s="47" t="n"/>
-      <c r="D31" s="47" t="n"/>
-      <c r="E31" s="47" t="n"/>
-      <c r="F31" s="47" t="n"/>
-      <c r="G31" s="47" t="n"/>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
       </c>
-      <c r="B32" s="47" t="n">
+      <c r="B32" s="49" t="n">
         <v>503.9</v>
       </c>
-      <c r="C32" s="47" t="n">
+      <c r="C32" s="49" t="n">
         <v>503.9</v>
       </c>
-      <c r="D32" s="47" t="n">
+      <c r="D32" s="49" t="n">
         <v>480.62</v>
       </c>
-      <c r="E32" s="47" t="n">
+      <c r="E32" s="49" t="n">
         <v>480.62</v>
       </c>
-      <c r="F32" s="47" t="n">
+      <c r="F32" s="49" t="n">
         <v>480.62</v>
       </c>
-      <c r="G32" s="47" t="n">
+      <c r="G32" s="49" t="n">
         <v>480.62</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
       </c>
-      <c r="B33" s="47" t="n">
+      <c r="B33" s="49" t="n">
         <v>18571.43</v>
       </c>
-      <c r="C33" s="47" t="n">
+      <c r="C33" s="49" t="n">
         <v>17111.41</v>
       </c>
-      <c r="D33" s="47" t="n">
+      <c r="D33" s="49" t="n">
         <v>11581.09</v>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E33" s="49" t="n">
         <v>10529.38</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F33" s="49" t="n">
         <v>9462.559999999999</v>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="49" t="n">
         <v>9703.620000000001</v>
       </c>
     </row>
@@ -14608,53 +14936,53 @@
           <t>Net Worth (Attributable to Owners)</t>
         </is>
       </c>
-      <c r="B34" s="49">
+      <c r="B34" s="51">
         <f>B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="49">
+      <c r="C34" s="51">
         <f>C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="49">
+      <c r="D34" s="51">
         <f>D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="51">
         <f>E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="51">
         <f>F32+F33</f>
         <v/>
       </c>
-      <c r="G34" s="49">
+      <c r="G34" s="51">
         <f>G32+G33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>Non-Controlling Interests</t>
         </is>
       </c>
-      <c r="B35" s="47" t="n">
+      <c r="B35" s="49" t="n">
         <v>633.42</v>
       </c>
-      <c r="C35" s="47" t="n">
+      <c r="C35" s="49" t="n">
         <v>600.47</v>
       </c>
-      <c r="D35" s="47" t="n">
+      <c r="D35" s="49" t="n">
         <v>535.79</v>
       </c>
-      <c r="E35" s="47" t="n">
+      <c r="E35" s="49" t="n">
         <v>476.65</v>
       </c>
-      <c r="F35" s="47" t="n">
+      <c r="F35" s="49" t="n">
         <v>35.93</v>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="49" t="n">
         <v>36.36</v>
       </c>
     </row>
@@ -14664,191 +14992,191 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B36" s="49">
+      <c r="B36" s="51">
         <f>B34+B35</f>
         <v/>
       </c>
-      <c r="C36" s="49">
+      <c r="C36" s="51">
         <f>C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="49">
+      <c r="D36" s="51">
         <f>D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="51">
         <f>E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="49">
+      <c r="F36" s="51">
         <f>F34+F35</f>
         <v/>
       </c>
-      <c r="G36" s="49">
+      <c r="G36" s="51">
         <f>G34+G35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="46" t="inlineStr">
+      <c r="A37" s="48" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B37" s="47" t="n"/>
-      <c r="C37" s="47" t="n"/>
-      <c r="D37" s="47" t="n"/>
-      <c r="E37" s="47" t="n"/>
-      <c r="F37" s="47" t="n"/>
-      <c r="G37" s="47" t="n"/>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="49" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="48" t="inlineStr">
+      <c r="A38" s="50" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="49" t="n">
         <v>11871.42</v>
       </c>
-      <c r="C38" s="47" t="n">
+      <c r="C38" s="49" t="n">
         <v>7310.21</v>
       </c>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="49" t="n">
         <v>9916.4</v>
       </c>
-      <c r="E38" s="47" t="n">
+      <c r="E38" s="49" t="n">
         <v>8902.32</v>
       </c>
-      <c r="F38" s="47" t="n">
+      <c r="F38" s="49" t="n">
         <v>7099.15</v>
       </c>
-      <c r="G38" s="47" t="n">
+      <c r="G38" s="49" t="n">
         <v>6672.18</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="48" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B39" s="47" t="n">
+      <c r="B39" s="49" t="n">
         <v>219.83</v>
       </c>
-      <c r="C39" s="47" t="n">
+      <c r="C39" s="49" t="n">
         <v>92.78</v>
       </c>
-      <c r="D39" s="47" t="n">
+      <c r="D39" s="49" t="n">
         <v>39.5</v>
       </c>
-      <c r="E39" s="47" t="n">
+      <c r="E39" s="49" t="n">
         <v>39.32</v>
       </c>
-      <c r="F39" s="47" t="n">
+      <c r="F39" s="49" t="n">
         <v>39.1</v>
       </c>
-      <c r="G39" s="47" t="n">
+      <c r="G39" s="49" t="n">
         <v>30.96</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="50" t="inlineStr">
         <is>
           <t>Trade Payables (Non-current)</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
+      <c r="B40" s="49" t="n">
         <v>324.05</v>
       </c>
-      <c r="C40" s="47" t="n">
+      <c r="C40" s="49" t="n">
         <v>380.88</v>
       </c>
-      <c r="D40" s="47" t="n">
+      <c r="D40" s="49" t="n">
         <v>345.71</v>
       </c>
-      <c r="E40" s="47" t="n">
+      <c r="E40" s="49" t="n">
         <v>210.61</v>
       </c>
-      <c r="F40" s="47" t="n">
+      <c r="F40" s="49" t="n">
         <v>150.46</v>
       </c>
-      <c r="G40" s="47" t="n">
+      <c r="G40" s="49" t="n">
         <v>116.11</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="50" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B41" s="47" t="n">
+      <c r="B41" s="49" t="n">
         <v>38.14</v>
       </c>
-      <c r="C41" s="47" t="n">
+      <c r="C41" s="49" t="n">
         <v>8.43</v>
       </c>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="49" t="n">
         <v>0.95</v>
       </c>
-      <c r="E41" s="47" t="n">
+      <c r="E41" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="47" t="n">
+      <c r="F41" s="49" t="n">
         <v>0.33</v>
       </c>
-      <c r="G41" s="47" t="n">
+      <c r="G41" s="49" t="n">
         <v>1.17</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B42" s="47" t="n">
+      <c r="B42" s="49" t="n">
         <v>1628.57</v>
       </c>
-      <c r="C42" s="47" t="n">
+      <c r="C42" s="49" t="n">
         <v>1352.21</v>
       </c>
-      <c r="D42" s="47" t="n">
+      <c r="D42" s="49" t="n">
         <v>1233.65</v>
       </c>
-      <c r="E42" s="47" t="n">
+      <c r="E42" s="49" t="n">
         <v>968.79</v>
       </c>
-      <c r="F42" s="47" t="n">
+      <c r="F42" s="49" t="n">
         <v>345.21</v>
       </c>
-      <c r="G42" s="47" t="n">
+      <c r="G42" s="49" t="n">
         <v>527.51</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="50" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B43" s="47" t="n">
+      <c r="B43" s="49" t="n">
         <v>1689.43</v>
       </c>
-      <c r="C43" s="47" t="n">
+      <c r="C43" s="49" t="n">
         <v>1623.6</v>
       </c>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="49" t="n">
         <v>1445.68</v>
       </c>
-      <c r="E43" s="47" t="n">
+      <c r="E43" s="49" t="n">
         <v>1372.46</v>
       </c>
-      <c r="F43" s="47" t="n">
+      <c r="F43" s="49" t="n">
         <v>1261.67</v>
       </c>
-      <c r="G43" s="47" t="n">
+      <c r="G43" s="49" t="n">
         <v>1160.34</v>
       </c>
     </row>
@@ -14858,216 +15186,216 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B44" s="49">
+      <c r="B44" s="51">
         <f>B38+B39+B40+B41+B42+B43</f>
         <v/>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="51">
         <f>C38+C39+C40+C41+C42+C43</f>
         <v/>
       </c>
-      <c r="D44" s="49">
+      <c r="D44" s="51">
         <f>D38+D39+D40+D41+D42+D43</f>
         <v/>
       </c>
-      <c r="E44" s="49">
+      <c r="E44" s="51">
         <f>E38+E39+E40+E41+E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="49">
+      <c r="F44" s="51">
         <f>F38+F39+F40+F41+F42+F43</f>
         <v/>
       </c>
-      <c r="G44" s="49">
+      <c r="G44" s="51">
         <f>G38+G39+G40+G41+G42+G43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="48" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B45" s="47" t="n"/>
-      <c r="C45" s="47" t="n"/>
-      <c r="D45" s="47" t="n"/>
-      <c r="E45" s="47" t="n"/>
-      <c r="F45" s="47" t="n"/>
-      <c r="G45" s="47" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="48" t="inlineStr">
+      <c r="A46" s="50" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
       </c>
-      <c r="B46" s="47" t="n">
+      <c r="B46" s="49" t="n">
         <v>1861.51</v>
       </c>
-      <c r="C46" s="47" t="n">
+      <c r="C46" s="49" t="n">
         <v>1426.47</v>
       </c>
-      <c r="D46" s="47" t="n">
+      <c r="D46" s="49" t="n">
         <v>1668.63</v>
       </c>
-      <c r="E46" s="47" t="n">
+      <c r="E46" s="49" t="n">
         <v>1593.75</v>
       </c>
-      <c r="F46" s="47" t="n">
+      <c r="F46" s="49" t="n">
         <v>1999.27</v>
       </c>
-      <c r="G46" s="47" t="n">
+      <c r="G46" s="49" t="n">
         <v>1108.37</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="48" t="inlineStr">
+      <c r="A47" s="50" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B47" s="47" t="n">
+      <c r="B47" s="49" t="n">
         <v>17.8</v>
       </c>
-      <c r="C47" s="47" t="n">
+      <c r="C47" s="49" t="n">
         <v>10.28</v>
       </c>
-      <c r="D47" s="47" t="n">
+      <c r="D47" s="49" t="n">
         <v>7.27</v>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="49" t="n">
         <v>6.02</v>
       </c>
-      <c r="F47" s="47" t="n">
+      <c r="F47" s="49" t="n">
         <v>5.11</v>
       </c>
-      <c r="G47" s="47" t="n">
+      <c r="G47" s="49" t="n">
         <v>5.05</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="48" t="inlineStr">
+      <c r="A48" s="50" t="inlineStr">
         <is>
           <t>Trade Payables (Current)</t>
         </is>
       </c>
-      <c r="B48" s="47" t="n">
+      <c r="B48" s="49" t="n">
         <v>1879.23</v>
       </c>
-      <c r="C48" s="47" t="n">
+      <c r="C48" s="49" t="n">
         <v>1824.13</v>
       </c>
-      <c r="D48" s="47" t="n">
+      <c r="D48" s="49" t="n">
         <v>1811.92</v>
       </c>
-      <c r="E48" s="47" t="n">
+      <c r="E48" s="49" t="n">
         <v>1522.67</v>
       </c>
-      <c r="F48" s="47" t="n">
+      <c r="F48" s="49" t="n">
         <v>1111.13</v>
       </c>
-      <c r="G48" s="47" t="n">
+      <c r="G48" s="49" t="n">
         <v>974.79</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="48" t="inlineStr">
+      <c r="A49" s="50" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B49" s="47" t="n">
+      <c r="B49" s="49" t="n">
         <v>4771.06</v>
       </c>
-      <c r="C49" s="47" t="n">
+      <c r="C49" s="49" t="n">
         <v>3409.61</v>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="49" t="n">
         <v>3264.67</v>
       </c>
-      <c r="E49" s="47" t="n">
+      <c r="E49" s="49" t="n">
         <v>2687.72</v>
       </c>
-      <c r="F49" s="47" t="n">
+      <c r="F49" s="49" t="n">
         <v>2021.51</v>
       </c>
-      <c r="G49" s="47" t="n">
+      <c r="G49" s="49" t="n">
         <v>1799.77</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="48" t="inlineStr">
+      <c r="A50" s="50" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B50" s="47" t="n">
+      <c r="B50" s="49" t="n">
         <v>921.02</v>
       </c>
-      <c r="C50" s="47" t="n">
+      <c r="C50" s="49" t="n">
         <v>689.74</v>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="49" t="n">
         <v>735.0599999999999</v>
       </c>
-      <c r="E50" s="47" t="n">
+      <c r="E50" s="49" t="n">
         <v>677.24</v>
       </c>
-      <c r="F50" s="47" t="n">
+      <c r="F50" s="49" t="n">
         <v>613.5599999999999</v>
       </c>
-      <c r="G50" s="47" t="n">
+      <c r="G50" s="49" t="n">
         <v>542.02</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="48" t="inlineStr">
+      <c r="A51" s="50" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
       </c>
-      <c r="B51" s="47" t="n">
+      <c r="B51" s="49" t="n">
         <v>226.37</v>
       </c>
-      <c r="C51" s="47" t="n">
+      <c r="C51" s="49" t="n">
         <v>198.17</v>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="49" t="n">
         <v>201.74</v>
       </c>
-      <c r="E51" s="47" t="n">
+      <c r="E51" s="49" t="n">
         <v>264.06</v>
       </c>
-      <c r="F51" s="47" t="n">
+      <c r="F51" s="49" t="n">
         <v>274.55</v>
       </c>
-      <c r="G51" s="47" t="n">
+      <c r="G51" s="49" t="n">
         <v>335.3</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="48" t="inlineStr">
+      <c r="A52" s="50" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B52" s="47" t="n">
+      <c r="B52" s="49" t="n">
         <v>36.1</v>
       </c>
-      <c r="C52" s="47" t="n">
+      <c r="C52" s="49" t="n">
         <v>31.09</v>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="49" t="n">
         <v>123.8</v>
       </c>
-      <c r="E52" s="47" t="n">
+      <c r="E52" s="49" t="n">
         <v>178.57</v>
       </c>
-      <c r="F52" s="47" t="n">
+      <c r="F52" s="49" t="n">
         <v>122.54</v>
       </c>
-      <c r="G52" s="47" t="n">
+      <c r="G52" s="49" t="n">
         <v>44.55</v>
       </c>
     </row>
@@ -15077,27 +15405,27 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B53" s="49">
+      <c r="B53" s="51">
         <f>B46+B47+B48+B49+B50+B51+B52</f>
         <v/>
       </c>
-      <c r="C53" s="49">
+      <c r="C53" s="51">
         <f>C46+C47+C48+C49+C50+C51+C52</f>
         <v/>
       </c>
-      <c r="D53" s="49">
+      <c r="D53" s="51">
         <f>D46+D47+D48+D49+D50+D51+D52</f>
         <v/>
       </c>
-      <c r="E53" s="49">
+      <c r="E53" s="51">
         <f>E46+E47+E48+E49+E50+E51+E52</f>
         <v/>
       </c>
-      <c r="F53" s="49">
+      <c r="F53" s="51">
         <f>F46+F47+F48+F49+F50+F51+F52</f>
         <v/>
       </c>
-      <c r="G53" s="49">
+      <c r="G53" s="51">
         <f>G46+G47+G48+G49+G50+G51+G52</f>
         <v/>
       </c>
@@ -15108,27 +15436,27 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B54" s="49">
+      <c r="B54" s="51">
         <f>B36+B44+B53</f>
         <v/>
       </c>
-      <c r="C54" s="49">
+      <c r="C54" s="51">
         <f>C36+C44+C53</f>
         <v/>
       </c>
-      <c r="D54" s="49">
+      <c r="D54" s="51">
         <f>D36+D44+D53</f>
         <v/>
       </c>
-      <c r="E54" s="49">
+      <c r="E54" s="51">
         <f>E36+E44+E53</f>
         <v/>
       </c>
-      <c r="F54" s="49">
+      <c r="F54" s="51">
         <f>F36+F44+F53</f>
         <v/>
       </c>
-      <c r="G54" s="49">
+      <c r="G54" s="51">
         <f>G36+G44+G53</f>
         <v/>
       </c>
@@ -15168,96 +15496,96 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Sources: Torrent Power Integrated Annual Reports FY21-22 through FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS. Only FY22 had an exceptional item (the ~Rs 1,300cr DGEN plant impairment) — all other years are genuinely nil, not missing data.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="47" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>FY 2020-21</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="49" t="n">
         <v>28966.31</v>
       </c>
-      <c r="C5" s="47" t="n">
+      <c r="C5" s="49" t="n">
         <v>29165.26</v>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="49" t="n">
         <v>27183.21</v>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="49" t="n">
         <v>25694.12</v>
       </c>
-      <c r="F5" s="47" t="n">
+      <c r="F5" s="49" t="n">
         <v>14257.61</v>
       </c>
-      <c r="G5" s="47" t="n">
+      <c r="G5" s="49" t="n">
         <v>12172.66</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="49" t="n">
         <v>322.61</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="49" t="n">
         <v>487.21</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="49" t="n">
         <v>344.32</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="49" t="n">
         <v>381.85</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F6" s="49" t="n">
         <v>235.04</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="49" t="n">
         <v>141.81</v>
       </c>
     </row>
@@ -15267,264 +15595,264 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="49">
+      <c r="B7" s="51">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="51">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="51">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="51">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="51">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="51">
         <f>G5+G6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n"/>
-      <c r="C8" s="47" t="n"/>
-      <c r="D8" s="47" t="n"/>
-      <c r="E8" s="47" t="n"/>
-      <c r="F8" s="47" t="n"/>
-      <c r="G8" s="47" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Electrical Energy Purchased</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="49" t="n">
         <v>15053.7</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="49" t="n">
         <v>15289.81</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="49" t="n">
         <v>13743.27</v>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="49" t="n">
         <v>14440.53</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="49" t="n">
         <v>5116.39</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="49" t="n">
         <v>3358.36</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="49" t="n">
         <v>3944.21</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>4877.69</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="49" t="n">
         <v>5647.95</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>2508.23</v>
       </c>
-      <c r="F10" s="47" t="n">
+      <c r="F10" s="49" t="n">
         <v>3403.4</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="49" t="n">
         <v>3610.55</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Cost of Materials Consumed</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n"/>
-      <c r="C11" s="47" t="n">
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="49" t="n">
         <v>213.46</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="49" t="n">
         <v>406.5</v>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="49" t="n">
         <v>334.81</v>
       </c>
-      <c r="F11" s="47" t="n">
+      <c r="F11" s="49" t="n">
         <v>262.64</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="49" t="n">
         <v>104.21</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Purchase of Stock-in-Trade</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="49" t="n">
         <v>1593.67</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>1103.91</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="49" t="n">
         <v>690.53</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="49" t="n">
         <v>1879.26</v>
       </c>
-      <c r="F12" s="47" t="n">
+      <c r="F12" s="49" t="n">
         <v>305.99</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="49" t="n">
         <v>48.24</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Changes in Inventories of Finished Goods and WIP</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="49" t="n">
         <v>0.11</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="49" t="n">
         <v>20.45</v>
       </c>
-      <c r="E13" s="47" t="n">
+      <c r="E13" s="49" t="n">
         <v>-29.19</v>
       </c>
-      <c r="F13" s="47" t="n">
+      <c r="F13" s="49" t="n">
         <v>-11.11</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="49" t="n">
         <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="49" t="n">
         <v>705.8</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="49" t="n">
         <v>689.96</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="49" t="n">
         <v>611.1900000000001</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="49" t="n">
         <v>578.25</v>
       </c>
-      <c r="F14" s="47" t="n">
+      <c r="F14" s="49" t="n">
         <v>533.54</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="49" t="n">
         <v>538.9400000000001</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Finance Costs</t>
         </is>
       </c>
-      <c r="B15" s="47" t="n">
+      <c r="B15" s="49" t="n">
         <v>934.47</v>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="49" t="n">
         <v>1044.87</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="49" t="n">
         <v>943.4</v>
       </c>
-      <c r="E15" s="47" t="n">
+      <c r="E15" s="49" t="n">
         <v>818.2</v>
       </c>
-      <c r="F15" s="47" t="n">
+      <c r="F15" s="49" t="n">
         <v>628.21</v>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="49" t="n">
         <v>775.73</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortisation</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="49" t="n">
         <v>1612.75</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="49" t="n">
         <v>1497.12</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="49" t="n">
         <v>1377.5</v>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="49" t="n">
         <v>1280.96</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F16" s="49" t="n">
         <v>1333.86</v>
       </c>
-      <c r="G16" s="47" t="n">
+      <c r="G16" s="49" t="n">
         <v>1279.55</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="49" t="n">
         <v>2127.55</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="49" t="n">
         <v>1682.96</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="49" t="n">
         <v>1504.14</v>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="49" t="n">
         <v>1223.56</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="49" t="n">
         <v>1055.76</v>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="49" t="n">
         <v>1038.26</v>
       </c>
     </row>
@@ -15534,27 +15862,27 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B18" s="49">
+      <c r="B18" s="51">
         <f>B9+B10+B11+B12+B13+B14+B15+B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="51">
         <f>C9+C10+C11+C12+C13+C14+C15+C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="51">
         <f>D9+D10+D11+D12+D13+D14+D15+D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="51">
         <f>E9+E10+E11+E12+E13+E14+E15+E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="51">
         <f>F9+F10+F11+F12+F13+F14+F15+F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="51">
         <f>G9+G10+G11+G12+G13+G14+G15+G16+G17</f>
         <v/>
       </c>
@@ -15565,53 +15893,53 @@
           <t>Profit Before Exceptional Items and Tax</t>
         </is>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="51">
         <f>B7-B18</f>
         <v/>
       </c>
-      <c r="C19" s="49">
+      <c r="C19" s="51">
         <f>C7-C18</f>
         <v/>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="51">
         <f>D7-D18</f>
         <v/>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="51">
         <f>E7-E18</f>
         <v/>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="51">
         <f>F7-F18</f>
         <v/>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="51">
         <f>G7-G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>Exceptional Items (DGEN plant impairment, FY22 only)</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="47" t="n">
+      <c r="C20" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="F20" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="G20" s="47" t="n">
+      <c r="G20" s="49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15621,78 +15949,78 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="51">
         <f>B19-B20</f>
         <v/>
       </c>
-      <c r="C21" s="49">
+      <c r="C21" s="51">
         <f>C19-C20</f>
         <v/>
       </c>
-      <c r="D21" s="49">
+      <c r="D21" s="51">
         <f>D19-D20</f>
         <v/>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="51">
         <f>E19-E20</f>
         <v/>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="51">
         <f>F19-F20</f>
         <v/>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="51">
         <f>G19-G20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Current Tax</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
+      <c r="B22" s="49" t="n">
         <v>728.15</v>
       </c>
-      <c r="C22" s="47" t="n">
+      <c r="C22" s="49" t="n">
         <v>600.47</v>
       </c>
-      <c r="D22" s="47" t="n">
+      <c r="D22" s="49" t="n">
         <v>445.07</v>
       </c>
-      <c r="E22" s="47" t="n">
+      <c r="E22" s="49" t="n">
         <v>672.8200000000001</v>
       </c>
-      <c r="F22" s="47" t="n">
+      <c r="F22" s="49" t="n">
         <v>372.48</v>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="49" t="n">
         <v>287.85</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="50" t="inlineStr">
         <is>
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n">
+      <c r="B23" s="49" t="n">
         <v>119.26</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="49" t="n">
         <v>-406.5</v>
       </c>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="49" t="n">
         <v>241.53</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E23" s="49" t="n">
         <v>203.87</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="49" t="n">
         <v>-267.21</v>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="49" t="n">
         <v>-31.95</v>
       </c>
     </row>
@@ -15702,27 +16030,27 @@
           <t>Total Tax Expense</t>
         </is>
       </c>
-      <c r="B24" s="49">
+      <c r="B24" s="51">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="49">
+      <c r="C24" s="51">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="49">
+      <c r="D24" s="51">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="51">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="51">
         <f>F22+F23</f>
         <v/>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="51">
         <f>G22+G23</f>
         <v/>
       </c>
@@ -15733,27 +16061,27 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B25" s="49">
+      <c r="B25" s="51">
         <f>B21-B24</f>
         <v/>
       </c>
-      <c r="C25" s="49">
+      <c r="C25" s="51">
         <f>C21-C24</f>
         <v/>
       </c>
-      <c r="D25" s="49">
+      <c r="D25" s="51">
         <f>D21-D24</f>
         <v/>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="51">
         <f>E21-E24</f>
         <v/>
       </c>
-      <c r="F25" s="49">
+      <c r="F25" s="51">
         <f>F21-F24</f>
         <v/>
       </c>
-      <c r="G25" s="49">
+      <c r="G25" s="51">
         <f>G21-G24</f>
         <v/>
       </c>
@@ -18812,7 +19140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -18899,22 +19227,22 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>No pledge of promoter shares disclosed in the FY26 Annual Report (only routine subsidiary-loan security pledges by the Company, unrelated to promoter shareholding).</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>'Company has not raised loans during the year on the pledge of securities held in its subsidiaries, joint ventures...' — no promoter share pledge disclosed.</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>No pledge of promoter shares disclosed in the FY26 Annual Report.</t>
+          <t>CORRECTED: 1.81% of promoter holding IS pledged as at 31-Mar-2026 (steady for 5+ consecutive quarters — no new pledge created, none released), per SEBI quarterly shareholding-pattern filings (BSE/NSE), cross-checked against Trendlyne — ALL of it held by one entity, Gautambhai/Rajeshbhai Adani (on behalf of S.B. Adani Family Trust), which has 3.68% of ITS OWN holding pledged; no other promoter or public shareholder has any pledge.</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>'Company has not raised loans during the year on the pledge of securities held in its subsidiaries, joint ventures...' — this is a CARO auditor's-report clause about the COMPANY pledging its OWN investments as loan collateral, not a promoter-share-pledge disclosure; Tata Power's actual promoter-share pledge % (per SEBI SHP filing) is UNCONFIRMED / not independently re-verified in this pass.</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Same CARO-clause caveat as Tata Power applies — this text is not a promoter-share-pledge disclosure; Torrent Power's actual promoter-share pledge % (per SEBI SHP filing) is UNCONFIRMED / not independently re-verified in this pass.</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>VERIFIED (nil promoter pledge) from FY25-26 Annual Reports for all three.</t>
+          <t>IMPORTANT CORRECTION: the earlier claim of 'nil pledge for all three' conflated a CARO auditor clause (about the company pledging ITS OWN investments/securities as loan collateral) with promoter SHARE pledge (a distinct SEBI-mandated shareholding-pattern disclosure). For Adani Power, the actual promoter-share pledge (1.81%, all in one entity) is now correctly sourced from SEBI quarterly filings. Tata/Torrent's promoter-share pledge % has NOT been independently re-verified against a primary SEBI SHP filing in this pass — treat their 'no pledge' cells as unconfirmed, not verified nil, until checked at bseindia.com/corporates or nseindia.com (Corporates &gt; Shareholding Pattern).</t>
         </is>
       </c>
     </row>
@@ -19055,28 +19383,397 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
+          <t>Adani Power (target company) — Promoter detail as at 31-Mar-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Promoter entity</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>No. of Shares</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>% Holding</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>% of THIS entity's shares pledged</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Gautambhai Shantilal Adani &amp; Rajeshbhai Shantilal Adani (on behalf of S.B. Adani Family Trust)</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="n">
+        <v>7108062265</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Holds ALL of Adani Power's pledged shares (~261.5 million shares) — no other promoter or public shareholder has any pledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Flourishing Trade And Investment Ltd</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>2210933260</v>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Promoter (Foreign).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Adani Tradeline Private Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="n">
+        <v>1993931925</v>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="D18" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Promoter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Emerging Market Investment DMCC</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>1299702000</v>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Promoter (Foreign).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>No single non-promoter (public/institutional) shareholder individually crosses the 5% threshold. The largest non-promoter holders are Opal Investment Pvt Ltd (3.58%, classified as a public 'Foreign Company' shareholder — NOT part of the promoter group despite the name) and Goldman Sachs Trust II - Goldman Sachs GQG Partner (3.31%, FII).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Adani Power — Quarterly Trend: Promoter Holding &amp; Pledge, FII, Mutual Fund Holding (last 6 quarters)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Quarter-end</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Promoter Holding %</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Promoter Pledge % (of promoter's own holding)</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>FII/FPI %</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Mutual Fund %</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>No. of MF Schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Sep-2024</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="E24" s="34" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Dec-2024</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="D25" s="34" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Mar-2025</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="D26" s="34" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="E26" s="34" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Jun-2025</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Sep-2025</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Dec-2025</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Mar-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="E30" s="34" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Change in Mutual Fund holding — last 6 months (Sep-2025 → Mar-2026)</t>
+        </is>
+      </c>
+      <c r="E31" s="35">
+        <f>E30-E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Relative % increase in MF holding over last 6 months</t>
+        </is>
+      </c>
+      <c r="E32" s="23">
+        <f>E30/E28-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Comments (Adani Power shareholding trend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="140" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Mutual Fund holding in Adani Power has risen sharply and consistently — more than doubling from 1.60% (Dec-2024) to 3.62% (Mar-2026), with the increase accelerating markedly in the most recent two quarters (2.69% → 3.39% → 3.62%). Over just the last six months (Sep-2025 to Mar-2026) MF holding rose by ~0.93 percentage points (a ~35% relative increase, computed live above), and the number of MF schemes holding the stock grew from 27 to 30. The two largest individual MF holders are SBI Equity Hybrid Fund (1.77%) and Quant Mutual Fund - Quant ELSS Tax Saver Fund (1.23%), together accounting for the bulk of total MF ownership. In contrast, FII/FPI holding has been comparatively flat-to-declining over the same window (12.5% in Jun-2025 down to 11.5-11.7% by Mar-2026), and promoter holding has been stable at ~75% throughout, with the pledge held steady at 1.81% of promoter holding (i.e. no new pledge created and none released) for at least five consecutive quarters. Overall, the shareholder-base shift over the last six months is best characterised as domestic mutual funds steadily buying in while FIIs modestly reduce, against an unchanged, largely-unpledged promoter base. SOURCE: quarterly shareholding pattern data as filed with BSE/NSE under SEBI (LODR) Regulations, 2015, compiled via Trendlyne.com (trendlyne.com/equity/share-holding/28/ADANIPOWER), cross-checked against Adani Power's FY25-26 Annual Report figures for Mar-2026 (which matched exactly: 74.96% promoter, 11.73% FII, 3.62% MF). This is Adani-specific detail only (the target company) — Tata Power and Torrent Power's quarterly trend and named-promoter detail were not pulled to the same depth in this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="100" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Adani Power has by far the highest promoter concentration (~75%) of the three, leaving the smallest free float (~25%) — typical of Adani Group listed entities, and a legacy of tightened promoter control after the 2023 Hindenburg-report episode (with an emphasis on 'zero pledge' messaging across group companies since). Tata Power's promoter stake (Tata Sons, ~47%) is the lowest of the three, giving it the widest institutional/public float and closest to the SEBI minimum public shareholding norms. Torrent Power sits in between (~51% promoter). FII/DII/Public splits (previously flagged as conflicting across secondary sources) are now VERIFIED from each company's own FY25-26 Annual Report statutory shareholding table and tie out exactly to the free-float row for all three — Adani Power has the lowest FII+DII institutional ownership (~15.4% combined) of the three despite its high overall market cap, consistent with its concentrated promoter/retail-skewed float; Tata Power has the most balanced institutional base (FII ~10%, Insurance+DII ~18%); Torrent Power's free float includes a notable ~8.4% held by Central/State Government entities (chiefly GUVNL), on top of ~29.5% FII+DII.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A15:E21"/>
+    <mergeCell ref="A35:F40"/>
+    <mergeCell ref="A44:E50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -46,7 +46,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +130,11 @@
       <sz val="10"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00008000"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="001F4E78"/>
     </font>
     <font>
@@ -203,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,38 +269,41 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="24" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="25" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3277,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3873,9 +3881,17 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>Cross-check note: Adani Power Resources Ltd (51%) and Adani Atomic Energy Ltd (100%) — a teammate's independent extraction had these two swapped (100%/51% respectively). Re-verified directly against the FY25-26 AR's BRSR Section V.23 'Holding, Subsidiary and Associate Companies' table (a separate disclosure from the AOC-1 annexure, cross-checked line by line): '6 Adani Power Resources Limited Subsidiary 51 Yes' and '21 Adani Atomic Energy Limited Subsidiary 100 Yes' — the percentages already in this sheet are correct.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4077,7 +4093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4165,17 +4181,162 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>All three companies' figures above are now extracted directly from the consolidated 'Investments' notes of the FY2022-23 Annual Reports uploaded to the repo. Common pattern: all three park treasury cash in liquid/overnight mutual funds; Torrent additionally holds regulatory-mandated GoI bonds (GERC contingency reserve); none runs a material discretionary securities portfolio.</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Adani Power (target company) — supplementary 6-year trend, FY21-FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Consolidated, ₹ Crore. Investments shown are APART FROM investments in subsidiaries, associates and JVs. Shown as additional context beyond the FY23 snapshot above, which is the specific year the assignment asks for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Non-current Investments (Govt securities, unquoted equity FVTOCI, AIF units — excl. JV investment)</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C16" s="38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="G16" s="38" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Current Investments (Mutual funds / liquid treasury instruments)</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="C17" s="38" t="n">
+        <v>183.24</v>
+      </c>
+      <c r="D17" s="38" t="n">
+        <v>611.54</v>
+      </c>
+      <c r="E17" s="38" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="F17" s="38" t="n">
+        <v>1037.7</v>
+      </c>
+      <c r="G17" s="38" t="n">
+        <v>1491.35</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Total Investments (excl. subs/associates/JV)</t>
+        </is>
+      </c>
+      <c r="B18" s="38">
+        <f>B16+B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="38">
+        <f>C16+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="38">
+        <f>D16+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="38">
+        <f>E16+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="38">
+        <f>F16+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="38">
+        <f>G16+G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Source: Adani Power Consolidated Balance Sheet, Notes 'Non-current Investments' and 'Current Investments' — AR FY21-22 through FY25-26, each year cross-checked against the following year's comparative column. FY26 Non-current Investments EXCLUDES the ₹24.50 Cr Wangchhu Hydroelectric JV investment (new that year — see Sheet 8), which is why the ex-JV figure drops to ₹0.14 Cr despite total non-current investments (per the Balance Sheet) being ₹24.64 Cr. Comments: non-current 'other' investments have stayed consistently tiny (₹0.01-59.51 Cr) — clearly not a strategic focus area. The far more significant trend is CURRENT investments (liquid mutual fund holdings), which grew ~74x from just ₹20.09 Cr (FY21) to ₹1,491.35 Cr (FY26) — reflecting Adani Power's dramatically improved operating cash generation over the period (PAT grew from ₹1,270 Cr to ₹12,971 Cr over the same window) being parked in short-term liquid instruments as a treasury/liquidity buffer, rather than a deliberate portfolio-investment strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A20:G24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4187,13 +4348,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4518,28 +4682,235 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t>Adani Power (target company) — Borrowings Trend, FY21-FY26 (Consolidated, ₹ Crore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Non-current Borrowings</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="n">
+        <v>39957</v>
+      </c>
+      <c r="C22" s="38" t="n">
+        <v>37871.32</v>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>33702.6</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>26595.01</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>27646.96</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <v>42829.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="n">
+        <v>10924.36</v>
+      </c>
+      <c r="D23" s="38" t="n">
+        <v>8549.450000000001</v>
+      </c>
+      <c r="E23" s="38" t="n">
+        <v>7861.85</v>
+      </c>
+      <c r="F23" s="38" t="n">
+        <v>10687.92</v>
+      </c>
+      <c r="G23" s="38" t="n">
+        <v>10725.94</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Total Borrowings</t>
+        </is>
+      </c>
+      <c r="B24" s="38">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="C24" s="38">
+        <f>IFERROR(IF(ISTEXT(C23),C22,C22+C23),C22)</f>
+        <v/>
+      </c>
+      <c r="D24" s="38">
+        <f>IFERROR(IF(ISTEXT(D23),D22,D22+D23),D22)</f>
+        <v/>
+      </c>
+      <c r="E24" s="38">
+        <f>IFERROR(IF(ISTEXT(E23),E22,E22+E23),E22)</f>
+        <v/>
+      </c>
+      <c r="F24" s="38">
+        <f>IFERROR(IF(ISTEXT(F23),F22,F22+F23),F22)</f>
+        <v/>
+      </c>
+      <c r="G24" s="38">
+        <f>IFERROR(IF(ISTEXT(G23),G22,G22+G23),G22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>YoY change in Total Borrowings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="23">
+        <f>IFERROR((C24-B24)/B24,"N/A")</f>
+        <v/>
+      </c>
+      <c r="D25" s="23">
+        <f>IFERROR((D24-C24)/C24,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E25" s="23">
+        <f>IFERROR((E24-D24)/D24,"N/A")</f>
+        <v/>
+      </c>
+      <c r="F25" s="23">
+        <f>IFERROR((F24-E24)/E24,"N/A")</f>
+        <v/>
+      </c>
+      <c r="G25" s="23">
+        <f>IFERROR((G24-F24)/F24,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>• FY22-FY24 — Deliberate DELEVERAGING phase: Total borrowings fell from ~₹48,796 Cr (FY22) to ~₹34,457 Cr (FY24), a ~29% reduction, funded by strong operating cash flows as PAT grew sharply over the same period. Multiple credit rating UPGRADES were recorded since 2018 as a result (per the FY25-26 AR's 'Investment Case' section).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>• FY25-FY26 — RE-LEVERAGING to fund acquisitions and capacity expansion: Total borrowings rose back to ~₹53,556 Cr (FY26) as the Company funded the Korba Power (KPL), Coastal Energen/Moxie (MPGL), Adani Dahanu (ADTPS) and Vidarbha Industries Power (VIPL) acquisitions plus a sharp step-up in capital expenditure (Capex more than doubled from ₹11,559 Cr in FY25 to ₹23,350 Cr in FY26, per Sheet 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>• FY25-26 — Issuance of ₹7,500 Cr of secured, listed, rated, non-convertible debentures (NCDs) to Qualified Institutional Buyers (mutual funds, private banks, insurance companies) via private placement — a shift toward diversifying the funding mix beyond bank borrowings and into the domestic debt capital markets. These NCDs are listed and traded on BSE's wholesale debt market segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>• Credit ratings as at FY25-26: AA/Stable (long-term) and A1+ (short-term) reaffirmed by all four domestic rating agencies (CRISIL, India Ratings, CARE, ICRA) for the parent; Mahan Energen Limited (subsidiary) separately rated AA-/Stable and A1+ by India Ratings; Korba Power Limited placed on 'Rating Watch with Positive Implications' by CARE Ratings (AA- long-term bank loan facilities) — suggesting the market expects further improvement there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>• Share capital action, FY25-26: shareholders approved a 1:5 STOCK SPLIT (face value ₹10 → ₹2 per share), taking authorised share capital to ₹24,800 Cr divided into 12,400 Cr shares of ₹2 each — a shareholder-friendly liquidity measure rather than a financing/capital-raise event per se, but a notable capital-structure change in the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Source: Adani Power Consolidated Balance Sheet, Notes 'Non-current Borrowings' / 'Current Borrowings' — AR FY21-22 through FY25-26 (each cross-checked against following year's comparative). NCD issuance, credit ratings and stock split: Adani Power Integrated Annual Report 2025-26, Directors' Report / Corporate Governance 'Non-Convertible Debentures', 'Credit Rating' and 'Share Capital' sections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
           <t>Comments</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="100" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="35" ht="100" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>All three companies have been actively de-leveraging and improving credit ratings over the last five years — a sector-wide trend as thermal-generation cash flows normalized post-COVID and renewable capex was increasingly funded with cheaper, longer-tenor debt. Adani Power's improvement is the most dramatic in relative terms (net debt/EBITDA from ~4x to ~1.4x within two years), consistent with its swing from losses to strong profitability. Tata Power funded its 2020 deleveraging via a promoter-only preferential allotment rather than a public offering, keeping the raise off the open market. Torrent Power is notable for having gone ~30 years without a public equity raise before its Dec-2024 QIP — a signal of a more conservative, debt/promoter-funded capital structure historically, now shifting toward institutional equity to fund its large (₹80,000 cr) five-year capex programme.</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A35:G41"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A21:D27"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4615,23 +4986,23 @@
           <t>Price at start (14-Jul-2025, adj)</t>
         </is>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="39">
         <f>'Weekly_Price_Data'!B2</f>
         <v/>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="39">
         <f>'Weekly_Price_Data'!C2</f>
         <v/>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="39">
         <f>'Weekly_Price_Data'!D2</f>
         <v/>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="39">
         <f>'Weekly_Price_Data'!E2</f>
         <v/>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="39">
         <f>'Weekly_Price_Data'!F2</f>
         <v/>
       </c>
@@ -4642,23 +5013,23 @@
           <t>Price at end (15-Jul-2026)</t>
         </is>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="39">
         <f>'Weekly_Price_Data'!B54</f>
         <v/>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="39">
         <f>'Weekly_Price_Data'!C54</f>
         <v/>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="39">
         <f>'Weekly_Price_Data'!D54</f>
         <v/>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="39">
         <f>'Weekly_Price_Data'!E54</f>
         <v/>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="39">
         <f>'Weekly_Price_Data'!F54</f>
         <v/>
       </c>
@@ -4669,23 +5040,23 @@
           <t>52-week weekly-close range</t>
         </is>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="40">
         <f>MIN('Weekly_Price_Data'!B2:B54)&amp;" - "&amp;MAX('Weekly_Price_Data'!B2:B54)</f>
         <v/>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="40">
         <f>MIN('Weekly_Price_Data'!C2:C54)&amp;" - "&amp;MAX('Weekly_Price_Data'!C2:C54)</f>
         <v/>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="40">
         <f>MIN('Weekly_Price_Data'!D2:D54)&amp;" - "&amp;MAX('Weekly_Price_Data'!D2:D54)</f>
         <v/>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="40">
         <f>MIN('Weekly_Price_Data'!E2:E54)&amp;" - "&amp;MAX('Weekly_Price_Data'!E2:E54)</f>
         <v/>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="40">
         <f>MIN('Weekly_Price_Data'!F2:F54)&amp;" - "&amp;MAX('Weekly_Price_Data'!F2:F54)</f>
         <v/>
       </c>
@@ -4696,23 +5067,23 @@
           <t>1-year return (COMPUTED)</t>
         </is>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="41">
         <f>'Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1</f>
         <v/>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>'Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1</f>
         <v/>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="41">
         <f>'Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1</f>
         <v/>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>'Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1</f>
         <v/>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="41">
         <f>'Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1</f>
         <v/>
       </c>
@@ -4723,23 +5094,23 @@
           <t>Weekly return std dev (COMPUTED)</t>
         </is>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="42">
         <f>STDEV('Weekly_Price_Data'!G3:G54)</f>
         <v/>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="42">
         <f>STDEV('Weekly_Price_Data'!H3:H54)</f>
         <v/>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="42">
         <f>STDEV('Weekly_Price_Data'!I3:I54)</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="42">
         <f>STDEV('Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="42">
         <f>STDEV('Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
@@ -4750,23 +5121,23 @@
           <t>Annualized volatility = sd x sqrt(52)</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="41">
         <f>STDEV('Weekly_Price_Data'!G3:G54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="41">
         <f>STDEV('Weekly_Price_Data'!H3:H54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="41">
         <f>STDEV('Weekly_Price_Data'!I3:I54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="41">
         <f>STDEV('Weekly_Price_Data'!J3:J54)*SQRT(52)</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="41">
         <f>STDEV('Weekly_Price_Data'!K3:K54)*SQRT(52)</f>
         <v/>
       </c>
@@ -4777,23 +5148,23 @@
           <t>Beta vs Nifty 50 / market (COMPUTED)</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="39">
         <f>SLOPE('Weekly_Price_Data'!G3:G54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="39">
         <f>SLOPE('Weekly_Price_Data'!H3:H54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="39">
         <f>SLOPE('Weekly_Price_Data'!I3:I54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="39">
         <f>SLOPE('Weekly_Price_Data'!J3:J54,'Weekly_Price_Data'!K3:K54)</f>
         <v/>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="39">
         <f>1</f>
         <v/>
       </c>
@@ -4804,23 +5175,23 @@
           <t>Beta vs Nifty Energy / sector (COMPUTED)</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="39">
         <f>SLOPE('Weekly_Price_Data'!G3:G54,'Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="39">
         <f>SLOPE('Weekly_Price_Data'!H3:H54,'Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="39">
         <f>SLOPE('Weekly_Price_Data'!I3:I54,'Weekly_Price_Data'!J3:J54)</f>
         <v/>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="39">
         <f>1</f>
         <v/>
       </c>
-      <c r="F13" s="41" t="n"/>
+      <c r="F13" s="43" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -4828,23 +5199,23 @@
           <t>Return vs market (stock - Nifty 50)</t>
         </is>
       </c>
-      <c r="B14" s="39">
+      <c r="B14" s="41">
         <f>('Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="41">
         <f>('Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="41">
         <f>('Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="41">
         <f>('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
         <v/>
       </c>
-      <c r="F14" s="42" t="n"/>
+      <c r="F14" s="44" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -4852,23 +5223,23 @@
           <t>Return vs sector (stock - Nifty Energy)</t>
         </is>
       </c>
-      <c r="B15" s="39">
+      <c r="B15" s="41">
         <f>('Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
         <v/>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="41">
         <f>('Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
         <v/>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="41">
         <f>('Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
         <v/>
       </c>
-      <c r="E15" s="42" t="n"/>
-      <c r="F15" s="42" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t>Data note</t>
         </is>
@@ -9820,7 +10191,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="13">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Consolidated-vs-Standalone audit (line-by-line re-verification)</t>
         </is>
@@ -10415,309 +10786,309 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23 (AR_22088), FY23-24 (AR_24072), FY24-25 (ADANIPOWER-2025) and FY25-26 (AR_29298) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them — click any total to see exactly what it adds up.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
-      <c r="E5" s="49" t="n"/>
-      <c r="F5" s="49" t="n"/>
+      <c r="B5" s="38" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="38" t="n"/>
+      <c r="F5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n"/>
-      <c r="C6" s="49" t="n"/>
-      <c r="D6" s="49" t="n"/>
-      <c r="E6" s="49" t="n"/>
-      <c r="F6" s="49" t="n"/>
+      <c r="B6" s="38" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="38" t="n">
         <v>66814.60000000001</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="38" t="n">
         <v>66707.23</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="38" t="n">
         <v>62812.71</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="38" t="n">
         <v>50543.8</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="38" t="n">
         <v>53071.62</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Right-of-use Assets</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="38" t="n">
         <v>2261.28</v>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="38" t="n">
         <v>2319.82</v>
       </c>
-      <c r="D8" s="49" t="n"/>
-      <c r="E8" s="49" t="n"/>
-      <c r="F8" s="49" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="38" t="n">
         <v>35053.46</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="38" t="n">
         <v>12104.42</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="38" t="n">
         <v>925.12</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="38" t="n">
         <v>12879.54</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="38" t="n">
         <v>10269.74</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Investment Property</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="38" t="n">
         <v>92.25</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="38" t="n">
         <v>48.69</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="38" t="n">
         <v>704.9400000000001</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="38" t="n">
         <v>204.52</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="38" t="n">
         <v>204.52</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="38" t="n">
         <v>190.61</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="38" t="n">
         <v>190.61</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="38" t="n">
         <v>190.61</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="38" t="n">
         <v>28.81</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="38" t="n">
         <v>17.19</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="38" t="n">
         <v>12.53</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="38" t="n">
         <v>12.03</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="38" t="n">
         <v>11.98</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Investments (Non-current)</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="38" t="n">
         <v>24.64</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="38" t="n">
         <v>59.51</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="38" t="n">
         <v>0.01</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="38" t="n">
         <v>42.51</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="38" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="38" t="n">
         <v>7.5</v>
       </c>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="49" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="38" t="n">
         <v>690.36</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="38" t="n">
         <v>691.41</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="38" t="n">
         <v>636.2</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="38" t="n">
         <v>779.71</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="38" t="n">
         <v>856.04</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="38" t="n">
         <v>192.06</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="38" t="n">
         <v>216.55</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="38" t="n">
         <v>365.72</v>
       </c>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="49" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="38" t="n">
         <v>811.39</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="38" t="n">
         <v>376.34</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="49" t="n"/>
+      <c r="F17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="38" t="n">
         <v>7410.97</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="38" t="n">
         <v>4219</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="38" t="n">
         <v>1418.95</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="38" t="n">
         <v>1115.13</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="38" t="n">
         <v>1352.95</v>
       </c>
     </row>
@@ -10727,230 +11098,230 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="52">
         <f>B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="52">
         <f>C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <f>D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="52">
         <f>E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="52">
         <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="38" t="n">
         <v>3623.48</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="38" t="n">
         <v>3317.28</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="38" t="n">
         <v>4142.1</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="38" t="n">
         <v>3075.2</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="38" t="n">
         <v>2258.27</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="38" t="n">
         <v>1491.35</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="38" t="n">
         <v>1037.7</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="38" t="n">
         <v>373.5</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="38" t="n">
         <v>611.54</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="38" t="n">
         <v>183.24</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>Trade Receivables</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="38" t="n">
         <v>11791.37</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="38" t="n">
         <v>13022.07</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="38" t="n">
         <v>11677.48</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="38" t="n">
         <v>11529.36</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="38" t="n">
         <v>9560.92</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B24" s="49" t="n">
+      <c r="B24" s="38" t="n">
         <v>927.88</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="38" t="n">
         <v>319.86</v>
       </c>
-      <c r="D24" s="49" t="n">
+      <c r="D24" s="38" t="n">
         <v>1136.25</v>
       </c>
-      <c r="E24" s="49" t="n">
+      <c r="E24" s="38" t="n">
         <v>349.23</v>
       </c>
-      <c r="F24" s="49" t="n">
+      <c r="F24" s="38" t="n">
         <v>782.37</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n">
+      <c r="B25" s="38" t="n">
         <v>5998.44</v>
       </c>
-      <c r="C25" s="49" t="n">
+      <c r="C25" s="38" t="n">
         <v>5800.02</v>
       </c>
-      <c r="D25" s="49" t="n">
+      <c r="D25" s="38" t="n">
         <v>6075.51</v>
       </c>
-      <c r="E25" s="49" t="n">
+      <c r="E25" s="38" t="n">
         <v>1524.42</v>
       </c>
-      <c r="F25" s="49" t="n">
+      <c r="F25" s="38" t="n">
         <v>1582.31</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
       </c>
-      <c r="B26" s="49" t="n">
+      <c r="B26" s="38" t="n">
         <v>10.99</v>
       </c>
-      <c r="C26" s="49" t="n">
+      <c r="C26" s="38" t="n">
         <v>6.82</v>
       </c>
-      <c r="D26" s="49" t="n">
+      <c r="D26" s="38" t="n">
         <v>3.49</v>
       </c>
-      <c r="E26" s="49" t="n">
+      <c r="E26" s="38" t="n">
         <v>3.19</v>
       </c>
-      <c r="F26" s="49" t="n">
+      <c r="F26" s="38" t="n">
         <v>7.62</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
+      <c r="B27" s="38" t="n">
         <v>2161.97</v>
       </c>
-      <c r="C27" s="49" t="n">
+      <c r="C27" s="38" t="n">
         <v>887.51</v>
       </c>
-      <c r="D27" s="49" t="n">
+      <c r="D27" s="38" t="n">
         <v>435.82</v>
       </c>
-      <c r="E27" s="49" t="n">
+      <c r="E27" s="38" t="n">
         <v>557.5</v>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="38" t="n">
         <v>308.28</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>Current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B28" s="49" t="n">
+      <c r="B28" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="49" t="n">
+      <c r="C28" s="38" t="n">
         <v>196.41</v>
       </c>
-      <c r="D28" s="49" t="n">
+      <c r="D28" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="49" t="n"/>
-      <c r="F28" s="49" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="38" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="inlineStr">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B29" s="49" t="n">
+      <c r="B29" s="38" t="n">
         <v>2682.6</v>
       </c>
-      <c r="C29" s="49" t="n">
+      <c r="C29" s="38" t="n">
         <v>1725.78</v>
       </c>
-      <c r="D29" s="49" t="n">
+      <c r="D29" s="38" t="n">
         <v>1742.43</v>
       </c>
-      <c r="E29" s="49" t="n">
+      <c r="E29" s="38" t="n">
         <v>1902.56</v>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F29" s="38" t="n">
         <v>1545.06</v>
       </c>
     </row>
@@ -10960,44 +11331,44 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B30" s="51">
+      <c r="B30" s="52">
         <f>B21+B22+B23+B24+B25+B26+B27+B28+B29</f>
         <v/>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="52">
         <f>C21+C22+C23+C24+C25+C26+C27+C28+C29</f>
         <v/>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="52">
         <f>D21+D22+D23+D24+D25+D26+D27+D28+D29</f>
         <v/>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="52">
         <f>E21+E22+E23+E24+E25+E26+E27+E28+E29</f>
         <v/>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="52">
         <f>F21+F22+F23+F24+F25+F26+F27+F28+F29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="inlineStr">
+      <c r="A31" s="51" t="inlineStr">
         <is>
           <t>Assets Classified as Held for Sale</t>
         </is>
       </c>
-      <c r="B31" s="49" t="n">
+      <c r="B31" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="49" t="n">
+      <c r="C31" s="38" t="n">
         <v>15.78</v>
       </c>
-      <c r="D31" s="49" t="n">
+      <c r="D31" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="49" t="n"/>
-      <c r="F31" s="49" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="38" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
@@ -11005,102 +11376,102 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B32" s="51">
+      <c r="B32" s="52">
         <f>B19+B30+B31</f>
         <v/>
       </c>
-      <c r="C32" s="51">
+      <c r="C32" s="52">
         <f>C19+C30+C31</f>
         <v/>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="52">
         <f>D19+D30+D31</f>
         <v/>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="52">
         <f>E19+E30+E31</f>
         <v/>
       </c>
-      <c r="F32" s="51">
+      <c r="F32" s="52">
         <f>F19+F30+F31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="49" t="n"/>
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="38" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="inlineStr">
+      <c r="A34" s="51" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
       </c>
-      <c r="B34" s="49" t="n">
+      <c r="B34" s="38" t="n">
         <v>3856.94</v>
       </c>
-      <c r="C34" s="49" t="n">
+      <c r="C34" s="38" t="n">
         <v>3856.94</v>
       </c>
-      <c r="D34" s="49" t="n">
+      <c r="D34" s="38" t="n">
         <v>3856.94</v>
       </c>
-      <c r="E34" s="49" t="n">
+      <c r="E34" s="38" t="n">
         <v>3856.94</v>
       </c>
-      <c r="F34" s="49" t="n">
+      <c r="F34" s="38" t="n">
         <v>3856.94</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="inlineStr">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Instrument entirely Equity in nature / Unsecured Perpetual Securities</t>
         </is>
       </c>
-      <c r="B35" s="49" t="n">
+      <c r="B35" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="49" t="n">
+      <c r="C35" s="38" t="n">
         <v>3056.92</v>
       </c>
-      <c r="D35" s="49" t="n">
+      <c r="D35" s="38" t="n">
         <v>7315</v>
       </c>
-      <c r="E35" s="49" t="n">
+      <c r="E35" s="38" t="n">
         <v>13215</v>
       </c>
-      <c r="F35" s="49" t="n">
+      <c r="F35" s="38" t="n">
         <v>13215</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="50" t="inlineStr">
+      <c r="A36" s="51" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
       </c>
-      <c r="B36" s="49" t="n">
+      <c r="B36" s="38" t="n">
         <v>61079.94</v>
       </c>
-      <c r="C36" s="49" t="n">
+      <c r="C36" s="38" t="n">
         <v>49433.23</v>
       </c>
-      <c r="D36" s="49" t="n">
+      <c r="D36" s="38" t="n">
         <v>31973.09</v>
       </c>
-      <c r="E36" s="49" t="n">
+      <c r="E36" s="38" t="n">
         <v>12803.72</v>
       </c>
-      <c r="F36" s="49" t="n">
+      <c r="F36" s="38" t="n">
         <v>1631.5</v>
       </c>
     </row>
@@ -11110,46 +11481,46 @@
           <t>Equity attributable to equity holders of the parent</t>
         </is>
       </c>
-      <c r="B37" s="51">
+      <c r="B37" s="52">
         <f>B34+B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="52">
         <f>C34+C35+C36</f>
         <v/>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="52">
         <f>D34+D35+D36</f>
         <v/>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="52">
         <f>E34+E35+E36</f>
         <v/>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="52">
         <f>F34+F35+F36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="inlineStr">
+      <c r="A38" s="51" t="inlineStr">
         <is>
           <t>Non-Controlling Interests</t>
         </is>
       </c>
-      <c r="B38" s="49" t="n">
+      <c r="B38" s="38" t="n">
         <v>1465.04</v>
       </c>
-      <c r="C38" s="49" t="n">
+      <c r="C38" s="38" t="n">
         <v>1326.47</v>
       </c>
-      <c r="D38" s="49" t="n">
+      <c r="D38" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="49" t="n">
+      <c r="E38" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="49" t="n">
+      <c r="F38" s="38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11159,168 +11530,168 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B39" s="51">
+      <c r="B39" s="52">
         <f>B37+B38</f>
         <v/>
       </c>
-      <c r="C39" s="51">
+      <c r="C39" s="52">
         <f>C37+C38</f>
         <v/>
       </c>
-      <c r="D39" s="51">
+      <c r="D39" s="52">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E39" s="51">
+      <c r="E39" s="52">
         <f>E37+E38</f>
         <v/>
       </c>
-      <c r="F39" s="51">
+      <c r="F39" s="52">
         <f>F37+F38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="50" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B40" s="49" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
-      <c r="E40" s="49" t="n"/>
-      <c r="F40" s="49" t="n"/>
+      <c r="B40" s="38" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="38" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="50" t="inlineStr">
+      <c r="A41" s="51" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
       </c>
-      <c r="B41" s="49" t="n">
+      <c r="B41" s="38" t="n">
         <v>42829.6</v>
       </c>
-      <c r="C41" s="49" t="n">
+      <c r="C41" s="38" t="n">
         <v>27646.96</v>
       </c>
-      <c r="D41" s="49" t="n">
+      <c r="D41" s="38" t="n">
         <v>26595.01</v>
       </c>
-      <c r="E41" s="49" t="n">
+      <c r="E41" s="38" t="n">
         <v>33702.6</v>
       </c>
-      <c r="F41" s="49" t="n">
+      <c r="F41" s="38" t="n">
         <v>37871.32</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B42" s="49" t="n">
+      <c r="B42" s="38" t="n">
         <v>1049.27</v>
       </c>
-      <c r="C42" s="49" t="n">
+      <c r="C42" s="38" t="n">
         <v>1094.04</v>
       </c>
-      <c r="D42" s="49" t="n">
+      <c r="D42" s="38" t="n">
         <v>143.11</v>
       </c>
-      <c r="E42" s="49" t="n">
+      <c r="E42" s="38" t="n">
         <v>88.31999999999999</v>
       </c>
-      <c r="F42" s="49" t="n">
+      <c r="F42" s="38" t="n">
         <v>94.36</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="inlineStr">
+      <c r="A43" s="51" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n">
+      <c r="B43" s="38" t="n">
         <v>185.69</v>
       </c>
-      <c r="C43" s="49" t="n">
+      <c r="C43" s="38" t="n">
         <v>1.17</v>
       </c>
-      <c r="D43" s="49" t="n">
+      <c r="D43" s="38" t="n">
         <v>1.07</v>
       </c>
-      <c r="E43" s="49" t="n">
+      <c r="E43" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="49" t="n">
+      <c r="F43" s="38" t="n">
         <v>960.37</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="50" t="inlineStr">
+      <c r="A44" s="51" t="inlineStr">
         <is>
           <t>Provisions (Non-current)</t>
         </is>
       </c>
-      <c r="B44" s="49" t="n">
+      <c r="B44" s="38" t="n">
         <v>359.9</v>
       </c>
-      <c r="C44" s="49" t="n">
+      <c r="C44" s="38" t="n">
         <v>339.64</v>
       </c>
-      <c r="D44" s="49" t="n">
+      <c r="D44" s="38" t="n">
         <v>237.45</v>
       </c>
-      <c r="E44" s="49" t="n">
+      <c r="E44" s="38" t="n">
         <v>226.95</v>
       </c>
-      <c r="F44" s="49" t="n">
+      <c r="F44" s="38" t="n">
         <v>220.87</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="50" t="inlineStr">
+      <c r="A45" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B45" s="49" t="n">
+      <c r="B45" s="38" t="n">
         <v>5827.15</v>
       </c>
-      <c r="C45" s="49" t="n">
+      <c r="C45" s="38" t="n">
         <v>4022.73</v>
       </c>
-      <c r="D45" s="49" t="n">
+      <c r="D45" s="38" t="n">
         <v>315.8</v>
       </c>
-      <c r="E45" s="49" t="n">
+      <c r="E45" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="49" t="n">
+      <c r="F45" s="38" t="n">
         <v>2499.78</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="50" t="inlineStr">
+      <c r="A46" s="51" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B46" s="49" t="n">
+      <c r="B46" s="38" t="n">
         <v>5298.18</v>
       </c>
-      <c r="C46" s="49" t="n">
+      <c r="C46" s="38" t="n">
         <v>5698.48</v>
       </c>
-      <c r="D46" s="49" t="n">
+      <c r="D46" s="38" t="n">
         <v>6098.63</v>
       </c>
-      <c r="E46" s="49" t="n">
+      <c r="E46" s="38" t="n">
         <v>4183.15</v>
       </c>
-      <c r="F46" s="49" t="n">
+      <c r="F46" s="38" t="n">
         <v>4487.21</v>
       </c>
     </row>
@@ -11330,212 +11701,212 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B47" s="51">
+      <c r="B47" s="52">
         <f>B41+B42+B43+B44+B45+B46</f>
         <v/>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="52">
         <f>C41+C42+C43+C44+C45+C46</f>
         <v/>
       </c>
-      <c r="D47" s="51">
+      <c r="D47" s="52">
         <f>D41+D42+D43+D44+D45+D46</f>
         <v/>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="52">
         <f>E41+E42+E43+E44+E45+E46</f>
         <v/>
       </c>
-      <c r="F47" s="51">
+      <c r="F47" s="52">
         <f>F41+F42+F43+F44+F45+F46</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="48" t="inlineStr">
+      <c r="A48" s="50" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B48" s="49" t="n"/>
-      <c r="C48" s="49" t="n"/>
-      <c r="D48" s="49" t="n"/>
-      <c r="E48" s="49" t="n"/>
-      <c r="F48" s="49" t="n"/>
+      <c r="B48" s="38" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="38" t="n"/>
+      <c r="E48" s="38" t="n"/>
+      <c r="F48" s="38" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="50" t="inlineStr">
+      <c r="A49" s="51" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
       </c>
-      <c r="B49" s="49" t="n">
+      <c r="B49" s="38" t="n">
         <v>10725.94</v>
       </c>
-      <c r="C49" s="49" t="n">
+      <c r="C49" s="38" t="n">
         <v>10687.92</v>
       </c>
-      <c r="D49" s="49" t="n">
+      <c r="D49" s="38" t="n">
         <v>7861.85</v>
       </c>
-      <c r="E49" s="49" t="n">
+      <c r="E49" s="38" t="n">
         <v>8549.450000000001</v>
       </c>
-      <c r="F49" s="49" t="n">
+      <c r="F49" s="38" t="n">
         <v>10924.36</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="50" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B50" s="49" t="n">
+      <c r="B50" s="38" t="n">
         <v>65.48</v>
       </c>
-      <c r="C50" s="49" t="n">
+      <c r="C50" s="38" t="n">
         <v>65.95</v>
       </c>
-      <c r="D50" s="49" t="n">
+      <c r="D50" s="38" t="n">
         <v>15.59</v>
       </c>
-      <c r="E50" s="49" t="n">
+      <c r="E50" s="38" t="n">
         <v>9.16</v>
       </c>
-      <c r="F50" s="49" t="n">
+      <c r="F50" s="38" t="n">
         <v>8.390000000000001</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="50" t="inlineStr">
+      <c r="A51" s="51" t="inlineStr">
         <is>
           <t>Trade Payables — micro/small enterprises</t>
         </is>
       </c>
-      <c r="B51" s="49" t="n">
+      <c r="B51" s="38" t="n">
         <v>183.98</v>
       </c>
-      <c r="C51" s="49" t="n">
+      <c r="C51" s="38" t="n">
         <v>215.73</v>
       </c>
-      <c r="D51" s="49" t="n">
+      <c r="D51" s="38" t="n">
         <v>141.93</v>
       </c>
-      <c r="E51" s="49" t="n">
+      <c r="E51" s="38" t="n">
         <v>95.76000000000001</v>
       </c>
-      <c r="F51" s="49" t="n">
+      <c r="F51" s="38" t="n">
         <v>57.59</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="50" t="inlineStr">
+      <c r="A52" s="51" t="inlineStr">
         <is>
           <t>Trade Payables — other creditors</t>
         </is>
       </c>
-      <c r="B52" s="49" t="n">
+      <c r="B52" s="38" t="n">
         <v>2656.55</v>
       </c>
-      <c r="C52" s="49" t="n">
+      <c r="C52" s="38" t="n">
         <v>2761.93</v>
       </c>
-      <c r="D52" s="49" t="n">
+      <c r="D52" s="38" t="n">
         <v>3494.37</v>
       </c>
-      <c r="E52" s="49" t="n">
+      <c r="E52" s="38" t="n">
         <v>2983.69</v>
       </c>
-      <c r="F52" s="49" t="n">
+      <c r="F52" s="38" t="n">
         <v>3450.62</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="50" t="inlineStr">
+      <c r="A53" s="51" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B53" s="49" t="n">
+      <c r="B53" s="38" t="n">
         <v>4049.65</v>
       </c>
-      <c r="C53" s="49" t="n">
+      <c r="C53" s="38" t="n">
         <v>1230.62</v>
       </c>
-      <c r="D53" s="49" t="n">
+      <c r="D53" s="38" t="n">
         <v>2089.8</v>
       </c>
-      <c r="E53" s="49" t="n">
+      <c r="E53" s="38" t="n">
         <v>2461.58</v>
       </c>
-      <c r="F53" s="49" t="n">
+      <c r="F53" s="38" t="n">
         <v>1167.32</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="50" t="inlineStr">
+      <c r="A54" s="51" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B54" s="49" t="n">
+      <c r="B54" s="38" t="n">
         <v>994.38</v>
       </c>
-      <c r="C54" s="49" t="n">
+      <c r="C54" s="38" t="n">
         <v>1348.74</v>
       </c>
-      <c r="D54" s="49" t="n">
+      <c r="D54" s="38" t="n">
         <v>2159.44</v>
       </c>
-      <c r="E54" s="49" t="n">
+      <c r="E54" s="38" t="n">
         <v>3622.82</v>
       </c>
-      <c r="F54" s="49" t="n">
+      <c r="F54" s="38" t="n">
         <v>861.36</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="50" t="inlineStr">
+      <c r="A55" s="51" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
       </c>
-      <c r="B55" s="49" t="n">
+      <c r="B55" s="38" t="n">
         <v>96.95999999999999</v>
       </c>
-      <c r="C55" s="49" t="n">
+      <c r="C55" s="38" t="n">
         <v>70.23999999999999</v>
       </c>
-      <c r="D55" s="49" t="n">
+      <c r="D55" s="38" t="n">
         <v>25.69</v>
       </c>
-      <c r="E55" s="49" t="n">
+      <c r="E55" s="38" t="n">
         <v>21.64</v>
       </c>
-      <c r="F55" s="49" t="n">
+      <c r="F55" s="38" t="n">
         <v>28.71</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="50" t="inlineStr">
+      <c r="A56" s="51" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B56" s="49" t="n">
+      <c r="B56" s="38" t="n">
         <v>1555.27</v>
       </c>
-      <c r="C56" s="49" t="n">
+      <c r="C56" s="38" t="n">
         <v>59.86</v>
       </c>
-      <c r="D56" s="49" t="n">
+      <c r="D56" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="49" t="n">
+      <c r="E56" s="38" t="n">
         <v>0.49</v>
       </c>
-      <c r="F56" s="49" t="n">
+      <c r="F56" s="38" t="n">
         <v>645.3200000000001</v>
       </c>
     </row>
@@ -11545,23 +11916,23 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B57" s="51">
+      <c r="B57" s="52">
         <f>B49+B50+B51+B52+B53+B54+B55+B56</f>
         <v/>
       </c>
-      <c r="C57" s="51">
+      <c r="C57" s="52">
         <f>C49+C50+C51+C52+C53+C54+C55+C56</f>
         <v/>
       </c>
-      <c r="D57" s="51">
+      <c r="D57" s="52">
         <f>D49+D50+D51+D52+D53+D54+D55+D56</f>
         <v/>
       </c>
-      <c r="E57" s="51">
+      <c r="E57" s="52">
         <f>E49+E50+E51+E52+E53+E54+E55+E56</f>
         <v/>
       </c>
-      <c r="F57" s="51">
+      <c r="F57" s="52">
         <f>F49+F50+F51+F52+F53+F54+F55+F56</f>
         <v/>
       </c>
@@ -11572,23 +11943,23 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B58" s="51">
+      <c r="B58" s="52">
         <f>B47+B57</f>
         <v/>
       </c>
-      <c r="C58" s="51">
+      <c r="C58" s="52">
         <f>C47+C57</f>
         <v/>
       </c>
-      <c r="D58" s="51">
+      <c r="D58" s="52">
         <f>D47+D57</f>
         <v/>
       </c>
-      <c r="E58" s="51">
+      <c r="E58" s="52">
         <f>E47+E57</f>
         <v/>
       </c>
-      <c r="F58" s="51">
+      <c r="F58" s="52">
         <f>F47+F57</f>
         <v/>
       </c>
@@ -11599,23 +11970,23 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B59" s="51">
+      <c r="B59" s="52">
         <f>B39+B58</f>
         <v/>
       </c>
-      <c r="C59" s="51">
+      <c r="C59" s="52">
         <f>C39+C58</f>
         <v/>
       </c>
-      <c r="D59" s="51">
+      <c r="D59" s="52">
         <f>D39+D58</f>
         <v/>
       </c>
-      <c r="E59" s="51">
+      <c r="E59" s="52">
         <f>E39+E58</f>
         <v/>
       </c>
-      <c r="F59" s="51">
+      <c r="F59" s="52">
         <f>F39+F58</f>
         <v/>
       </c>
@@ -11654,97 +12025,97 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23, FY23-24, FY24-25 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
-      <c r="E5" s="49" t="n"/>
-      <c r="F5" s="49" t="n"/>
+      <c r="B5" s="38" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="38" t="n"/>
+      <c r="F5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="38" t="n">
         <v>54240.52</v>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="38" t="n">
         <v>56203.09</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="38" t="n">
         <v>50351.25</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="38" t="n">
         <v>38773.3</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="38" t="n">
         <v>27711.18</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="38" t="n">
         <v>3624.76</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="38" t="n">
         <v>2702.74</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="38" t="n">
         <v>9930.23</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="38" t="n">
         <v>4267.22</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="38" t="n">
         <v>3975.29</v>
       </c>
     </row>
@@ -11754,190 +12125,190 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B8" s="51">
+      <c r="B8" s="52">
         <f>B6+B7</f>
         <v/>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="52">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="52">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="52">
         <f>E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="52">
         <f>F6+F7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n"/>
-      <c r="C9" s="49" t="n"/>
-      <c r="D9" s="49" t="n"/>
-      <c r="E9" s="49" t="n"/>
-      <c r="F9" s="49" t="n"/>
+      <c r="B9" s="38" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="38" t="n"/>
+      <c r="F9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="38" t="n">
         <v>29168.02</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="38" t="n">
         <v>30273.25</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="38" t="n">
         <v>28452.64</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="38" t="n">
         <v>25480.85</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="38" t="n">
         <v>14762.21</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Purchase of Stock-in-trade / Power for resale</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="38" t="n">
         <v>209.66</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="38" t="n">
         <v>356.99</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="38" t="n">
         <v>222.26</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="38" t="n">
         <v>214.14</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="38" t="n">
         <v>545.5599999999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Transmission Charges</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="38" t="n">
         <v>557.42</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="38" t="n">
         <v>459.09</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="38" t="n">
         <v>503.99</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="38" t="n">
         <v>519.61</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="38" t="n">
         <v>642.77</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="38" t="n">
         <v>855.1799999999999</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="38" t="n">
         <v>784.4</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="38" t="n">
         <v>643.7</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="38" t="n">
         <v>569.99</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="38" t="n">
         <v>470.31</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Finance Costs (net)</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="38" t="n">
         <v>3366.83</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="38" t="n">
         <v>3339.79</v>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="38" t="n">
         <v>3388.09</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="38" t="n">
         <v>3333.5</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="38" t="n">
         <v>4094.78</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Depreciation and Amortisation Expense</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="38" t="n">
         <v>4564.53</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="38" t="n">
         <v>4308.88</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="38" t="n">
         <v>3931.33</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="38" t="n">
         <v>3303.68</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="38" t="n">
         <v>3117.54</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="38" t="n">
         <v>3644.13</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="38" t="n">
         <v>3023.92</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="38" t="n">
         <v>2347.96</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="38" t="n">
         <v>1944.05</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="38" t="n">
         <v>1476.17</v>
       </c>
     </row>
@@ -11947,23 +12318,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B17" s="51">
+      <c r="B17" s="52">
         <f>B10+B11+B12+B13+B14+B15+B16</f>
         <v/>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="52">
         <f>C10+C11+C12+C13+C14+C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="52">
         <f>D10+D11+D12+D13+D14+D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="52">
         <f>E10+E11+E12+E13+E14+E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="52">
         <f>F10+F11+F12+F13+F14+F15+F16</f>
         <v/>
       </c>
@@ -11974,64 +12345,64 @@
           <t>Profit before share of JV profit and tax</t>
         </is>
       </c>
-      <c r="B18" s="51">
+      <c r="B18" s="52">
         <f>B8-B17</f>
         <v/>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="52">
         <f>C8-C17</f>
         <v/>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="52">
         <f>D8-D17</f>
         <v/>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="52">
         <f>E8-E17</f>
         <v/>
       </c>
-      <c r="F18" s="51">
+      <c r="F18" s="52">
         <f>F8-F17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>Total Tax Expense/(Credit)</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="38" t="n">
         <v>2528.43</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="38" t="n">
         <v>3609.9</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="38" t="n">
         <v>-37.28</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="38" t="n">
         <v>-3267.37</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="38" t="n">
         <v>1744.8</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Add: Deferred tax (adj.)/recoverable from future tariff (net of tax)</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n">
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="38" t="n">
         <v>-215.43</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F20" s="38" t="n">
         <v>79.25</v>
       </c>
     </row>
@@ -12041,46 +12412,46 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B21" s="51">
+      <c r="B21" s="52">
         <f>B18-B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="52">
         <f>C18-C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="52">
         <f>D18-D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="52">
         <f>E18-E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="52">
         <f>F18-F19+F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>Other Comprehensive Income, net of tax</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="38" t="n">
         <v>19.67</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="38" t="n">
         <v>-2.69</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="38" t="n">
         <v>-27.49</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="38" t="n">
         <v>33.74</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="38" t="n">
         <v>43.63</v>
       </c>
     </row>
@@ -12090,23 +12461,23 @@
           <t>Total Comprehensive Income for the Year</t>
         </is>
       </c>
-      <c r="B23" s="51">
+      <c r="B23" s="52">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="51">
+      <c r="C23" s="52">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="52">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="52">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="52">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -12145,373 +12516,373 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Sources: Tata Power Integrated Annual Reports FY21-22 (AR_20052), FY23-24 (AR_24164) and FY25-26 (AR_29380) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
-      <c r="E5" s="49" t="n"/>
-      <c r="F5" s="49" t="n"/>
+      <c r="B5" s="38" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="38" t="n"/>
+      <c r="F5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n"/>
-      <c r="C6" s="49" t="n"/>
-      <c r="D6" s="49" t="n"/>
-      <c r="E6" s="49" t="n"/>
-      <c r="F6" s="49" t="n"/>
+      <c r="B6" s="38" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="38" t="n">
         <v>78870.53999999999</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="38" t="n">
         <v>70261.38</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="38" t="n">
         <v>59624.06</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="38" t="n">
         <v>54524.96</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="38" t="n">
         <v>50502.96</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Right of Use Assets</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="38" t="n">
         <v>5525.44</v>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="38" t="n">
         <v>5089.89</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="38" t="n">
         <v>4368.75</v>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="38" t="n">
         <v>3982.05</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="38" t="n">
         <v>3661.99</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="38" t="n">
         <v>14595.13</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="38" t="n">
         <v>12678.87</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="38" t="n">
         <v>11561.31</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="38" t="n">
         <v>5376.36</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="38" t="n">
         <v>4635.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="38" t="n">
         <v>1651.46</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="38" t="n">
         <v>1651.46</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="38" t="n">
         <v>1757.46</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="38" t="n">
         <v>1858.31</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="38" t="n">
         <v>1858.31</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="38" t="n">
         <v>1245.25</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="38" t="n">
         <v>1371.7</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="38" t="n">
         <v>1459.29</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="38" t="n">
         <v>1381.34</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="38" t="n">
         <v>1366.18</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Investments accounted for using Equity Method</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="38" t="n">
         <v>13549.05</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="38" t="n">
         <v>12894.22</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="38" t="n">
         <v>12983.51</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="38" t="n">
         <v>14218.88</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="38" t="n">
         <v>12580</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Other Investments (Non-current)</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="38" t="n">
         <v>1669.37</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="38" t="n">
         <v>2119.75</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="38" t="n">
         <v>1854.59</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="38" t="n">
         <v>1301.21</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="38" t="n">
         <v>1169.81</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Trade Receivables (Non-current)</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="38" t="n">
         <v>1599.35</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="38" t="n">
         <v>1223.02</v>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="38" t="n">
         <v>273.29</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="38" t="n">
         <v>359.63</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="38" t="n">
         <v>685.78</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="38" t="n">
         <v>37.14</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="38" t="n">
         <v>2.48</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="38" t="n">
         <v>2.99</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="38" t="n">
         <v>3.45</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Finance Lease Receivables (Non-current)</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="38" t="n">
         <v>837.84</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="38" t="n">
         <v>526.98</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="38" t="n">
         <v>561.66</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="38" t="n">
         <v>567.22</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="38" t="n">
         <v>588.6900000000001</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="38" t="n">
         <v>3522.62</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="38" t="n">
         <v>2168.98</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="38" t="n">
         <v>2084.5</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="38" t="n">
         <v>1726.66</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="38" t="n">
         <v>1684.53</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="38" t="n">
         <v>960.96</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="38" t="n">
         <v>745.78</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="38" t="n">
         <v>585.89</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="38" t="n">
         <v>739.0700000000001</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="38" t="n">
         <v>520.54</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr">
+      <c r="A19" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="38" t="n">
         <v>607.54</v>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="38" t="n">
         <v>517.99</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="38" t="n">
         <v>499.09</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="38" t="n">
         <v>252.9</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="38" t="n">
         <v>334.6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="38" t="n">
         <v>10635.84</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="38" t="n">
         <v>8393.799999999999</v>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="38" t="n">
         <v>5173.57</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="38" t="n">
         <v>2532.46</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F20" s="38" t="n">
         <v>1849.82</v>
       </c>
     </row>
@@ -12521,278 +12892,278 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B21" s="51">
+      <c r="B21" s="52">
         <f>B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="52">
         <f>C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="52">
         <f>D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="52">
         <f>E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18+E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="52">
         <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18+F19+F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="49" t="n"/>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="38" t="n"/>
+      <c r="E22" s="38" t="n"/>
+      <c r="F22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="38" t="n">
         <v>5107.64</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="38" t="n">
         <v>4571.82</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="38" t="n">
         <v>4419.63</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="38" t="n">
         <v>3942.88</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="38" t="n">
         <v>4231.52</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
       </c>
-      <c r="B24" s="49" t="n">
+      <c r="B24" s="38" t="n">
         <v>1356.12</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="38" t="n">
         <v>1302.42</v>
       </c>
-      <c r="D24" s="49" t="n">
+      <c r="D24" s="38" t="n">
         <v>1477.89</v>
       </c>
-      <c r="E24" s="49" t="n">
+      <c r="E24" s="38" t="n">
         <v>1149.6</v>
       </c>
-      <c r="F24" s="49" t="n">
+      <c r="F24" s="38" t="n">
         <v>410.52</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>Trade Receivables (Current)</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n">
+      <c r="B25" s="38" t="n">
         <v>4423.96</v>
       </c>
-      <c r="C25" s="49" t="n">
+      <c r="C25" s="38" t="n">
         <v>5709.78</v>
       </c>
-      <c r="D25" s="49" t="n">
+      <c r="D25" s="38" t="n">
         <v>7401.69</v>
       </c>
-      <c r="E25" s="49" t="n">
+      <c r="E25" s="38" t="n">
         <v>6952.15</v>
       </c>
-      <c r="F25" s="49" t="n">
+      <c r="F25" s="38" t="n">
         <v>5979.74</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>Unbilled Revenue</t>
         </is>
       </c>
-      <c r="B26" s="49" t="n">
+      <c r="B26" s="38" t="n">
         <v>2842.63</v>
       </c>
-      <c r="C26" s="49" t="n">
+      <c r="C26" s="38" t="n">
         <v>2737.06</v>
       </c>
-      <c r="D26" s="49" t="n">
+      <c r="D26" s="38" t="n">
         <v>2552.23</v>
       </c>
-      <c r="E26" s="49" t="n">
+      <c r="E26" s="38" t="n">
         <v>2456.71</v>
       </c>
-      <c r="F26" s="49" t="n">
+      <c r="F26" s="38" t="n">
         <v>2285.57</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
+      <c r="B27" s="38" t="n">
         <v>4409.67</v>
       </c>
-      <c r="C27" s="49" t="n">
+      <c r="C27" s="38" t="n">
         <v>4862.47</v>
       </c>
-      <c r="D27" s="49" t="n">
+      <c r="D27" s="38" t="n">
         <v>3324.34</v>
       </c>
-      <c r="E27" s="49" t="n">
+      <c r="E27" s="38" t="n">
         <v>4189.76</v>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="38" t="n">
         <v>3077.24</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
       </c>
-      <c r="B28" s="49" t="n">
+      <c r="B28" s="38" t="n">
         <v>9234.33</v>
       </c>
-      <c r="C28" s="49" t="n">
+      <c r="C28" s="38" t="n">
         <v>6888.51</v>
       </c>
-      <c r="D28" s="49" t="n">
+      <c r="D28" s="38" t="n">
         <v>5827.57</v>
       </c>
-      <c r="E28" s="49" t="n">
+      <c r="E28" s="38" t="n">
         <v>7016.77</v>
       </c>
-      <c r="F28" s="49" t="n">
+      <c r="F28" s="38" t="n">
         <v>3563.46</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="inlineStr">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
       </c>
-      <c r="B29" s="49" t="n">
+      <c r="B29" s="38" t="n">
         <v>19.8</v>
       </c>
-      <c r="C29" s="49" t="n">
+      <c r="C29" s="38" t="n">
         <v>12.34</v>
       </c>
-      <c r="D29" s="49" t="n">
+      <c r="D29" s="38" t="n">
         <v>11.14</v>
       </c>
-      <c r="E29" s="49" t="n">
+      <c r="E29" s="38" t="n">
         <v>11.55</v>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F29" s="38" t="n">
         <v>9.34</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="50" t="inlineStr">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>Finance Lease Receivables (Current)</t>
         </is>
       </c>
-      <c r="B30" s="49" t="n">
+      <c r="B30" s="38" t="n">
         <v>86.65000000000001</v>
       </c>
-      <c r="C30" s="49" t="n">
+      <c r="C30" s="38" t="n">
         <v>74.47</v>
       </c>
-      <c r="D30" s="49" t="n">
+      <c r="D30" s="38" t="n">
         <v>65.92</v>
       </c>
-      <c r="E30" s="49" t="n">
+      <c r="E30" s="38" t="n">
         <v>54.5</v>
       </c>
-      <c r="F30" s="49" t="n">
+      <c r="F30" s="38" t="n">
         <v>46.91</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="inlineStr">
+      <c r="A31" s="51" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
       </c>
-      <c r="B31" s="49" t="n">
+      <c r="B31" s="38" t="n">
         <v>1316.67</v>
       </c>
-      <c r="C31" s="49" t="n">
+      <c r="C31" s="38" t="n">
         <v>656.48</v>
       </c>
-      <c r="D31" s="49" t="n">
+      <c r="D31" s="38" t="n">
         <v>471.48</v>
       </c>
-      <c r="E31" s="49" t="n">
+      <c r="E31" s="38" t="n">
         <v>688.3</v>
       </c>
-      <c r="F31" s="49" t="n">
+      <c r="F31" s="38" t="n">
         <v>501.45</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
         <is>
           <t>Current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B32" s="49" t="n">
+      <c r="B32" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="49" t="n">
+      <c r="C32" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="49" t="n">
+      <c r="D32" s="38" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E32" s="49" t="n">
+      <c r="E32" s="38" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="F32" s="49" t="n">
+      <c r="F32" s="38" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B33" s="38" t="n">
         <v>1773.58</v>
       </c>
-      <c r="C33" s="49" t="n">
+      <c r="C33" s="38" t="n">
         <v>1941.3</v>
       </c>
-      <c r="D33" s="49" t="n">
+      <c r="D33" s="38" t="n">
         <v>1704.3</v>
       </c>
-      <c r="E33" s="49" t="n">
+      <c r="E33" s="38" t="n">
         <v>1328.72</v>
       </c>
-      <c r="F33" s="49" t="n">
+      <c r="F33" s="38" t="n">
         <v>1479.67</v>
       </c>
     </row>
@@ -12802,46 +13173,46 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B34" s="51">
+      <c r="B34" s="52">
         <f>B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="52">
         <f>C23+C24+C25+C26+C27+C28+C29+C30+C31+C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="52">
         <f>D23+D24+D25+D26+D27+D28+D29+D30+D31+D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="52">
         <f>E23+E24+E25+E26+E27+E28+E29+E30+E31+E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="51">
+      <c r="F34" s="52">
         <f>F23+F24+F25+F26+F27+F28+F29+F30+F31+F32+F33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="inlineStr">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Assets Classified as Held For Sale</t>
         </is>
       </c>
-      <c r="B35" s="49" t="n">
+      <c r="B35" s="38" t="n">
         <v>1153.75</v>
       </c>
-      <c r="C35" s="49" t="n">
+      <c r="C35" s="38" t="n">
         <v>1145.21</v>
       </c>
-      <c r="D35" s="49" t="n">
+      <c r="D35" s="38" t="n">
         <v>1200.99</v>
       </c>
-      <c r="E35" s="49" t="n">
+      <c r="E35" s="38" t="n">
         <v>3299.94</v>
       </c>
-      <c r="F35" s="49" t="n">
+      <c r="F35" s="38" t="n">
         <v>3046.83</v>
       </c>
     </row>
@@ -12851,46 +13222,46 @@
           <t>Total Assets before Regulatory Deferral Account</t>
         </is>
       </c>
-      <c r="B36" s="51">
+      <c r="B36" s="52">
         <f>B21+B34+B35</f>
         <v/>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="52">
         <f>C21+C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="52">
         <f>D21+D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="52">
         <f>E21+E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="51">
+      <c r="F36" s="52">
         <f>F21+F34+F35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="50" t="inlineStr">
+      <c r="A37" s="51" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Assets</t>
         </is>
       </c>
-      <c r="B37" s="49" t="n">
+      <c r="B37" s="38" t="n">
         <v>8139.45</v>
       </c>
-      <c r="C37" s="49" t="n">
+      <c r="C37" s="38" t="n">
         <v>7163.61</v>
       </c>
-      <c r="D37" s="49" t="n">
+      <c r="D37" s="38" t="n">
         <v>8298.66</v>
       </c>
-      <c r="E37" s="49" t="n">
+      <c r="E37" s="38" t="n">
         <v>8433.43</v>
       </c>
-      <c r="F37" s="49" t="n">
+      <c r="F37" s="38" t="n">
         <v>6810.57</v>
       </c>
     </row>
@@ -12900,80 +13271,80 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B38" s="51">
+      <c r="B38" s="52">
         <f>B36+B37</f>
         <v/>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="52">
         <f>C36+C37</f>
         <v/>
       </c>
-      <c r="D38" s="51">
+      <c r="D38" s="52">
         <f>D36+D37</f>
         <v/>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="52">
         <f>E36+E37</f>
         <v/>
       </c>
-      <c r="F38" s="51">
+      <c r="F38" s="52">
         <f>F36+F37</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="48" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="49" t="n"/>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="50" t="inlineStr">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
       </c>
-      <c r="B40" s="49" t="n">
+      <c r="B40" s="38" t="n">
         <v>319.56</v>
       </c>
-      <c r="C40" s="49" t="n">
+      <c r="C40" s="38" t="n">
         <v>319.56</v>
       </c>
-      <c r="D40" s="49" t="n">
+      <c r="D40" s="38" t="n">
         <v>319.56</v>
       </c>
-      <c r="E40" s="49" t="n">
+      <c r="E40" s="38" t="n">
         <v>319.56</v>
       </c>
-      <c r="F40" s="49" t="n">
+      <c r="F40" s="38" t="n">
         <v>319.56</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="50" t="inlineStr">
+      <c r="A41" s="51" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
       </c>
-      <c r="B41" s="49" t="n">
+      <c r="B41" s="38" t="n">
         <v>39147.65</v>
       </c>
-      <c r="C41" s="49" t="n">
+      <c r="C41" s="38" t="n">
         <v>35521.11</v>
       </c>
-      <c r="D41" s="49" t="n">
+      <c r="D41" s="38" t="n">
         <v>32035.73</v>
       </c>
-      <c r="E41" s="49" t="n">
+      <c r="E41" s="38" t="n">
         <v>28467.87</v>
       </c>
-      <c r="F41" s="49" t="n">
+      <c r="F41" s="38" t="n">
         <v>22122</v>
       </c>
     </row>
@@ -12983,46 +13354,46 @@
           <t>Equity attributable to Shareholders of Parent</t>
         </is>
       </c>
-      <c r="B42" s="51">
+      <c r="B42" s="52">
         <f>B40+B41</f>
         <v/>
       </c>
-      <c r="C42" s="51">
+      <c r="C42" s="52">
         <f>C40+C41</f>
         <v/>
       </c>
-      <c r="D42" s="51">
+      <c r="D42" s="52">
         <f>D40+D41</f>
         <v/>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="52">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F42" s="51">
+      <c r="F42" s="52">
         <f>F40+F41</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="inlineStr">
+      <c r="A43" s="51" t="inlineStr">
         <is>
           <t>Non-controlling Interests</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n">
+      <c r="B43" s="38" t="n">
         <v>8070.86</v>
       </c>
-      <c r="C43" s="49" t="n">
+      <c r="C43" s="38" t="n">
         <v>6765.37</v>
       </c>
-      <c r="D43" s="49" t="n">
+      <c r="D43" s="38" t="n">
         <v>5977.48</v>
       </c>
-      <c r="E43" s="49" t="n">
+      <c r="E43" s="38" t="n">
         <v>5416.69</v>
       </c>
-      <c r="F43" s="49" t="n">
+      <c r="F43" s="38" t="n">
         <v>3586.9</v>
       </c>
     </row>
@@ -13032,196 +13403,196 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B44" s="51">
+      <c r="B44" s="52">
         <f>B42+B43</f>
         <v/>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="52">
         <f>C42+C43</f>
         <v/>
       </c>
-      <c r="D44" s="51">
+      <c r="D44" s="52">
         <f>D42+D43</f>
         <v/>
       </c>
-      <c r="E44" s="51">
+      <c r="E44" s="52">
         <f>E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="51">
+      <c r="F44" s="52">
         <f>F42+F43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="48" t="inlineStr">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="49" t="n"/>
-      <c r="E45" s="49" t="n"/>
-      <c r="F45" s="49" t="n"/>
+      <c r="B45" s="38" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="38" t="n"/>
+      <c r="F45" s="38" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="50" t="inlineStr">
+      <c r="A46" s="51" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
       </c>
-      <c r="B46" s="49" t="n">
+      <c r="B46" s="38" t="n">
         <v>61608.57</v>
       </c>
-      <c r="C46" s="49" t="n">
+      <c r="C46" s="38" t="n">
         <v>44129.72</v>
       </c>
-      <c r="D46" s="49" t="n">
+      <c r="D46" s="38" t="n">
         <v>37392.25</v>
       </c>
-      <c r="E46" s="49" t="n">
+      <c r="E46" s="38" t="n">
         <v>30708.49</v>
       </c>
-      <c r="F46" s="49" t="n">
+      <c r="F46" s="38" t="n">
         <v>32729.7</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="50" t="inlineStr">
+      <c r="A47" s="51" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B47" s="49" t="n">
+      <c r="B47" s="38" t="n">
         <v>4549.94</v>
       </c>
-      <c r="C47" s="49" t="n">
+      <c r="C47" s="38" t="n">
         <v>4196.21</v>
       </c>
-      <c r="D47" s="49" t="n">
+      <c r="D47" s="38" t="n">
         <v>3742.48</v>
       </c>
-      <c r="E47" s="49" t="n">
+      <c r="E47" s="38" t="n">
         <v>3510.7</v>
       </c>
-      <c r="F47" s="49" t="n">
+      <c r="F47" s="38" t="n">
         <v>3207.79</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="50" t="inlineStr">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>Trade Payables (Non-current)</t>
         </is>
       </c>
-      <c r="B48" s="49" t="n"/>
-      <c r="C48" s="49" t="n"/>
-      <c r="D48" s="49" t="n"/>
-      <c r="E48" s="49" t="n"/>
-      <c r="F48" s="49" t="n">
+      <c r="B48" s="38" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="38" t="n"/>
+      <c r="E48" s="38" t="n"/>
+      <c r="F48" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="50" t="inlineStr">
+      <c r="A49" s="51" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B49" s="49" t="n">
+      <c r="B49" s="38" t="n">
         <v>694.64</v>
       </c>
-      <c r="C49" s="49" t="n">
+      <c r="C49" s="38" t="n">
         <v>674.12</v>
       </c>
-      <c r="D49" s="49" t="n">
+      <c r="D49" s="38" t="n">
         <v>1507.55</v>
       </c>
-      <c r="E49" s="49" t="n">
+      <c r="E49" s="38" t="n">
         <v>1410.4</v>
       </c>
-      <c r="F49" s="49" t="n">
+      <c r="F49" s="38" t="n">
         <v>1156.56</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="50" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>Non-current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B50" s="49" t="n"/>
-      <c r="C50" s="49" t="n"/>
-      <c r="D50" s="49" t="n"/>
-      <c r="E50" s="49" t="n"/>
-      <c r="F50" s="49" t="n">
+      <c r="B50" s="38" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="38" t="n"/>
+      <c r="E50" s="38" t="n"/>
+      <c r="F50" s="38" t="n">
         <v>3.03</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="50" t="inlineStr">
+      <c r="A51" s="51" t="inlineStr">
         <is>
           <t>Provisions (Non-current)</t>
         </is>
       </c>
-      <c r="B51" s="49" t="n">
+      <c r="B51" s="38" t="n">
         <v>3213.85</v>
       </c>
-      <c r="C51" s="49" t="n">
+      <c r="C51" s="38" t="n">
         <v>2548.69</v>
       </c>
-      <c r="D51" s="49" t="n">
+      <c r="D51" s="38" t="n">
         <v>1865.08</v>
       </c>
-      <c r="E51" s="49" t="n">
+      <c r="E51" s="38" t="n">
         <v>1420.02</v>
       </c>
-      <c r="F51" s="49" t="n">
+      <c r="F51" s="38" t="n">
         <v>1218.18</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="50" t="inlineStr">
+      <c r="A52" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B52" s="49" t="n">
+      <c r="B52" s="38" t="n">
         <v>4807.88</v>
       </c>
-      <c r="C52" s="49" t="n">
+      <c r="C52" s="38" t="n">
         <v>4104.12</v>
       </c>
-      <c r="D52" s="49" t="n">
+      <c r="D52" s="38" t="n">
         <v>2772.33</v>
       </c>
-      <c r="E52" s="49" t="n">
+      <c r="E52" s="38" t="n">
         <v>1919.37</v>
       </c>
-      <c r="F52" s="49" t="n">
+      <c r="F52" s="38" t="n">
         <v>1033.3</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="50" t="inlineStr">
+      <c r="A53" s="51" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B53" s="49" t="n">
+      <c r="B53" s="38" t="n">
         <v>13411.97</v>
       </c>
-      <c r="C53" s="49" t="n">
+      <c r="C53" s="38" t="n">
         <v>12930.57</v>
       </c>
-      <c r="D53" s="49" t="n">
+      <c r="D53" s="38" t="n">
         <v>11973.08</v>
       </c>
-      <c r="E53" s="49" t="n">
+      <c r="E53" s="38" t="n">
         <v>9847.82</v>
       </c>
-      <c r="F53" s="49" t="n">
+      <c r="F53" s="38" t="n">
         <v>8139.29</v>
       </c>
     </row>
@@ -13231,226 +13602,226 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B54" s="51">
+      <c r="B54" s="52">
         <f>B46+B47+B48+B49+B50+B51+B52+B53</f>
         <v/>
       </c>
-      <c r="C54" s="51">
+      <c r="C54" s="52">
         <f>C46+C47+C48+C49+C50+C51+C52+C53</f>
         <v/>
       </c>
-      <c r="D54" s="51">
+      <c r="D54" s="52">
         <f>D46+D47+D48+D49+D50+D51+D52+D53</f>
         <v/>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="52">
         <f>E46+E47+E48+E49+E50+E51+E52+E53</f>
         <v/>
       </c>
-      <c r="F54" s="51">
+      <c r="F54" s="52">
         <f>F46+F47+F48+F49+F50+F51+F52+F53</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="48" t="inlineStr">
+      <c r="A55" s="50" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="49" t="n"/>
-      <c r="D55" s="49" t="n"/>
-      <c r="E55" s="49" t="n"/>
-      <c r="F55" s="49" t="n"/>
+      <c r="B55" s="38" t="n"/>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="38" t="n"/>
+      <c r="E55" s="38" t="n"/>
+      <c r="F55" s="38" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="50" t="inlineStr">
+      <c r="A56" s="51" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
       </c>
-      <c r="B56" s="49" t="n">
+      <c r="B56" s="38" t="n">
         <v>9513.82</v>
       </c>
-      <c r="C56" s="49" t="n">
+      <c r="C56" s="38" t="n">
         <v>14015.84</v>
       </c>
-      <c r="D56" s="49" t="n">
+      <c r="D56" s="38" t="n">
         <v>12087.56</v>
       </c>
-      <c r="E56" s="49" t="n">
+      <c r="E56" s="38" t="n">
         <v>18265.94</v>
       </c>
-      <c r="F56" s="49" t="n">
+      <c r="F56" s="38" t="n">
         <v>14860.3</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="50" t="inlineStr">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B57" s="49" t="n">
+      <c r="B57" s="38" t="n">
         <v>468.94</v>
       </c>
-      <c r="C57" s="49" t="n">
+      <c r="C57" s="38" t="n">
         <v>524.03</v>
       </c>
-      <c r="D57" s="49" t="n">
+      <c r="D57" s="38" t="n">
         <v>467.16</v>
       </c>
-      <c r="E57" s="49" t="n">
+      <c r="E57" s="38" t="n">
         <v>437.87</v>
       </c>
-      <c r="F57" s="49" t="n">
+      <c r="F57" s="38" t="n">
         <v>397.33</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="50" t="inlineStr">
+      <c r="A58" s="51" t="inlineStr">
         <is>
           <t>Acceptances (Current)</t>
         </is>
       </c>
-      <c r="B58" s="49" t="n">
+      <c r="B58" s="38" t="n">
         <v>3647.97</v>
       </c>
-      <c r="C58" s="49" t="n">
+      <c r="C58" s="38" t="n">
         <v>5129.93</v>
       </c>
-      <c r="D58" s="49" t="n"/>
-      <c r="E58" s="49" t="n"/>
-      <c r="F58" s="49" t="n"/>
+      <c r="D58" s="38" t="n"/>
+      <c r="E58" s="38" t="n"/>
+      <c r="F58" s="38" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="50" t="inlineStr">
+      <c r="A59" s="51" t="inlineStr">
         <is>
           <t>Trade Payables — micro/small enterprises</t>
         </is>
       </c>
-      <c r="B59" s="49" t="n">
+      <c r="B59" s="38" t="n">
         <v>809.84</v>
       </c>
-      <c r="C59" s="49" t="n">
+      <c r="C59" s="38" t="n">
         <v>784.21</v>
       </c>
-      <c r="D59" s="49" t="n">
+      <c r="D59" s="38" t="n">
         <v>870</v>
       </c>
-      <c r="E59" s="49" t="n">
+      <c r="E59" s="38" t="n">
         <v>537.6</v>
       </c>
-      <c r="F59" s="49" t="n"/>
+      <c r="F59" s="38" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="50" t="inlineStr">
+      <c r="A60" s="51" t="inlineStr">
         <is>
           <t>Trade Payables — other creditors / total</t>
         </is>
       </c>
-      <c r="B60" s="49" t="n">
+      <c r="B60" s="38" t="n">
         <v>6328.39</v>
       </c>
-      <c r="C60" s="49" t="n">
+      <c r="C60" s="38" t="n">
         <v>8070.34</v>
       </c>
-      <c r="D60" s="49" t="n">
+      <c r="D60" s="38" t="n">
         <v>8451.370000000001</v>
       </c>
-      <c r="E60" s="49" t="n">
+      <c r="E60" s="38" t="n">
         <v>6869.6</v>
       </c>
-      <c r="F60" s="49" t="n">
+      <c r="F60" s="38" t="n">
         <v>10459.6</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="50" t="inlineStr">
+      <c r="A61" s="51" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B61" s="49" t="n">
+      <c r="B61" s="38" t="n">
         <v>13897.6</v>
       </c>
-      <c r="C61" s="49" t="n">
+      <c r="C61" s="38" t="n">
         <v>12427.03</v>
       </c>
-      <c r="D61" s="49" t="n">
+      <c r="D61" s="38" t="n">
         <v>14796.16</v>
       </c>
-      <c r="E61" s="49" t="n">
+      <c r="E61" s="38" t="n">
         <v>13150.77</v>
       </c>
-      <c r="F61" s="49" t="n">
+      <c r="F61" s="38" t="n">
         <v>9631.959999999999</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="50" t="inlineStr">
+      <c r="A62" s="51" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
       </c>
-      <c r="B62" s="49" t="n">
+      <c r="B62" s="38" t="n">
         <v>680.4400000000001</v>
       </c>
-      <c r="C62" s="49" t="n">
+      <c r="C62" s="38" t="n">
         <v>437.56</v>
       </c>
-      <c r="D62" s="49" t="n">
+      <c r="D62" s="38" t="n">
         <v>294.34</v>
       </c>
-      <c r="E62" s="49" t="n">
+      <c r="E62" s="38" t="n">
         <v>311.07</v>
       </c>
-      <c r="F62" s="49" t="n">
+      <c r="F62" s="38" t="n">
         <v>344.82</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="50" t="inlineStr">
+      <c r="A63" s="51" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B63" s="49" t="n">
+      <c r="B63" s="38" t="n">
         <v>185.42</v>
       </c>
-      <c r="C63" s="49" t="n">
+      <c r="C63" s="38" t="n">
         <v>208.2</v>
       </c>
-      <c r="D63" s="49" t="n">
+      <c r="D63" s="38" t="n">
         <v>291.54</v>
       </c>
-      <c r="E63" s="49" t="n">
+      <c r="E63" s="38" t="n">
         <v>217.96</v>
       </c>
-      <c r="F63" s="49" t="n">
+      <c r="F63" s="38" t="n">
         <v>147</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="50" t="inlineStr">
+      <c r="A64" s="51" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B64" s="49" t="n">
+      <c r="B64" s="38" t="n">
         <v>3691.15</v>
       </c>
-      <c r="C64" s="49" t="n">
+      <c r="C64" s="38" t="n">
         <v>3672.38</v>
       </c>
-      <c r="D64" s="49" t="n">
+      <c r="D64" s="38" t="n">
         <v>3879.84</v>
       </c>
-      <c r="E64" s="49" t="n">
+      <c r="E64" s="38" t="n">
         <v>4188.41</v>
       </c>
-      <c r="F64" s="49" t="n">
+      <c r="F64" s="38" t="n">
         <v>2779.08</v>
       </c>
     </row>
@@ -13460,68 +13831,68 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B65" s="51">
+      <c r="B65" s="52">
         <f>B56+B57+B58+B59+B60+B61+B62+B63+B64</f>
         <v/>
       </c>
-      <c r="C65" s="51">
+      <c r="C65" s="52">
         <f>C56+C57+C58+C59+C60+C61+C62+C63+C64</f>
         <v/>
       </c>
-      <c r="D65" s="51">
+      <c r="D65" s="52">
         <f>D56+D57+D58+D59+D60+D61+D62+D63+D64</f>
         <v/>
       </c>
-      <c r="E65" s="51">
+      <c r="E65" s="52">
         <f>E56+E57+E58+E59+E60+E61+E62+E63+E64</f>
         <v/>
       </c>
-      <c r="F65" s="51">
+      <c r="F65" s="52">
         <f>F56+F57+F58+F59+F60+F61+F62+F63+F64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="50" t="inlineStr">
+      <c r="A66" s="51" t="inlineStr">
         <is>
           <t>Liabilities re: Assets Held For Sale</t>
         </is>
       </c>
-      <c r="B66" s="49" t="n">
+      <c r="B66" s="38" t="n">
         <v>114.24</v>
       </c>
-      <c r="C66" s="49" t="n">
+      <c r="C66" s="38" t="n">
         <v>113.56</v>
       </c>
-      <c r="D66" s="49" t="n">
+      <c r="D66" s="38" t="n">
         <v>113.56</v>
       </c>
-      <c r="E66" s="49" t="n">
+      <c r="E66" s="38" t="n">
         <v>113.56</v>
       </c>
-      <c r="F66" s="49" t="n">
+      <c r="F66" s="38" t="n">
         <v>113.56</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="50" t="inlineStr">
+      <c r="A67" s="51" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Liability</t>
         </is>
       </c>
-      <c r="B67" s="49" t="n">
+      <c r="B67" s="38" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="C67" s="49" t="n">
+      <c r="C67" s="38" t="n">
         <v>138.74</v>
       </c>
-      <c r="D67" s="49" t="n">
+      <c r="D67" s="38" t="n">
         <v>716.42</v>
       </c>
-      <c r="E67" s="49" t="n">
+      <c r="E67" s="38" t="n">
         <v>1235.34</v>
       </c>
-      <c r="F67" s="49" t="n">
+      <c r="F67" s="38" t="n">
         <v>634.63</v>
       </c>
     </row>
@@ -13531,23 +13902,23 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B68" s="51">
+      <c r="B68" s="52">
         <f>B44+B54+B65+B66+B67</f>
         <v/>
       </c>
-      <c r="C68" s="51">
+      <c r="C68" s="52">
         <f>C44+C54+C65+C66+C67</f>
         <v/>
       </c>
-      <c r="D68" s="51">
+      <c r="D68" s="52">
         <f>D44+D54+D65+D66+D67</f>
         <v/>
       </c>
-      <c r="E68" s="51">
+      <c r="E68" s="52">
         <f>E44+E54+E65+E66+E67</f>
         <v/>
       </c>
-      <c r="F68" s="51">
+      <c r="F68" s="52">
         <f>F44+F54+F65+F66+F67</f>
         <v/>
       </c>
@@ -13586,85 +13957,85 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Sources: Tata Power Integrated Annual Reports FY21-22, FY23-24 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="38" t="n">
         <v>62428.59</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="38" t="n">
         <v>65478.24</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="38" t="n">
         <v>61448.9</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="38" t="n">
         <v>55109.08</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="38" t="n">
         <v>42815.67</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="38" t="n">
         <v>1743.07</v>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="38" t="n">
         <v>1513.93</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="38" t="n">
         <v>1823.42</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="38" t="n">
         <v>1438.02</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="38" t="n">
         <v>919.96</v>
       </c>
     </row>
@@ -13674,256 +14045,256 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="51">
+      <c r="B7" s="52">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="52">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="52">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="52">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="52">
         <f>F5+F6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="49" t="n"/>
-      <c r="E8" s="49" t="n"/>
-      <c r="F8" s="49" t="n"/>
+      <c r="B8" s="38" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Cost of Power Purchased</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="38" t="n">
         <v>19647.25</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="38" t="n">
         <v>20523.61</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="38" t="n">
         <v>20014.46</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="38" t="n">
         <v>19062.67</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="38" t="n">
         <v>14640.62</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Cost of Fuel</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="38" t="n">
         <v>7498.39</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="38" t="n">
         <v>13918.47</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="38" t="n">
         <v>14130.47</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="38" t="n">
         <v>13763.59</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="38" t="n">
         <v>8290.92</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Transmission Charges</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="38" t="n">
         <v>1467.98</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="38" t="n">
         <v>1277.81</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="38" t="n">
         <v>1168.69</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="38" t="n">
         <v>1194.95</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="38" t="n">
         <v>1018.19</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Raw Material Consumed / Construction Cost</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="38" t="n">
         <v>8618.4</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="38" t="n">
         <v>4921.46</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="38" t="n">
         <v>5439.86</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="38" t="n">
         <v>3882.3</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="38" t="n">
         <v>3832.83</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Purchase of Finished Goods and Spares</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="38" t="n">
         <v>42.35</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="38" t="n">
         <v>31.84</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="38" t="n">
         <v>39.89</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="38" t="n">
         <v>56.15</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="38" t="n">
         <v>49.11</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>(Increase)/Decrease in Stock-in-Trade &amp; WIP</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="38" t="n">
         <v>-84.11</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="38" t="n">
         <v>-440.76</v>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="38" t="n">
         <v>-51.78</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="38" t="n">
         <v>43.53</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="38" t="n">
         <v>-199.22</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="38" t="n">
         <v>4693.73</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="38" t="n">
         <v>4372.92</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="38" t="n">
         <v>4036.09</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="38" t="n">
         <v>3624.26</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="38" t="n">
         <v>3611.63</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Finance Costs</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="38" t="n">
         <v>5256.79</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="38" t="n">
         <v>4702.44</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="38" t="n">
         <v>4633.22</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="38" t="n">
         <v>4371.65</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="38" t="n">
         <v>3859.02</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Depreciation and Amortisation Expense</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="38" t="n">
         <v>4811.09</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="38" t="n">
         <v>4116.86</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="38" t="n">
         <v>3786.37</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="38" t="n">
         <v>3439.2</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="38" t="n">
         <v>3122.2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="38" t="n">
         <v>7449.54</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="38" t="n">
         <v>6943.02</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="38" t="n">
         <v>5887.39</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="38" t="n">
         <v>5775.31</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="38" t="n">
         <v>4060.42</v>
       </c>
     </row>
@@ -13933,23 +14304,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="52">
         <f>B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="52">
         <f>C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <f>D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="52">
         <f>E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="52">
         <f>F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
@@ -13960,46 +14331,46 @@
           <t>Profit before Regulatory Deferral, Exceptional Items &amp; Assoc./JV share</t>
         </is>
       </c>
-      <c r="B20" s="51">
+      <c r="B20" s="52">
         <f>B7-B19</f>
         <v/>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="52">
         <f>C7-C19</f>
         <v/>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="52">
         <f>D7-D19</f>
         <v/>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="52">
         <f>E7-E19</f>
         <v/>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="52">
         <f>F7-F19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>Net Movement in Regulatory Deferral Balances (incl. earlier years, net tax)</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="38" t="n">
         <v>1252.04</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="38" t="n">
         <v>-976.16</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="38" t="n">
         <v>93.43000000000001</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="38" t="n">
         <v>924.05</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="38" t="n">
         <v>-239.47</v>
       </c>
     </row>
@@ -14009,46 +14380,46 @@
           <t>Profit Before Exceptional Items, Tax &amp; Assoc./JV Share</t>
         </is>
       </c>
-      <c r="B22" s="51">
+      <c r="B22" s="52">
         <f>B20+B21</f>
         <v/>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="52">
         <f>C20+C21</f>
         <v/>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="52">
         <f>D20+D21</f>
         <v/>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="52">
         <f>E20+E21</f>
         <v/>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="52">
         <f>F20+F21</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>Share of Net Profit of Associates and JVs (Equity Method)</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="38" t="n">
         <v>707.87</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="38" t="n">
         <v>793.33</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="38" t="n">
         <v>1177.57</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="38" t="n">
         <v>3199.46</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="38" t="n">
         <v>1942.83</v>
       </c>
     </row>
@@ -14058,46 +14429,46 @@
           <t>Profit Before Exceptional Items and Tax</t>
         </is>
       </c>
-      <c r="B24" s="51">
+      <c r="B24" s="52">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="52">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="52">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="52">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="52">
         <f>F22+F23</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>Exceptional Items (net)</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n">
+      <c r="B25" s="38" t="n">
         <v>-94.17</v>
       </c>
-      <c r="C25" s="49" t="n">
+      <c r="C25" s="38" t="n">
         <v>-122.05</v>
       </c>
-      <c r="D25" s="49" t="n">
+      <c r="D25" s="38" t="n">
         <v>273.36</v>
       </c>
-      <c r="E25" s="49" t="n">
+      <c r="E25" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="49" t="n">
+      <c r="F25" s="38" t="n">
         <v>-150.27</v>
       </c>
     </row>
@@ -14107,46 +14478,46 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B26" s="51">
+      <c r="B26" s="52">
         <f>B24+B25</f>
         <v/>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="52">
         <f>C24+C25</f>
         <v/>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="52">
         <f>D24+D25</f>
         <v/>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="52">
         <f>E24+E25</f>
         <v/>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="52">
         <f>F24+F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>Total Tax Expense/(Credit)</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
+      <c r="B27" s="38" t="n">
         <v>1518.43</v>
       </c>
-      <c r="C27" s="49" t="n">
+      <c r="C27" s="38" t="n">
         <v>1544.25</v>
       </c>
-      <c r="D27" s="49" t="n">
+      <c r="D27" s="38" t="n">
         <v>1451.92</v>
       </c>
-      <c r="E27" s="49" t="n">
+      <c r="E27" s="38" t="n">
         <v>1647.33</v>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="38" t="n">
         <v>379.56</v>
       </c>
     </row>
@@ -14156,23 +14527,23 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B28" s="51">
+      <c r="B28" s="52">
         <f>B26-B27</f>
         <v/>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="52">
         <f>C26-C27</f>
         <v/>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="52">
         <f>D26-D27</f>
         <v/>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="52">
         <f>E26-E27</f>
         <v/>
       </c>
-      <c r="F28" s="51">
+      <c r="F28" s="52">
         <f>F26-F27</f>
         <v/>
       </c>
@@ -14212,360 +14583,360 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Sources: Torrent Power Integrated Annual Reports FY21-22 (AR_20392) through FY25-26 (AR_29704) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>Mar-2021</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
-      <c r="E5" s="49" t="n"/>
-      <c r="F5" s="49" t="n"/>
-      <c r="G5" s="49" t="n"/>
+      <c r="B5" s="38" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="38" t="n"/>
+      <c r="E5" s="38" t="n"/>
+      <c r="F5" s="38" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="38" t="n">
         <v>24200.83</v>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="38" t="n">
         <v>23028.29</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="38" t="n">
         <v>20653.68</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="38" t="n">
         <v>18115.94</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="38" t="n">
         <v>16759.39</v>
       </c>
-      <c r="G6" s="49" t="n">
+      <c r="G6" s="38" t="n">
         <v>17129.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Right-of-use Assets</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="38" t="n">
         <v>585.35</v>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="38" t="n">
         <v>398.86</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="38" t="n">
         <v>259.07</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="38" t="n">
         <v>216.46</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="38" t="n">
         <v>214.6</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="38" t="n">
         <v>178.35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="38" t="n">
         <v>6961.53</v>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="38" t="n">
         <v>2249.81</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="38" t="n">
         <v>2472.36</v>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="38" t="n">
         <v>2624.69</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="38" t="n">
         <v>1297.27</v>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="38" t="n">
         <v>837.73</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Investment Property</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="38" t="n">
         <v>0.37</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="38" t="n">
         <v>0.37</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="38" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="F9" s="49" t="n"/>
-      <c r="G9" s="49" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="38" t="n">
         <v>171.07</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="38" t="n">
         <v>171.07</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="38" t="n">
         <v>171.07</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="38" t="n">
         <v>171.07</v>
       </c>
-      <c r="F10" s="49" t="n"/>
-      <c r="G10" s="49" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="38" t="n">
         <v>653.66</v>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="38" t="n">
         <v>687.46</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="38" t="n">
         <v>718.46</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="38" t="n">
         <v>756.33</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="38" t="n">
         <v>123.29</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="38" t="n">
         <v>18.44</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Intangible Assets Under Development</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="38" t="n">
         <v>3.25</v>
       </c>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="49" t="n"/>
-      <c r="G12" s="49" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Investments (Non-current)</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="38" t="n">
         <v>24.1</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="38" t="n">
         <v>22.15</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="38" t="n">
         <v>17.02</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="38" t="n">
         <v>15.94</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="38" t="n">
         <v>132.82</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="38" t="n">
         <v>124.2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n">
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="38" t="n">
         <v>121.87</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="38" t="n">
         <v>155.7</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="38" t="n">
         <v>349.43</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="38" t="n">
         <v>105.75</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="38" t="n">
         <v>94.68000000000001</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="38" t="n">
         <v>135.38</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="38" t="n">
         <v>101.55</v>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="38" t="n">
         <v>75.83</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="38" t="n">
         <v>148.21</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="38" t="n">
         <v>114.67</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="38" t="n">
         <v>66.38</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="38" t="n">
         <v>38.65</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="38" t="n">
         <v>35.12</v>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="38" t="n">
         <v>24.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="38" t="n">
         <v>18.85</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="38" t="n">
         <v>16.27</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="38" t="n">
         <v>12.64</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="38" t="n">
         <v>12.5</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="38" t="n">
         <v>10.56</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="38" t="n">
         <v>12.83</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="38" t="n">
         <v>2837.21</v>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="38" t="n">
         <v>1158.63</v>
       </c>
-      <c r="D18" s="49" t="n">
+      <c r="D18" s="38" t="n">
         <v>420.76</v>
       </c>
-      <c r="E18" s="49" t="n">
+      <c r="E18" s="38" t="n">
         <v>361.04</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="38" t="n">
         <v>1000.47</v>
       </c>
-      <c r="G18" s="49" t="n">
+      <c r="G18" s="38" t="n">
         <v>337.48</v>
       </c>
     </row>
@@ -14575,233 +14946,233 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="52">
         <f>B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="52">
         <f>C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <f>D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="52">
         <f>E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="52">
         <f>F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="52">
         <f>G6+G7+G8+G9+G10+G11+G12+G13+G14+G15+G16+G17+G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
-      <c r="G20" s="49" t="n"/>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n">
+      <c r="B21" s="38" t="n">
         <v>507.18</v>
       </c>
-      <c r="C21" s="49" t="n">
+      <c r="C21" s="38" t="n">
         <v>658.02</v>
       </c>
-      <c r="D21" s="49" t="n">
+      <c r="D21" s="38" t="n">
         <v>800.45</v>
       </c>
-      <c r="E21" s="49" t="n">
+      <c r="E21" s="38" t="n">
         <v>820.28</v>
       </c>
-      <c r="F21" s="49" t="n">
+      <c r="F21" s="38" t="n">
         <v>537.5700000000001</v>
       </c>
-      <c r="G21" s="49" t="n">
+      <c r="G21" s="38" t="n">
         <v>450.35</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="38" t="n">
         <v>1507.19</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="38" t="n">
         <v>873.03</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="38" t="n">
         <v>937.37</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="38" t="n">
         <v>787.75</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="38" t="n">
         <v>273.7</v>
       </c>
-      <c r="G22" s="49" t="n">
+      <c r="G22" s="38" t="n">
         <v>341.58</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>Trade Receivables</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="38" t="n">
         <v>2329.76</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="38" t="n">
         <v>2362.25</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="38" t="n">
         <v>2190.86</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="38" t="n">
         <v>2246.33</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="38" t="n">
         <v>1602.7</v>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="38" t="n">
         <v>1420.29</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B24" s="49" t="n">
+      <c r="B24" s="38" t="n">
         <v>766.61</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="38" t="n">
         <v>289.11</v>
       </c>
-      <c r="D24" s="49" t="n">
+      <c r="D24" s="38" t="n">
         <v>350.83</v>
       </c>
-      <c r="E24" s="49" t="n">
+      <c r="E24" s="38" t="n">
         <v>188.23</v>
       </c>
-      <c r="F24" s="49" t="n">
+      <c r="F24" s="38" t="n">
         <v>289.41</v>
       </c>
-      <c r="G24" s="49" t="n">
+      <c r="G24" s="38" t="n">
         <v>107.28</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
       </c>
-      <c r="B25" s="49" t="n">
+      <c r="B25" s="38" t="n">
         <v>64.81999999999999</v>
       </c>
-      <c r="C25" s="49" t="n">
+      <c r="C25" s="38" t="n">
         <v>90.89</v>
       </c>
-      <c r="D25" s="49" t="n">
+      <c r="D25" s="38" t="n">
         <v>67.91</v>
       </c>
-      <c r="E25" s="49" t="n">
+      <c r="E25" s="38" t="n">
         <v>155.29</v>
       </c>
-      <c r="F25" s="49" t="n">
+      <c r="F25" s="38" t="n">
         <v>62.93</v>
       </c>
-      <c r="G25" s="49" t="n">
+      <c r="G25" s="38" t="n">
         <v>95.14</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
       </c>
-      <c r="B26" s="49" t="n"/>
-      <c r="C26" s="49" t="n"/>
-      <c r="D26" s="49" t="n"/>
-      <c r="E26" s="49" t="n"/>
-      <c r="F26" s="49" t="n">
+      <c r="B26" s="38" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="38" t="n">
         <v>19.9</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="51" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
       </c>
-      <c r="B27" s="49" t="n">
+      <c r="B27" s="38" t="n">
         <v>3516.62</v>
       </c>
-      <c r="C27" s="49" t="n">
+      <c r="C27" s="38" t="n">
         <v>4188.37</v>
       </c>
-      <c r="D27" s="49" t="n">
+      <c r="D27" s="38" t="n">
         <v>3989.23</v>
       </c>
-      <c r="E27" s="49" t="n">
+      <c r="E27" s="38" t="n">
         <v>3111.4</v>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="38" t="n">
         <v>2298.81</v>
       </c>
-      <c r="G27" s="49" t="n">
+      <c r="G27" s="38" t="n">
         <v>2153.41</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B28" s="49" t="n">
+      <c r="B28" s="38" t="n">
         <v>547.24</v>
       </c>
-      <c r="C28" s="49" t="n">
+      <c r="C28" s="38" t="n">
         <v>158.38</v>
       </c>
-      <c r="D28" s="49" t="n">
+      <c r="D28" s="38" t="n">
         <v>169.71</v>
       </c>
-      <c r="E28" s="49" t="n">
+      <c r="E28" s="38" t="n">
         <v>143.51</v>
       </c>
-      <c r="F28" s="49" t="n">
+      <c r="F28" s="38" t="n">
         <v>140.74</v>
       </c>
-      <c r="G28" s="49" t="n">
+      <c r="G28" s="38" t="n">
         <v>76.36</v>
       </c>
     </row>
@@ -14811,27 +15182,27 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B29" s="51">
+      <c r="B29" s="52">
         <f>B21+B22+B23+B24+B25+B26+B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="52">
         <f>C21+C22+C23+C24+C25+C26+C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="52">
         <f>D21+D22+D23+D24+D25+D26+D27+D28</f>
         <v/>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="52">
         <f>E21+E22+E23+E24+E25+E26+E27+E28</f>
         <v/>
       </c>
-      <c r="F29" s="51">
+      <c r="F29" s="52">
         <f>F21+F22+F23+F24+F25+F26+F27+F28</f>
         <v/>
       </c>
-      <c r="G29" s="51">
+      <c r="G29" s="52">
         <f>G21+G22+G23+G24+G25+G26+G27+G28</f>
         <v/>
       </c>
@@ -14842,91 +15213,91 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B30" s="51">
+      <c r="B30" s="52">
         <f>B19+B29</f>
         <v/>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="52">
         <f>C19+C29</f>
         <v/>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="52">
         <f>D19+D29</f>
         <v/>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="52">
         <f>E19+E29</f>
         <v/>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="52">
         <f>F19+F29</f>
         <v/>
       </c>
-      <c r="G30" s="51">
+      <c r="G30" s="52">
         <f>G19+G29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="50" t="inlineStr">
         <is>
           <t>EQUITY &amp; LIABILITIES</t>
         </is>
       </c>
-      <c r="B31" s="49" t="n"/>
-      <c r="C31" s="49" t="n"/>
-      <c r="D31" s="49" t="n"/>
-      <c r="E31" s="49" t="n"/>
-      <c r="F31" s="49" t="n"/>
-      <c r="G31" s="49" t="n"/>
+      <c r="B31" s="38" t="n"/>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="38" t="n"/>
+      <c r="G31" s="38" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
       </c>
-      <c r="B32" s="49" t="n">
+      <c r="B32" s="38" t="n">
         <v>503.9</v>
       </c>
-      <c r="C32" s="49" t="n">
+      <c r="C32" s="38" t="n">
         <v>503.9</v>
       </c>
-      <c r="D32" s="49" t="n">
+      <c r="D32" s="38" t="n">
         <v>480.62</v>
       </c>
-      <c r="E32" s="49" t="n">
+      <c r="E32" s="38" t="n">
         <v>480.62</v>
       </c>
-      <c r="F32" s="49" t="n">
+      <c r="F32" s="38" t="n">
         <v>480.62</v>
       </c>
-      <c r="G32" s="49" t="n">
+      <c r="G32" s="38" t="n">
         <v>480.62</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
       </c>
-      <c r="B33" s="49" t="n">
+      <c r="B33" s="38" t="n">
         <v>18571.43</v>
       </c>
-      <c r="C33" s="49" t="n">
+      <c r="C33" s="38" t="n">
         <v>17111.41</v>
       </c>
-      <c r="D33" s="49" t="n">
+      <c r="D33" s="38" t="n">
         <v>11581.09</v>
       </c>
-      <c r="E33" s="49" t="n">
+      <c r="E33" s="38" t="n">
         <v>10529.38</v>
       </c>
-      <c r="F33" s="49" t="n">
+      <c r="F33" s="38" t="n">
         <v>9462.559999999999</v>
       </c>
-      <c r="G33" s="49" t="n">
+      <c r="G33" s="38" t="n">
         <v>9703.620000000001</v>
       </c>
     </row>
@@ -14936,53 +15307,53 @@
           <t>Net Worth (Attributable to Owners)</t>
         </is>
       </c>
-      <c r="B34" s="51">
+      <c r="B34" s="52">
         <f>B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="52">
         <f>C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="52">
         <f>D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="52">
         <f>E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="51">
+      <c r="F34" s="52">
         <f>F32+F33</f>
         <v/>
       </c>
-      <c r="G34" s="51">
+      <c r="G34" s="52">
         <f>G32+G33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="inlineStr">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>Non-Controlling Interests</t>
         </is>
       </c>
-      <c r="B35" s="49" t="n">
+      <c r="B35" s="38" t="n">
         <v>633.42</v>
       </c>
-      <c r="C35" s="49" t="n">
+      <c r="C35" s="38" t="n">
         <v>600.47</v>
       </c>
-      <c r="D35" s="49" t="n">
+      <c r="D35" s="38" t="n">
         <v>535.79</v>
       </c>
-      <c r="E35" s="49" t="n">
+      <c r="E35" s="38" t="n">
         <v>476.65</v>
       </c>
-      <c r="F35" s="49" t="n">
+      <c r="F35" s="38" t="n">
         <v>35.93</v>
       </c>
-      <c r="G35" s="49" t="n">
+      <c r="G35" s="38" t="n">
         <v>36.36</v>
       </c>
     </row>
@@ -14992,191 +15363,191 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B36" s="51">
+      <c r="B36" s="52">
         <f>B34+B35</f>
         <v/>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="52">
         <f>C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="52">
         <f>D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="52">
         <f>E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="51">
+      <c r="F36" s="52">
         <f>F34+F35</f>
         <v/>
       </c>
-      <c r="G36" s="51">
+      <c r="G36" s="52">
         <f>G34+G35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="50" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="38" t="n"/>
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="38" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="inlineStr">
+      <c r="A38" s="51" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
       </c>
-      <c r="B38" s="49" t="n">
+      <c r="B38" s="38" t="n">
         <v>11871.42</v>
       </c>
-      <c r="C38" s="49" t="n">
+      <c r="C38" s="38" t="n">
         <v>7310.21</v>
       </c>
-      <c r="D38" s="49" t="n">
+      <c r="D38" s="38" t="n">
         <v>9916.4</v>
       </c>
-      <c r="E38" s="49" t="n">
+      <c r="E38" s="38" t="n">
         <v>8902.32</v>
       </c>
-      <c r="F38" s="49" t="n">
+      <c r="F38" s="38" t="n">
         <v>7099.15</v>
       </c>
-      <c r="G38" s="49" t="n">
+      <c r="G38" s="38" t="n">
         <v>6672.18</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="50" t="inlineStr">
+      <c r="A39" s="51" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B39" s="49" t="n">
+      <c r="B39" s="38" t="n">
         <v>219.83</v>
       </c>
-      <c r="C39" s="49" t="n">
+      <c r="C39" s="38" t="n">
         <v>92.78</v>
       </c>
-      <c r="D39" s="49" t="n">
+      <c r="D39" s="38" t="n">
         <v>39.5</v>
       </c>
-      <c r="E39" s="49" t="n">
+      <c r="E39" s="38" t="n">
         <v>39.32</v>
       </c>
-      <c r="F39" s="49" t="n">
+      <c r="F39" s="38" t="n">
         <v>39.1</v>
       </c>
-      <c r="G39" s="49" t="n">
+      <c r="G39" s="38" t="n">
         <v>30.96</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="50" t="inlineStr">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>Trade Payables (Non-current)</t>
         </is>
       </c>
-      <c r="B40" s="49" t="n">
+      <c r="B40" s="38" t="n">
         <v>324.05</v>
       </c>
-      <c r="C40" s="49" t="n">
+      <c r="C40" s="38" t="n">
         <v>380.88</v>
       </c>
-      <c r="D40" s="49" t="n">
+      <c r="D40" s="38" t="n">
         <v>345.71</v>
       </c>
-      <c r="E40" s="49" t="n">
+      <c r="E40" s="38" t="n">
         <v>210.61</v>
       </c>
-      <c r="F40" s="49" t="n">
+      <c r="F40" s="38" t="n">
         <v>150.46</v>
       </c>
-      <c r="G40" s="49" t="n">
+      <c r="G40" s="38" t="n">
         <v>116.11</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="50" t="inlineStr">
+      <c r="A41" s="51" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
       </c>
-      <c r="B41" s="49" t="n">
+      <c r="B41" s="38" t="n">
         <v>38.14</v>
       </c>
-      <c r="C41" s="49" t="n">
+      <c r="C41" s="38" t="n">
         <v>8.43</v>
       </c>
-      <c r="D41" s="49" t="n">
+      <c r="D41" s="38" t="n">
         <v>0.95</v>
       </c>
-      <c r="E41" s="49" t="n">
+      <c r="E41" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="49" t="n">
+      <c r="F41" s="38" t="n">
         <v>0.33</v>
       </c>
-      <c r="G41" s="49" t="n">
+      <c r="G41" s="38" t="n">
         <v>1.17</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B42" s="49" t="n">
+      <c r="B42" s="38" t="n">
         <v>1628.57</v>
       </c>
-      <c r="C42" s="49" t="n">
+      <c r="C42" s="38" t="n">
         <v>1352.21</v>
       </c>
-      <c r="D42" s="49" t="n">
+      <c r="D42" s="38" t="n">
         <v>1233.65</v>
       </c>
-      <c r="E42" s="49" t="n">
+      <c r="E42" s="38" t="n">
         <v>968.79</v>
       </c>
-      <c r="F42" s="49" t="n">
+      <c r="F42" s="38" t="n">
         <v>345.21</v>
       </c>
-      <c r="G42" s="49" t="n">
+      <c r="G42" s="38" t="n">
         <v>527.51</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="inlineStr">
+      <c r="A43" s="51" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B43" s="49" t="n">
+      <c r="B43" s="38" t="n">
         <v>1689.43</v>
       </c>
-      <c r="C43" s="49" t="n">
+      <c r="C43" s="38" t="n">
         <v>1623.6</v>
       </c>
-      <c r="D43" s="49" t="n">
+      <c r="D43" s="38" t="n">
         <v>1445.68</v>
       </c>
-      <c r="E43" s="49" t="n">
+      <c r="E43" s="38" t="n">
         <v>1372.46</v>
       </c>
-      <c r="F43" s="49" t="n">
+      <c r="F43" s="38" t="n">
         <v>1261.67</v>
       </c>
-      <c r="G43" s="49" t="n">
+      <c r="G43" s="38" t="n">
         <v>1160.34</v>
       </c>
     </row>
@@ -15186,216 +15557,216 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B44" s="51">
+      <c r="B44" s="52">
         <f>B38+B39+B40+B41+B42+B43</f>
         <v/>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="52">
         <f>C38+C39+C40+C41+C42+C43</f>
         <v/>
       </c>
-      <c r="D44" s="51">
+      <c r="D44" s="52">
         <f>D38+D39+D40+D41+D42+D43</f>
         <v/>
       </c>
-      <c r="E44" s="51">
+      <c r="E44" s="52">
         <f>E38+E39+E40+E41+E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="51">
+      <c r="F44" s="52">
         <f>F38+F39+F40+F41+F42+F43</f>
         <v/>
       </c>
-      <c r="G44" s="51">
+      <c r="G44" s="52">
         <f>G38+G39+G40+G41+G42+G43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="48" t="inlineStr">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="49" t="n"/>
-      <c r="E45" s="49" t="n"/>
-      <c r="F45" s="49" t="n"/>
-      <c r="G45" s="49" t="n"/>
+      <c r="B45" s="38" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="38" t="n"/>
+      <c r="F45" s="38" t="n"/>
+      <c r="G45" s="38" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="50" t="inlineStr">
+      <c r="A46" s="51" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
       </c>
-      <c r="B46" s="49" t="n">
+      <c r="B46" s="38" t="n">
         <v>1861.51</v>
       </c>
-      <c r="C46" s="49" t="n">
+      <c r="C46" s="38" t="n">
         <v>1426.47</v>
       </c>
-      <c r="D46" s="49" t="n">
+      <c r="D46" s="38" t="n">
         <v>1668.63</v>
       </c>
-      <c r="E46" s="49" t="n">
+      <c r="E46" s="38" t="n">
         <v>1593.75</v>
       </c>
-      <c r="F46" s="49" t="n">
+      <c r="F46" s="38" t="n">
         <v>1999.27</v>
       </c>
-      <c r="G46" s="49" t="n">
+      <c r="G46" s="38" t="n">
         <v>1108.37</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="50" t="inlineStr">
+      <c r="A47" s="51" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B47" s="49" t="n">
+      <c r="B47" s="38" t="n">
         <v>17.8</v>
       </c>
-      <c r="C47" s="49" t="n">
+      <c r="C47" s="38" t="n">
         <v>10.28</v>
       </c>
-      <c r="D47" s="49" t="n">
+      <c r="D47" s="38" t="n">
         <v>7.27</v>
       </c>
-      <c r="E47" s="49" t="n">
+      <c r="E47" s="38" t="n">
         <v>6.02</v>
       </c>
-      <c r="F47" s="49" t="n">
+      <c r="F47" s="38" t="n">
         <v>5.11</v>
       </c>
-      <c r="G47" s="49" t="n">
+      <c r="G47" s="38" t="n">
         <v>5.05</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="50" t="inlineStr">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>Trade Payables (Current)</t>
         </is>
       </c>
-      <c r="B48" s="49" t="n">
+      <c r="B48" s="38" t="n">
         <v>1879.23</v>
       </c>
-      <c r="C48" s="49" t="n">
+      <c r="C48" s="38" t="n">
         <v>1824.13</v>
       </c>
-      <c r="D48" s="49" t="n">
+      <c r="D48" s="38" t="n">
         <v>1811.92</v>
       </c>
-      <c r="E48" s="49" t="n">
+      <c r="E48" s="38" t="n">
         <v>1522.67</v>
       </c>
-      <c r="F48" s="49" t="n">
+      <c r="F48" s="38" t="n">
         <v>1111.13</v>
       </c>
-      <c r="G48" s="49" t="n">
+      <c r="G48" s="38" t="n">
         <v>974.79</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="50" t="inlineStr">
+      <c r="A49" s="51" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
       </c>
-      <c r="B49" s="49" t="n">
+      <c r="B49" s="38" t="n">
         <v>4771.06</v>
       </c>
-      <c r="C49" s="49" t="n">
+      <c r="C49" s="38" t="n">
         <v>3409.61</v>
       </c>
-      <c r="D49" s="49" t="n">
+      <c r="D49" s="38" t="n">
         <v>3264.67</v>
       </c>
-      <c r="E49" s="49" t="n">
+      <c r="E49" s="38" t="n">
         <v>2687.72</v>
       </c>
-      <c r="F49" s="49" t="n">
+      <c r="F49" s="38" t="n">
         <v>2021.51</v>
       </c>
-      <c r="G49" s="49" t="n">
+      <c r="G49" s="38" t="n">
         <v>1799.77</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="50" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B50" s="49" t="n">
+      <c r="B50" s="38" t="n">
         <v>921.02</v>
       </c>
-      <c r="C50" s="49" t="n">
+      <c r="C50" s="38" t="n">
         <v>689.74</v>
       </c>
-      <c r="D50" s="49" t="n">
+      <c r="D50" s="38" t="n">
         <v>735.0599999999999</v>
       </c>
-      <c r="E50" s="49" t="n">
+      <c r="E50" s="38" t="n">
         <v>677.24</v>
       </c>
-      <c r="F50" s="49" t="n">
+      <c r="F50" s="38" t="n">
         <v>613.5599999999999</v>
       </c>
-      <c r="G50" s="49" t="n">
+      <c r="G50" s="38" t="n">
         <v>542.02</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="50" t="inlineStr">
+      <c r="A51" s="51" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
       </c>
-      <c r="B51" s="49" t="n">
+      <c r="B51" s="38" t="n">
         <v>226.37</v>
       </c>
-      <c r="C51" s="49" t="n">
+      <c r="C51" s="38" t="n">
         <v>198.17</v>
       </c>
-      <c r="D51" s="49" t="n">
+      <c r="D51" s="38" t="n">
         <v>201.74</v>
       </c>
-      <c r="E51" s="49" t="n">
+      <c r="E51" s="38" t="n">
         <v>264.06</v>
       </c>
-      <c r="F51" s="49" t="n">
+      <c r="F51" s="38" t="n">
         <v>274.55</v>
       </c>
-      <c r="G51" s="49" t="n">
+      <c r="G51" s="38" t="n">
         <v>335.3</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="50" t="inlineStr">
+      <c r="A52" s="51" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
       </c>
-      <c r="B52" s="49" t="n">
+      <c r="B52" s="38" t="n">
         <v>36.1</v>
       </c>
-      <c r="C52" s="49" t="n">
+      <c r="C52" s="38" t="n">
         <v>31.09</v>
       </c>
-      <c r="D52" s="49" t="n">
+      <c r="D52" s="38" t="n">
         <v>123.8</v>
       </c>
-      <c r="E52" s="49" t="n">
+      <c r="E52" s="38" t="n">
         <v>178.57</v>
       </c>
-      <c r="F52" s="49" t="n">
+      <c r="F52" s="38" t="n">
         <v>122.54</v>
       </c>
-      <c r="G52" s="49" t="n">
+      <c r="G52" s="38" t="n">
         <v>44.55</v>
       </c>
     </row>
@@ -15405,27 +15776,27 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B53" s="51">
+      <c r="B53" s="52">
         <f>B46+B47+B48+B49+B50+B51+B52</f>
         <v/>
       </c>
-      <c r="C53" s="51">
+      <c r="C53" s="52">
         <f>C46+C47+C48+C49+C50+C51+C52</f>
         <v/>
       </c>
-      <c r="D53" s="51">
+      <c r="D53" s="52">
         <f>D46+D47+D48+D49+D50+D51+D52</f>
         <v/>
       </c>
-      <c r="E53" s="51">
+      <c r="E53" s="52">
         <f>E46+E47+E48+E49+E50+E51+E52</f>
         <v/>
       </c>
-      <c r="F53" s="51">
+      <c r="F53" s="52">
         <f>F46+F47+F48+F49+F50+F51+F52</f>
         <v/>
       </c>
-      <c r="G53" s="51">
+      <c r="G53" s="52">
         <f>G46+G47+G48+G49+G50+G51+G52</f>
         <v/>
       </c>
@@ -15436,27 +15807,27 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B54" s="51">
+      <c r="B54" s="52">
         <f>B36+B44+B53</f>
         <v/>
       </c>
-      <c r="C54" s="51">
+      <c r="C54" s="52">
         <f>C36+C44+C53</f>
         <v/>
       </c>
-      <c r="D54" s="51">
+      <c r="D54" s="52">
         <f>D36+D44+D53</f>
         <v/>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="52">
         <f>E36+E44+E53</f>
         <v/>
       </c>
-      <c r="F54" s="51">
+      <c r="F54" s="52">
         <f>F36+F44+F53</f>
         <v/>
       </c>
-      <c r="G54" s="51">
+      <c r="G54" s="52">
         <f>G36+G44+G53</f>
         <v/>
       </c>
@@ -15496,96 +15867,96 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Sources: Torrent Power Integrated Annual Reports FY21-22 through FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS. Only FY22 had an exceptional item (the ~Rs 1,300cr DGEN plant impairment) — all other years are genuinely nil, not missing data.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="47" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
-      <c r="G4" s="47" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>FY 2020-21</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="38" t="n">
         <v>28966.31</v>
       </c>
-      <c r="C5" s="49" t="n">
+      <c r="C5" s="38" t="n">
         <v>29165.26</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="38" t="n">
         <v>27183.21</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="38" t="n">
         <v>25694.12</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="38" t="n">
         <v>14257.61</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="38" t="n">
         <v>12172.66</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="38" t="n">
         <v>322.61</v>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="38" t="n">
         <v>487.21</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="38" t="n">
         <v>344.32</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="38" t="n">
         <v>381.85</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="38" t="n">
         <v>235.04</v>
       </c>
-      <c r="G6" s="49" t="n">
+      <c r="G6" s="38" t="n">
         <v>141.81</v>
       </c>
     </row>
@@ -15595,264 +15966,264 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="51">
+      <c r="B7" s="52">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="52">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="52">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="52">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="52">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="52">
         <f>G5+G6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="49" t="n"/>
-      <c r="E8" s="49" t="n"/>
-      <c r="F8" s="49" t="n"/>
-      <c r="G8" s="49" t="n"/>
+      <c r="B8" s="38" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Electrical Energy Purchased</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="38" t="n">
         <v>15053.7</v>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="38" t="n">
         <v>15289.81</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="38" t="n">
         <v>13743.27</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="38" t="n">
         <v>14440.53</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="38" t="n">
         <v>5116.39</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="38" t="n">
         <v>3358.36</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="38" t="n">
         <v>3944.21</v>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="38" t="n">
         <v>4877.69</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="38" t="n">
         <v>5647.95</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="38" t="n">
         <v>2508.23</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="38" t="n">
         <v>3403.4</v>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="G10" s="38" t="n">
         <v>3610.55</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Cost of Materials Consumed</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n">
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n">
         <v>213.46</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="38" t="n">
         <v>406.5</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="38" t="n">
         <v>334.81</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="38" t="n">
         <v>262.64</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="38" t="n">
         <v>104.21</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Purchase of Stock-in-Trade</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="38" t="n">
         <v>1593.67</v>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="38" t="n">
         <v>1103.91</v>
       </c>
-      <c r="D12" s="49" t="n">
+      <c r="D12" s="38" t="n">
         <v>690.53</v>
       </c>
-      <c r="E12" s="49" t="n">
+      <c r="E12" s="38" t="n">
         <v>1879.26</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="38" t="n">
         <v>305.99</v>
       </c>
-      <c r="G12" s="49" t="n">
+      <c r="G12" s="38" t="n">
         <v>48.24</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>Changes in Inventories of Finished Goods and WIP</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="38" t="n">
         <v>0.11</v>
       </c>
-      <c r="D13" s="49" t="n">
+      <c r="D13" s="38" t="n">
         <v>20.45</v>
       </c>
-      <c r="E13" s="49" t="n">
+      <c r="E13" s="38" t="n">
         <v>-29.19</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="38" t="n">
         <v>-11.11</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="38" t="n">
         <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="38" t="n">
         <v>705.8</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="38" t="n">
         <v>689.96</v>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="38" t="n">
         <v>611.1900000000001</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="38" t="n">
         <v>578.25</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="38" t="n">
         <v>533.54</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="38" t="n">
         <v>538.9400000000001</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>Finance Costs</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="38" t="n">
         <v>934.47</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="38" t="n">
         <v>1044.87</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="38" t="n">
         <v>943.4</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="38" t="n">
         <v>818.2</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="38" t="n">
         <v>628.21</v>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="38" t="n">
         <v>775.73</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortisation</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="38" t="n">
         <v>1612.75</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="38" t="n">
         <v>1497.12</v>
       </c>
-      <c r="D16" s="49" t="n">
+      <c r="D16" s="38" t="n">
         <v>1377.5</v>
       </c>
-      <c r="E16" s="49" t="n">
+      <c r="E16" s="38" t="n">
         <v>1280.96</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="38" t="n">
         <v>1333.86</v>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="38" t="n">
         <v>1279.55</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="51" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="38" t="n">
         <v>2127.55</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="38" t="n">
         <v>1682.96</v>
       </c>
-      <c r="D17" s="49" t="n">
+      <c r="D17" s="38" t="n">
         <v>1504.14</v>
       </c>
-      <c r="E17" s="49" t="n">
+      <c r="E17" s="38" t="n">
         <v>1223.56</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="38" t="n">
         <v>1055.76</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="38" t="n">
         <v>1038.26</v>
       </c>
     </row>
@@ -15862,27 +16233,27 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B18" s="51">
+      <c r="B18" s="52">
         <f>B9+B10+B11+B12+B13+B14+B15+B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="52">
         <f>C9+C10+C11+C12+C13+C14+C15+C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="52">
         <f>D9+D10+D11+D12+D13+D14+D15+D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="52">
         <f>E9+E10+E11+E12+E13+E14+E15+E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="51">
+      <c r="F18" s="52">
         <f>F9+F10+F11+F12+F13+F14+F15+F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="52">
         <f>G9+G10+G11+G12+G13+G14+G15+G16+G17</f>
         <v/>
       </c>
@@ -15893,53 +16264,53 @@
           <t>Profit Before Exceptional Items and Tax</t>
         </is>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="52">
         <f>B7-B18</f>
         <v/>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="52">
         <f>C7-C18</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="52">
         <f>D7-D18</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="52">
         <f>E7-E18</f>
         <v/>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="52">
         <f>F7-F18</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="52">
         <f>G7-G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Exceptional Items (DGEN plant impairment, FY22 only)</t>
         </is>
       </c>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F20" s="38" t="n">
         <v>1300</v>
       </c>
-      <c r="G20" s="49" t="n">
+      <c r="G20" s="38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15949,78 +16320,78 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B21" s="51">
+      <c r="B21" s="52">
         <f>B19-B20</f>
         <v/>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="52">
         <f>C19-C20</f>
         <v/>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="52">
         <f>D19-D20</f>
         <v/>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="52">
         <f>E19-E20</f>
         <v/>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="52">
         <f>F19-F20</f>
         <v/>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="52">
         <f>G19-G20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>Current Tax</t>
         </is>
       </c>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="38" t="n">
         <v>728.15</v>
       </c>
-      <c r="C22" s="49" t="n">
+      <c r="C22" s="38" t="n">
         <v>600.47</v>
       </c>
-      <c r="D22" s="49" t="n">
+      <c r="D22" s="38" t="n">
         <v>445.07</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="38" t="n">
         <v>672.8200000000001</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="38" t="n">
         <v>372.48</v>
       </c>
-      <c r="G22" s="49" t="n">
+      <c r="G22" s="38" t="n">
         <v>287.85</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="B23" s="49" t="n">
+      <c r="B23" s="38" t="n">
         <v>119.26</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="38" t="n">
         <v>-406.5</v>
       </c>
-      <c r="D23" s="49" t="n">
+      <c r="D23" s="38" t="n">
         <v>241.53</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="38" t="n">
         <v>203.87</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="38" t="n">
         <v>-267.21</v>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="38" t="n">
         <v>-31.95</v>
       </c>
     </row>
@@ -16030,27 +16401,27 @@
           <t>Total Tax Expense</t>
         </is>
       </c>
-      <c r="B24" s="51">
+      <c r="B24" s="52">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="52">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="52">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="52">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="52">
         <f>F22+F23</f>
         <v/>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="52">
         <f>G22+G23</f>
         <v/>
       </c>
@@ -16061,27 +16432,27 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B25" s="51">
+      <c r="B25" s="52">
         <f>B21-B24</f>
         <v/>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="52">
         <f>C21-C24</f>
         <v/>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="52">
         <f>D21-D24</f>
         <v/>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="52">
         <f>E21-E24</f>
         <v/>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="52">
         <f>F21-F24</f>
         <v/>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="52">
         <f>G21-G24</f>
         <v/>
       </c>

--- a/FADM_AdaniPower_Analysis.xlsx
+++ b/FADM_AdaniPower_Analysis.xlsx
@@ -46,7 +46,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -146,6 +146,12 @@
     </font>
     <font>
       <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00008000"/>
       <sz val="12"/>
     </font>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,9 +283,6 @@
     <xf numFmtId="4" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -293,17 +296,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="25" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="26" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1118,7 +1123,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>1-Year Performance, Rebased to 100 (weekly adj close, 14-Jul-2025 = 100)</a:t>
+              <a:t>Performance, Rebased to 100 (weekly, 27-Jun-2025 = 100)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1130,6 +1135,38 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Weekly_Price_Data'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Weekly_Price_Data'!$A$2:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Weekly_Price_Data'!$K$2:$K$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
           <tx>
             <strRef>
               <f>'Weekly_Price_Data'!L1</f>
@@ -1150,18 +1187,18 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Weekly_Price_Data'!$A$2:$A$54</f>
+              <f>'Weekly_Price_Data'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Weekly_Price_Data'!$L$2:$L$54</f>
+              <f>'Weekly_Price_Data'!$L$2:$L$46</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'Weekly_Price_Data'!M1</f>
@@ -1182,18 +1219,18 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Weekly_Price_Data'!$A$2:$A$54</f>
+              <f>'Weekly_Price_Data'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Weekly_Price_Data'!$M$2:$M$54</f>
+              <f>'Weekly_Price_Data'!$M$2:$M$46</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'Weekly_Price_Data'!N1</f>
@@ -1214,76 +1251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Weekly_Price_Data'!$A$2:$A$54</f>
+              <f>'Weekly_Price_Data'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Weekly_Price_Data'!$N$2:$N$54</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Weekly_Price_Data'!O1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Weekly_Price_Data'!$A$2:$A$54</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Weekly_Price_Data'!$O$2:$O$54</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Weekly_Price_Data'!P1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Weekly_Price_Data'!$A$2:$A$54</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Weekly_Price_Data'!$P$2:$P$54</f>
+              <f>'Weekly_Price_Data'!$N$2:$N$46</f>
             </numRef>
           </val>
         </ser>
@@ -1364,7 +1337,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Adani Power weekly adj close, Jul-2025 to Jul-2026 — events marked in hidden data sheet col C</a:t>
+              <a:t>Adani Power weekly close, Jun-2025 to Jun-2026 — events marked in hidden data sheet col C (split-adjusted for the 22-Sep-2025 1:5 split, for a continuous price line)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1396,12 +1369,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'12b_Announcement_Chart_Data'!$A$2:$A$54</f>
+              <f>'12b_Announcement_Chart_Data'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'12b_Announcement_Chart_Data'!$B$2:$B$54</f>
+              <f>'12b_Announcement_Chart_Data'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -1543,7 +1516,7 @@
     </comment>
     <comment ref="F37" authorId="0" shapeId="0">
       <text>
-        <t>Adjusted close of the week containing 31-Mar-2026 (week starting 30-Mar-2026), from the Yahoo Finance weekly series stored in this repo (see Weekly_Price_Data sheet). Split-adjusted.</t>
+        <t>Close price for the week ending 27-Mar-2026 (nearest available date to 31-Mar-2026), from the user-supplied weekly price data (Daily_Share1.csv) — see the Weekly_Price_Data sheet. Already post 1:5 Adani stock split (22-Sep-2025), no further adjustment needed.</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
@@ -1568,7 +1541,7 @@
     </comment>
     <comment ref="F38" authorId="0" shapeId="0">
       <text>
-        <t>Adjusted close of the week containing 31-Mar-2026 (week starting 30-Mar-2026), from the Yahoo Finance weekly series stored in this repo (see Weekly_Price_Data sheet). Split-adjusted.</t>
+        <t>Close price for the week ending 27-Mar-2026 (nearest available date to 31-Mar-2026), from the user-supplied weekly price data (Daily_Share1.csv) — see the Weekly_Price_Data sheet. Already post 1:5 Adani stock split (22-Sep-2025), no further adjustment needed.</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
@@ -1593,7 +1566,7 @@
     </comment>
     <comment ref="F39" authorId="0" shapeId="0">
       <text>
-        <t>Adjusted close of the week containing 31-Mar-2026 (week starting 30-Mar-2026), from the Yahoo Finance weekly series stored in this repo (see Weekly_Price_Data sheet). Split-adjusted.</t>
+        <t>Close price for the week ending 27-Mar-2026 (nearest available date to 31-Mar-2026), from the user-supplied weekly price data (Daily_Share1.csv) — see the Weekly_Price_Data sheet. Already post 1:5 Adani stock split (22-Sep-2025), no further adjustment needed.</t>
       </text>
     </comment>
   </commentList>
@@ -1704,7 +1677,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5040000"/>
@@ -4922,28 +4895,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>11. Share Price Return vs Sector Index (weekly, 14-Jul-2025 to 15-Jul-2026) &amp; Volatility</t>
+          <t>11. Share Price Return vs Sector Index &amp; Market Index (weekly, 27-Jun-2025 to Jun-2026) &amp; Volatility</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>COMPUTED from actual Yahoo Finance weekly adjusted-close data (split-adjusted), saved to repo as *_weekly.htm and parsed, then aligned to the 53 dates common to all 5 series (Nifty Energy was missing one date the others had). All 'Total'/stat cells below are LIVE FORMULAS referencing the Weekly_Price_Data sheet.</t>
+          <t>REBUILT from the user-supplied weekly price/return data (Daily_Share1.csv), replacing the earlier Yahoo-Finance-derived series. Sector index = Nifty Energy; Market index = Nifty Next 50 (replaces Nifty 50 per the new source). All 'Total'/stat cells below are LIVE FORMULAS referencing the Weekly_Price_Data sheet.</t>
         </is>
       </c>
     </row>
@@ -4976,26 +4949,26 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Nifty 50 (market)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
+          <t>Nifty Next 50 (market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Price at start (14-Jul-2025, adj)</t>
+          <t>Price at start (27-Jun-2025, ₹ as-quoted; Adani NOT split-adj.)</t>
         </is>
       </c>
       <c r="B6" s="39">
+        <f>'Weekly_Price_Data'!C2</f>
+        <v/>
+      </c>
+      <c r="C6" s="39">
+        <f>'Weekly_Price_Data'!D2</f>
+        <v/>
+      </c>
+      <c r="D6" s="39">
         <f>'Weekly_Price_Data'!B2</f>
-        <v/>
-      </c>
-      <c r="C6" s="39">
-        <f>'Weekly_Price_Data'!C2</f>
-        <v/>
-      </c>
-      <c r="D6" s="39">
-        <f>'Weekly_Price_Data'!D2</f>
         <v/>
       </c>
       <c r="E6" s="39">
@@ -5003,284 +4976,237 @@
         <v/>
       </c>
       <c r="F6" s="39">
-        <f>'Weekly_Price_Data'!F2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
+        <f>'Weekly_Price_Data'!B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Price at end (15-Jul-2026)</t>
+          <t>Price at end (₹ as-quoted; Adani NOT split-adj. - not comparable to start)</t>
         </is>
       </c>
       <c r="B7" s="39">
-        <f>'Weekly_Price_Data'!B54</f>
+        <f>'Weekly_Price_Data'!C46</f>
         <v/>
       </c>
       <c r="C7" s="39">
-        <f>'Weekly_Price_Data'!C54</f>
+        <f>'Weekly_Price_Data'!D46</f>
         <v/>
       </c>
       <c r="D7" s="39">
-        <f>'Weekly_Price_Data'!D54</f>
+        <f>'Weekly_Price_Data'!B46</f>
         <v/>
       </c>
       <c r="E7" s="39">
-        <f>'Weekly_Price_Data'!E54</f>
+        <f>'Weekly_Price_Data'!E46</f>
         <v/>
       </c>
       <c r="F7" s="39">
-        <f>'Weekly_Price_Data'!F54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
+        <f>'Weekly_Price_Data'!B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>52-week weekly-close range</t>
+          <t>Period return (COMPUTED by compounding weekly returns - split-safe)</t>
         </is>
       </c>
       <c r="B8" s="40">
-        <f>MIN('Weekly_Price_Data'!B2:B54)&amp;" - "&amp;MAX('Weekly_Price_Data'!B2:B54)</f>
+        <f>'Weekly_Price_Data'!M46/100-1</f>
         <v/>
       </c>
       <c r="C8" s="40">
-        <f>MIN('Weekly_Price_Data'!C2:C54)&amp;" - "&amp;MAX('Weekly_Price_Data'!C2:C54)</f>
+        <f>'Weekly_Price_Data'!N46/100-1</f>
         <v/>
       </c>
       <c r="D8" s="40">
-        <f>MIN('Weekly_Price_Data'!D2:D54)&amp;" - "&amp;MAX('Weekly_Price_Data'!D2:D54)</f>
+        <f>'Weekly_Price_Data'!L46/100-1</f>
         <v/>
       </c>
       <c r="E8" s="40">
-        <f>MIN('Weekly_Price_Data'!E2:E54)&amp;" - "&amp;MAX('Weekly_Price_Data'!E2:E54)</f>
+        <f>'Weekly_Price_Data'!O46/100-1</f>
         <v/>
       </c>
       <c r="F8" s="40">
-        <f>MIN('Weekly_Price_Data'!F2:F54)&amp;" - "&amp;MAX('Weekly_Price_Data'!F2:F54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
+        <f>PRODUCT(1+'Weekly_Price_Data'!C50:C78)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1-year return (COMPUTED)</t>
+          <t>Weekly return std dev (COMPUTED)</t>
         </is>
       </c>
       <c r="B9" s="41">
-        <f>'Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1</f>
+        <f>STDEV('Weekly_Price_Data'!H2:H46)</f>
         <v/>
       </c>
       <c r="C9" s="41">
-        <f>'Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1</f>
+        <f>STDEV('Weekly_Price_Data'!I2:I46)</f>
         <v/>
       </c>
       <c r="D9" s="41">
-        <f>'Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1</f>
+        <f>STDEV('Weekly_Price_Data'!G2:G46)</f>
         <v/>
       </c>
       <c r="E9" s="41">
-        <f>'Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1</f>
+        <f>STDEV('Weekly_Price_Data'!J2:J46)</f>
         <v/>
       </c>
       <c r="F9" s="41">
-        <f>'Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
+        <f>STDEV('Weekly_Price_Data'!C50:C78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Weekly return std dev (COMPUTED)</t>
-        </is>
-      </c>
-      <c r="B10" s="42">
-        <f>STDEV('Weekly_Price_Data'!G3:G54)</f>
-        <v/>
-      </c>
-      <c r="C10" s="42">
-        <f>STDEV('Weekly_Price_Data'!H3:H54)</f>
-        <v/>
-      </c>
-      <c r="D10" s="42">
-        <f>STDEV('Weekly_Price_Data'!I3:I54)</f>
-        <v/>
-      </c>
-      <c r="E10" s="42">
-        <f>STDEV('Weekly_Price_Data'!J3:J54)</f>
-        <v/>
-      </c>
-      <c r="F10" s="42">
-        <f>STDEV('Weekly_Price_Data'!K3:K54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
+          <t>Annualized volatility = sd x sqrt(52)</t>
+        </is>
+      </c>
+      <c r="B10" s="40">
+        <f>STDEV('Weekly_Price_Data'!H2:H46)*SQRT(52)</f>
+        <v/>
+      </c>
+      <c r="C10" s="40">
+        <f>STDEV('Weekly_Price_Data'!I2:I46)*SQRT(52)</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
+        <f>STDEV('Weekly_Price_Data'!G2:G46)*SQRT(52)</f>
+        <v/>
+      </c>
+      <c r="E10" s="40">
+        <f>STDEV('Weekly_Price_Data'!J2:J46)*SQRT(52)</f>
+        <v/>
+      </c>
+      <c r="F10" s="40">
+        <f>STDEV('Weekly_Price_Data'!C50:C78)*SQRT(52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Annualized volatility = sd x sqrt(52)</t>
-        </is>
-      </c>
-      <c r="B11" s="41">
-        <f>STDEV('Weekly_Price_Data'!G3:G54)*SQRT(52)</f>
-        <v/>
-      </c>
-      <c r="C11" s="41">
-        <f>STDEV('Weekly_Price_Data'!H3:H54)*SQRT(52)</f>
-        <v/>
-      </c>
-      <c r="D11" s="41">
-        <f>STDEV('Weekly_Price_Data'!I3:I54)*SQRT(52)</f>
-        <v/>
-      </c>
-      <c r="E11" s="41">
-        <f>STDEV('Weekly_Price_Data'!J3:J54)*SQRT(52)</f>
-        <v/>
-      </c>
-      <c r="F11" s="41">
-        <f>STDEV('Weekly_Price_Data'!K3:K54)*SQRT(52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
+          <t>Beta vs Nifty Next 50 / market (n=22 matched weeks only - LOW SAMPLE, directional)</t>
+        </is>
+      </c>
+      <c r="B11" s="39">
+        <f>SLOPE('Weekly_Price_Data'!H2:H46,'Weekly_Price_Data'!K2:K46)</f>
+        <v/>
+      </c>
+      <c r="C11" s="39">
+        <f>SLOPE('Weekly_Price_Data'!I2:I46,'Weekly_Price_Data'!K2:K46)</f>
+        <v/>
+      </c>
+      <c r="D11" s="39">
+        <f>SLOPE('Weekly_Price_Data'!G2:G46,'Weekly_Price_Data'!K2:K46)</f>
+        <v/>
+      </c>
+      <c r="E11" s="39">
+        <f>SLOPE('Weekly_Price_Data'!J2:J46,'Weekly_Price_Data'!K2:K46)</f>
+        <v/>
+      </c>
+      <c r="F11" s="39">
+        <f>1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Beta vs Nifty 50 / market (COMPUTED)</t>
+          <t>Beta vs Nifty Energy / sector (COMPUTED, n=44)</t>
         </is>
       </c>
       <c r="B12" s="39">
-        <f>SLOPE('Weekly_Price_Data'!G3:G54,'Weekly_Price_Data'!K3:K54)</f>
+        <f>SLOPE('Weekly_Price_Data'!H2:H46,'Weekly_Price_Data'!J2:J46)</f>
         <v/>
       </c>
       <c r="C12" s="39">
-        <f>SLOPE('Weekly_Price_Data'!H3:H54,'Weekly_Price_Data'!K3:K54)</f>
+        <f>SLOPE('Weekly_Price_Data'!I2:I46,'Weekly_Price_Data'!J2:J46)</f>
         <v/>
       </c>
       <c r="D12" s="39">
-        <f>SLOPE('Weekly_Price_Data'!I3:I54,'Weekly_Price_Data'!K3:K54)</f>
+        <f>SLOPE('Weekly_Price_Data'!G2:G46,'Weekly_Price_Data'!J2:J46)</f>
         <v/>
       </c>
       <c r="E12" s="39">
-        <f>SLOPE('Weekly_Price_Data'!J3:J54,'Weekly_Price_Data'!K3:K54)</f>
-        <v/>
-      </c>
-      <c r="F12" s="39">
         <f>1</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
+      <c r="F12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Beta vs Nifty Energy / sector (COMPUTED)</t>
-        </is>
-      </c>
-      <c r="B13" s="39">
-        <f>SLOPE('Weekly_Price_Data'!G3:G54,'Weekly_Price_Data'!J3:J54)</f>
-        <v/>
-      </c>
-      <c r="C13" s="39">
-        <f>SLOPE('Weekly_Price_Data'!H3:H54,'Weekly_Price_Data'!J3:J54)</f>
-        <v/>
-      </c>
-      <c r="D13" s="39">
-        <f>SLOPE('Weekly_Price_Data'!I3:I54,'Weekly_Price_Data'!J3:J54)</f>
-        <v/>
-      </c>
-      <c r="E13" s="39">
-        <f>1</f>
-        <v/>
-      </c>
+          <t>Return vs sector (stock - Nifty Energy)</t>
+        </is>
+      </c>
+      <c r="B13" s="40">
+        <f>('Weekly_Price_Data'!M46/100-1)-('Weekly_Price_Data'!O46/100-1)</f>
+        <v/>
+      </c>
+      <c r="C13" s="40">
+        <f>('Weekly_Price_Data'!N46/100-1)-('Weekly_Price_Data'!O46/100-1)</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
+        <f>('Weekly_Price_Data'!L46/100-1)-('Weekly_Price_Data'!O46/100-1)</f>
+        <v/>
+      </c>
+      <c r="E13" s="43" t="n"/>
       <c r="F13" s="43" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Return vs market (stock - Nifty 50)</t>
-        </is>
-      </c>
-      <c r="B14" s="41">
-        <f>('Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
-        <v/>
-      </c>
-      <c r="C14" s="41">
-        <f>('Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
-        <v/>
-      </c>
-      <c r="D14" s="41">
-        <f>('Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
-        <v/>
-      </c>
-      <c r="E14" s="41">
-        <f>('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)-('Weekly_Price_Data'!F54/'Weekly_Price_Data'!F2-1)</f>
-        <v/>
-      </c>
-      <c r="F14" s="44" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Return vs sector (stock - Nifty Energy)</t>
-        </is>
-      </c>
-      <c r="B15" s="41">
-        <f>('Weekly_Price_Data'!B54/'Weekly_Price_Data'!B2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
-        <v/>
-      </c>
-      <c r="C15" s="41">
-        <f>('Weekly_Price_Data'!C54/'Weekly_Price_Data'!C2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
-        <v/>
-      </c>
-      <c r="D15" s="41">
-        <f>('Weekly_Price_Data'!D54/'Weekly_Price_Data'!D2-1)-('Weekly_Price_Data'!E54/'Weekly_Price_Data'!E2-1)</f>
-        <v/>
-      </c>
-      <c r="E15" s="44" t="n"/>
-      <c r="F15" s="44" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="45" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>Data note</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>COMPLETE: all five series (3 stocks + Nifty 50 + Nifty Energy) parsed from the Yahoo Finance Historical Data pages saved in the repo (53 weekly adjusted-close points each, common to all 5 series, 14-Jul-2025 to 15-Jul-2026, split-adjusted). Weekly returns, standard deviations, annualized volatility, and betas computed from this data - see the Weekly_Price_Data sheet for the full series and the rebased performance chart below.</t>
-        </is>
-      </c>
-    </row>
+    <row r="16" ht="115" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>REPLACED per user instruction with the supplied weekly price/return data (Daily_Share1.csv). Window: 27-Jun-2025 to 12-Jun-2026 (45 ISO-weeks common to Torrent/Adani/Tata/Nifty Energy; Torrent/Adani/Tata individually cover to 19-Jun-2026, one week beyond where Nifty Energy's series ends, so that last week is excluded from all cross-series stats for a clean common base - same alignment discipline as before). VERIFIED BEFORE USE: the source's own 'Close Price' and 'Weekly Returns' columns do not reconcile with each other (confirmed via a controlled check across all 5 series) - the returns column is correctly split-adjusted (Adani Power's 22-Sep-2025 1:5 split shows a sane -1.85% weekly return, not a fabricated crash) while the raw Close Price column is NOT split-adjusted, so this workbook uses the WEEKLY RETURNS as the authoritative input and derives Cumulative/Period Return by properly compounding them, rather than trusting the source's own stated 'Cumulative Return' figures (which were computed as a naive non-split-adjusted price ratio and are WRONG for Adani Power specifically - the source states -60.34%, the correct compounded figure is -2.5%). MARKET INDEX CHANGED from Nifty 50 to Nifty Next 50 per the new source data. Nifty Next 50's coverage is sparse and irregular (29 of a possible ~51 weeks, gaps of up to several weeks) - its own return/volatility/period-return stats above use its full 29-point series; its BETA figures use only the 22 weeks that happen to align with the main 45-week grid, so treat Nifty Next 50 betas as directional, not as statistically robust as the Nifty Energy betas (n=44).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19"/>
     <row r="20"/>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="21"/>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Comments — which share is most volatile?</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="130" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>ANSWER (computed from 53 weekly observations, split-adjusted, dates common to all 5 series): ADANI POWER is the most volatile of the three — weekly-return standard deviation 4.95% (annualized ~36%), vs Torrent Power 4.57% (~33%) and Tata Power 2.92% (~21%). The sector index (Nifty Energy) sat at 2.30% weekly (~17% annualized) — all three stocks were roughly 1.3-2.2x as volatile as their sector index. RETURNS: Adani Power massively outperformed (+84% vs the sector's +9%), Torrent Power roughly tracked the sector (+6.8%), and Tata Power underperformed (-6.0%). BETA vs NIFTY ENERGY: 1.33 (Adani), 1.00 (Tata), 1.38 (Torrent) — all near or above 1.0, meaning these stocks move roughly in line with (Adani/Torrent: somewhat more than) their sector index, not decoupled from it. VS THE MARKET: Nifty 50 fell -3.6% over the window, so all three power stocks outperformed the broad market (Adani by ~88 points); market betas vs Nifty 50 are 1.15 (Adani), 0.62 (Tata) and 1.47 (Torrent) — Torrent is the most market-sensitive, Tata the most defensive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>ANSWER (computed from the supplied weekly data, 45 common weeks, 27-Jun-2025 to 12-Jun-2026): ADANI POWER is the most volatile of the three - weekly-return standard deviation 2.95% (annualized ~21%), vs Torrent Power 1.73% (~12%) and Tata Power 1.12% (~8%) - the same volatility ranking as before, though the magnitudes have shifted with this new data window. The sector index (Nifty Energy) sat at 1.23% weekly (~9% annualized) - all three stocks were more volatile than their sector index, Adani markedly so. RETURNS (properly compounded, split-adjusted): all three stocks AND the sector index finished negative over this window, but Adani Power's decline was by far the SMALLEST of the three (-2.5%, actually milder than the sector index itself), while Torrent Power (-5.9%), Tata Power (-7.1%) and Nifty Energy (-7.9%) all fell further - a materially different picture from a naive read of the source file's own (uncorrected, non-split-adjusted) cumulative-return figures, which wrongly showed Adani Power collapsing ~60% when in fact, once the 22-Sep-2025 stock split is correctly accounted for, it was the best-performing (least-bad) of the three. BETA vs NIFTY ENERGY (sector, n=44): 1.10 (Adani), 0.52 (Tata), 0.53 (Torrent) - Adani Power is the only one ABOVE 1.0 (moves somewhat more sharply than the sector), while Tata and Torrent both sit near 0.5 (notably more defensive than the sector index this window). VS THE MARKET (Nifty Next 50, n=22 matched weeks - directional only): period return -2.8%, so all three power stocks' returns diverged from the broad-market proxy; betas vs Nifty Next 50 are low/near-zero for all three (consistent with the sparse, irregular sample rather than necessarily reflecting a true low market sensitivity) - the sector-index comparison above is the more reliable read of these stocks' systematic risk.</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A16:F21"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:F20"/>
-    <mergeCell ref="A23:F30"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5293,25 +5219,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5322,19 +5247,19 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Adani Power (adj ₹)</t>
+          <t>Torrent Power (₹)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Adani Power (₹, raw/not split-adj.)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Tata Power (₹)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Torrent Power (₹)</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>Nifty Energy</t>
@@ -5342,24 +5267,24 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nifty 50</t>
+          <t>Nifty Next 50 (sparse, this week only if matched)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Torrent wk ret</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Adani wk ret</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tata wk ret</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Torrent wk ret</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>NiftyEnergy wk ret</t>
@@ -5367,3299 +5292,2672 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Nifty50 wk ret</t>
+          <t>NiftyNext50 wk ret (sparse)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Torrent (base=100)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Adani (base=100)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Tata (base=100)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Torrent (base=100)</t>
-        </is>
-      </c>
       <c r="O1" t="inlineStr">
         <is>
           <t>NiftyEnergy (base=100)</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Nifty50 (base=100)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118.93</v>
+        <v>1473.2</v>
       </c>
       <c r="C2" t="n">
-        <v>405.39</v>
+        <v>584.35</v>
       </c>
       <c r="D2" t="n">
-        <v>1349.89</v>
+        <v>408.85</v>
       </c>
       <c r="E2" t="n">
-        <v>36231.65</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24968.4</v>
-      </c>
-      <c r="L2" s="25">
-        <f>B2/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M2" s="25">
-        <f>C2/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N2" s="25">
-        <f>D2/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O2" s="25">
-        <f>E2/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P2" s="25">
-        <f>F2/F$2*100</f>
-        <v/>
+        <v>8188.24</v>
+      </c>
+      <c r="G2" s="45" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="H2" s="45" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="I2" s="45" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="J2" s="45" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="L2" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="25" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>114</v>
+        <v>1439.8</v>
       </c>
       <c r="C3" t="n">
-        <v>392.92</v>
+        <v>584.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1307.38</v>
+        <v>401</v>
       </c>
       <c r="E3" t="n">
-        <v>35250.5</v>
+        <v>8107.54</v>
       </c>
       <c r="F3" t="n">
-        <v>24837</v>
-      </c>
-      <c r="G3" s="35">
-        <f>B3/B2-1</f>
-        <v/>
-      </c>
-      <c r="H3" s="35">
-        <f>C3/C2-1</f>
-        <v/>
-      </c>
-      <c r="I3" s="35">
-        <f>D3/D2-1</f>
-        <v/>
-      </c>
-      <c r="J3" s="35">
-        <f>E3/E2-1</f>
-        <v/>
-      </c>
-      <c r="K3" s="35">
-        <f>F3/F2-1</f>
-        <v/>
+        <v>68998.2</v>
+      </c>
+      <c r="G3" s="45" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="H3" s="45" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="I3" s="45" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J3" s="45" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K3" s="45" t="n">
+        <v>0.0042</v>
       </c>
       <c r="L3" s="25">
-        <f>B3/B$2*100</f>
+        <f>L2*(1+G3)</f>
         <v/>
       </c>
       <c r="M3" s="25">
-        <f>C3/C$2*100</f>
+        <f>M2*(1+H3)</f>
         <v/>
       </c>
       <c r="N3" s="25">
-        <f>D3/D$2*100</f>
+        <f>N2*(1+I3)</f>
         <v/>
       </c>
       <c r="O3" s="25">
-        <f>E3/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P3" s="25">
-        <f>F3/F$2*100</f>
+        <f>O2*(1+J3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113.4</v>
+        <v>1408.1</v>
       </c>
       <c r="C4" t="n">
-        <v>386.9</v>
+        <v>603.95</v>
       </c>
       <c r="D4" t="n">
-        <v>1270.59</v>
+        <v>396.85</v>
       </c>
       <c r="E4" t="n">
-        <v>34889</v>
+        <v>8233.1</v>
       </c>
       <c r="F4" t="n">
-        <v>24565.35</v>
-      </c>
-      <c r="G4" s="35">
-        <f>B4/B3-1</f>
-        <v/>
-      </c>
-      <c r="H4" s="35">
-        <f>C4/C3-1</f>
-        <v/>
-      </c>
-      <c r="I4" s="35">
-        <f>D4/D3-1</f>
-        <v/>
-      </c>
-      <c r="J4" s="35">
-        <f>E4/E3-1</f>
-        <v/>
-      </c>
-      <c r="K4" s="35">
-        <f>F4/F3-1</f>
-        <v/>
+        <v>68725.8</v>
+      </c>
+      <c r="G4" s="45" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="H4" s="45" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="I4" s="45" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="J4" s="45" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="K4" s="45" t="n">
+        <v>0.0017</v>
       </c>
       <c r="L4" s="25">
-        <f>B4/B$2*100</f>
+        <f>L3*(1+G4)</f>
         <v/>
       </c>
       <c r="M4" s="25">
-        <f>C4/C$2*100</f>
+        <f>M3*(1+H4)</f>
         <v/>
       </c>
       <c r="N4" s="25">
-        <f>D4/D$2*100</f>
+        <f>N3*(1+I4)</f>
         <v/>
       </c>
       <c r="O4" s="25">
-        <f>E4/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P4" s="25">
-        <f>F4/F$2*100</f>
+        <f>O3*(1+J4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.38</v>
+        <v>1368.6</v>
       </c>
       <c r="C5" t="n">
-        <v>376.47</v>
+        <v>594.65</v>
       </c>
       <c r="D5" t="n">
-        <v>1317.54</v>
+        <v>407.9</v>
       </c>
       <c r="E5" t="n">
-        <v>34391.95</v>
+        <v>8227.98</v>
       </c>
       <c r="F5" t="n">
-        <v>24363.3</v>
-      </c>
-      <c r="G5" s="35">
-        <f>B5/B4-1</f>
-        <v/>
-      </c>
-      <c r="H5" s="35">
-        <f>C5/C4-1</f>
-        <v/>
-      </c>
-      <c r="I5" s="35">
-        <f>D5/D4-1</f>
-        <v/>
-      </c>
-      <c r="J5" s="35">
-        <f>E5/E4-1</f>
-        <v/>
-      </c>
-      <c r="K5" s="35">
-        <f>F5/F4-1</f>
-        <v/>
+        <v>68711.45</v>
+      </c>
+      <c r="G5" s="45" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="H5" s="45" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="I5" s="45" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="J5" s="45" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="K5" s="45" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="L5" s="25">
-        <f>B5/B$2*100</f>
+        <f>L4*(1+G5)</f>
         <v/>
       </c>
       <c r="M5" s="25">
-        <f>C5/C$2*100</f>
+        <f>M4*(1+H5)</f>
         <v/>
       </c>
       <c r="N5" s="25">
-        <f>D5/D$2*100</f>
+        <f>N4*(1+I5)</f>
         <v/>
       </c>
       <c r="O5" s="25">
-        <f>E5/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P5" s="25">
-        <f>F5/F$2*100</f>
+        <f>O4*(1+J5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.81</v>
+        <v>1325.5</v>
       </c>
       <c r="C6" t="n">
-        <v>382.93</v>
+        <v>570</v>
       </c>
       <c r="D6" t="n">
-        <v>1311.42</v>
+        <v>395.35</v>
       </c>
       <c r="E6" t="n">
-        <v>34469.05</v>
+        <v>7977.92</v>
       </c>
       <c r="F6" t="n">
-        <v>24631.3</v>
-      </c>
-      <c r="G6" s="35">
-        <f>B6/B5-1</f>
-        <v/>
-      </c>
-      <c r="H6" s="35">
-        <f>C6/C5-1</f>
-        <v/>
-      </c>
-      <c r="I6" s="35">
-        <f>D6/D5-1</f>
-        <v/>
-      </c>
-      <c r="J6" s="35">
-        <f>E6/E5-1</f>
-        <v/>
-      </c>
-      <c r="K6" s="35">
-        <f>F6/F5-1</f>
-        <v/>
+        <v>68207.3</v>
+      </c>
+      <c r="G6" s="45" t="n">
+        <v>-0.0228</v>
+      </c>
+      <c r="H6" s="45" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="I6" s="45" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="J6" s="45" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="K6" s="45" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="L6" s="25">
-        <f>B6/B$2*100</f>
+        <f>L5*(1+G6)</f>
         <v/>
       </c>
       <c r="M6" s="25">
-        <f>C6/C$2*100</f>
+        <f>M5*(1+H6)</f>
         <v/>
       </c>
       <c r="N6" s="25">
-        <f>D6/D$2*100</f>
+        <f>N5*(1+I6)</f>
         <v/>
       </c>
       <c r="O6" s="25">
-        <f>E6/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P6" s="25">
-        <f>F6/F$2*100</f>
+        <f>O5*(1+J6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118.86</v>
+        <v>1288.2</v>
       </c>
       <c r="C7" t="n">
-        <v>383.23</v>
+        <v>567</v>
       </c>
       <c r="D7" t="n">
-        <v>1264.47</v>
+        <v>389.3</v>
       </c>
       <c r="E7" t="n">
-        <v>34507.6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24870.1</v>
-      </c>
-      <c r="G7" s="35">
-        <f>B7/B6-1</f>
-        <v/>
-      </c>
-      <c r="H7" s="35">
-        <f>C7/C6-1</f>
-        <v/>
-      </c>
-      <c r="I7" s="35">
-        <f>D7/D6-1</f>
-        <v/>
-      </c>
-      <c r="J7" s="35">
-        <f>E7/E6-1</f>
-        <v/>
-      </c>
-      <c r="K7" s="35">
-        <f>F7/F6-1</f>
-        <v/>
+        <v>7894.41</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="H7" s="45" t="n">
+        <v>-0.0359</v>
+      </c>
+      <c r="I7" s="45" t="n">
+        <v>-0.0212</v>
+      </c>
+      <c r="J7" s="45" t="n">
+        <v>-0.013</v>
       </c>
       <c r="L7" s="25">
-        <f>B7/B$2*100</f>
+        <f>L6*(1+G7)</f>
         <v/>
       </c>
       <c r="M7" s="25">
-        <f>C7/C$2*100</f>
+        <f>M6*(1+H7)</f>
         <v/>
       </c>
       <c r="N7" s="25">
-        <f>D7/D$2*100</f>
+        <f>N6*(1+I7)</f>
         <v/>
       </c>
       <c r="O7" s="25">
-        <f>E7/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P7" s="25">
-        <f>F7/F$2*100</f>
+        <f>O6*(1+J7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>120.13</v>
+        <v>1282</v>
       </c>
       <c r="C8" t="n">
-        <v>371.85</v>
+        <v>594.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1210.52</v>
+        <v>385.6</v>
       </c>
       <c r="E8" t="n">
-        <v>33638.65</v>
-      </c>
-      <c r="F8" t="n">
-        <v>24426.85</v>
-      </c>
-      <c r="G8" s="35">
-        <f>B8/B7-1</f>
-        <v/>
-      </c>
-      <c r="H8" s="35">
-        <f>C8/C7-1</f>
-        <v/>
-      </c>
-      <c r="I8" s="35">
-        <f>D8/D7-1</f>
-        <v/>
-      </c>
-      <c r="J8" s="35">
-        <f>E8/E7-1</f>
-        <v/>
-      </c>
-      <c r="K8" s="35">
-        <f>F8/F7-1</f>
-        <v/>
+        <v>7947.13</v>
+      </c>
+      <c r="G8" s="45" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="H8" s="45" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="I8" s="45" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="J8" s="45" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="L8" s="25">
-        <f>B8/B$2*100</f>
+        <f>L7*(1+G8)</f>
         <v/>
       </c>
       <c r="M8" s="25">
-        <f>C8/C$2*100</f>
+        <f>M7*(1+H8)</f>
         <v/>
       </c>
       <c r="N8" s="25">
-        <f>D8/D$2*100</f>
+        <f>N7*(1+I8)</f>
         <v/>
       </c>
       <c r="O8" s="25">
-        <f>E8/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P8" s="25">
-        <f>F8/F$2*100</f>
+        <f>O7*(1+J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121.94</v>
+        <v>1227.3</v>
       </c>
       <c r="C9" t="n">
-        <v>383.42</v>
+        <v>600.65</v>
       </c>
       <c r="D9" t="n">
-        <v>1245.63</v>
+        <v>374.15</v>
       </c>
       <c r="E9" t="n">
-        <v>34297.9</v>
+        <v>7661.83</v>
       </c>
       <c r="F9" t="n">
-        <v>24741</v>
-      </c>
-      <c r="G9" s="35">
-        <f>B9/B8-1</f>
-        <v/>
-      </c>
-      <c r="H9" s="35">
-        <f>C9/C8-1</f>
-        <v/>
-      </c>
-      <c r="I9" s="35">
-        <f>D9/D8-1</f>
-        <v/>
-      </c>
-      <c r="J9" s="35">
-        <f>E9/E8-1</f>
-        <v/>
-      </c>
-      <c r="K9" s="35">
-        <f>F9/F8-1</f>
-        <v/>
+        <v>66800.35000000001</v>
+      </c>
+      <c r="G9" s="45" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="H9" s="45" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>0.008199999999999999</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="K9" s="45" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="L9" s="25">
-        <f>B9/B$2*100</f>
+        <f>L8*(1+G9)</f>
         <v/>
       </c>
       <c r="M9" s="25">
-        <f>C9/C$2*100</f>
+        <f>M8*(1+H9)</f>
         <v/>
       </c>
       <c r="N9" s="25">
-        <f>D9/D$2*100</f>
+        <f>N8*(1+I9)</f>
         <v/>
       </c>
       <c r="O9" s="25">
-        <f>E9/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P9" s="25">
-        <f>F9/F$2*100</f>
+        <f>O8*(1+J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129.71</v>
+        <v>1262.9</v>
       </c>
       <c r="C10" t="n">
-        <v>383.87</v>
+        <v>609.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1250.47</v>
+        <v>385.8</v>
       </c>
       <c r="E10" t="n">
-        <v>34940.3</v>
+        <v>7799.95</v>
       </c>
       <c r="F10" t="n">
-        <v>25114</v>
-      </c>
-      <c r="G10" s="35">
-        <f>B10/B9-1</f>
-        <v/>
-      </c>
-      <c r="H10" s="35">
-        <f>C10/C9-1</f>
-        <v/>
-      </c>
-      <c r="I10" s="35">
-        <f>D10/D9-1</f>
-        <v/>
-      </c>
-      <c r="J10" s="35">
-        <f>E10/E9-1</f>
-        <v/>
-      </c>
-      <c r="K10" s="35">
-        <f>F10/F9-1</f>
-        <v/>
+        <v>67017.75</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="H10" s="45" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="I10" s="45" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="J10" s="45" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="K10" s="45" t="n">
+        <v>0.0052</v>
       </c>
       <c r="L10" s="25">
-        <f>B10/B$2*100</f>
+        <f>L9*(1+G10)</f>
         <v/>
       </c>
       <c r="M10" s="25">
-        <f>C10/C$2*100</f>
+        <f>M9*(1+H10)</f>
         <v/>
       </c>
       <c r="N10" s="25">
-        <f>D10/D$2*100</f>
+        <f>N9*(1+I10)</f>
         <v/>
       </c>
       <c r="O10" s="25">
-        <f>E10/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P10" s="25">
-        <f>F10/F$2*100</f>
+        <f>O9*(1+J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141.88</v>
+        <v>1267.8</v>
       </c>
       <c r="C11" t="n">
-        <v>393.86</v>
+        <v>648.55</v>
       </c>
       <c r="D11" t="n">
-        <v>1247.21</v>
+        <v>386.25</v>
       </c>
       <c r="E11" t="n">
-        <v>35745.75</v>
-      </c>
-      <c r="F11" t="n">
-        <v>25327.05</v>
-      </c>
-      <c r="G11" s="35">
-        <f>B11/B10-1</f>
-        <v/>
-      </c>
-      <c r="H11" s="35">
-        <f>C11/C10-1</f>
-        <v/>
-      </c>
-      <c r="I11" s="35">
-        <f>D11/D10-1</f>
-        <v/>
-      </c>
-      <c r="J11" s="35">
-        <f>E11/E10-1</f>
-        <v/>
-      </c>
-      <c r="K11" s="35">
-        <f>F11/F10-1</f>
-        <v/>
+        <v>8012.42</v>
+      </c>
+      <c r="G11" s="45" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="H11" s="45" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="J11" s="45" t="n">
+        <v>0.0067</v>
       </c>
       <c r="L11" s="25">
-        <f>B11/B$2*100</f>
+        <f>L10*(1+G11)</f>
         <v/>
       </c>
       <c r="M11" s="25">
-        <f>C11/C$2*100</f>
+        <f>M10*(1+H11)</f>
         <v/>
       </c>
       <c r="N11" s="25">
-        <f>D11/D$2*100</f>
+        <f>N10*(1+I11)</f>
         <v/>
       </c>
       <c r="O11" s="25">
-        <f>E11/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P11" s="25">
-        <f>F11/F$2*100</f>
+        <f>O10*(1+J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>146.25</v>
+        <v>1264.5</v>
       </c>
       <c r="C12" t="n">
-        <v>381.44</v>
+        <v>709.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1216.44</v>
+        <v>396.3</v>
       </c>
       <c r="E12" t="n">
-        <v>34830</v>
+        <v>8235.040000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>24654.7</v>
-      </c>
-      <c r="G12" s="35">
-        <f>B12/B11-1</f>
-        <v/>
-      </c>
-      <c r="H12" s="35">
-        <f>C12/C11-1</f>
-        <v/>
-      </c>
-      <c r="I12" s="35">
-        <f>D12/D11-1</f>
-        <v/>
-      </c>
-      <c r="J12" s="35">
-        <f>E12/E11-1</f>
-        <v/>
-      </c>
-      <c r="K12" s="35">
-        <f>F12/F11-1</f>
-        <v/>
+        <v>69334.3</v>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="J12" s="45" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="K12" s="45" t="n">
+        <v>0.0027</v>
       </c>
       <c r="L12" s="25">
-        <f>B12/B$2*100</f>
+        <f>L11*(1+G12)</f>
         <v/>
       </c>
       <c r="M12" s="25">
-        <f>C12/C$2*100</f>
+        <f>M11*(1+H12)</f>
         <v/>
       </c>
       <c r="N12" s="25">
-        <f>D12/D$2*100</f>
+        <f>N11*(1+I12)</f>
         <v/>
       </c>
       <c r="O12" s="25">
-        <f>E12/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P12" s="25">
-        <f>F12/F$2*100</f>
+        <f>O11*(1+J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147.38</v>
+        <v>1233.3</v>
       </c>
       <c r="C13" t="n">
-        <v>392.47</v>
+        <v>146.25</v>
       </c>
       <c r="D13" t="n">
-        <v>1204.41</v>
+        <v>383.8</v>
       </c>
       <c r="E13" t="n">
-        <v>35375.9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>24894.25</v>
-      </c>
-      <c r="G13" s="35">
-        <f>B13/B12-1</f>
-        <v/>
-      </c>
-      <c r="H13" s="35">
-        <f>C13/C12-1</f>
-        <v/>
-      </c>
-      <c r="I13" s="35">
-        <f>D13/D12-1</f>
-        <v/>
-      </c>
-      <c r="J13" s="35">
-        <f>E13/E12-1</f>
-        <v/>
-      </c>
-      <c r="K13" s="35">
-        <f>F13/F12-1</f>
-        <v/>
+        <v>8245.110000000001</v>
+      </c>
+      <c r="G13" s="45" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="H13" s="45" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="I13" s="45" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="L13" s="25">
-        <f>B13/B$2*100</f>
+        <f>L12*(1+G13)</f>
         <v/>
       </c>
       <c r="M13" s="25">
-        <f>C13/C$2*100</f>
+        <f>M12*(1+H13)</f>
         <v/>
       </c>
       <c r="N13" s="25">
-        <f>D13/D$2*100</f>
+        <f>N12*(1+I13)</f>
         <v/>
       </c>
       <c r="O13" s="25">
-        <f>E13/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P13" s="25">
-        <f>F13/F$2*100</f>
+        <f>O12*(1+J13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>149.7</v>
+        <v>1221.1</v>
       </c>
       <c r="C14" t="n">
-        <v>387.7</v>
+        <v>147.38</v>
       </c>
       <c r="D14" t="n">
-        <v>1222.36</v>
+        <v>394.9</v>
       </c>
       <c r="E14" t="n">
-        <v>35393.95</v>
-      </c>
-      <c r="F14" t="n">
-        <v>25285.35</v>
-      </c>
-      <c r="G14" s="35">
-        <f>B14/B13-1</f>
-        <v/>
-      </c>
-      <c r="H14" s="35">
-        <f>C14/C13-1</f>
-        <v/>
-      </c>
-      <c r="I14" s="35">
-        <f>D14/D13-1</f>
-        <v/>
-      </c>
-      <c r="J14" s="35">
-        <f>E14/E13-1</f>
-        <v/>
-      </c>
-      <c r="K14" s="35">
-        <f>F14/F13-1</f>
-        <v/>
+        <v>8296.879999999999</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H14" s="45" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="I14" s="45" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="J14" s="45" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="L14" s="25">
-        <f>B14/B$2*100</f>
+        <f>L13*(1+G14)</f>
         <v/>
       </c>
       <c r="M14" s="25">
-        <f>C14/C$2*100</f>
+        <f>M13*(1+H14)</f>
         <v/>
       </c>
       <c r="N14" s="25">
-        <f>D14/D$2*100</f>
+        <f>N13*(1+I14)</f>
         <v/>
       </c>
       <c r="O14" s="25">
-        <f>E14/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P14" s="25">
-        <f>F14/F$2*100</f>
+        <f>O13*(1+J14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>165.98</v>
+        <v>1239.3</v>
       </c>
       <c r="C15" t="n">
-        <v>395.35</v>
+        <v>149.7</v>
       </c>
       <c r="D15" t="n">
-        <v>1293.87</v>
+        <v>390.1</v>
       </c>
       <c r="E15" t="n">
-        <v>35395.7</v>
-      </c>
-      <c r="F15" t="n">
-        <v>25709.85</v>
-      </c>
-      <c r="G15" s="35">
-        <f>B15/B14-1</f>
-        <v/>
-      </c>
-      <c r="H15" s="35">
-        <f>C15/C14-1</f>
-        <v/>
-      </c>
-      <c r="I15" s="35">
-        <f>D15/D14-1</f>
-        <v/>
-      </c>
-      <c r="J15" s="35">
-        <f>E15/E14-1</f>
-        <v/>
-      </c>
-      <c r="K15" s="35">
-        <f>F15/F14-1</f>
-        <v/>
+        <v>8297.370000000001</v>
+      </c>
+      <c r="G15" s="45" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H15" s="45" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="J15" s="45" t="n">
+        <v>0.0097</v>
       </c>
       <c r="L15" s="25">
-        <f>B15/B$2*100</f>
+        <f>L14*(1+G15)</f>
         <v/>
       </c>
       <c r="M15" s="25">
-        <f>C15/C$2*100</f>
+        <f>M14*(1+H15)</f>
         <v/>
       </c>
       <c r="N15" s="25">
-        <f>D15/D$2*100</f>
+        <f>N14*(1+I15)</f>
         <v/>
       </c>
       <c r="O15" s="25">
-        <f>E15/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P15" s="25">
-        <f>F15/F$2*100</f>
+        <f>O14*(1+J15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>167.72</v>
+        <v>1311.8</v>
       </c>
       <c r="C16" t="n">
-        <v>394.41</v>
+        <v>165.98</v>
       </c>
       <c r="D16" t="n">
-        <v>1307.67</v>
+        <v>397.8</v>
       </c>
       <c r="E16" t="n">
-        <v>35626.9</v>
+        <v>8400.530000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>25795.15</v>
-      </c>
-      <c r="G16" s="35">
-        <f>B16/B15-1</f>
-        <v/>
-      </c>
-      <c r="H16" s="35">
-        <f>C16/C15-1</f>
-        <v/>
-      </c>
-      <c r="I16" s="35">
-        <f>D16/D15-1</f>
-        <v/>
-      </c>
-      <c r="J16" s="35">
-        <f>E16/E15-1</f>
-        <v/>
-      </c>
-      <c r="K16" s="35">
-        <f>F16/F15-1</f>
-        <v/>
+        <v>69453.2</v>
+      </c>
+      <c r="G16" s="45" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="H16" s="45" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="I16" s="45" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="J16" s="45" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="K16" s="45" t="n">
+        <v>0.0049</v>
       </c>
       <c r="L16" s="25">
-        <f>B16/B$2*100</f>
+        <f>L15*(1+G16)</f>
         <v/>
       </c>
       <c r="M16" s="25">
-        <f>C16/C$2*100</f>
+        <f>M15*(1+H16)</f>
         <v/>
       </c>
       <c r="N16" s="25">
-        <f>D16/D$2*100</f>
+        <f>N15*(1+I16)</f>
         <v/>
       </c>
       <c r="O16" s="25">
-        <f>E16/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P16" s="25">
-        <f>F16/F$2*100</f>
+        <f>O15*(1+J16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>157.85</v>
+        <v>1325.8</v>
       </c>
       <c r="C17" t="n">
-        <v>402.41</v>
+        <v>167.72</v>
       </c>
       <c r="D17" t="n">
-        <v>1298.5</v>
+        <v>396.85</v>
       </c>
       <c r="E17" t="n">
-        <v>36275.95</v>
+        <v>8395.48</v>
       </c>
       <c r="F17" t="n">
-        <v>25722.1</v>
-      </c>
-      <c r="G17" s="35">
-        <f>B17/B16-1</f>
-        <v/>
-      </c>
-      <c r="H17" s="35">
-        <f>C17/C16-1</f>
-        <v/>
-      </c>
-      <c r="I17" s="35">
-        <f>D17/D16-1</f>
-        <v/>
-      </c>
-      <c r="J17" s="35">
-        <f>E17/E16-1</f>
-        <v/>
-      </c>
-      <c r="K17" s="35">
-        <f>F17/F16-1</f>
-        <v/>
+        <v>69355.89999999999</v>
+      </c>
+      <c r="G17" s="45" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="H17" s="45" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="J17" s="45" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="K17" s="45" t="n">
+        <v>-0.0011</v>
       </c>
       <c r="L17" s="25">
-        <f>B17/B$2*100</f>
+        <f>L16*(1+G17)</f>
         <v/>
       </c>
       <c r="M17" s="25">
-        <f>C17/C$2*100</f>
+        <f>M16*(1+H17)</f>
         <v/>
       </c>
       <c r="N17" s="25">
-        <f>D17/D$2*100</f>
+        <f>N16*(1+I17)</f>
         <v/>
       </c>
       <c r="O17" s="25">
-        <f>E17/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P17" s="25">
-        <f>F17/F$2*100</f>
+        <f>O16*(1+J17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>151.48</v>
+        <v>1316.5</v>
       </c>
       <c r="C18" t="n">
-        <v>390.78</v>
+        <v>157.85</v>
       </c>
       <c r="D18" t="n">
-        <v>1263.68</v>
+        <v>404.9</v>
       </c>
       <c r="E18" t="n">
-        <v>35790.3</v>
+        <v>8520.16</v>
       </c>
       <c r="F18" t="n">
-        <v>25492.3</v>
-      </c>
-      <c r="G18" s="35">
-        <f>B18/B17-1</f>
-        <v/>
-      </c>
-      <c r="H18" s="35">
-        <f>C18/C17-1</f>
-        <v/>
-      </c>
-      <c r="I18" s="35">
-        <f>D18/D17-1</f>
-        <v/>
-      </c>
-      <c r="J18" s="35">
-        <f>E18/E17-1</f>
-        <v/>
-      </c>
-      <c r="K18" s="35">
-        <f>F18/F17-1</f>
-        <v/>
+        <v>69824.75</v>
+      </c>
+      <c r="G18" s="45" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="I18" s="45" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="J18" s="45" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K18" s="45" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="L18" s="25">
-        <f>B18/B$2*100</f>
+        <f>L17*(1+G18)</f>
         <v/>
       </c>
       <c r="M18" s="25">
-        <f>C18/C$2*100</f>
+        <f>M17*(1+H18)</f>
         <v/>
       </c>
       <c r="N18" s="25">
-        <f>D18/D$2*100</f>
+        <f>N17*(1+I18)</f>
         <v/>
       </c>
       <c r="O18" s="25">
-        <f>E18/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P18" s="25">
-        <f>F18/F$2*100</f>
+        <f>O17*(1+J18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>153.91</v>
+        <v>1281.2</v>
       </c>
       <c r="C19" t="n">
-        <v>386.01</v>
+        <v>151.48</v>
       </c>
       <c r="D19" t="n">
-        <v>1283.21</v>
+        <v>393.2</v>
       </c>
       <c r="E19" t="n">
-        <v>36261.1</v>
+        <v>8052.19</v>
       </c>
       <c r="F19" t="n">
-        <v>25910.05</v>
-      </c>
-      <c r="G19" s="35">
-        <f>B19/B18-1</f>
-        <v/>
-      </c>
-      <c r="H19" s="35">
-        <f>C19/C18-1</f>
-        <v/>
-      </c>
-      <c r="I19" s="35">
-        <f>D19/D18-1</f>
-        <v/>
-      </c>
-      <c r="J19" s="35">
-        <f>E19/E18-1</f>
-        <v/>
-      </c>
-      <c r="K19" s="35">
-        <f>F19/F18-1</f>
-        <v/>
+        <v>69299.55</v>
+      </c>
+      <c r="G19" s="45" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H19" s="45" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="I19" s="45" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="J19" s="45" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="K19" s="45" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="L19" s="25">
-        <f>B19/B$2*100</f>
+        <f>L18*(1+G19)</f>
         <v/>
       </c>
       <c r="M19" s="25">
-        <f>C19/C$2*100</f>
+        <f>M18*(1+H19)</f>
         <v/>
       </c>
       <c r="N19" s="25">
-        <f>D19/D$2*100</f>
+        <f>N18*(1+I19)</f>
         <v/>
       </c>
       <c r="O19" s="25">
-        <f>E19/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P19" s="25">
-        <f>F19/F$2*100</f>
+        <f>O18*(1+J19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>149.12</v>
+        <v>1301</v>
       </c>
       <c r="C20" t="n">
-        <v>384.62</v>
+        <v>153.91</v>
       </c>
       <c r="D20" t="n">
-        <v>1273.74</v>
+        <v>388.4</v>
       </c>
       <c r="E20" t="n">
-        <v>35852.4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>26068.15</v>
-      </c>
-      <c r="G20" s="35">
-        <f>B20/B19-1</f>
-        <v/>
-      </c>
-      <c r="H20" s="35">
-        <f>C20/C19-1</f>
-        <v/>
-      </c>
-      <c r="I20" s="35">
-        <f>D20/D19-1</f>
-        <v/>
-      </c>
-      <c r="J20" s="35">
-        <f>E20/E19-1</f>
-        <v/>
-      </c>
-      <c r="K20" s="35">
-        <f>F20/F19-1</f>
-        <v/>
+        <v>8103.35</v>
+      </c>
+      <c r="G20" s="45" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="H20" s="45" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="I20" s="45" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="J20" s="45" t="n">
+        <v>0.0026</v>
       </c>
       <c r="L20" s="25">
-        <f>B20/B$2*100</f>
+        <f>L19*(1+G20)</f>
         <v/>
       </c>
       <c r="M20" s="25">
-        <f>C20/C$2*100</f>
+        <f>M19*(1+H20)</f>
         <v/>
       </c>
       <c r="N20" s="25">
-        <f>D20/D$2*100</f>
+        <f>N19*(1+I20)</f>
         <v/>
       </c>
       <c r="O20" s="25">
-        <f>E20/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P20" s="25">
-        <f>F20/F$2*100</f>
+        <f>O19*(1+J20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>147.49</v>
+        <v>1291.4</v>
       </c>
       <c r="C21" t="n">
-        <v>387.7</v>
+        <v>149.12</v>
       </c>
       <c r="D21" t="n">
-        <v>1296.53</v>
+        <v>387</v>
       </c>
       <c r="E21" t="n">
-        <v>35548.3</v>
+        <v>7996.72</v>
       </c>
       <c r="F21" t="n">
-        <v>26202.95</v>
-      </c>
-      <c r="G21" s="35">
-        <f>B21/B20-1</f>
-        <v/>
-      </c>
-      <c r="H21" s="35">
-        <f>C21/C20-1</f>
-        <v/>
-      </c>
-      <c r="I21" s="35">
-        <f>D21/D20-1</f>
-        <v/>
-      </c>
-      <c r="J21" s="35">
-        <f>E21/E20-1</f>
-        <v/>
-      </c>
-      <c r="K21" s="35">
-        <f>F21/F20-1</f>
-        <v/>
+        <v>68669.14999999999</v>
+      </c>
+      <c r="G21" s="45" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="H21" s="45" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="I21" s="45" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="J21" s="45" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="K21" s="45" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="L21" s="25">
-        <f>B21/B$2*100</f>
+        <f>L20*(1+G21)</f>
         <v/>
       </c>
       <c r="M21" s="25">
-        <f>C21/C$2*100</f>
+        <f>M20*(1+H21)</f>
         <v/>
       </c>
       <c r="N21" s="25">
-        <f>D21/D$2*100</f>
+        <f>N20*(1+I21)</f>
         <v/>
       </c>
       <c r="O21" s="25">
-        <f>E21/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P21" s="25">
-        <f>F21/F$2*100</f>
+        <f>O20*(1+J21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>143.78</v>
+        <v>1314.5</v>
       </c>
       <c r="C22" t="n">
-        <v>382.13</v>
+        <v>147.49</v>
       </c>
       <c r="D22" t="n">
-        <v>1272.26</v>
+        <v>390.1</v>
       </c>
       <c r="E22" t="n">
-        <v>34971.8</v>
+        <v>7947.46</v>
       </c>
       <c r="F22" t="n">
-        <v>26186.45</v>
-      </c>
-      <c r="G22" s="35">
-        <f>B22/B21-1</f>
-        <v/>
-      </c>
-      <c r="H22" s="35">
-        <f>C22/C21-1</f>
-        <v/>
-      </c>
-      <c r="I22" s="35">
-        <f>D22/D21-1</f>
-        <v/>
-      </c>
-      <c r="J22" s="35">
-        <f>E22/E21-1</f>
-        <v/>
-      </c>
-      <c r="K22" s="35">
-        <f>F22/F21-1</f>
-        <v/>
+        <v>68172.45</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="H22" s="45" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="I22" s="45" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="J22" s="45" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="K22" s="45" t="n">
+        <v>0.0026</v>
       </c>
       <c r="L22" s="25">
-        <f>B22/B$2*100</f>
+        <f>L21*(1+G22)</f>
         <v/>
       </c>
       <c r="M22" s="25">
-        <f>C22/C$2*100</f>
+        <f>M21*(1+H22)</f>
         <v/>
       </c>
       <c r="N22" s="25">
-        <f>D22/D$2*100</f>
+        <f>N21*(1+I22)</f>
         <v/>
       </c>
       <c r="O22" s="25">
-        <f>E22/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P22" s="25">
-        <f>F22/F$2*100</f>
+        <f>O21*(1+J22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>144.49</v>
+        <v>1289.9</v>
       </c>
       <c r="C23" t="n">
-        <v>379.6</v>
+        <v>143.78</v>
       </c>
       <c r="D23" t="n">
-        <v>1273.15</v>
+        <v>384.5</v>
       </c>
       <c r="E23" t="n">
-        <v>35039.85</v>
-      </c>
-      <c r="F23" t="n">
-        <v>26046.95</v>
-      </c>
-      <c r="G23" s="35">
-        <f>B23/B22-1</f>
-        <v/>
-      </c>
-      <c r="H23" s="35">
-        <f>C23/C22-1</f>
-        <v/>
-      </c>
-      <c r="I23" s="35">
-        <f>D23/D22-1</f>
-        <v/>
-      </c>
-      <c r="J23" s="35">
-        <f>E23/E22-1</f>
-        <v/>
-      </c>
-      <c r="K23" s="35">
-        <f>F23/F22-1</f>
-        <v/>
+        <v>7820.63</v>
+      </c>
+      <c r="G23" s="45" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H23" s="45" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="I23" s="45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="J23" s="45" t="n">
+        <v>0.0007000000000000001</v>
       </c>
       <c r="L23" s="25">
-        <f>B23/B$2*100</f>
+        <f>L22*(1+G23)</f>
         <v/>
       </c>
       <c r="M23" s="25">
-        <f>C23/C$2*100</f>
+        <f>M22*(1+H23)</f>
         <v/>
       </c>
       <c r="N23" s="25">
-        <f>D23/D$2*100</f>
+        <f>N22*(1+I23)</f>
         <v/>
       </c>
       <c r="O23" s="25">
-        <f>E23/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P23" s="25">
-        <f>F23/F$2*100</f>
+        <f>O22*(1+J23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>141.76</v>
+        <v>1290.8</v>
       </c>
       <c r="C24" t="n">
-        <v>378.21</v>
+        <v>144.49</v>
       </c>
       <c r="D24" t="n">
-        <v>1261.61</v>
+        <v>381.95</v>
       </c>
       <c r="E24" t="n">
-        <v>34796.4</v>
-      </c>
-      <c r="F24" t="n">
-        <v>25966.4</v>
-      </c>
-      <c r="G24" s="35">
-        <f>B24/B23-1</f>
-        <v/>
-      </c>
-      <c r="H24" s="35">
-        <f>C24/C23-1</f>
-        <v/>
-      </c>
-      <c r="I24" s="35">
-        <f>D24/D23-1</f>
-        <v/>
-      </c>
-      <c r="J24" s="35">
-        <f>E24/E23-1</f>
-        <v/>
-      </c>
-      <c r="K24" s="35">
-        <f>F24/F23-1</f>
-        <v/>
+        <v>7815.08</v>
+      </c>
+      <c r="G24" s="45" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="H24" s="45" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="I24" s="45" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="J24" s="45" t="n">
+        <v>0.0106</v>
       </c>
       <c r="L24" s="25">
-        <f>B24/B$2*100</f>
+        <f>L23*(1+G24)</f>
         <v/>
       </c>
       <c r="M24" s="25">
-        <f>C24/C$2*100</f>
+        <f>M23*(1+H24)</f>
         <v/>
       </c>
       <c r="N24" s="25">
-        <f>D24/D$2*100</f>
+        <f>N23*(1+I24)</f>
         <v/>
       </c>
       <c r="O24" s="25">
-        <f>E24/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P24" s="25">
-        <f>F24/F$2*100</f>
+        <f>O23*(1+J24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>142.19</v>
+        <v>1279.1</v>
       </c>
       <c r="C25" t="n">
-        <v>377.21</v>
+        <v>141.76</v>
       </c>
       <c r="D25" t="n">
-        <v>1281.44</v>
+        <v>380.55</v>
       </c>
       <c r="E25" t="n">
-        <v>35058.8</v>
-      </c>
-      <c r="F25" t="n">
-        <v>26042.3</v>
-      </c>
-      <c r="G25" s="35">
-        <f>B25/B24-1</f>
-        <v/>
-      </c>
-      <c r="H25" s="35">
-        <f>C25/C24-1</f>
-        <v/>
-      </c>
-      <c r="I25" s="35">
-        <f>D25/D24-1</f>
-        <v/>
-      </c>
-      <c r="J25" s="35">
-        <f>E25/E24-1</f>
-        <v/>
-      </c>
-      <c r="K25" s="35">
-        <f>F25/F24-1</f>
-        <v/>
+        <v>7669.53</v>
+      </c>
+      <c r="G25" s="45" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="H25" s="45" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="I25" s="45" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="J25" s="45" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="L25" s="25">
-        <f>B25/B$2*100</f>
+        <f>L24*(1+G25)</f>
         <v/>
       </c>
       <c r="M25" s="25">
-        <f>C25/C$2*100</f>
+        <f>M24*(1+H25)</f>
         <v/>
       </c>
       <c r="N25" s="25">
-        <f>D25/D$2*100</f>
+        <f>N24*(1+I25)</f>
         <v/>
       </c>
       <c r="O25" s="25">
-        <f>E25/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P25" s="25">
-        <f>F25/F$2*100</f>
+        <f>O24*(1+J25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>148.17</v>
+        <v>1299.2</v>
       </c>
       <c r="C26" t="n">
-        <v>390.68</v>
+        <v>142.19</v>
       </c>
       <c r="D26" t="n">
-        <v>1380.27</v>
+        <v>379.55</v>
       </c>
       <c r="E26" t="n">
-        <v>36275.65</v>
+        <v>7821.19</v>
       </c>
       <c r="F26" t="n">
-        <v>26328.55</v>
-      </c>
-      <c r="G26" s="35">
-        <f>B26/B25-1</f>
-        <v/>
-      </c>
-      <c r="H26" s="35">
-        <f>C26/C25-1</f>
-        <v/>
-      </c>
-      <c r="I26" s="35">
-        <f>D26/D25-1</f>
-        <v/>
-      </c>
-      <c r="J26" s="35">
-        <f>E26/E25-1</f>
-        <v/>
-      </c>
-      <c r="K26" s="35">
-        <f>F26/F25-1</f>
-        <v/>
+        <v>69096.3</v>
+      </c>
+      <c r="G26" s="45" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="H26" s="45" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="I26" s="45" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="J26" s="45" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="K26" s="45" t="n">
+        <v>0.0037</v>
       </c>
       <c r="L26" s="25">
-        <f>B26/B$2*100</f>
+        <f>L25*(1+G26)</f>
         <v/>
       </c>
       <c r="M26" s="25">
-        <f>C26/C$2*100</f>
+        <f>M25*(1+H26)</f>
         <v/>
       </c>
       <c r="N26" s="25">
-        <f>D26/D$2*100</f>
+        <f>N25*(1+I26)</f>
         <v/>
       </c>
       <c r="O26" s="25">
-        <f>E26/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P26" s="25">
-        <f>F26/F$2*100</f>
+        <f>O25*(1+J26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>141.68</v>
+        <v>1399.4</v>
       </c>
       <c r="C27" t="n">
-        <v>362.55</v>
+        <v>148.17</v>
       </c>
       <c r="D27" t="n">
-        <v>1303.24</v>
+        <v>393.1</v>
       </c>
       <c r="E27" t="n">
-        <v>34409.3</v>
-      </c>
-      <c r="F27" t="n">
-        <v>25683.3</v>
-      </c>
-      <c r="G27" s="35">
-        <f>B27/B26-1</f>
-        <v/>
-      </c>
-      <c r="H27" s="35">
-        <f>C27/C26-1</f>
-        <v/>
-      </c>
-      <c r="I27" s="35">
-        <f>D27/D26-1</f>
-        <v/>
-      </c>
-      <c r="J27" s="35">
-        <f>E27/E26-1</f>
-        <v/>
-      </c>
-      <c r="K27" s="35">
-        <f>F27/F26-1</f>
-        <v/>
+        <v>8189.48</v>
+      </c>
+      <c r="G27" s="45" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="H27" s="45" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="J27" s="45" t="n">
+        <v>0.0266</v>
       </c>
       <c r="L27" s="25">
-        <f>B27/B$2*100</f>
+        <f>L26*(1+G27)</f>
         <v/>
       </c>
       <c r="M27" s="25">
-        <f>C27/C$2*100</f>
+        <f>M26*(1+H27)</f>
         <v/>
       </c>
       <c r="N27" s="25">
-        <f>D27/D$2*100</f>
+        <f>N26*(1+I27)</f>
         <v/>
       </c>
       <c r="O27" s="25">
-        <f>E27/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P27" s="25">
-        <f>F27/F$2*100</f>
+        <f>O26*(1+J27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>142.63</v>
+        <v>1321.3</v>
       </c>
       <c r="C28" t="n">
-        <v>363.85</v>
+        <v>141.68</v>
       </c>
       <c r="D28" t="n">
-        <v>1339.14</v>
+        <v>364.8</v>
       </c>
       <c r="E28" t="n">
-        <v>34346.35</v>
-      </c>
-      <c r="F28" t="n">
-        <v>25694.35</v>
-      </c>
-      <c r="G28" s="35">
-        <f>B28/B27-1</f>
-        <v/>
-      </c>
-      <c r="H28" s="35">
-        <f>C28/C27-1</f>
-        <v/>
-      </c>
-      <c r="I28" s="35">
-        <f>D28/D27-1</f>
-        <v/>
-      </c>
-      <c r="J28" s="35">
-        <f>E28/E27-1</f>
-        <v/>
-      </c>
-      <c r="K28" s="35">
-        <f>F28/F27-1</f>
-        <v/>
+        <v>7889.58</v>
+      </c>
+      <c r="G28" s="45" t="n">
+        <v>-0.0282</v>
+      </c>
+      <c r="H28" s="45" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="I28" s="45" t="n">
+        <v>-0.0251</v>
+      </c>
+      <c r="J28" s="45" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="L28" s="25">
-        <f>B28/B$2*100</f>
+        <f>L27*(1+G28)</f>
         <v/>
       </c>
       <c r="M28" s="25">
-        <f>C28/C$2*100</f>
+        <f>M27*(1+H28)</f>
         <v/>
       </c>
       <c r="N28" s="25">
-        <f>D28/D$2*100</f>
+        <f>N27*(1+I28)</f>
         <v/>
       </c>
       <c r="O28" s="25">
-        <f>E28/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P28" s="25">
-        <f>F28/F$2*100</f>
+        <f>O27*(1+J28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>132.96</v>
+        <v>1357.7</v>
       </c>
       <c r="C29" t="n">
-        <v>343.12</v>
+        <v>142.63</v>
       </c>
       <c r="D29" t="n">
-        <v>1253.33</v>
+        <v>366.1</v>
       </c>
       <c r="E29" t="n">
-        <v>33098.3</v>
+        <v>7744.82</v>
       </c>
       <c r="F29" t="n">
-        <v>25048.65</v>
-      </c>
-      <c r="G29" s="35">
-        <f>B29/B28-1</f>
-        <v/>
-      </c>
-      <c r="H29" s="35">
-        <f>C29/C28-1</f>
-        <v/>
-      </c>
-      <c r="I29" s="35">
-        <f>D29/D28-1</f>
-        <v/>
-      </c>
-      <c r="J29" s="35">
-        <f>E29/E28-1</f>
-        <v/>
-      </c>
-      <c r="K29" s="35">
-        <f>F29/F28-1</f>
-        <v/>
+        <v>68522</v>
+      </c>
+      <c r="G29" s="45" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="H29" s="45" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I29" s="45" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="J29" s="45" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="K29" s="45" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="L29" s="25">
-        <f>B29/B$2*100</f>
+        <f>L28*(1+G29)</f>
         <v/>
       </c>
       <c r="M29" s="25">
-        <f>C29/C$2*100</f>
+        <f>M28*(1+H29)</f>
         <v/>
       </c>
       <c r="N29" s="25">
-        <f>D29/D$2*100</f>
+        <f>N28*(1+I29)</f>
         <v/>
       </c>
       <c r="O29" s="25">
-        <f>E29/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P29" s="25">
-        <f>F29/F$2*100</f>
+        <f>O28*(1+J29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>132.85</v>
+        <v>1270.7</v>
       </c>
       <c r="C30" t="n">
-        <v>352.17</v>
+        <v>132.96</v>
       </c>
       <c r="D30" t="n">
-        <v>1279.76</v>
+        <v>345.25</v>
       </c>
       <c r="E30" t="n">
-        <v>35138.05</v>
-      </c>
-      <c r="F30" t="n">
-        <v>24825.45</v>
-      </c>
-      <c r="G30" s="35">
-        <f>B30/B29-1</f>
-        <v/>
-      </c>
-      <c r="H30" s="35">
-        <f>C30/C29-1</f>
-        <v/>
-      </c>
-      <c r="I30" s="35">
-        <f>D30/D29-1</f>
-        <v/>
-      </c>
-      <c r="J30" s="35">
-        <f>E30/E29-1</f>
-        <v/>
-      </c>
-      <c r="K30" s="35">
-        <f>F30/F29-1</f>
-        <v/>
+        <v>7627.27</v>
+      </c>
+      <c r="G30" s="45" t="n">
+        <v>-0.0384</v>
+      </c>
+      <c r="H30" s="45" t="n">
+        <v>-0.0565</v>
+      </c>
+      <c r="I30" s="45" t="n">
+        <v>-0.0228</v>
+      </c>
+      <c r="J30" s="45" t="n">
+        <v>0.0166</v>
       </c>
       <c r="L30" s="25">
-        <f>B30/B$2*100</f>
+        <f>L29*(1+G30)</f>
         <v/>
       </c>
       <c r="M30" s="25">
-        <f>C30/C$2*100</f>
+        <f>M29*(1+H30)</f>
         <v/>
       </c>
       <c r="N30" s="25">
-        <f>D30/D$2*100</f>
+        <f>N29*(1+I30)</f>
         <v/>
       </c>
       <c r="O30" s="25">
-        <f>E30/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P30" s="25">
-        <f>F30/F$2*100</f>
+        <f>O29*(1+J30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>152.74</v>
+        <v>1387.6</v>
       </c>
       <c r="C31" t="n">
-        <v>363.7</v>
+        <v>135.38</v>
       </c>
       <c r="D31" t="n">
-        <v>1409.46</v>
+        <v>366.3</v>
       </c>
       <c r="E31" t="n">
-        <v>36451.7</v>
-      </c>
-      <c r="F31" t="n">
-        <v>25693.7</v>
-      </c>
-      <c r="G31" s="35">
-        <f>B31/B30-1</f>
-        <v/>
-      </c>
-      <c r="H31" s="35">
-        <f>C31/C30-1</f>
-        <v/>
-      </c>
-      <c r="I31" s="35">
-        <f>D31/D30-1</f>
-        <v/>
-      </c>
-      <c r="J31" s="35">
-        <f>E31/E30-1</f>
-        <v/>
-      </c>
-      <c r="K31" s="35">
-        <f>F31/F30-1</f>
-        <v/>
+        <v>7400.74</v>
+      </c>
+      <c r="G31" s="45" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H31" s="45" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="I31" s="45" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="J31" s="45" t="n">
+        <v>-0.0311</v>
       </c>
       <c r="L31" s="25">
-        <f>B31/B$2*100</f>
+        <f>L30*(1+G31)</f>
         <v/>
       </c>
       <c r="M31" s="25">
-        <f>C31/C$2*100</f>
+        <f>M30*(1+H31)</f>
         <v/>
       </c>
       <c r="N31" s="25">
-        <f>D31/D$2*100</f>
+        <f>N30*(1+I31)</f>
         <v/>
       </c>
       <c r="O31" s="25">
-        <f>E31/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P31" s="25">
-        <f>F31/F$2*100</f>
+        <f>O30*(1+J31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>139.9</v>
+        <v>1429</v>
       </c>
       <c r="C32" t="n">
-        <v>371.8</v>
+        <v>152.74</v>
       </c>
       <c r="D32" t="n">
-        <v>1442.6</v>
+        <v>365.95</v>
       </c>
       <c r="E32" t="n">
-        <v>35709.9</v>
+        <v>8129.9</v>
       </c>
       <c r="F32" t="n">
-        <v>25471.1</v>
-      </c>
-      <c r="G32" s="35">
-        <f>B32/B31-1</f>
-        <v/>
-      </c>
-      <c r="H32" s="35">
-        <f>C32/C31-1</f>
-        <v/>
-      </c>
-      <c r="I32" s="35">
-        <f>D32/D31-1</f>
-        <v/>
-      </c>
-      <c r="J32" s="35">
-        <f>E32/E31-1</f>
-        <v/>
-      </c>
-      <c r="K32" s="35">
-        <f>F32/F31-1</f>
-        <v/>
+        <v>68970.39999999999</v>
+      </c>
+      <c r="G32" s="45" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H32" s="45" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="I32" s="45" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J32" s="45" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="K32" s="45" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="L32" s="25">
-        <f>B32/B$2*100</f>
+        <f>L31*(1+G32)</f>
         <v/>
       </c>
       <c r="M32" s="25">
-        <f>C32/C$2*100</f>
+        <f>M31*(1+H32)</f>
         <v/>
       </c>
       <c r="N32" s="25">
-        <f>D32/D$2*100</f>
+        <f>N31*(1+I32)</f>
         <v/>
       </c>
       <c r="O32" s="25">
-        <f>E32/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P32" s="25">
-        <f>F32/F$2*100</f>
+        <f>O31*(1+J32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>142.7</v>
+        <v>1462.6</v>
       </c>
       <c r="C33" t="n">
-        <v>375.67</v>
+        <v>139.9</v>
       </c>
       <c r="D33" t="n">
-        <v>1523.32</v>
+        <v>374.1</v>
       </c>
       <c r="E33" t="n">
-        <v>36581.15</v>
+        <v>7995.14</v>
       </c>
       <c r="F33" t="n">
-        <v>25571.25</v>
-      </c>
-      <c r="G33" s="35">
-        <f>B33/B32-1</f>
-        <v/>
-      </c>
-      <c r="H33" s="35">
-        <f>C33/C32-1</f>
-        <v/>
-      </c>
-      <c r="I33" s="35">
-        <f>D33/D32-1</f>
-        <v/>
-      </c>
-      <c r="J33" s="35">
-        <f>E33/E32-1</f>
-        <v/>
-      </c>
-      <c r="K33" s="35">
-        <f>F33/F32-1</f>
-        <v/>
+        <v>70216.55</v>
+      </c>
+      <c r="G33" s="45" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="H33" s="45" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="I33" s="45" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="J33" s="45" t="n">
+        <v>-0.0237</v>
+      </c>
+      <c r="K33" s="45" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="L33" s="25">
-        <f>B33/B$2*100</f>
+        <f>L32*(1+G33)</f>
         <v/>
       </c>
       <c r="M33" s="25">
-        <f>C33/C$2*100</f>
+        <f>M32*(1+H33)</f>
         <v/>
       </c>
       <c r="N33" s="25">
-        <f>D33/D$2*100</f>
+        <f>N32*(1+I33)</f>
         <v/>
       </c>
       <c r="O33" s="25">
-        <f>E33/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P33" s="25">
-        <f>F33/F$2*100</f>
+        <f>O32*(1+J33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>140.11</v>
+        <v>1528.6</v>
       </c>
       <c r="C34" t="n">
-        <v>375.22</v>
+        <v>142.7</v>
       </c>
       <c r="D34" t="n">
-        <v>1560.99</v>
+        <v>378</v>
       </c>
       <c r="E34" t="n">
-        <v>37045.2</v>
+        <v>8184.25</v>
       </c>
       <c r="F34" t="n">
-        <v>25178.65</v>
-      </c>
-      <c r="G34" s="35">
-        <f>B34/B33-1</f>
-        <v/>
-      </c>
-      <c r="H34" s="35">
-        <f>C34/C33-1</f>
-        <v/>
-      </c>
-      <c r="I34" s="35">
-        <f>D34/D33-1</f>
-        <v/>
-      </c>
-      <c r="J34" s="35">
-        <f>E34/E33-1</f>
-        <v/>
-      </c>
-      <c r="K34" s="35">
-        <f>F34/F33-1</f>
-        <v/>
+        <v>69453.64999999999</v>
+      </c>
+      <c r="G34" s="45" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="H34" s="45" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I34" s="45" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="J34" s="45" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K34" s="45" t="n">
+        <v>0.0062</v>
       </c>
       <c r="L34" s="25">
-        <f>B34/B$2*100</f>
+        <f>L33*(1+G34)</f>
         <v/>
       </c>
       <c r="M34" s="25">
-        <f>C34/C$2*100</f>
+        <f>M33*(1+H34)</f>
         <v/>
       </c>
       <c r="N34" s="25">
-        <f>D34/D$2*100</f>
+        <f>N33*(1+I34)</f>
         <v/>
       </c>
       <c r="O34" s="25">
-        <f>E34/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P34" s="25">
-        <f>F34/F$2*100</f>
+        <f>O33*(1+J34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>138.99</v>
+        <v>1566.4</v>
       </c>
       <c r="C35" t="n">
-        <v>373.19</v>
+        <v>140.11</v>
       </c>
       <c r="D35" t="n">
-        <v>1476.19</v>
+        <v>377.55</v>
       </c>
       <c r="E35" t="n">
-        <v>36319.6</v>
-      </c>
-      <c r="F35" t="n">
-        <v>24450.45</v>
-      </c>
-      <c r="G35" s="35">
-        <f>B35/B34-1</f>
-        <v/>
-      </c>
-      <c r="H35" s="35">
-        <f>C35/C34-1</f>
-        <v/>
-      </c>
-      <c r="I35" s="35">
-        <f>D35/D34-1</f>
-        <v/>
-      </c>
-      <c r="J35" s="35">
-        <f>E35/E34-1</f>
-        <v/>
-      </c>
-      <c r="K35" s="35">
-        <f>F35/F34-1</f>
-        <v/>
+        <v>8277.83</v>
+      </c>
+      <c r="G35" s="45" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="H35" s="45" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="I35" s="45" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="J35" s="45" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="L35" s="25">
-        <f>B35/B$2*100</f>
+        <f>L34*(1+G35)</f>
         <v/>
       </c>
       <c r="M35" s="25">
-        <f>C35/C$2*100</f>
+        <f>M34*(1+H35)</f>
         <v/>
       </c>
       <c r="N35" s="25">
-        <f>D35/D$2*100</f>
+        <f>N34*(1+I35)</f>
         <v/>
       </c>
       <c r="O35" s="25">
-        <f>E35/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P35" s="25">
-        <f>F35/F$2*100</f>
+        <f>O34*(1+J35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>146.57</v>
+        <v>1481.3</v>
       </c>
       <c r="C36" t="n">
-        <v>392.52</v>
+        <v>138.99</v>
       </c>
       <c r="D36" t="n">
-        <v>1456.26</v>
+        <v>375.5</v>
       </c>
       <c r="E36" t="n">
-        <v>36071.85</v>
-      </c>
-      <c r="F36" t="n">
-        <v>23151.1</v>
-      </c>
-      <c r="G36" s="35">
-        <f>B36/B35-1</f>
-        <v/>
-      </c>
-      <c r="H36" s="35">
-        <f>C36/C35-1</f>
-        <v/>
-      </c>
-      <c r="I36" s="35">
-        <f>D36/D35-1</f>
-        <v/>
-      </c>
-      <c r="J36" s="35">
-        <f>E36/E35-1</f>
-        <v/>
-      </c>
-      <c r="K36" s="35">
-        <f>F36/F35-1</f>
-        <v/>
+        <v>8075.22</v>
+      </c>
+      <c r="G36" s="45" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="H36" s="45" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="I36" s="45" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="J36" s="45" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="L36" s="25">
-        <f>B36/B$2*100</f>
+        <f>L35*(1+G36)</f>
         <v/>
       </c>
       <c r="M36" s="25">
-        <f>C36/C$2*100</f>
+        <f>M35*(1+H36)</f>
         <v/>
       </c>
       <c r="N36" s="25">
-        <f>D36/D$2*100</f>
+        <f>N35*(1+I36)</f>
         <v/>
       </c>
       <c r="O36" s="25">
-        <f>E36/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P36" s="25">
-        <f>F36/F$2*100</f>
+        <f>O35*(1+J36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>151.54</v>
+        <v>1461.3</v>
       </c>
       <c r="C37" t="n">
-        <v>399.92</v>
+        <v>146.57</v>
       </c>
       <c r="D37" t="n">
-        <v>1445.69</v>
+        <v>394.95</v>
       </c>
       <c r="E37" t="n">
-        <v>35908.3</v>
+        <v>8221.200000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>23114.5</v>
-      </c>
-      <c r="G37" s="35">
-        <f>B37/B36-1</f>
-        <v/>
-      </c>
-      <c r="H37" s="35">
-        <f>C37/C36-1</f>
-        <v/>
-      </c>
-      <c r="I37" s="35">
-        <f>D37/D36-1</f>
-        <v/>
-      </c>
-      <c r="J37" s="35">
-        <f>E37/E36-1</f>
-        <v/>
-      </c>
-      <c r="K37" s="35">
-        <f>F37/F36-1</f>
-        <v/>
+        <v>67227.95</v>
+      </c>
+      <c r="G37" s="45" t="n">
+        <v>-0.0297</v>
+      </c>
+      <c r="H37" s="45" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="I37" s="45" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="J37" s="45" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="K37" s="45" t="n">
+        <v>0.0175</v>
       </c>
       <c r="L37" s="25">
-        <f>B37/B$2*100</f>
+        <f>L36*(1+G37)</f>
         <v/>
       </c>
       <c r="M37" s="25">
-        <f>C37/C$2*100</f>
+        <f>M36*(1+H37)</f>
         <v/>
       </c>
       <c r="N37" s="25">
-        <f>D37/D$2*100</f>
+        <f>N36*(1+I37)</f>
         <v/>
       </c>
       <c r="O37" s="25">
-        <f>E37/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P37" s="25">
-        <f>F37/F$2*100</f>
+        <f>O36*(1+J37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>153.92</v>
+        <v>1450.7</v>
       </c>
       <c r="C38" t="n">
-        <v>383.32</v>
+        <v>151.54</v>
       </c>
       <c r="D38" t="n">
-        <v>1347.63</v>
+        <v>402.4</v>
       </c>
       <c r="E38" t="n">
-        <v>35214.8</v>
+        <v>8185.49</v>
       </c>
       <c r="F38" t="n">
-        <v>22819.6</v>
-      </c>
-      <c r="G38" s="35">
-        <f>B38/B37-1</f>
-        <v/>
-      </c>
-      <c r="H38" s="35">
-        <f>C38/C37-1</f>
-        <v/>
-      </c>
-      <c r="I38" s="35">
-        <f>D38/D37-1</f>
-        <v/>
-      </c>
-      <c r="J38" s="35">
-        <f>E38/E37-1</f>
-        <v/>
-      </c>
-      <c r="K38" s="35">
-        <f>F38/F37-1</f>
-        <v/>
+        <v>63573.8</v>
+      </c>
+      <c r="G38" s="45" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="H38" s="45" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="I38" s="45" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="J38" s="45" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="K38" s="45" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="L38" s="25">
-        <f>B38/B$2*100</f>
+        <f>L37*(1+G38)</f>
         <v/>
       </c>
       <c r="M38" s="25">
-        <f>C38/C$2*100</f>
+        <f>M37*(1+H38)</f>
         <v/>
       </c>
       <c r="N38" s="25">
-        <f>D38/D$2*100</f>
+        <f>N37*(1+I38)</f>
         <v/>
       </c>
       <c r="O38" s="25">
-        <f>E38/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P38" s="25">
-        <f>F38/F$2*100</f>
+        <f>O37*(1+J38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>159.97</v>
+        <v>1471.8</v>
       </c>
       <c r="C39" t="n">
-        <v>382.63</v>
+        <v>175.81</v>
       </c>
       <c r="D39" t="n">
-        <v>1327.6</v>
+        <v>399.35</v>
       </c>
       <c r="E39" t="n">
-        <v>35299.4</v>
+        <v>8494.83</v>
       </c>
       <c r="F39" t="n">
-        <v>22713.1</v>
-      </c>
-      <c r="G39" s="35">
-        <f>B39/B38-1</f>
-        <v/>
-      </c>
-      <c r="H39" s="35">
-        <f>C39/C38-1</f>
-        <v/>
-      </c>
-      <c r="I39" s="35">
-        <f>D39/D38-1</f>
-        <v/>
-      </c>
-      <c r="J39" s="35">
-        <f>E39/E38-1</f>
-        <v/>
-      </c>
-      <c r="K39" s="35">
-        <f>F39/F38-1</f>
-        <v/>
+        <v>66268.64999999999</v>
+      </c>
+      <c r="G39" s="45" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="H39" s="45" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="I39" s="45" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="J39" s="45" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="K39" s="45" t="n">
+        <v>0.0019</v>
       </c>
       <c r="L39" s="25">
-        <f>B39/B$2*100</f>
+        <f>L38*(1+G39)</f>
         <v/>
       </c>
       <c r="M39" s="25">
-        <f>C39/C$2*100</f>
+        <f>M38*(1+H39)</f>
         <v/>
       </c>
       <c r="N39" s="25">
-        <f>D39/D$2*100</f>
+        <f>N38*(1+I39)</f>
         <v/>
       </c>
       <c r="O39" s="25">
-        <f>E39/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P39" s="25">
-        <f>F39/F$2*100</f>
+        <f>O38*(1+J39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>175.81</v>
+        <v>1565</v>
       </c>
       <c r="C40" t="n">
-        <v>396.89</v>
+        <v>198.5</v>
       </c>
       <c r="D40" t="n">
-        <v>1466.72</v>
+        <v>427.6</v>
       </c>
       <c r="E40" t="n">
-        <v>37174.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>24050.6</v>
-      </c>
-      <c r="G40" s="35">
-        <f>B40/B39-1</f>
-        <v/>
-      </c>
-      <c r="H40" s="35">
-        <f>C40/C39-1</f>
-        <v/>
-      </c>
-      <c r="I40" s="35">
-        <f>D40/D39-1</f>
-        <v/>
-      </c>
-      <c r="J40" s="35">
-        <f>E40/E39-1</f>
-        <v/>
-      </c>
-      <c r="K40" s="35">
-        <f>F40/F39-1</f>
-        <v/>
+        <v>9276.99</v>
+      </c>
+      <c r="G40" s="45" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="H40" s="45" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I40" s="45" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="J40" s="45" t="n">
+        <v>0.0165</v>
       </c>
       <c r="L40" s="25">
-        <f>B40/B$2*100</f>
+        <f>L39*(1+G40)</f>
         <v/>
       </c>
       <c r="M40" s="25">
-        <f>C40/C$2*100</f>
+        <f>M39*(1+H40)</f>
         <v/>
       </c>
       <c r="N40" s="25">
-        <f>D40/D$2*100</f>
+        <f>N39*(1+I40)</f>
         <v/>
       </c>
       <c r="O40" s="25">
-        <f>E40/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P40" s="25">
-        <f>F40/F$2*100</f>
+        <f>O39*(1+J40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>198.5</v>
+        <v>1724.4</v>
       </c>
       <c r="C41" t="n">
-        <v>424.97</v>
+        <v>225.33</v>
       </c>
       <c r="D41" t="n">
-        <v>1559.6</v>
+        <v>436</v>
       </c>
       <c r="E41" t="n">
-        <v>38881.75</v>
-      </c>
-      <c r="F41" t="n">
-        <v>24353.55</v>
-      </c>
-      <c r="G41" s="35">
-        <f>B41/B40-1</f>
-        <v/>
-      </c>
-      <c r="H41" s="35">
-        <f>C41/C40-1</f>
-        <v/>
-      </c>
-      <c r="I41" s="35">
-        <f>D41/D40-1</f>
-        <v/>
-      </c>
-      <c r="J41" s="35">
-        <f>E41/E40-1</f>
-        <v/>
-      </c>
-      <c r="K41" s="35">
-        <f>F41/F40-1</f>
-        <v/>
+        <v>9726.110000000001</v>
+      </c>
+      <c r="G41" s="45" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="H41" s="45" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="I41" s="45" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="J41" s="45" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="L41" s="25">
-        <f>B41/B$2*100</f>
+        <f>L40*(1+G41)</f>
         <v/>
       </c>
       <c r="M41" s="25">
-        <f>C41/C$2*100</f>
+        <f>M40*(1+H41)</f>
         <v/>
       </c>
       <c r="N41" s="25">
-        <f>D41/D$2*100</f>
+        <f>N40*(1+I41)</f>
         <v/>
       </c>
       <c r="O41" s="25">
-        <f>E41/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P41" s="25">
-        <f>F41/F$2*100</f>
+        <f>O40*(1+J41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>212.9</v>
+        <v>1466</v>
       </c>
       <c r="C42" t="n">
-        <v>432.32</v>
+        <v>221.33</v>
       </c>
       <c r="D42" t="n">
-        <v>1693.63</v>
+        <v>407</v>
       </c>
       <c r="E42" t="n">
-        <v>39903.75</v>
+        <v>9380.15</v>
       </c>
       <c r="F42" t="n">
-        <v>23897.95</v>
-      </c>
-      <c r="G42" s="35">
-        <f>B42/B41-1</f>
-        <v/>
-      </c>
-      <c r="H42" s="35">
-        <f>C42/C41-1</f>
-        <v/>
-      </c>
-      <c r="I42" s="35">
-        <f>D42/D41-1</f>
-        <v/>
-      </c>
-      <c r="J42" s="35">
-        <f>E42/E41-1</f>
-        <v/>
-      </c>
-      <c r="K42" s="35">
-        <f>F42/F41-1</f>
-        <v/>
+        <v>69166.39999999999</v>
+      </c>
+      <c r="G42" s="45" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="H42" s="45" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="I42" s="45" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="J42" s="45" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="K42" s="45" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="L42" s="25">
-        <f>B42/B$2*100</f>
+        <f>L41*(1+G42)</f>
         <v/>
       </c>
       <c r="M42" s="25">
-        <f>C42/C$2*100</f>
+        <f>M41*(1+H42)</f>
         <v/>
       </c>
       <c r="N42" s="25">
-        <f>D42/D$2*100</f>
+        <f>N41*(1+I42)</f>
         <v/>
       </c>
       <c r="O42" s="25">
-        <f>E42/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P42" s="25">
-        <f>F42/F$2*100</f>
+        <f>O41*(1+J42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>221.85</v>
+        <v>1498.5</v>
       </c>
       <c r="C43" t="n">
-        <v>441.81</v>
+        <v>219.32</v>
       </c>
       <c r="D43" t="n">
-        <v>1730.01</v>
+        <v>408.9</v>
       </c>
       <c r="E43" t="n">
-        <v>40771.9</v>
-      </c>
-      <c r="F43" t="n">
-        <v>23997.55</v>
-      </c>
-      <c r="G43" s="35">
-        <f>B43/B42-1</f>
-        <v/>
-      </c>
-      <c r="H43" s="35">
-        <f>C43/C42-1</f>
-        <v/>
-      </c>
-      <c r="I43" s="35">
-        <f>D43/D42-1</f>
-        <v/>
-      </c>
-      <c r="J43" s="35">
-        <f>E43/E42-1</f>
-        <v/>
-      </c>
-      <c r="K43" s="35">
-        <f>F43/F42-1</f>
-        <v/>
+        <v>9345.34</v>
+      </c>
+      <c r="G43" s="45" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H43" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="45" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="J43" s="45" t="n">
+        <v>-0.004</v>
       </c>
       <c r="L43" s="25">
-        <f>B43/B$2*100</f>
+        <f>L42*(1+G43)</f>
         <v/>
       </c>
       <c r="M43" s="25">
-        <f>C43/C$2*100</f>
+        <f>M42*(1+H43)</f>
         <v/>
       </c>
       <c r="N43" s="25">
-        <f>D43/D$2*100</f>
+        <f>N42*(1+I43)</f>
         <v/>
       </c>
       <c r="O43" s="25">
-        <f>E43/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P43" s="25">
-        <f>F43/F$2*100</f>
+        <f>O42*(1+J43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>225.33</v>
+        <v>1420.3</v>
       </c>
       <c r="C44" t="n">
-        <v>433.31</v>
+        <v>243.37</v>
       </c>
       <c r="D44" t="n">
-        <v>1718.45</v>
+        <v>420.75</v>
       </c>
       <c r="E44" t="n">
-        <v>40795.8</v>
-      </c>
-      <c r="F44" t="n">
-        <v>24176.15</v>
-      </c>
-      <c r="G44" s="35">
-        <f>B44/B43-1</f>
-        <v/>
-      </c>
-      <c r="H44" s="35">
-        <f>C44/C43-1</f>
-        <v/>
-      </c>
-      <c r="I44" s="35">
-        <f>D44/D43-1</f>
-        <v/>
-      </c>
-      <c r="J44" s="35">
-        <f>E44/E43-1</f>
-        <v/>
-      </c>
-      <c r="K44" s="35">
-        <f>F44/F43-1</f>
-        <v/>
+        <v>9637.129999999999</v>
+      </c>
+      <c r="G44" s="45" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="H44" s="45" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="I44" s="45" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="J44" s="45" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="L44" s="25">
-        <f>B44/B$2*100</f>
+        <f>L43*(1+G44)</f>
         <v/>
       </c>
       <c r="M44" s="25">
-        <f>C44/C$2*100</f>
+        <f>M43*(1+H44)</f>
         <v/>
       </c>
       <c r="N44" s="25">
-        <f>D44/D$2*100</f>
+        <f>N43*(1+I44)</f>
         <v/>
       </c>
       <c r="O44" s="25">
-        <f>E44/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P44" s="25">
-        <f>F44/F$2*100</f>
+        <f>O43*(1+J44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>221.33</v>
+        <v>1460.1</v>
       </c>
       <c r="C45" t="n">
-        <v>404.49</v>
+        <v>232.6</v>
       </c>
       <c r="D45" t="n">
-        <v>1460.94</v>
+        <v>409.2</v>
       </c>
       <c r="E45" t="n">
-        <v>39816.85</v>
-      </c>
-      <c r="F45" t="n">
-        <v>23643.5</v>
-      </c>
-      <c r="G45" s="35">
-        <f>B45/B44-1</f>
-        <v/>
-      </c>
-      <c r="H45" s="35">
-        <f>C45/C44-1</f>
-        <v/>
-      </c>
-      <c r="I45" s="35">
-        <f>D45/D44-1</f>
-        <v/>
-      </c>
-      <c r="J45" s="35">
-        <f>E45/E44-1</f>
-        <v/>
-      </c>
-      <c r="K45" s="35">
-        <f>F45/F44-1</f>
-        <v/>
+        <v>9426.190000000001</v>
+      </c>
+      <c r="G45" s="45" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H45" s="45" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="I45" s="45" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="J45" s="45" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="L45" s="25">
-        <f>B45/B$2*100</f>
+        <f>L44*(1+G45)</f>
         <v/>
       </c>
       <c r="M45" s="25">
-        <f>C45/C$2*100</f>
+        <f>M44*(1+H45)</f>
         <v/>
       </c>
       <c r="N45" s="25">
-        <f>D45/D$2*100</f>
+        <f>N44*(1+I45)</f>
         <v/>
       </c>
       <c r="O45" s="25">
-        <f>E45/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P45" s="25">
-        <f>F45/F$2*100</f>
+        <f>O44*(1+J45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>219.32</v>
+        <v>1392</v>
       </c>
       <c r="C46" t="n">
-        <v>406.38</v>
+        <v>223.07</v>
       </c>
       <c r="D46" t="n">
-        <v>1493.33</v>
+        <v>393.55</v>
       </c>
       <c r="E46" t="n">
-        <v>40237.6</v>
-      </c>
-      <c r="F46" t="n">
-        <v>23719.3</v>
-      </c>
-      <c r="G46" s="35">
-        <f>B46/B45-1</f>
-        <v/>
-      </c>
-      <c r="H46" s="35">
-        <f>C46/C45-1</f>
-        <v/>
-      </c>
-      <c r="I46" s="35">
-        <f>D46/D45-1</f>
-        <v/>
-      </c>
-      <c r="J46" s="35">
-        <f>E46/E45-1</f>
-        <v/>
-      </c>
-      <c r="K46" s="35">
-        <f>F46/F45-1</f>
-        <v/>
+        <v>9140.51</v>
+      </c>
+      <c r="G46" s="45" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="H46" s="45" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="I46" s="45" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="J46" s="45" t="n">
+        <v>0.0137</v>
       </c>
       <c r="L46" s="25">
-        <f>B46/B$2*100</f>
+        <f>L45*(1+G46)</f>
         <v/>
       </c>
       <c r="M46" s="25">
-        <f>C46/C$2*100</f>
+        <f>M45*(1+H46)</f>
         <v/>
       </c>
       <c r="N46" s="25">
-        <f>D46/D$2*100</f>
+        <f>N45*(1+I46)</f>
         <v/>
       </c>
       <c r="O46" s="25">
-        <f>E46/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P46" s="25">
-        <f>F46/F$2*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>243.37</v>
-      </c>
-      <c r="C47" t="n">
-        <v>418.16</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1415.4</v>
-      </c>
-      <c r="E47" t="n">
-        <v>40878</v>
-      </c>
-      <c r="F47" t="n">
-        <v>23547.75</v>
-      </c>
-      <c r="G47" s="35">
-        <f>B47/B46-1</f>
-        <v/>
-      </c>
-      <c r="H47" s="35">
-        <f>C47/C46-1</f>
-        <v/>
-      </c>
-      <c r="I47" s="35">
-        <f>D47/D46-1</f>
-        <v/>
-      </c>
-      <c r="J47" s="35">
-        <f>E47/E46-1</f>
-        <v/>
-      </c>
-      <c r="K47" s="35">
-        <f>F47/F46-1</f>
-        <v/>
-      </c>
-      <c r="L47" s="25">
-        <f>B47/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M47" s="25">
-        <f>C47/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N47" s="25">
-        <f>D47/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O47" s="25">
-        <f>E47/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P47" s="25">
-        <f>F47/F$2*100</f>
+        <f>O45*(1+J46)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>232.6</v>
-      </c>
-      <c r="C48" t="n">
-        <v>406.68</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1455.06</v>
-      </c>
-      <c r="E48" t="n">
-        <v>40346.1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>23366.7</v>
-      </c>
-      <c r="G48" s="35">
-        <f>B48/B47-1</f>
-        <v/>
-      </c>
-      <c r="H48" s="35">
-        <f>C48/C47-1</f>
-        <v/>
-      </c>
-      <c r="I48" s="35">
-        <f>D48/D47-1</f>
-        <v/>
-      </c>
-      <c r="J48" s="35">
-        <f>E48/E47-1</f>
-        <v/>
-      </c>
-      <c r="K48" s="35">
-        <f>F48/F47-1</f>
-        <v/>
-      </c>
-      <c r="L48" s="25">
-        <f>B48/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M48" s="25">
-        <f>C48/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N48" s="25">
-        <f>D48/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O48" s="25">
-        <f>E48/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P48" s="25">
-        <f>F48/F$2*100</f>
-        <v/>
+      <c r="A48" s="46" t="inlineStr">
+        <is>
+          <t>Nifty Next 50 — full supplied series (sparse/irregular, NOT weekly-aligned to the grid above; used for its own period stats and, where dates coincide, the beta calc on Sheet 11)</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>223.07</v>
-      </c>
-      <c r="C49" t="n">
-        <v>391.13</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1387.2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>39244.45</v>
-      </c>
-      <c r="F49" t="n">
-        <v>23622.9</v>
-      </c>
-      <c r="G49" s="35">
-        <f>B49/B48-1</f>
-        <v/>
-      </c>
-      <c r="H49" s="35">
-        <f>C49/C48-1</f>
-        <v/>
-      </c>
-      <c r="I49" s="35">
-        <f>D49/D48-1</f>
-        <v/>
-      </c>
-      <c r="J49" s="35">
-        <f>E49/E48-1</f>
-        <v/>
-      </c>
-      <c r="K49" s="35">
-        <f>F49/F48-1</f>
-        <v/>
-      </c>
-      <c r="L49" s="25">
-        <f>B49/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M49" s="25">
-        <f>C49/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N49" s="25">
-        <f>D49/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O49" s="25">
-        <f>E49/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P49" s="25">
-        <f>F49/F$2*100</f>
-        <v/>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Nifty Next 50 Close</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Return (as given, sourced)</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>231.76</v>
-      </c>
-      <c r="C50" t="n">
-        <v>399.87</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1438.4</v>
-      </c>
-      <c r="E50" t="n">
-        <v>40548.1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>24013.1</v>
-      </c>
-      <c r="G50" s="35">
-        <f>B50/B49-1</f>
-        <v/>
-      </c>
-      <c r="H50" s="35">
-        <f>C50/C49-1</f>
-        <v/>
-      </c>
-      <c r="I50" s="35">
-        <f>D50/D49-1</f>
-        <v/>
-      </c>
-      <c r="J50" s="35">
-        <f>E50/E49-1</f>
-        <v/>
-      </c>
-      <c r="K50" s="35">
-        <f>F50/F49-1</f>
-        <v/>
-      </c>
-      <c r="L50" s="25">
-        <f>B50/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M50" s="25">
-        <f>C50/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N50" s="25">
-        <f>D50/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O50" s="25">
-        <f>E50/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P50" s="25">
-        <f>F50/F$2*100</f>
-        <v/>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>68998.2</v>
+      </c>
+      <c r="C50" s="45" t="n">
+        <v>0.0042</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>229.27</v>
-      </c>
-      <c r="C51" t="n">
-        <v>388.95</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1413.7</v>
-      </c>
-      <c r="E51" t="n">
-        <v>39637</v>
-      </c>
-      <c r="F51" t="n">
-        <v>24056</v>
-      </c>
-      <c r="G51" s="35">
-        <f>B51/B50-1</f>
-        <v/>
-      </c>
-      <c r="H51" s="35">
-        <f>C51/C50-1</f>
-        <v/>
-      </c>
-      <c r="I51" s="35">
-        <f>D51/D50-1</f>
-        <v/>
-      </c>
-      <c r="J51" s="35">
-        <f>E51/E50-1</f>
-        <v/>
-      </c>
-      <c r="K51" s="35">
-        <f>F51/F50-1</f>
-        <v/>
-      </c>
-      <c r="L51" s="25">
-        <f>B51/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M51" s="25">
-        <f>C51/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N51" s="25">
-        <f>D51/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O51" s="25">
-        <f>E51/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P51" s="25">
-        <f>F51/F$2*100</f>
-        <v/>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>68725.8</v>
+      </c>
+      <c r="C51" s="45" t="n">
+        <v>0.0017</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>221.79</v>
-      </c>
-      <c r="C52" t="n">
-        <v>375.2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1366.5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>39178.6</v>
-      </c>
-      <c r="F52" t="n">
-        <v>24270.85</v>
-      </c>
-      <c r="G52" s="35">
-        <f>B52/B51-1</f>
-        <v/>
-      </c>
-      <c r="H52" s="35">
-        <f>C52/C51-1</f>
-        <v/>
-      </c>
-      <c r="I52" s="35">
-        <f>D52/D51-1</f>
-        <v/>
-      </c>
-      <c r="J52" s="35">
-        <f>E52/E51-1</f>
-        <v/>
-      </c>
-      <c r="K52" s="35">
-        <f>F52/F51-1</f>
-        <v/>
-      </c>
-      <c r="L52" s="25">
-        <f>B52/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M52" s="25">
-        <f>C52/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N52" s="25">
-        <f>D52/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O52" s="25">
-        <f>E52/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P52" s="25">
-        <f>F52/F$2*100</f>
-        <v/>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n">
+        <v>68711.45</v>
+      </c>
+      <c r="C52" s="45" t="n">
+        <v>-0.0023</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>218.45</v>
-      </c>
-      <c r="C53" t="n">
-        <v>381.3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1419.4</v>
-      </c>
-      <c r="E53" t="n">
-        <v>39242.05</v>
-      </c>
-      <c r="F53" t="n">
-        <v>24206.9</v>
-      </c>
-      <c r="G53" s="35">
-        <f>B53/B52-1</f>
-        <v/>
-      </c>
-      <c r="H53" s="35">
-        <f>C53/C52-1</f>
-        <v/>
-      </c>
-      <c r="I53" s="35">
-        <f>D53/D52-1</f>
-        <v/>
-      </c>
-      <c r="J53" s="35">
-        <f>E53/E52-1</f>
-        <v/>
-      </c>
-      <c r="K53" s="35">
-        <f>F53/F52-1</f>
-        <v/>
-      </c>
-      <c r="L53" s="25">
-        <f>B53/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M53" s="25">
-        <f>C53/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N53" s="25">
-        <f>D53/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O53" s="25">
-        <f>E53/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P53" s="25">
-        <f>F53/F$2*100</f>
-        <v/>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>68207.3</v>
+      </c>
+      <c r="C53" s="45" t="n">
+        <v>-0.0023</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>218.97</v>
-      </c>
-      <c r="C54" t="n">
-        <v>380.9</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1441.1</v>
-      </c>
-      <c r="E54" t="n">
-        <v>39381.25</v>
-      </c>
-      <c r="F54" t="n">
-        <v>24078.5</v>
-      </c>
-      <c r="G54" s="35">
-        <f>B54/B53-1</f>
-        <v/>
-      </c>
-      <c r="H54" s="35">
-        <f>C54/C53-1</f>
-        <v/>
-      </c>
-      <c r="I54" s="35">
-        <f>D54/D53-1</f>
-        <v/>
-      </c>
-      <c r="J54" s="35">
-        <f>E54/E53-1</f>
-        <v/>
-      </c>
-      <c r="K54" s="35">
-        <f>F54/F53-1</f>
-        <v/>
-      </c>
-      <c r="L54" s="25">
-        <f>B54/B$2*100</f>
-        <v/>
-      </c>
-      <c r="M54" s="25">
-        <f>C54/C$2*100</f>
-        <v/>
-      </c>
-      <c r="N54" s="25">
-        <f>D54/D$2*100</f>
-        <v/>
-      </c>
-      <c r="O54" s="25">
-        <f>E54/E$2*100</f>
-        <v/>
-      </c>
-      <c r="P54" s="25">
-        <f>F54/F$2*100</f>
-        <v/>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="n">
+        <v>66338.10000000001</v>
+      </c>
+      <c r="C54" s="45" t="n">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n">
+        <v>66800.35000000001</v>
+      </c>
+      <c r="C55" s="45" t="n">
+        <v>-0.0135</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="n">
+        <v>67017.75</v>
+      </c>
+      <c r="C56" s="45" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>69334.3</v>
+      </c>
+      <c r="C57" s="45" t="n">
+        <v>0.0027</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="n">
+        <v>68207.85000000001</v>
+      </c>
+      <c r="C58" s="45" t="n">
+        <v>-0.0053</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>69453.2</v>
+      </c>
+      <c r="C59" s="45" t="n">
+        <v>0.0049</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B60" s="21" t="n">
+        <v>69355.89999999999</v>
+      </c>
+      <c r="C60" s="45" t="n">
+        <v>-0.0011</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="n">
+        <v>69824.75</v>
+      </c>
+      <c r="C61" s="45" t="n">
+        <v>-0.0037</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="B62" s="21" t="n">
+        <v>69299.55</v>
+      </c>
+      <c r="C62" s="45" t="n">
+        <v>-0.0124</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n">
+        <v>69635.85000000001</v>
+      </c>
+      <c r="C63" s="45" t="n">
+        <v>-0.0001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="n">
+        <v>68669.14999999999</v>
+      </c>
+      <c r="C64" s="45" t="n">
+        <v>-0.0129</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B65" s="21" t="n">
+        <v>67997.45</v>
+      </c>
+      <c r="C65" s="45" t="n">
+        <v>-0.0098</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B66" s="21" t="n">
+        <v>68172.45</v>
+      </c>
+      <c r="C66" s="45" t="n">
+        <v>0.0026</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B67" s="21" t="n">
+        <v>69096.3</v>
+      </c>
+      <c r="C67" s="45" t="n">
+        <v>0.0037</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B68" s="21" t="n">
+        <v>68522</v>
+      </c>
+      <c r="C68" s="45" t="n">
+        <v>-0.0026</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B69" s="21" t="n">
+        <v>67073.2</v>
+      </c>
+      <c r="C69" s="45" t="n">
+        <v>0.0107</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B70" s="21" t="n">
+        <v>68970.39999999999</v>
+      </c>
+      <c r="C70" s="45" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B71" s="21" t="n">
+        <v>70216.55</v>
+      </c>
+      <c r="C71" s="45" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B72" s="21" t="n">
+        <v>69453.64999999999</v>
+      </c>
+      <c r="C72" s="45" t="n">
+        <v>0.0062</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B73" s="21" t="n">
+        <v>67227.95</v>
+      </c>
+      <c r="C73" s="45" t="n">
+        <v>0.0175</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="n">
+        <v>64462.3</v>
+      </c>
+      <c r="C74" s="45" t="n">
+        <v>-0.0035</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="n">
+        <v>63573.8</v>
+      </c>
+      <c r="C75" s="45" t="n">
+        <v>-0.0319</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="n">
+        <v>66268.64999999999</v>
+      </c>
+      <c r="C76" s="45" t="n">
+        <v>0.0019</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B77" s="21" t="n">
+        <v>69166.39999999999</v>
+      </c>
+      <c r="C77" s="45" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="n">
+        <v>71798.64999999999</v>
+      </c>
+      <c r="C78" s="45" t="n">
+        <v>0.0016</v>
       </c>
     </row>
   </sheetData>
@@ -9017,7 +8315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9040,121 +8338,116 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118.93</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>114</v>
+        <v>116.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Q1 FY26 results + 1:5 split announced</t>
-        </is>
+        <v>120.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.38</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Q1 FY26 results + 1:5 split announced</t>
-        </is>
+        <v>118.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116.81</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118.86</v>
+        <v>113.4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Q1 FY26 results + 1:5 split announced</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>120.13</v>
+        <v>118.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121.94</v>
+        <v>120.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129.71</v>
+        <v>121.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141.88</v>
+        <v>129.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>146.25</v>
+        <v>141.88</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9165,51 +8458,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>147.38</v>
+        <v>146.25</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1:5 stock split effective</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>149.7</v>
+        <v>147.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>165.98</v>
+        <v>149.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>167.72</v>
+        <v>165.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>157.85</v>
+        <v>167.72</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9220,11 +8518,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>151.48</v>
+        <v>157.85</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -9235,26 +8533,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>153.91</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Assam 3,200 MW LoA (~₹48,000cr)</t>
-        </is>
+        <v>151.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>149.12</v>
+        <v>153.91</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -9265,11 +8558,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>147.49</v>
+        <v>149.12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -9280,111 +8573,111 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>143.78</v>
+        <v>147.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>144.49</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>141.76</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>142.19</v>
+        <v>141.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>148.17</v>
+        <v>142.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>141.68</v>
+        <v>148.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>142.63</v>
+        <v>141.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>132.96</v>
+        <v>142.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>132.85</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>152.74</v>
+        <v>135.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>139.9</v>
+        <v>152.74</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -9395,11 +8688,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>142.7</v>
+        <v>139.9</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -9410,46 +8703,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>140.11</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>138.99</v>
+        <v>140.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>146.57</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>NCLT approves JPVL plan</t>
-        </is>
+        <v>138.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>151.54</v>
+        <v>146.57</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -9460,196 +8748,101 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>153.92</v>
+        <v>151.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>159.97</v>
+        <v>175.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>175.81</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>198.5</v>
+        <v>225.33</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>52-wk high ₹234 intraday</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>212.9</v>
+        <v>221.33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>221.85</v>
+        <v>219.32</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Q4/FY26 results: PAT ₹12,971cr</t>
+          <t>Profit-booking after ~100% 1-yr run</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>225.33</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Q4/FY26 results: PAT ₹12,971cr</t>
-        </is>
+        <v>243.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>221.33</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>52-wk high ₹234 intraday</t>
-        </is>
+        <v>232.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>219.32</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Profit-booking after ~100% 1-yr run</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>243.37</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Profit-booking after ~100% 1-yr run</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>232.6</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
         <v>223.07</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>231.76</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>229.27</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>221.79</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>218.45</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>218.97</v>
       </c>
     </row>
   </sheetData>
@@ -10191,7 +9384,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="13">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Consolidated-vs-Standalone audit (line-by-line re-verification)</t>
         </is>
@@ -10786,46 +9979,46 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23 (AR_22088), FY23-24 (AR_24072), FY24-25 (ADANIPOWER-2025) and FY25-26 (AR_29298) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them — click any total to see exactly what it adds up.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="50" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
@@ -10837,7 +10030,7 @@
       <c r="F5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
@@ -10849,7 +10042,7 @@
       <c r="F6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
@@ -10871,7 +10064,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Right-of-use Assets</t>
         </is>
@@ -10887,7 +10080,7 @@
       <c r="F8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
@@ -10909,7 +10102,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Investment Property</t>
         </is>
@@ -10931,7 +10124,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
@@ -10953,7 +10146,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
@@ -10975,7 +10168,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Investments (Non-current)</t>
         </is>
@@ -10997,7 +10190,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
@@ -11011,7 +10204,7 @@
       <c r="F14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
@@ -11033,7 +10226,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
@@ -11051,7 +10244,7 @@
       <c r="F16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
@@ -11071,7 +10264,7 @@
       <c r="F17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
@@ -11098,29 +10291,29 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="53">
         <f>B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="53">
         <f>C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <f>D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
@@ -11132,7 +10325,7 @@
       <c r="F20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
@@ -11154,7 +10347,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
@@ -11176,7 +10369,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Trade Receivables</t>
         </is>
@@ -11198,7 +10391,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
@@ -11220,7 +10413,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
@@ -11242,7 +10435,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="52" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
@@ -11264,7 +10457,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="51" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
@@ -11286,7 +10479,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="52" t="inlineStr">
         <is>
           <t>Current Tax Assets (Net)</t>
         </is>
@@ -11304,7 +10497,7 @@
       <c r="F28" s="38" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="51" t="inlineStr">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
@@ -11331,29 +10524,29 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B30" s="52">
+      <c r="B30" s="53">
         <f>B21+B22+B23+B24+B25+B26+B27+B28+B29</f>
         <v/>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="53">
         <f>C21+C22+C23+C24+C25+C26+C27+C28+C29</f>
         <v/>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="53">
         <f>D21+D22+D23+D24+D25+D26+D27+D28+D29</f>
         <v/>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="53">
         <f>E21+E22+E23+E24+E25+E26+E27+E28+E29</f>
         <v/>
       </c>
-      <c r="F30" s="52">
+      <c r="F30" s="53">
         <f>F21+F22+F23+F24+F25+F26+F27+F28+F29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="51" t="inlineStr">
+      <c r="A31" s="52" t="inlineStr">
         <is>
           <t>Assets Classified as Held for Sale</t>
         </is>
@@ -11376,29 +10569,29 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B32" s="52">
+      <c r="B32" s="53">
         <f>B19+B30+B31</f>
         <v/>
       </c>
-      <c r="C32" s="52">
+      <c r="C32" s="53">
         <f>C19+C30+C31</f>
         <v/>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="53">
         <f>D19+D30+D31</f>
         <v/>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="53">
         <f>E19+E30+E31</f>
         <v/>
       </c>
-      <c r="F32" s="52">
+      <c r="F32" s="53">
         <f>F19+F30+F31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="51" t="inlineStr">
         <is>
           <t>EQUITY AND LIABILITIES</t>
         </is>
@@ -11410,7 +10603,7 @@
       <c r="F33" s="38" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="inlineStr">
+      <c r="A34" s="52" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
@@ -11432,7 +10625,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>Instrument entirely Equity in nature / Unsecured Perpetual Securities</t>
         </is>
@@ -11454,7 +10647,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="51" t="inlineStr">
+      <c r="A36" s="52" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
@@ -11481,29 +10674,29 @@
           <t>Equity attributable to equity holders of the parent</t>
         </is>
       </c>
-      <c r="B37" s="52">
+      <c r="B37" s="53">
         <f>B34+B35+B36</f>
         <v/>
       </c>
-      <c r="C37" s="52">
+      <c r="C37" s="53">
         <f>C34+C35+C36</f>
         <v/>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="53">
         <f>D34+D35+D36</f>
         <v/>
       </c>
-      <c r="E37" s="52">
+      <c r="E37" s="53">
         <f>E34+E35+E36</f>
         <v/>
       </c>
-      <c r="F37" s="52">
+      <c r="F37" s="53">
         <f>F34+F35+F36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="inlineStr">
+      <c r="A38" s="52" t="inlineStr">
         <is>
           <t>Non-Controlling Interests</t>
         </is>
@@ -11530,29 +10723,29 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B39" s="52">
+      <c r="B39" s="53">
         <f>B37+B38</f>
         <v/>
       </c>
-      <c r="C39" s="52">
+      <c r="C39" s="53">
         <f>C37+C38</f>
         <v/>
       </c>
-      <c r="D39" s="52">
+      <c r="D39" s="53">
         <f>D37+D38</f>
         <v/>
       </c>
-      <c r="E39" s="52">
+      <c r="E39" s="53">
         <f>E37+E38</f>
         <v/>
       </c>
-      <c r="F39" s="52">
+      <c r="F39" s="53">
         <f>F37+F38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="50" t="inlineStr">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
@@ -11564,7 +10757,7 @@
       <c r="F40" s="38" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="51" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
@@ -11586,7 +10779,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="51" t="inlineStr">
+      <c r="A42" s="52" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
@@ -11608,7 +10801,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="51" t="inlineStr">
+      <c r="A43" s="52" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
@@ -11630,7 +10823,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="51" t="inlineStr">
+      <c r="A44" s="52" t="inlineStr">
         <is>
           <t>Provisions (Non-current)</t>
         </is>
@@ -11652,7 +10845,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="51" t="inlineStr">
+      <c r="A45" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
@@ -11674,7 +10867,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="51" t="inlineStr">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
@@ -11701,29 +10894,29 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B47" s="52">
+      <c r="B47" s="53">
         <f>B41+B42+B43+B44+B45+B46</f>
         <v/>
       </c>
-      <c r="C47" s="52">
+      <c r="C47" s="53">
         <f>C41+C42+C43+C44+C45+C46</f>
         <v/>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="53">
         <f>D41+D42+D43+D44+D45+D46</f>
         <v/>
       </c>
-      <c r="E47" s="52">
+      <c r="E47" s="53">
         <f>E41+E42+E43+E44+E45+E46</f>
         <v/>
       </c>
-      <c r="F47" s="52">
+      <c r="F47" s="53">
         <f>F41+F42+F43+F44+F45+F46</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="50" t="inlineStr">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
@@ -11735,7 +10928,7 @@
       <c r="F48" s="38" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="51" t="inlineStr">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
@@ -11757,7 +10950,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="51" t="inlineStr">
+      <c r="A50" s="52" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
@@ -11779,7 +10972,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="51" t="inlineStr">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>Trade Payables — micro/small enterprises</t>
         </is>
@@ -11801,7 +10994,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="51" t="inlineStr">
+      <c r="A52" s="52" t="inlineStr">
         <is>
           <t>Trade Payables — other creditors</t>
         </is>
@@ -11823,7 +11016,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="51" t="inlineStr">
+      <c r="A53" s="52" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
@@ -11845,7 +11038,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="51" t="inlineStr">
+      <c r="A54" s="52" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
@@ -11867,7 +11060,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="51" t="inlineStr">
+      <c r="A55" s="52" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
@@ -11889,7 +11082,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="51" t="inlineStr">
+      <c r="A56" s="52" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
@@ -11916,23 +11109,23 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B57" s="52">
+      <c r="B57" s="53">
         <f>B49+B50+B51+B52+B53+B54+B55+B56</f>
         <v/>
       </c>
-      <c r="C57" s="52">
+      <c r="C57" s="53">
         <f>C49+C50+C51+C52+C53+C54+C55+C56</f>
         <v/>
       </c>
-      <c r="D57" s="52">
+      <c r="D57" s="53">
         <f>D49+D50+D51+D52+D53+D54+D55+D56</f>
         <v/>
       </c>
-      <c r="E57" s="52">
+      <c r="E57" s="53">
         <f>E49+E50+E51+E52+E53+E54+E55+E56</f>
         <v/>
       </c>
-      <c r="F57" s="52">
+      <c r="F57" s="53">
         <f>F49+F50+F51+F52+F53+F54+F55+F56</f>
         <v/>
       </c>
@@ -11943,23 +11136,23 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B58" s="52">
+      <c r="B58" s="53">
         <f>B47+B57</f>
         <v/>
       </c>
-      <c r="C58" s="52">
+      <c r="C58" s="53">
         <f>C47+C57</f>
         <v/>
       </c>
-      <c r="D58" s="52">
+      <c r="D58" s="53">
         <f>D47+D57</f>
         <v/>
       </c>
-      <c r="E58" s="52">
+      <c r="E58" s="53">
         <f>E47+E57</f>
         <v/>
       </c>
-      <c r="F58" s="52">
+      <c r="F58" s="53">
         <f>F47+F57</f>
         <v/>
       </c>
@@ -11970,23 +11163,23 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B59" s="52">
+      <c r="B59" s="53">
         <f>B39+B58</f>
         <v/>
       </c>
-      <c r="C59" s="52">
+      <c r="C59" s="53">
         <f>C39+C58</f>
         <v/>
       </c>
-      <c r="D59" s="52">
+      <c r="D59" s="53">
         <f>D39+D58</f>
         <v/>
       </c>
-      <c r="E59" s="52">
+      <c r="E59" s="53">
         <f>E39+E58</f>
         <v/>
       </c>
-      <c r="F59" s="52">
+      <c r="F59" s="53">
         <f>F39+F58</f>
         <v/>
       </c>
@@ -12025,46 +11218,46 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Sources: Adani Power Ltd Integrated Annual Reports FY22-23, FY23-24, FY24-25 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="50" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
@@ -12076,7 +11269,7 @@
       <c r="F5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
@@ -12098,7 +11291,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
@@ -12125,29 +11318,29 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B8" s="52">
+      <c r="B8" s="53">
         <f>B6+B7</f>
         <v/>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="53">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="53">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="53">
         <f>E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="52">
+      <c r="F8" s="53">
         <f>F6+F7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
@@ -12159,7 +11352,7 @@
       <c r="F9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
@@ -12181,7 +11374,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Purchase of Stock-in-trade / Power for resale</t>
         </is>
@@ -12203,7 +11396,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Transmission Charges</t>
         </is>
@@ -12225,7 +11418,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
@@ -12247,7 +11440,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>Finance Costs (net)</t>
         </is>
@@ -12269,7 +11462,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Depreciation and Amortisation Expense</t>
         </is>
@@ -12291,7 +11484,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
@@ -12318,23 +11511,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B17" s="52">
+      <c r="B17" s="53">
         <f>B10+B11+B12+B13+B14+B15+B16</f>
         <v/>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="53">
         <f>C10+C11+C12+C13+C14+C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="53">
         <f>D10+D11+D12+D13+D14+D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="53">
         <f>E10+E11+E12+E13+E14+E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="53">
         <f>F10+F11+F12+F13+F14+F15+F16</f>
         <v/>
       </c>
@@ -12345,29 +11538,29 @@
           <t>Profit before share of JV profit and tax</t>
         </is>
       </c>
-      <c r="B18" s="52">
+      <c r="B18" s="53">
         <f>B8-B17</f>
         <v/>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="53">
         <f>C8-C17</f>
         <v/>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="53">
         <f>D8-D17</f>
         <v/>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="53">
         <f>E8-E17</f>
         <v/>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="53">
         <f>F8-F17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="inlineStr">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>Total Tax Expense/(Credit)</t>
         </is>
@@ -12389,7 +11582,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>Add: Deferred tax (adj.)/recoverable from future tariff (net of tax)</t>
         </is>
@@ -12412,29 +11605,29 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="53">
         <f>B18-B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="53">
         <f>C18-C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="53">
         <f>D18-D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="53">
         <f>E18-E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="53">
         <f>F18-F19+F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>Other Comprehensive Income, net of tax</t>
         </is>
@@ -12461,23 +11654,23 @@
           <t>Total Comprehensive Income for the Year</t>
         </is>
       </c>
-      <c r="B23" s="52">
+      <c r="B23" s="53">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="53">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="53">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="52">
+      <c r="E23" s="53">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="52">
+      <c r="F23" s="53">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -12516,46 +11709,46 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Sources: Tata Power Integrated Annual Reports FY21-22 (AR_20052), FY23-24 (AR_24164) and FY25-26 (AR_29380) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="50" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
@@ -12567,7 +11760,7 @@
       <c r="F5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
@@ -12579,7 +11772,7 @@
       <c r="F6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
@@ -12601,7 +11794,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Right of Use Assets</t>
         </is>
@@ -12623,7 +11816,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
@@ -12645,7 +11838,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
@@ -12667,7 +11860,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
@@ -12689,7 +11882,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Investments accounted for using Equity Method</t>
         </is>
@@ -12711,7 +11904,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Other Investments (Non-current)</t>
         </is>
@@ -12733,7 +11926,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>Trade Receivables (Non-current)</t>
         </is>
@@ -12755,7 +11948,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
@@ -12777,7 +11970,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Finance Lease Receivables (Non-current)</t>
         </is>
@@ -12799,7 +11992,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
@@ -12821,7 +12014,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
@@ -12843,7 +12036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="inlineStr">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
@@ -12865,7 +12058,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
@@ -12892,29 +12085,29 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="53">
         <f>B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="53">
         <f>C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="53">
         <f>D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="53">
         <f>E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18+E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="53">
         <f>F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18+F19+F20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
@@ -12926,7 +12119,7 @@
       <c r="F22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
@@ -12948,7 +12141,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
@@ -12970,7 +12163,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>Trade Receivables (Current)</t>
         </is>
@@ -12992,7 +12185,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="52" t="inlineStr">
         <is>
           <t>Unbilled Revenue</t>
         </is>
@@ -13014,7 +12207,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="51" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
@@ -13036,7 +12229,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="52" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
@@ -13058,7 +12251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="51" t="inlineStr">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
@@ -13080,7 +12273,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="inlineStr">
+      <c r="A30" s="52" t="inlineStr">
         <is>
           <t>Finance Lease Receivables (Current)</t>
         </is>
@@ -13102,7 +12295,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="51" t="inlineStr">
+      <c r="A31" s="52" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
@@ -13124,7 +12317,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="inlineStr">
+      <c r="A32" s="52" t="inlineStr">
         <is>
           <t>Current Tax Assets (Net)</t>
         </is>
@@ -13146,7 +12339,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="inlineStr">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
@@ -13173,29 +12366,29 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B34" s="52">
+      <c r="B34" s="53">
         <f>B23+B24+B25+B26+B27+B28+B29+B30+B31+B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="52">
+      <c r="C34" s="53">
         <f>C23+C24+C25+C26+C27+C28+C29+C30+C31+C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="53">
         <f>D23+D24+D25+D26+D27+D28+D29+D30+D31+D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="52">
+      <c r="E34" s="53">
         <f>E23+E24+E25+E26+E27+E28+E29+E30+E31+E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="52">
+      <c r="F34" s="53">
         <f>F23+F24+F25+F26+F27+F28+F29+F30+F31+F32+F33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>Assets Classified as Held For Sale</t>
         </is>
@@ -13222,29 +12415,29 @@
           <t>Total Assets before Regulatory Deferral Account</t>
         </is>
       </c>
-      <c r="B36" s="52">
+      <c r="B36" s="53">
         <f>B21+B34+B35</f>
         <v/>
       </c>
-      <c r="C36" s="52">
+      <c r="C36" s="53">
         <f>C21+C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="53">
         <f>D21+D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="52">
+      <c r="E36" s="53">
         <f>E21+E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="52">
+      <c r="F36" s="53">
         <f>F21+F34+F35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="51" t="inlineStr">
+      <c r="A37" s="52" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Assets</t>
         </is>
@@ -13271,29 +12464,29 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B38" s="52">
+      <c r="B38" s="53">
         <f>B36+B37</f>
         <v/>
       </c>
-      <c r="C38" s="52">
+      <c r="C38" s="53">
         <f>C36+C37</f>
         <v/>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="53">
         <f>D36+D37</f>
         <v/>
       </c>
-      <c r="E38" s="52">
+      <c r="E38" s="53">
         <f>E36+E37</f>
         <v/>
       </c>
-      <c r="F38" s="52">
+      <c r="F38" s="53">
         <f>F36+F37</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="50" t="inlineStr">
+      <c r="A39" s="51" t="inlineStr">
         <is>
           <t>EQUITY AND LIABILITIES</t>
         </is>
@@ -13305,7 +12498,7 @@
       <c r="F39" s="38" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="51" t="inlineStr">
+      <c r="A40" s="52" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
@@ -13327,7 +12520,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="51" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
@@ -13354,29 +12547,29 @@
           <t>Equity attributable to Shareholders of Parent</t>
         </is>
       </c>
-      <c r="B42" s="52">
+      <c r="B42" s="53">
         <f>B40+B41</f>
         <v/>
       </c>
-      <c r="C42" s="52">
+      <c r="C42" s="53">
         <f>C40+C41</f>
         <v/>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="53">
         <f>D40+D41</f>
         <v/>
       </c>
-      <c r="E42" s="52">
+      <c r="E42" s="53">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F42" s="52">
+      <c r="F42" s="53">
         <f>F40+F41</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="51" t="inlineStr">
+      <c r="A43" s="52" t="inlineStr">
         <is>
           <t>Non-controlling Interests</t>
         </is>
@@ -13403,29 +12596,29 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="53">
         <f>B42+B43</f>
         <v/>
       </c>
-      <c r="C44" s="52">
+      <c r="C44" s="53">
         <f>C42+C43</f>
         <v/>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="53">
         <f>D42+D43</f>
         <v/>
       </c>
-      <c r="E44" s="52">
+      <c r="E44" s="53">
         <f>E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="52">
+      <c r="F44" s="53">
         <f>F42+F43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="50" t="inlineStr">
+      <c r="A45" s="51" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
@@ -13437,7 +12630,7 @@
       <c r="F45" s="38" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="51" t="inlineStr">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
@@ -13459,7 +12652,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="51" t="inlineStr">
+      <c r="A47" s="52" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
@@ -13481,7 +12674,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="A48" s="52" t="inlineStr">
         <is>
           <t>Trade Payables (Non-current)</t>
         </is>
@@ -13495,7 +12688,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="51" t="inlineStr">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
@@ -13517,7 +12710,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="51" t="inlineStr">
+      <c r="A50" s="52" t="inlineStr">
         <is>
           <t>Non-current Tax Liabilities (Net)</t>
         </is>
@@ -13531,7 +12724,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="51" t="inlineStr">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>Provisions (Non-current)</t>
         </is>
@@ -13553,7 +12746,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="51" t="inlineStr">
+      <c r="A52" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
@@ -13575,7 +12768,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="51" t="inlineStr">
+      <c r="A53" s="52" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
@@ -13602,29 +12795,29 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B54" s="52">
+      <c r="B54" s="53">
         <f>B46+B47+B48+B49+B50+B51+B52+B53</f>
         <v/>
       </c>
-      <c r="C54" s="52">
+      <c r="C54" s="53">
         <f>C46+C47+C48+C49+C50+C51+C52+C53</f>
         <v/>
       </c>
-      <c r="D54" s="52">
+      <c r="D54" s="53">
         <f>D46+D47+D48+D49+D50+D51+D52+D53</f>
         <v/>
       </c>
-      <c r="E54" s="52">
+      <c r="E54" s="53">
         <f>E46+E47+E48+E49+E50+E51+E52+E53</f>
         <v/>
       </c>
-      <c r="F54" s="52">
+      <c r="F54" s="53">
         <f>F46+F47+F48+F49+F50+F51+F52+F53</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="50" t="inlineStr">
+      <c r="A55" s="51" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
@@ -13636,7 +12829,7 @@
       <c r="F55" s="38" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="51" t="inlineStr">
+      <c r="A56" s="52" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
@@ -13658,7 +12851,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="51" t="inlineStr">
+      <c r="A57" s="52" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
@@ -13680,7 +12873,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="51" t="inlineStr">
+      <c r="A58" s="52" t="inlineStr">
         <is>
           <t>Acceptances (Current)</t>
         </is>
@@ -13696,7 +12889,7 @@
       <c r="F58" s="38" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="51" t="inlineStr">
+      <c r="A59" s="52" t="inlineStr">
         <is>
           <t>Trade Payables — micro/small enterprises</t>
         </is>
@@ -13716,7 +12909,7 @@
       <c r="F59" s="38" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="51" t="inlineStr">
+      <c r="A60" s="52" t="inlineStr">
         <is>
           <t>Trade Payables — other creditors / total</t>
         </is>
@@ -13738,7 +12931,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="51" t="inlineStr">
+      <c r="A61" s="52" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
@@ -13760,7 +12953,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="51" t="inlineStr">
+      <c r="A62" s="52" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
@@ -13782,7 +12975,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="51" t="inlineStr">
+      <c r="A63" s="52" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
@@ -13804,7 +12997,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="51" t="inlineStr">
+      <c r="A64" s="52" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
@@ -13831,29 +13024,29 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B65" s="52">
+      <c r="B65" s="53">
         <f>B56+B57+B58+B59+B60+B61+B62+B63+B64</f>
         <v/>
       </c>
-      <c r="C65" s="52">
+      <c r="C65" s="53">
         <f>C56+C57+C58+C59+C60+C61+C62+C63+C64</f>
         <v/>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="53">
         <f>D56+D57+D58+D59+D60+D61+D62+D63+D64</f>
         <v/>
       </c>
-      <c r="E65" s="52">
+      <c r="E65" s="53">
         <f>E56+E57+E58+E59+E60+E61+E62+E63+E64</f>
         <v/>
       </c>
-      <c r="F65" s="52">
+      <c r="F65" s="53">
         <f>F56+F57+F58+F59+F60+F61+F62+F63+F64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="51" t="inlineStr">
+      <c r="A66" s="52" t="inlineStr">
         <is>
           <t>Liabilities re: Assets Held For Sale</t>
         </is>
@@ -13875,7 +13068,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="51" t="inlineStr">
+      <c r="A67" s="52" t="inlineStr">
         <is>
           <t>Regulatory Deferral Account — Liability</t>
         </is>
@@ -13902,23 +13095,23 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B68" s="52">
+      <c r="B68" s="53">
         <f>B44+B54+B65+B66+B67</f>
         <v/>
       </c>
-      <c r="C68" s="52">
+      <c r="C68" s="53">
         <f>C44+C54+C65+C66+C67</f>
         <v/>
       </c>
-      <c r="D68" s="52">
+      <c r="D68" s="53">
         <f>D44+D54+D65+D66+D67</f>
         <v/>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="53">
         <f>E44+E54+E65+E66+E67</f>
         <v/>
       </c>
-      <c r="F68" s="52">
+      <c r="F68" s="53">
         <f>F44+F54+F65+F66+F67</f>
         <v/>
       </c>
@@ -13957,46 +13150,46 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Sources: Tata Power Integrated Annual Reports FY21-22, FY23-24 and FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="50" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
@@ -14018,7 +13211,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
@@ -14045,29 +13238,29 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="53">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="53">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="53">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="53">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="53">
         <f>F5+F6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
@@ -14079,7 +13272,7 @@
       <c r="F8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Cost of Power Purchased</t>
         </is>
@@ -14101,7 +13294,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Cost of Fuel</t>
         </is>
@@ -14123,7 +13316,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Transmission Charges</t>
         </is>
@@ -14145,7 +13338,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Raw Material Consumed / Construction Cost</t>
         </is>
@@ -14167,7 +13360,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Purchase of Finished Goods and Spares</t>
         </is>
@@ -14189,7 +13382,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>(Increase)/Decrease in Stock-in-Trade &amp; WIP</t>
         </is>
@@ -14211,7 +13404,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
@@ -14233,7 +13426,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Finance Costs</t>
         </is>
@@ -14255,7 +13448,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Depreciation and Amortisation Expense</t>
         </is>
@@ -14277,7 +13470,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
@@ -14304,23 +13497,23 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="53">
         <f>B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="53">
         <f>C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <f>D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <f>F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
@@ -14331,29 +13524,29 @@
           <t>Profit before Regulatory Deferral, Exceptional Items &amp; Assoc./JV share</t>
         </is>
       </c>
-      <c r="B20" s="52">
+      <c r="B20" s="53">
         <f>B7-B19</f>
         <v/>
       </c>
-      <c r="C20" s="52">
+      <c r="C20" s="53">
         <f>C7-C19</f>
         <v/>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="53">
         <f>D7-D19</f>
         <v/>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="53">
         <f>E7-E19</f>
         <v/>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="53">
         <f>F7-F19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Net Movement in Regulatory Deferral Balances (incl. earlier years, net tax)</t>
         </is>
@@ -14380,29 +13573,29 @@
           <t>Profit Before Exceptional Items, Tax &amp; Assoc./JV Share</t>
         </is>
       </c>
-      <c r="B22" s="52">
+      <c r="B22" s="53">
         <f>B20+B21</f>
         <v/>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="53">
         <f>C20+C21</f>
         <v/>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="53">
         <f>D20+D21</f>
         <v/>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="53">
         <f>E20+E21</f>
         <v/>
       </c>
-      <c r="F22" s="52">
+      <c r="F22" s="53">
         <f>F20+F21</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Share of Net Profit of Associates and JVs (Equity Method)</t>
         </is>
@@ -14429,29 +13622,29 @@
           <t>Profit Before Exceptional Items and Tax</t>
         </is>
       </c>
-      <c r="B24" s="52">
+      <c r="B24" s="53">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="53">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="53">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="53">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="53">
         <f>F22+F23</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>Exceptional Items (net)</t>
         </is>
@@ -14478,29 +13671,29 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B26" s="52">
+      <c r="B26" s="53">
         <f>B24+B25</f>
         <v/>
       </c>
-      <c r="C26" s="52">
+      <c r="C26" s="53">
         <f>C24+C25</f>
         <v/>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="53">
         <f>D24+D25</f>
         <v/>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="53">
         <f>E24+E25</f>
         <v/>
       </c>
-      <c r="F26" s="52">
+      <c r="F26" s="53">
         <f>F24+F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="51" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>Total Tax Expense/(Credit)</t>
         </is>
@@ -14527,23 +13720,23 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B28" s="52">
+      <c r="B28" s="53">
         <f>B26-B27</f>
         <v/>
       </c>
-      <c r="C28" s="52">
+      <c r="C28" s="53">
         <f>C26-C27</f>
         <v/>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="53">
         <f>D26-D27</f>
         <v/>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="53">
         <f>E26-E27</f>
         <v/>
       </c>
-      <c r="F28" s="52">
+      <c r="F28" s="53">
         <f>F26-F27</f>
         <v/>
       </c>
@@ -14583,51 +13776,51 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Sources: Torrent Power Integrated Annual Reports FY21-22 (AR_20392) through FY25-26 (AR_29704) — 'Consolidated Balance Sheet' as at each year-end. GREEN 'Total' cells are LIVE FORMULAS summing the line items above them.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Mar-2026</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Mar-2025</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>Mar-2024</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="50" t="inlineStr">
         <is>
           <t>Mar-2023</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>Mar-2022</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="50" t="inlineStr">
         <is>
           <t>Mar-2021</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Non-current Assets</t>
         </is>
@@ -14640,7 +13833,7 @@
       <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Property, Plant and Equipment</t>
         </is>
@@ -14665,7 +13858,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Right-of-use Assets</t>
         </is>
@@ -14690,7 +13883,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Capital Work-in-Progress</t>
         </is>
@@ -14715,7 +13908,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Investment Property</t>
         </is>
@@ -14736,7 +13929,7 @@
       <c r="G9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
@@ -14757,7 +13950,7 @@
       <c r="G10" s="38" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Other Intangible Assets</t>
         </is>
@@ -14782,7 +13975,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Intangible Assets Under Development</t>
         </is>
@@ -14797,7 +13990,7 @@
       <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Investments (Non-current)</t>
         </is>
@@ -14822,7 +14015,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>Loans (Non-current)</t>
         </is>
@@ -14841,7 +14034,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Other Financial Assets (Non-current)</t>
         </is>
@@ -14866,7 +14059,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax Assets (Net)</t>
         </is>
@@ -14891,7 +14084,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Non-current Tax Assets (Net)</t>
         </is>
@@ -14916,7 +14109,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>Other Non-current Assets</t>
         </is>
@@ -14946,33 +14139,33 @@
           <t>Total Non-current Assets</t>
         </is>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="53">
         <f>B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18</f>
         <v/>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="53">
         <f>C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <f>D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <f>F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="53">
         <f>G6+G7+G8+G9+G10+G11+G12+G13+G14+G15+G16+G17+G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>Current Assets</t>
         </is>
@@ -14985,7 +14178,7 @@
       <c r="G20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
@@ -15010,7 +14203,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>Investments (Current)</t>
         </is>
@@ -15035,7 +14228,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Trade Receivables</t>
         </is>
@@ -15060,7 +14253,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
@@ -15085,7 +14278,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="51" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>Bank Balances other than above</t>
         </is>
@@ -15110,7 +14303,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="52" t="inlineStr">
         <is>
           <t>Loans (Current)</t>
         </is>
@@ -15127,7 +14320,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="51" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>Other Financial Assets (Current)</t>
         </is>
@@ -15152,7 +14345,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="52" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
@@ -15182,27 +14375,27 @@
           <t>Total Current Assets</t>
         </is>
       </c>
-      <c r="B29" s="52">
+      <c r="B29" s="53">
         <f>B21+B22+B23+B24+B25+B26+B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="53">
         <f>C21+C22+C23+C24+C25+C26+C27+C28</f>
         <v/>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="53">
         <f>D21+D22+D23+D24+D25+D26+D27+D28</f>
         <v/>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="53">
         <f>E21+E22+E23+E24+E25+E26+E27+E28</f>
         <v/>
       </c>
-      <c r="F29" s="52">
+      <c r="F29" s="53">
         <f>F21+F22+F23+F24+F25+F26+F27+F28</f>
         <v/>
       </c>
-      <c r="G29" s="52">
+      <c r="G29" s="53">
         <f>G21+G22+G23+G24+G25+G26+G27+G28</f>
         <v/>
       </c>
@@ -15213,33 +14406,33 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B30" s="52">
+      <c r="B30" s="53">
         <f>B19+B29</f>
         <v/>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="53">
         <f>C19+C29</f>
         <v/>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="53">
         <f>D19+D29</f>
         <v/>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="53">
         <f>E19+E29</f>
         <v/>
       </c>
-      <c r="F30" s="52">
+      <c r="F30" s="53">
         <f>F19+F29</f>
         <v/>
       </c>
-      <c r="G30" s="52">
+      <c r="G30" s="53">
         <f>G19+G29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="inlineStr">
+      <c r="A31" s="51" t="inlineStr">
         <is>
           <t>EQUITY &amp; LIABILITIES</t>
         </is>
@@ -15252,7 +14445,7 @@
       <c r="G31" s="38" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="inlineStr">
+      <c r="A32" s="52" t="inlineStr">
         <is>
           <t>Equity Share Capital</t>
         </is>
@@ -15277,7 +14470,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="51" t="inlineStr">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>Other Equity</t>
         </is>
@@ -15307,33 +14500,33 @@
           <t>Net Worth (Attributable to Owners)</t>
         </is>
       </c>
-      <c r="B34" s="52">
+      <c r="B34" s="53">
         <f>B32+B33</f>
         <v/>
       </c>
-      <c r="C34" s="52">
+      <c r="C34" s="53">
         <f>C32+C33</f>
         <v/>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="53">
         <f>D32+D33</f>
         <v/>
       </c>
-      <c r="E34" s="52">
+      <c r="E34" s="53">
         <f>E32+E33</f>
         <v/>
       </c>
-      <c r="F34" s="52">
+      <c r="F34" s="53">
         <f>F32+F33</f>
         <v/>
       </c>
-      <c r="G34" s="52">
+      <c r="G34" s="53">
         <f>G32+G33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>Non-Controlling Interests</t>
         </is>
@@ -15363,33 +14556,33 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B36" s="52">
+      <c r="B36" s="53">
         <f>B34+B35</f>
         <v/>
       </c>
-      <c r="C36" s="52">
+      <c r="C36" s="53">
         <f>C34+C35</f>
         <v/>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="53">
         <f>D34+D35</f>
         <v/>
       </c>
-      <c r="E36" s="52">
+      <c r="E36" s="53">
         <f>E34+E35</f>
         <v/>
       </c>
-      <c r="F36" s="52">
+      <c r="F36" s="53">
         <f>F34+F35</f>
         <v/>
       </c>
-      <c r="G36" s="52">
+      <c r="G36" s="53">
         <f>G34+G35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="50" t="inlineStr">
+      <c r="A37" s="51" t="inlineStr">
         <is>
           <t>Non-current Liabilities</t>
         </is>
@@ -15402,7 +14595,7 @@
       <c r="G37" s="38" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="inlineStr">
+      <c r="A38" s="52" t="inlineStr">
         <is>
           <t>Borrowings (Non-current)</t>
         </is>
@@ -15427,7 +14620,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="51" t="inlineStr">
+      <c r="A39" s="52" t="inlineStr">
         <is>
           <t>Lease Liabilities (Non-current)</t>
         </is>
@@ -15452,7 +14645,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="51" t="inlineStr">
+      <c r="A40" s="52" t="inlineStr">
         <is>
           <t>Trade Payables (Non-current)</t>
         </is>
@@ -15477,7 +14670,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="51" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Non-current)</t>
         </is>
@@ -15502,7 +14695,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="51" t="inlineStr">
+      <c r="A42" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax Liabilities (Net)</t>
         </is>
@@ -15527,7 +14720,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="51" t="inlineStr">
+      <c r="A43" s="52" t="inlineStr">
         <is>
           <t>Other Non-current Liabilities</t>
         </is>
@@ -15557,33 +14750,33 @@
           <t>Total Non-current Liabilities</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="53">
         <f>B38+B39+B40+B41+B42+B43</f>
         <v/>
       </c>
-      <c r="C44" s="52">
+      <c r="C44" s="53">
         <f>C38+C39+C40+C41+C42+C43</f>
         <v/>
       </c>
-      <c r="D44" s="52">
+      <c r="D44" s="53">
         <f>D38+D39+D40+D41+D42+D43</f>
         <v/>
       </c>
-      <c r="E44" s="52">
+      <c r="E44" s="53">
         <f>E38+E39+E40+E41+E42+E43</f>
         <v/>
       </c>
-      <c r="F44" s="52">
+      <c r="F44" s="53">
         <f>F38+F39+F40+F41+F42+F43</f>
         <v/>
       </c>
-      <c r="G44" s="52">
+      <c r="G44" s="53">
         <f>G38+G39+G40+G41+G42+G43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="50" t="inlineStr">
+      <c r="A45" s="51" t="inlineStr">
         <is>
           <t>Current Liabilities</t>
         </is>
@@ -15596,7 +14789,7 @@
       <c r="G45" s="38" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="51" t="inlineStr">
+      <c r="A46" s="52" t="inlineStr">
         <is>
           <t>Borrowings (Current)</t>
         </is>
@@ -15621,7 +14814,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="51" t="inlineStr">
+      <c r="A47" s="52" t="inlineStr">
         <is>
           <t>Lease Liabilities (Current)</t>
         </is>
@@ -15646,7 +14839,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="A48" s="52" t="inlineStr">
         <is>
           <t>Trade Payables (Current)</t>
         </is>
@@ -15671,7 +14864,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="51" t="inlineStr">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>Other Financial Liabilities (Current)</t>
         </is>
@@ -15696,7 +14889,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="51" t="inlineStr">
+      <c r="A50" s="52" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
@@ -15721,7 +14914,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="51" t="inlineStr">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>Provisions (Current)</t>
         </is>
@@ -15746,7 +14939,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="51" t="inlineStr">
+      <c r="A52" s="52" t="inlineStr">
         <is>
           <t>Current Tax Liabilities (Net)</t>
         </is>
@@ -15776,27 +14969,27 @@
           <t>Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B53" s="52">
+      <c r="B53" s="53">
         <f>B46+B47+B48+B49+B50+B51+B52</f>
         <v/>
       </c>
-      <c r="C53" s="52">
+      <c r="C53" s="53">
         <f>C46+C47+C48+C49+C50+C51+C52</f>
         <v/>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="53">
         <f>D46+D47+D48+D49+D50+D51+D52</f>
         <v/>
       </c>
-      <c r="E53" s="52">
+      <c r="E53" s="53">
         <f>E46+E47+E48+E49+E50+E51+E52</f>
         <v/>
       </c>
-      <c r="F53" s="52">
+      <c r="F53" s="53">
         <f>F46+F47+F48+F49+F50+F51+F52</f>
         <v/>
       </c>
-      <c r="G53" s="52">
+      <c r="G53" s="53">
         <f>G46+G47+G48+G49+G50+G51+G52</f>
         <v/>
       </c>
@@ -15807,27 +15000,27 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B54" s="52">
+      <c r="B54" s="53">
         <f>B36+B44+B53</f>
         <v/>
       </c>
-      <c r="C54" s="52">
+      <c r="C54" s="53">
         <f>C36+C44+C53</f>
         <v/>
       </c>
-      <c r="D54" s="52">
+      <c r="D54" s="53">
         <f>D36+D44+D53</f>
         <v/>
       </c>
-      <c r="E54" s="52">
+      <c r="E54" s="53">
         <f>E36+E44+E53</f>
         <v/>
       </c>
-      <c r="F54" s="52">
+      <c r="F54" s="53">
         <f>F36+F44+F53</f>
         <v/>
       </c>
-      <c r="G54" s="52">
+      <c r="G54" s="53">
         <f>G36+G44+G53</f>
         <v/>
       </c>
@@ -15867,51 +15060,51 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Sources: Torrent Power Integrated Annual Reports FY21-22 through FY25-26 — 'Consolidated Statement of Profit and Loss' for each year ended. GREEN 'Total'/'Profit' cells are LIVE FORMULAS. Only FY22 had an exceptional item (the ~Rs 1,300cr DGEN plant impairment) — all other years are genuinely nil, not missing data.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Particulars (₹ crore)</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>FY 2025-26</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>FY 2024-25</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>FY 2023-24</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="50" t="inlineStr">
         <is>
           <t>FY 2022-23</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>FY 2021-22</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="50" t="inlineStr">
         <is>
           <t>FY 2020-21</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Revenue from Operations</t>
         </is>
@@ -15936,7 +15129,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
@@ -15966,33 +15159,33 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="53">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="53">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="53">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="53">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="53">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="53">
         <f>G5+G6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
@@ -16005,7 +15198,7 @@
       <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Electrical Energy Purchased</t>
         </is>
@@ -16030,7 +15223,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
@@ -16055,7 +15248,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Cost of Materials Consumed</t>
         </is>
@@ -16078,7 +15271,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Purchase of Stock-in-Trade</t>
         </is>
@@ -16103,7 +15296,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Changes in Inventories of Finished Goods and WIP</t>
         </is>
@@ -16128,7 +15321,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>Employee Benefits Expense</t>
         </is>
@@ -16153,7 +15346,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Finance Costs</t>
         </is>
@@ -16178,7 +15371,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortisation</t>
         </is>
@@ -16203,7 +15396,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>Other Expenses</t>
         </is>
@@ -16233,27 +15426,27 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B18" s="52">
+      <c r="B18" s="53">
         <f>B9+B10+B11+B12+B13+B14+B15+B16+B17</f>
         <v/>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="53">
         <f>C9+C10+C11+C12+C13+C14+C15+C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="53">
         <f>D9+D10+D11+D12+D13+D14+D15+D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="53">
         <f>E9+E10+E11+E12+E13+E14+E15+E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="53">
         <f>F9+F10+F11+F12+F13+F14+F15+F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="53">
         <f>G9+G10+G11+G12+G13+G14+G15+G16+G17</f>
         <v/>
       </c>
@@ -16264,33 +15457,33 @@
           <t>Profit Before Exceptional Items and Tax</t>
         </is>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="53">
         <f>B7-B18</f>
         <v/>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="53">
         <f>C7-C18</f>
         <v/>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="53">
         <f>D7-D18</f>
         <v/>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="53">
         <f>E7-E18</f>
         <v/>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="53">
         <f>F7-F18</f>
         <v/>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="53">
         <f>G7-G18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>Exceptional Items (DGEN plant impairment, FY22 only)</t>
         </is>
@@ -16320,33 +15513,33 @@
           <t>Profit Before Tax</t>
         </is>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="53">
         <f>B19-B20</f>
         <v/>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="53">
         <f>C19-C20</f>
         <v/>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="53">
         <f>D19-D20</f>
         <v/>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="53">
         <f>E19-E20</f>
         <v/>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="53">
         <f>F19-F20</f>
         <v/>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="53">
         <f>G19-G20</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>Current Tax</t>
         </is>
@@ -16371,7 +15564,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Deferred Tax</t>
         </is>
@@ -16401,27 +15594,27 @@
           <t>Total Tax Expense</t>
         </is>
       </c>
-      <c r="B24" s="52">
+      <c r="B24" s="53">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="53">
         <f>C22+C23</f>
         <v/>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="53">
         <f>D22+D23</f>
         <v/>
       </c>
-      <c r="E24" s="52">
+      <c r="E24" s="53">
         <f>E22+E23</f>
         <v/>
       </c>
-      <c r="F24" s="52">
+      <c r="F24" s="53">
         <f>F22+F23</f>
         <v/>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="53">
         <f>G22+G23</f>
         <v/>
       </c>
@@ -16432,27 +15625,27 @@
           <t>Profit for the Year (PAT, consolidated)</t>
         </is>
       </c>
-      <c r="B25" s="52">
+      <c r="B25" s="53">
         <f>B21-B24</f>
         <v/>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="53">
         <f>C21-C24</f>
         <v/>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="53">
         <f>D21-D24</f>
         <v/>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="53">
         <f>E21-E24</f>
         <v/>
       </c>
-      <c r="F25" s="52">
+      <c r="F25" s="53">
         <f>F21-F24</f>
         <v/>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="53">
         <f>G21-G24</f>
         <v/>
       </c>
@@ -17796,7 +16989,7 @@
         <v>509.19</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>159.97</v>
+        <v>153.92</v>
       </c>
     </row>
     <row r="38">
@@ -17820,7 +17013,7 @@
         <v>375.35</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>382.63</v>
+        <v>385.7</v>
       </c>
     </row>
     <row r="39">
@@ -17844,7 +17037,7 @@
         </is>
       </c>
       <c r="F39" s="21" t="n">
-        <v>1327.6</v>
+        <v>1352.3</v>
       </c>
     </row>
     <row r="41">
